--- a/config/Excel/Status.xlsx
+++ b/config/Excel/Status.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\AppData\Local\Temp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCC8624F-E5E5-4B0E-BE1F-888AAE146B1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0422718-BBDC-4904-B170-F2D8A50D25FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2730" yWindow="2730" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="850" uniqueCount="421">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="964" uniqueCount="456">
   <si>
     <t>狀態ID</t>
   </si>
@@ -1284,6 +1284,111 @@
   </si>
   <si>
     <t>留白＝該狀態沒有那一段畫面。</t>
+  </si>
+  <si>
+    <t>sgSlayerDomain</t>
+  </si>
+  <si>
+    <t>殺神領域</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>99999</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>ground-mire</t>
+  </si>
+  <si>
+    <t>超神進化【殺神領域】：展開中的領域，跟著你移動；持續特效依領域半徑縮放。持續時間只是讓它一直掛著：領域在不在由超神進化與技能列裝配決定，卸下或換掉超神就移除。</t>
+  </si>
+  <si>
+    <t>sgVenomDomain</t>
+  </si>
+  <si>
+    <t>萬毒血霧</t>
+  </si>
+  <si>
+    <t>☣️</t>
+  </si>
+  <si>
+    <t>ground-mire-poison</t>
+  </si>
+  <si>
+    <t>超神進化【萬毒血霧】：展開中的毒霧領域，跟著你移動；持續特效依領域半徑縮放（領域內敵人身上的【萬毒侵蝕】另計）。持續時間只是讓它一直掛著：領域在不在由超神進化與技能列裝配決定，卸下或換掉超神就移除。</t>
+  </si>
+  <si>
+    <t>sgFireGodBody</t>
+  </si>
+  <si>
+    <t>火神降臨</t>
+  </si>
+  <si>
+    <t>ground-domain-fire</t>
+  </si>
+  <si>
+    <t>超神進化【火神降臨】：火焰纏身，定時灼燒周圍敵人；持續特效依作用半徑縮放、跟著你移動。持續時間只是讓它一直掛著：領域在不在由超神進化與技能列裝配決定，卸下或換掉超神就移除。</t>
+  </si>
+  <si>
+    <t>sgPetrifyDomain</t>
+  </si>
+  <si>
+    <t>超重岩領域</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>ground-domain-earth</t>
+  </si>
+  <si>
+    <t>超神進化【超重岩之術】：岩甲護盾存在期間展開的領域，進入的敵人被石化；持續特效依領域半徑縮放、跟著你移動。持續到岩甲護盾結束（實際秒數由岩甲術給）。</t>
+  </si>
+  <si>
+    <t>sgGravityDomain</t>
+  </si>
+  <si>
+    <t>超重力場</t>
+  </si>
+  <si>
+    <t>超神進化【超重力場】：岩甲護盾存在期間展開的重力場，進入的敵人僵化；持續特效依領域半徑縮放、跟著你移動。持續到岩甲護盾結束（實際秒數由岩甲術給）。</t>
+  </si>
+  <si>
+    <t>sgWaterPrisonDomain</t>
+  </si>
+  <si>
+    <t>水牢天瀑</t>
+  </si>
+  <si>
+    <t>🫧</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>ground-domain-ice</t>
+  </si>
+  <si>
+    <t>超神進化【水牢天瀑】：圍在你周圍的水牢，持續期間跟著你移動；持續特效依水牢半徑縮放（牢內敵人身上的【水牢】與攻擊下降另計）。</t>
+  </si>
+  <si>
+    <t>sgAbyssDomain</t>
+  </si>
+  <si>
+    <t>海淵葬界</t>
+  </si>
+  <si>
+    <t>超神進化【海淵葬界】：永久展開的水之領域，跟著你移動；持續特效依領域半徑縮放。持續時間只是讓它一直掛著：領域在不在由超神進化與技能列裝配決定，卸下或換掉超神就移除。</t>
+  </si>
+  <si>
+    <t>　代表一個範圍的狀態（以玩家為中心的領域：殺神領域、火神降臨、海淵葬界…）例外：持續特效依領域的實際半徑縮放並跟著玩家走，範圍變大畫面就跟著變大；</t>
+  </si>
+  <si>
+    <t>　這類領域狀態的持續時間填 99999＝「領域在就一直在」，實際由技能決定何時撤掉；</t>
   </si>
 </sst>
 </file>
@@ -2261,7 +2366,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:T88"/>
+  <dimension ref="A1:T95"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:20" x14ac:dyDescent="0.25">
@@ -6317,6 +6422,356 @@
       </c>
       <c r="T88" t="s">
         <v>356</v>
+      </c>
+    </row>
+    <row r="89" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A89" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="B89" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="C89" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="D89" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="E89" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="F89" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="G89" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="I89" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="K89" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="L89" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="M89" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="N89" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="O89" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="P89" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="R89" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="T89" s="1" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="90" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A90" s="1" t="s">
+        <v>428</v>
+      </c>
+      <c r="B90" s="1" t="s">
+        <v>429</v>
+      </c>
+      <c r="C90" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="D90" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="E90" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="F90" s="1" t="s">
+        <v>428</v>
+      </c>
+      <c r="G90" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I90" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="K90" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="L90" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="M90" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="N90" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="O90" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="P90" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="R90" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="T90" s="1" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="91" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A91" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="B91" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="C91" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D91" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="E91" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="F91" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="G91" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="I91" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="K91" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="L91" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="M91" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="N91" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="O91" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="P91" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="R91" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="T91" s="1" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="92" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A92" s="1" t="s">
+        <v>437</v>
+      </c>
+      <c r="B92" s="1" t="s">
+        <v>438</v>
+      </c>
+      <c r="C92" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="D92" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="E92" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="F92" s="1" t="s">
+        <v>437</v>
+      </c>
+      <c r="G92" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="I92" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="K92" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="L92" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="M92" s="1" t="s">
+        <v>439</v>
+      </c>
+      <c r="N92" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="O92" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="P92" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="R92" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="T92" s="1" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="93" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A93" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="B93" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="C93" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="D93" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="E93" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="F93" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="G93" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="I93" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="K93" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="L93" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="M93" s="1" t="s">
+        <v>439</v>
+      </c>
+      <c r="N93" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="O93" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="P93" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="R93" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="T93" s="1" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="94" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A94" s="1" t="s">
+        <v>445</v>
+      </c>
+      <c r="B94" s="1" t="s">
+        <v>446</v>
+      </c>
+      <c r="C94" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="D94" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="E94" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="F94" s="1" t="s">
+        <v>445</v>
+      </c>
+      <c r="G94" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="I94" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="K94" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="L94" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="M94" s="1" t="s">
+        <v>448</v>
+      </c>
+      <c r="N94" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="O94" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="P94" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="R94" s="1" t="s">
+        <v>449</v>
+      </c>
+      <c r="T94" s="1" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="95" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A95" s="1" t="s">
+        <v>451</v>
+      </c>
+      <c r="B95" s="1" t="s">
+        <v>452</v>
+      </c>
+      <c r="C95" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="D95" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="E95" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="F95" s="1" t="s">
+        <v>451</v>
+      </c>
+      <c r="G95" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="I95" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="K95" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="L95" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="M95" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="N95" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="O95" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="P95" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="R95" s="1" t="s">
+        <v>449</v>
+      </c>
+      <c r="T95" s="1" t="s">
+        <v>453</v>
       </c>
     </row>
   </sheetData>
@@ -6327,7 +6782,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:A79"/>
+  <dimension ref="A1:A81"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="125.625" customWidth="1"/>
@@ -6718,13 +7173,23 @@
         <v>418</v>
       </c>
     </row>
-    <row r="78" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
-        <v>419</v>
+        <v>454</v>
       </c>
     </row>
     <row r="79" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A80" s="2" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A81" s="2" t="s">
         <v>420</v>
       </c>
     </row>

--- a/config/Excel/Status.xlsx
+++ b/config/Excel/Status.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\AppData\Local\Temp\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alway\AppData\Local\Temp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0422718-BBDC-4904-B170-F2D8A50D25FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{963113B6-683A-48FA-ACAC-241FD304F571}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2730" yWindow="2730" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Status" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="964" uniqueCount="456">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="964" uniqueCount="457">
   <si>
     <t>狀態ID</t>
   </si>
@@ -548,9 +548,6 @@
     <t>🌪️</t>
   </si>
   <si>
-    <t>新版技能【暴風之舞】：化身暴風，期間自動施放雙刀亂舞、無法普攻。</t>
-  </si>
-  <si>
     <t>sgBloodrage</t>
   </si>
   <si>
@@ -1389,6 +1386,14 @@
   </si>
   <si>
     <t>　這類領域狀態的持續時間填 99999＝「領域在就一直在」，實際由技能決定何時撤掉；</t>
+  </si>
+  <si>
+    <t>ground-storm-dance</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>新版技能【暴風亂舞】：化身暴風，期間自動施放雙刀亂舞、可以普攻及施放技能。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -2367,9 +2372,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:T95"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2431,7 +2436,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>20</v>
       </c>
@@ -2475,7 +2480,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>28</v>
       </c>
@@ -2522,7 +2527,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>33</v>
       </c>
@@ -2569,7 +2574,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>37</v>
       </c>
@@ -2616,7 +2621,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>42</v>
       </c>
@@ -2663,7 +2668,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>46</v>
       </c>
@@ -2713,7 +2718,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>52</v>
       </c>
@@ -2757,7 +2762,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>58</v>
       </c>
@@ -2801,7 +2806,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>62</v>
       </c>
@@ -2845,7 +2850,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>67</v>
       </c>
@@ -2892,7 +2897,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>72</v>
       </c>
@@ -2939,7 +2944,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>76</v>
       </c>
@@ -2983,7 +2988,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>81</v>
       </c>
@@ -3027,7 +3032,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>84</v>
       </c>
@@ -3071,7 +3076,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>88</v>
       </c>
@@ -3115,7 +3120,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="17" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>92</v>
       </c>
@@ -3159,7 +3164,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>96</v>
       </c>
@@ -3203,7 +3208,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="19" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>100</v>
       </c>
@@ -3247,7 +3252,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="20" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>104</v>
       </c>
@@ -3291,7 +3296,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="21" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>108</v>
       </c>
@@ -3335,7 +3340,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="22" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>112</v>
       </c>
@@ -3379,7 +3384,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="23" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>116</v>
       </c>
@@ -3423,7 +3428,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="24" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>120</v>
       </c>
@@ -3470,7 +3475,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="25" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>125</v>
       </c>
@@ -3514,7 +3519,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="26" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>129</v>
       </c>
@@ -3561,7 +3566,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="27" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>134</v>
       </c>
@@ -3608,7 +3613,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="28" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>138</v>
       </c>
@@ -3652,7 +3657,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="29" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>141</v>
       </c>
@@ -3699,7 +3704,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="30" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>144</v>
       </c>
@@ -3743,7 +3748,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="31" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>146</v>
       </c>
@@ -3787,7 +3792,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="32" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>148</v>
       </c>
@@ -3831,7 +3836,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="33" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>152</v>
       </c>
@@ -3875,7 +3880,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="34" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>155</v>
       </c>
@@ -3919,16 +3924,16 @@
         <v>1</v>
       </c>
       <c r="Q34" s="1" t="s">
+        <v>405</v>
+      </c>
+      <c r="S34" s="1" t="s">
         <v>406</v>
-      </c>
-      <c r="S34" s="1" t="s">
-        <v>407</v>
       </c>
       <c r="T34" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="35" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>158</v>
       </c>
@@ -3972,7 +3977,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="36" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>161</v>
       </c>
@@ -4016,7 +4021,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="37" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>164</v>
       </c>
@@ -4060,7 +4065,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="38" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>168</v>
       </c>
@@ -4104,7 +4109,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="39" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>172</v>
       </c>
@@ -4145,21 +4150,21 @@
         <v>1</v>
       </c>
       <c r="R39" s="1" t="s">
-        <v>408</v>
-      </c>
-      <c r="T39" t="s">
+        <v>455</v>
+      </c>
+      <c r="T39" s="1" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="40" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
         <v>175</v>
       </c>
-    </row>
-    <row r="40" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
+      <c r="B40" t="s">
         <v>176</v>
       </c>
-      <c r="B40" t="s">
+      <c r="C40" t="s">
         <v>177</v>
-      </c>
-      <c r="C40" t="s">
-        <v>178</v>
       </c>
       <c r="D40" t="s">
         <v>65</v>
@@ -4168,7 +4173,7 @@
         <v>79</v>
       </c>
       <c r="F40" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I40">
         <v>0</v>
@@ -4192,21 +4197,21 @@
         <v>1</v>
       </c>
       <c r="R40" s="1" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="T40" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="41" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
         <v>179</v>
       </c>
-    </row>
-    <row r="41" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
+      <c r="B41" t="s">
         <v>180</v>
       </c>
-      <c r="B41" t="s">
+      <c r="C41" t="s">
         <v>181</v>
-      </c>
-      <c r="C41" t="s">
-        <v>182</v>
       </c>
       <c r="D41" t="s">
         <v>23</v>
@@ -4215,7 +4220,7 @@
         <v>79</v>
       </c>
       <c r="F41" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="I41">
         <v>0</v>
@@ -4233,21 +4238,21 @@
         <v>0</v>
       </c>
       <c r="O41" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="P41">
         <v>4</v>
       </c>
       <c r="T41" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="42" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
         <v>185</v>
       </c>
-    </row>
-    <row r="42" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
+      <c r="B42" t="s">
         <v>186</v>
-      </c>
-      <c r="B42" t="s">
-        <v>187</v>
       </c>
       <c r="C42" t="s">
         <v>30</v>
@@ -4286,18 +4291,18 @@
         <v>1</v>
       </c>
       <c r="S42" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="T42" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="43" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
         <v>188</v>
       </c>
-    </row>
-    <row r="43" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
+      <c r="B43" t="s">
         <v>189</v>
-      </c>
-      <c r="B43" t="s">
-        <v>190</v>
       </c>
       <c r="C43" t="s">
         <v>30</v>
@@ -4309,7 +4314,7 @@
         <v>79</v>
       </c>
       <c r="F43" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="G43" t="s">
         <v>31</v>
@@ -4336,18 +4341,18 @@
         <v>1</v>
       </c>
       <c r="T43" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="44" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
         <v>191</v>
       </c>
-    </row>
-    <row r="44" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
+      <c r="B44" t="s">
         <v>192</v>
       </c>
-      <c r="B44" t="s">
+      <c r="C44" t="s">
         <v>193</v>
-      </c>
-      <c r="C44" t="s">
-        <v>194</v>
       </c>
       <c r="D44" t="s">
         <v>65</v>
@@ -4356,7 +4361,7 @@
         <v>79</v>
       </c>
       <c r="F44" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="G44" t="s">
         <v>31</v>
@@ -4383,18 +4388,18 @@
         <v>1</v>
       </c>
       <c r="T44" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="45" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
         <v>195</v>
       </c>
-    </row>
-    <row r="45" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
+      <c r="B45" t="s">
         <v>196</v>
       </c>
-      <c r="B45" t="s">
+      <c r="C45" t="s">
         <v>197</v>
-      </c>
-      <c r="C45" t="s">
-        <v>198</v>
       </c>
       <c r="D45" t="s">
         <v>65</v>
@@ -4403,10 +4408,10 @@
         <v>79</v>
       </c>
       <c r="F45" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G45" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="I45">
         <v>0</v>
@@ -4430,18 +4435,18 @@
         <v>1</v>
       </c>
       <c r="T45" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="46" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
         <v>200</v>
       </c>
-    </row>
-    <row r="46" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
+      <c r="B46" t="s">
         <v>201</v>
       </c>
-      <c r="B46" t="s">
-        <v>202</v>
-      </c>
       <c r="C46" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D46" t="s">
         <v>65</v>
@@ -4450,7 +4455,7 @@
         <v>79</v>
       </c>
       <c r="F46" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="I46">
         <v>0</v>
@@ -4474,18 +4479,18 @@
         <v>1</v>
       </c>
       <c r="T46" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="47" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
         <v>203</v>
       </c>
-    </row>
-    <row r="47" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
+      <c r="B47" t="s">
         <v>204</v>
       </c>
-      <c r="B47" t="s">
+      <c r="C47" t="s">
         <v>205</v>
-      </c>
-      <c r="C47" t="s">
-        <v>206</v>
       </c>
       <c r="D47" t="s">
         <v>23</v>
@@ -4494,10 +4499,10 @@
         <v>79</v>
       </c>
       <c r="F47" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="G47" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="I47">
         <v>0</v>
@@ -4521,15 +4526,15 @@
         <v>1</v>
       </c>
       <c r="T47" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="48" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
         <v>207</v>
       </c>
-    </row>
-    <row r="48" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
+      <c r="B48" t="s">
         <v>208</v>
-      </c>
-      <c r="B48" t="s">
-        <v>209</v>
       </c>
       <c r="C48" t="s">
         <v>35</v>
@@ -4568,18 +4573,18 @@
         <v>1</v>
       </c>
       <c r="T48" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="49" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
         <v>210</v>
       </c>
-    </row>
-    <row r="49" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
+      <c r="B49" t="s">
         <v>211</v>
       </c>
-      <c r="B49" t="s">
+      <c r="C49" t="s">
         <v>212</v>
-      </c>
-      <c r="C49" t="s">
-        <v>213</v>
       </c>
       <c r="D49" t="s">
         <v>23</v>
@@ -4615,18 +4620,18 @@
         <v>1</v>
       </c>
       <c r="T49" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="50" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
         <v>214</v>
       </c>
-    </row>
-    <row r="50" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
+      <c r="B50" t="s">
         <v>215</v>
       </c>
-      <c r="B50" t="s">
+      <c r="C50" t="s">
         <v>216</v>
-      </c>
-      <c r="C50" t="s">
-        <v>217</v>
       </c>
       <c r="D50" t="s">
         <v>65</v>
@@ -4635,7 +4640,7 @@
         <v>79</v>
       </c>
       <c r="F50" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="G50" t="s">
         <v>123</v>
@@ -4662,18 +4667,18 @@
         <v>1</v>
       </c>
       <c r="T50" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="51" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
         <v>218</v>
       </c>
-    </row>
-    <row r="51" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
+      <c r="B51" t="s">
         <v>219</v>
       </c>
-      <c r="B51" t="s">
+      <c r="C51" t="s">
         <v>220</v>
-      </c>
-      <c r="C51" t="s">
-        <v>221</v>
       </c>
       <c r="D51" t="s">
         <v>23</v>
@@ -4682,10 +4687,10 @@
         <v>79</v>
       </c>
       <c r="F51" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="G51" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="I51">
         <v>0</v>
@@ -4703,24 +4708,24 @@
         <v>0</v>
       </c>
       <c r="O51" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="P51">
         <v>5</v>
       </c>
       <c r="T51" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="52" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
         <v>223</v>
       </c>
-    </row>
-    <row r="52" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A52" t="s">
+      <c r="B52" t="s">
         <v>224</v>
       </c>
-      <c r="B52" t="s">
+      <c r="C52" t="s">
         <v>225</v>
-      </c>
-      <c r="C52" t="s">
-        <v>226</v>
       </c>
       <c r="D52" t="s">
         <v>23</v>
@@ -4729,7 +4734,7 @@
         <v>24</v>
       </c>
       <c r="G52" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H52" t="s">
         <v>25</v>
@@ -4756,21 +4761,21 @@
         <v>1</v>
       </c>
       <c r="S52" s="1" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="T52" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="53" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
         <v>227</v>
       </c>
-    </row>
-    <row r="53" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A53" t="s">
+      <c r="B53" t="s">
         <v>228</v>
       </c>
-      <c r="B53" t="s">
+      <c r="C53" t="s">
         <v>229</v>
-      </c>
-      <c r="C53" t="s">
-        <v>230</v>
       </c>
       <c r="D53" t="s">
         <v>23</v>
@@ -4779,10 +4784,10 @@
         <v>79</v>
       </c>
       <c r="F53" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="G53" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="I53">
         <v>0</v>
@@ -4806,18 +4811,18 @@
         <v>1</v>
       </c>
       <c r="T53" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="54" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A54" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="54" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A54" t="s">
+      <c r="B54" t="s">
         <v>232</v>
       </c>
-      <c r="B54" t="s">
+      <c r="C54" t="s">
         <v>233</v>
-      </c>
-      <c r="C54" t="s">
-        <v>234</v>
       </c>
       <c r="D54" t="s">
         <v>23</v>
@@ -4826,10 +4831,10 @@
         <v>79</v>
       </c>
       <c r="F54" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="G54" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="I54">
         <v>0</v>
@@ -4853,18 +4858,18 @@
         <v>1</v>
       </c>
       <c r="T54" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="55" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A55" t="s">
         <v>235</v>
       </c>
-    </row>
-    <row r="55" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A55" t="s">
+      <c r="B55" t="s">
         <v>236</v>
       </c>
-      <c r="B55" t="s">
-        <v>237</v>
-      </c>
       <c r="C55" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D55" t="s">
         <v>65</v>
@@ -4873,10 +4878,10 @@
         <v>79</v>
       </c>
       <c r="F55" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="G55" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="I55">
         <v>0</v>
@@ -4900,15 +4905,15 @@
         <v>1</v>
       </c>
       <c r="T55" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="56" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A56" t="s">
         <v>238</v>
       </c>
-    </row>
-    <row r="56" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A56" t="s">
+      <c r="B56" t="s">
         <v>239</v>
-      </c>
-      <c r="B56" t="s">
-        <v>240</v>
       </c>
       <c r="C56" t="s">
         <v>118</v>
@@ -4920,10 +4925,10 @@
         <v>79</v>
       </c>
       <c r="F56" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="G56" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="I56">
         <v>0</v>
@@ -4941,21 +4946,21 @@
         <v>0</v>
       </c>
       <c r="O56" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="P56">
         <v>6</v>
       </c>
       <c r="T56" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="57" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A57" t="s">
         <v>242</v>
       </c>
-    </row>
-    <row r="57" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A57" t="s">
+      <c r="B57" t="s">
         <v>243</v>
-      </c>
-      <c r="B57" t="s">
-        <v>244</v>
       </c>
       <c r="C57" t="s">
         <v>118</v>
@@ -4967,7 +4972,7 @@
         <v>24</v>
       </c>
       <c r="G57" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="H57" t="s">
         <v>25</v>
@@ -4994,18 +4999,18 @@
         <v>1</v>
       </c>
       <c r="T57" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="58" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A58" t="s">
         <v>245</v>
       </c>
-    </row>
-    <row r="58" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A58" t="s">
+      <c r="B58" t="s">
         <v>246</v>
       </c>
-      <c r="B58" t="s">
+      <c r="C58" t="s">
         <v>247</v>
-      </c>
-      <c r="C58" t="s">
-        <v>248</v>
       </c>
       <c r="D58" t="s">
         <v>23</v>
@@ -5014,10 +5019,10 @@
         <v>79</v>
       </c>
       <c r="F58" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="G58" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="I58">
         <v>0</v>
@@ -5041,15 +5046,15 @@
         <v>1</v>
       </c>
       <c r="T58" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="59" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
         <v>249</v>
       </c>
-    </row>
-    <row r="59" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A59" t="s">
+      <c r="B59" t="s">
         <v>250</v>
-      </c>
-      <c r="B59" t="s">
-        <v>251</v>
       </c>
       <c r="C59" t="s">
         <v>174</v>
@@ -5061,10 +5066,10 @@
         <v>79</v>
       </c>
       <c r="F59" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="G59" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="I59">
         <v>0</v>
@@ -5088,18 +5093,18 @@
         <v>1</v>
       </c>
       <c r="R59" s="1" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="T59" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="60" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A60" t="s">
         <v>252</v>
       </c>
-    </row>
-    <row r="60" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A60" t="s">
+      <c r="B60" t="s">
         <v>253</v>
-      </c>
-      <c r="B60" t="s">
-        <v>254</v>
       </c>
       <c r="C60" t="s">
         <v>90</v>
@@ -5111,10 +5116,10 @@
         <v>79</v>
       </c>
       <c r="F60" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="G60" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="I60">
         <v>0</v>
@@ -5138,18 +5143,18 @@
         <v>1</v>
       </c>
       <c r="T60" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="61" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A61" t="s">
         <v>255</v>
       </c>
-    </row>
-    <row r="61" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A61" t="s">
+      <c r="B61" t="s">
         <v>256</v>
       </c>
-      <c r="B61" t="s">
+      <c r="C61" t="s">
         <v>257</v>
-      </c>
-      <c r="C61" t="s">
-        <v>258</v>
       </c>
       <c r="D61" t="s">
         <v>65</v>
@@ -5158,10 +5163,10 @@
         <v>79</v>
       </c>
       <c r="F61" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="G61" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="I61">
         <v>0</v>
@@ -5185,18 +5190,18 @@
         <v>1</v>
       </c>
       <c r="R61" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="T61" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="62" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A62" t="s">
         <v>259</v>
       </c>
-    </row>
-    <row r="62" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A62" t="s">
+      <c r="B62" t="s">
         <v>260</v>
-      </c>
-      <c r="B62" t="s">
-        <v>261</v>
       </c>
       <c r="C62" t="s">
         <v>39</v>
@@ -5208,7 +5213,7 @@
         <v>79</v>
       </c>
       <c r="F62" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="I62">
         <v>0</v>
@@ -5226,24 +5231,24 @@
         <v>0</v>
       </c>
       <c r="O62" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="P62">
         <v>10</v>
       </c>
       <c r="T62" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="63" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A63" t="s">
         <v>262</v>
       </c>
-    </row>
-    <row r="63" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A63" t="s">
+      <c r="B63" t="s">
         <v>263</v>
       </c>
-      <c r="B63" t="s">
+      <c r="C63" t="s">
         <v>264</v>
-      </c>
-      <c r="C63" t="s">
-        <v>265</v>
       </c>
       <c r="D63" t="s">
         <v>23</v>
@@ -5252,7 +5257,7 @@
         <v>79</v>
       </c>
       <c r="F63" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="G63" t="s">
         <v>40</v>
@@ -5273,21 +5278,21 @@
         <v>0</v>
       </c>
       <c r="O63" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="P63">
         <v>100</v>
       </c>
       <c r="T63" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="64" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A64" t="s">
         <v>266</v>
       </c>
-    </row>
-    <row r="64" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A64" t="s">
+      <c r="B64" t="s">
         <v>267</v>
-      </c>
-      <c r="B64" t="s">
-        <v>268</v>
       </c>
       <c r="C64" t="s">
         <v>22</v>
@@ -5323,18 +5328,18 @@
         <v>1</v>
       </c>
       <c r="T64" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="65" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A65" t="s">
         <v>269</v>
       </c>
-    </row>
-    <row r="65" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A65" t="s">
+      <c r="B65" t="s">
         <v>270</v>
       </c>
-      <c r="B65" t="s">
+      <c r="C65" t="s">
         <v>271</v>
-      </c>
-      <c r="C65" t="s">
-        <v>272</v>
       </c>
       <c r="D65" t="s">
         <v>65</v>
@@ -5343,7 +5348,7 @@
         <v>79</v>
       </c>
       <c r="F65" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="I65">
         <v>0</v>
@@ -5367,15 +5372,15 @@
         <v>1</v>
       </c>
       <c r="T65" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="66" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A66" t="s">
         <v>273</v>
       </c>
-    </row>
-    <row r="66" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A66" t="s">
+      <c r="B66" t="s">
         <v>274</v>
-      </c>
-      <c r="B66" t="s">
-        <v>275</v>
       </c>
       <c r="C66" t="s">
         <v>35</v>
@@ -5387,7 +5392,7 @@
         <v>79</v>
       </c>
       <c r="F66" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="I66">
         <v>0</v>
@@ -5405,24 +5410,24 @@
         <v>0</v>
       </c>
       <c r="O66" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="P66">
         <v>20</v>
       </c>
       <c r="T66" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="67" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A67" t="s">
         <v>276</v>
       </c>
-    </row>
-    <row r="67" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A67" t="s">
+      <c r="B67" t="s">
         <v>277</v>
       </c>
-      <c r="B67" t="s">
+      <c r="C67" t="s">
         <v>278</v>
-      </c>
-      <c r="C67" t="s">
-        <v>279</v>
       </c>
       <c r="D67" t="s">
         <v>65</v>
@@ -5431,7 +5436,7 @@
         <v>79</v>
       </c>
       <c r="F67" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="I67">
         <v>0</v>
@@ -5455,18 +5460,18 @@
         <v>1</v>
       </c>
       <c r="T67" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="68" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A68" t="s">
         <v>280</v>
       </c>
-    </row>
-    <row r="68" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A68" t="s">
+      <c r="B68" t="s">
         <v>281</v>
       </c>
-      <c r="B68" t="s">
+      <c r="C68" t="s">
         <v>282</v>
-      </c>
-      <c r="C68" t="s">
-        <v>283</v>
       </c>
       <c r="D68" t="s">
         <v>65</v>
@@ -5475,7 +5480,7 @@
         <v>79</v>
       </c>
       <c r="F68" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="I68">
         <v>0</v>
@@ -5493,24 +5498,24 @@
         <v>0</v>
       </c>
       <c r="O68" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="P68">
         <v>100</v>
       </c>
       <c r="T68" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="69" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A69" t="s">
         <v>284</v>
       </c>
-    </row>
-    <row r="69" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A69" t="s">
+      <c r="B69" t="s">
         <v>285</v>
       </c>
-      <c r="B69" t="s">
+      <c r="C69" t="s">
         <v>286</v>
-      </c>
-      <c r="C69" t="s">
-        <v>287</v>
       </c>
       <c r="D69" t="s">
         <v>23</v>
@@ -5540,24 +5545,24 @@
         <v>0.5</v>
       </c>
       <c r="O69" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="P69">
         <v>10</v>
       </c>
       <c r="T69" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="70" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A70" t="s">
         <v>288</v>
       </c>
-    </row>
-    <row r="70" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A70" t="s">
+      <c r="B70" t="s">
         <v>289</v>
       </c>
-      <c r="B70" t="s">
+      <c r="C70" t="s">
         <v>290</v>
-      </c>
-      <c r="C70" t="s">
-        <v>291</v>
       </c>
       <c r="D70" t="s">
         <v>23</v>
@@ -5587,24 +5592,24 @@
         <v>0.5</v>
       </c>
       <c r="O70" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="P70">
         <v>20</v>
       </c>
       <c r="T70" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="71" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A71" t="s">
         <v>292</v>
       </c>
-    </row>
-    <row r="71" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A71" t="s">
+      <c r="B71" t="s">
         <v>293</v>
       </c>
-      <c r="B71" t="s">
+      <c r="C71" t="s">
         <v>294</v>
-      </c>
-      <c r="C71" t="s">
-        <v>295</v>
       </c>
       <c r="D71" t="s">
         <v>65</v>
@@ -5613,7 +5618,7 @@
         <v>79</v>
       </c>
       <c r="F71" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="I71">
         <v>0</v>
@@ -5637,21 +5642,21 @@
         <v>1</v>
       </c>
       <c r="R71" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="T71" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="72" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
         <v>296</v>
       </c>
-    </row>
-    <row r="72" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A72" t="s">
+      <c r="B72" t="s">
         <v>297</v>
       </c>
-      <c r="B72" t="s">
-        <v>298</v>
-      </c>
       <c r="C72" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="D72" t="s">
         <v>23</v>
@@ -5660,7 +5665,7 @@
         <v>79</v>
       </c>
       <c r="F72" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="I72">
         <v>0</v>
@@ -5684,18 +5689,18 @@
         <v>1</v>
       </c>
       <c r="T72" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="73" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
         <v>299</v>
       </c>
-    </row>
-    <row r="73" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A73" t="s">
+      <c r="B73" t="s">
         <v>300</v>
       </c>
-      <c r="B73" t="s">
+      <c r="C73" t="s">
         <v>301</v>
-      </c>
-      <c r="C73" t="s">
-        <v>302</v>
       </c>
       <c r="D73" t="s">
         <v>65</v>
@@ -5704,7 +5709,7 @@
         <v>79</v>
       </c>
       <c r="F73" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="I73">
         <v>0</v>
@@ -5728,15 +5733,15 @@
         <v>1</v>
       </c>
       <c r="T73" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="74" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
         <v>303</v>
       </c>
-    </row>
-    <row r="74" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A74" t="s">
+      <c r="B74" t="s">
         <v>304</v>
-      </c>
-      <c r="B74" t="s">
-        <v>305</v>
       </c>
       <c r="C74" t="s">
         <v>22</v>
@@ -5748,7 +5753,7 @@
         <v>79</v>
       </c>
       <c r="F74" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="I74">
         <v>0</v>
@@ -5766,24 +5771,24 @@
         <v>0</v>
       </c>
       <c r="O74" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="P74">
         <v>50</v>
       </c>
       <c r="T74" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="75" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
         <v>306</v>
       </c>
-    </row>
-    <row r="75" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A75" t="s">
+      <c r="B75" t="s">
         <v>307</v>
       </c>
-      <c r="B75" t="s">
+      <c r="C75" t="s">
         <v>308</v>
-      </c>
-      <c r="C75" t="s">
-        <v>309</v>
       </c>
       <c r="D75" t="s">
         <v>65</v>
@@ -5792,7 +5797,7 @@
         <v>79</v>
       </c>
       <c r="F75" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="I75">
         <v>0</v>
@@ -5810,24 +5815,24 @@
         <v>0</v>
       </c>
       <c r="O75" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="P75">
         <v>10</v>
       </c>
       <c r="T75" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="76" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
         <v>310</v>
       </c>
-    </row>
-    <row r="76" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A76" t="s">
+      <c r="B76" t="s">
         <v>311</v>
       </c>
-      <c r="B76" t="s">
+      <c r="C76" t="s">
         <v>312</v>
-      </c>
-      <c r="C76" t="s">
-        <v>313</v>
       </c>
       <c r="D76" t="s">
         <v>65</v>
@@ -5836,7 +5841,7 @@
         <v>79</v>
       </c>
       <c r="F76" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="I76">
         <v>0</v>
@@ -5854,24 +5859,24 @@
         <v>0</v>
       </c>
       <c r="O76" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="P76">
         <v>100</v>
       </c>
       <c r="T76" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="77" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
         <v>314</v>
       </c>
-    </row>
-    <row r="77" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A77" t="s">
+      <c r="B77" t="s">
         <v>315</v>
       </c>
-      <c r="B77" t="s">
+      <c r="C77" t="s">
         <v>316</v>
-      </c>
-      <c r="C77" t="s">
-        <v>317</v>
       </c>
       <c r="D77" t="s">
         <v>65</v>
@@ -5880,7 +5885,7 @@
         <v>79</v>
       </c>
       <c r="F77" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="I77">
         <v>0</v>
@@ -5904,21 +5909,21 @@
         <v>1</v>
       </c>
       <c r="R77" s="1" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="T77" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="78" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
         <v>318</v>
       </c>
-    </row>
-    <row r="78" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A78" t="s">
+      <c r="B78" t="s">
         <v>319</v>
       </c>
-      <c r="B78" t="s">
-        <v>320</v>
-      </c>
       <c r="C78" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D78" t="s">
         <v>65</v>
@@ -5927,7 +5932,7 @@
         <v>79</v>
       </c>
       <c r="F78" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="G78" t="s">
         <v>31</v>
@@ -5954,15 +5959,15 @@
         <v>1</v>
       </c>
       <c r="T78" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="79" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
         <v>321</v>
       </c>
-    </row>
-    <row r="79" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A79" t="s">
+      <c r="B79" t="s">
         <v>322</v>
-      </c>
-      <c r="B79" t="s">
-        <v>323</v>
       </c>
       <c r="C79" t="s">
         <v>30</v>
@@ -5974,7 +5979,7 @@
         <v>79</v>
       </c>
       <c r="F79" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="G79" t="s">
         <v>31</v>
@@ -6001,18 +6006,18 @@
         <v>1</v>
       </c>
       <c r="T79" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="80" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
         <v>324</v>
       </c>
-    </row>
-    <row r="80" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A80" t="s">
+      <c r="B80" t="s">
         <v>325</v>
       </c>
-      <c r="B80" t="s">
+      <c r="C80" t="s">
         <v>326</v>
-      </c>
-      <c r="C80" t="s">
-        <v>327</v>
       </c>
       <c r="D80" t="s">
         <v>23</v>
@@ -6021,10 +6026,10 @@
         <v>79</v>
       </c>
       <c r="F80" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="G80" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="I80">
         <v>0</v>
@@ -6048,18 +6053,18 @@
         <v>1</v>
       </c>
       <c r="T80" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="81" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A81" t="s">
         <v>328</v>
       </c>
-    </row>
-    <row r="81" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A81" t="s">
+      <c r="B81" t="s">
         <v>329</v>
       </c>
-      <c r="B81" t="s">
+      <c r="C81" t="s">
         <v>330</v>
-      </c>
-      <c r="C81" t="s">
-        <v>331</v>
       </c>
       <c r="D81" t="s">
         <v>23</v>
@@ -6068,10 +6073,10 @@
         <v>79</v>
       </c>
       <c r="F81" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="G81" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="I81">
         <v>0</v>
@@ -6095,15 +6100,15 @@
         <v>1</v>
       </c>
       <c r="T81" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="82" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A82" t="s">
         <v>332</v>
       </c>
-    </row>
-    <row r="82" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A82" t="s">
+      <c r="B82" t="s">
         <v>333</v>
-      </c>
-      <c r="B82" t="s">
-        <v>334</v>
       </c>
       <c r="C82" t="s">
         <v>22</v>
@@ -6139,15 +6144,15 @@
         <v>1</v>
       </c>
       <c r="T82" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="83" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A83" t="s">
         <v>335</v>
       </c>
-    </row>
-    <row r="83" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A83" t="s">
+      <c r="B83" t="s">
         <v>336</v>
-      </c>
-      <c r="B83" t="s">
-        <v>337</v>
       </c>
       <c r="C83" t="s">
         <v>44</v>
@@ -6186,18 +6191,18 @@
         <v>1</v>
       </c>
       <c r="T83" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="84" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A84" t="s">
         <v>338</v>
       </c>
-    </row>
-    <row r="84" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A84" t="s">
+      <c r="B84" t="s">
         <v>339</v>
       </c>
-      <c r="B84" t="s">
-        <v>340</v>
-      </c>
       <c r="C84" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D84" t="s">
         <v>23</v>
@@ -6206,7 +6211,7 @@
         <v>79</v>
       </c>
       <c r="F84" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="G84" t="s">
         <v>31</v>
@@ -6233,18 +6238,18 @@
         <v>1</v>
       </c>
       <c r="T84" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="85" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A85" t="s">
         <v>341</v>
       </c>
-    </row>
-    <row r="85" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A85" t="s">
+      <c r="B85" t="s">
         <v>342</v>
       </c>
-      <c r="B85" t="s">
+      <c r="C85" t="s">
         <v>343</v>
-      </c>
-      <c r="C85" t="s">
-        <v>344</v>
       </c>
       <c r="D85" t="s">
         <v>65</v>
@@ -6253,7 +6258,7 @@
         <v>79</v>
       </c>
       <c r="F85" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="G85" t="s">
         <v>123</v>
@@ -6274,21 +6279,21 @@
         <v>0</v>
       </c>
       <c r="O85" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="P85">
         <v>100</v>
       </c>
       <c r="T85" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="86" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A86" t="s">
         <v>345</v>
       </c>
-    </row>
-    <row r="86" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A86" t="s">
+      <c r="B86" t="s">
         <v>346</v>
-      </c>
-      <c r="B86" t="s">
-        <v>347</v>
       </c>
       <c r="C86" t="s">
         <v>86</v>
@@ -6300,7 +6305,7 @@
         <v>79</v>
       </c>
       <c r="F86" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="G86" t="s">
         <v>123</v>
@@ -6327,18 +6332,18 @@
         <v>1</v>
       </c>
       <c r="T86" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="87" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A87" t="s">
         <v>348</v>
       </c>
-    </row>
-    <row r="87" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A87" t="s">
+      <c r="B87" t="s">
         <v>349</v>
       </c>
-      <c r="B87" t="s">
+      <c r="C87" t="s">
         <v>350</v>
-      </c>
-      <c r="C87" t="s">
-        <v>351</v>
       </c>
       <c r="D87" t="s">
         <v>23</v>
@@ -6347,10 +6352,10 @@
         <v>79</v>
       </c>
       <c r="F87" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="G87" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="I87">
         <v>0</v>
@@ -6374,18 +6379,18 @@
         <v>1</v>
       </c>
       <c r="T87" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="88" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A88" t="s">
         <v>352</v>
       </c>
-    </row>
-    <row r="88" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A88" t="s">
+      <c r="B88" t="s">
         <v>353</v>
       </c>
-      <c r="B88" t="s">
+      <c r="C88" t="s">
         <v>354</v>
-      </c>
-      <c r="C88" t="s">
-        <v>355</v>
       </c>
       <c r="D88" t="s">
         <v>23</v>
@@ -6394,10 +6399,10 @@
         <v>79</v>
       </c>
       <c r="F88" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="G88" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="I88">
         <v>0</v>
@@ -6421,18 +6426,18 @@
         <v>1</v>
       </c>
       <c r="T88" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="89" spans="1:20" x14ac:dyDescent="0.25">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="89" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A89" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="B89" s="1" t="s">
         <v>421</v>
       </c>
-      <c r="B89" s="1" t="s">
-        <v>422</v>
-      </c>
       <c r="C89" s="1" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="D89" s="1" t="s">
         <v>65</v>
@@ -6441,48 +6446,48 @@
         <v>79</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="G89" s="1" t="s">
         <v>40</v>
       </c>
       <c r="I89" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="K89" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="L89" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="M89" s="1" t="s">
         <v>423</v>
       </c>
-      <c r="K89" s="1" t="s">
-        <v>423</v>
-      </c>
-      <c r="L89" s="1" t="s">
-        <v>423</v>
-      </c>
-      <c r="M89" s="1" t="s">
-        <v>424</v>
-      </c>
       <c r="N89" s="1" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="O89" s="1" t="s">
         <v>56</v>
       </c>
       <c r="P89" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="R89" s="1" t="s">
         <v>425</v>
       </c>
-      <c r="R89" s="1" t="s">
+      <c r="T89" s="1" t="s">
         <v>426</v>
       </c>
-      <c r="T89" s="1" t="s">
+    </row>
+    <row r="90" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A90" s="1" t="s">
         <v>427</v>
       </c>
-    </row>
-    <row r="90" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A90" s="1" t="s">
+      <c r="B90" s="1" t="s">
         <v>428</v>
       </c>
-      <c r="B90" s="1" t="s">
+      <c r="C90" s="1" t="s">
         <v>429</v>
-      </c>
-      <c r="C90" s="1" t="s">
-        <v>430</v>
       </c>
       <c r="D90" s="1" t="s">
         <v>65</v>
@@ -6491,45 +6496,45 @@
         <v>79</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="G90" s="1" t="s">
         <v>33</v>
       </c>
       <c r="I90" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="K90" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="L90" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="M90" s="1" t="s">
         <v>423</v>
       </c>
-      <c r="K90" s="1" t="s">
-        <v>423</v>
-      </c>
-      <c r="L90" s="1" t="s">
-        <v>423</v>
-      </c>
-      <c r="M90" s="1" t="s">
-        <v>424</v>
-      </c>
       <c r="N90" s="1" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="O90" s="1" t="s">
         <v>56</v>
       </c>
       <c r="P90" s="1" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="R90" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="T90" s="1" t="s">
         <v>431</v>
       </c>
-      <c r="T90" s="1" t="s">
+    </row>
+    <row r="91" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A91" s="1" t="s">
         <v>432</v>
       </c>
-    </row>
-    <row r="91" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A91" s="1" t="s">
+      <c r="B91" s="1" t="s">
         <v>433</v>
-      </c>
-      <c r="B91" s="1" t="s">
-        <v>434</v>
       </c>
       <c r="C91" s="1" t="s">
         <v>30</v>
@@ -6541,48 +6546,48 @@
         <v>79</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="G91" s="1" t="s">
         <v>31</v>
       </c>
       <c r="I91" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="K91" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="L91" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="M91" s="1" t="s">
         <v>423</v>
       </c>
-      <c r="K91" s="1" t="s">
-        <v>423</v>
-      </c>
-      <c r="L91" s="1" t="s">
-        <v>423</v>
-      </c>
-      <c r="M91" s="1" t="s">
-        <v>424</v>
-      </c>
       <c r="N91" s="1" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="O91" s="1" t="s">
         <v>56</v>
       </c>
       <c r="P91" s="1" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="R91" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="T91" s="1" t="s">
         <v>435</v>
       </c>
-      <c r="T91" s="1" t="s">
+    </row>
+    <row r="92" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A92" s="1" t="s">
         <v>436</v>
       </c>
-    </row>
-    <row r="92" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A92" s="1" t="s">
+      <c r="B92" s="1" t="s">
         <v>437</v>
       </c>
-      <c r="B92" s="1" t="s">
-        <v>438</v>
-      </c>
       <c r="C92" s="1" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="D92" s="1" t="s">
         <v>65</v>
@@ -6591,48 +6596,48 @@
         <v>79</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="G92" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="I92" s="1" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="K92" s="1" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="L92" s="1" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="M92" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="N92" s="1" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="O92" s="1" t="s">
         <v>56</v>
       </c>
       <c r="P92" s="1" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="R92" s="1" t="s">
+        <v>439</v>
+      </c>
+      <c r="T92" s="1" t="s">
         <v>440</v>
       </c>
-      <c r="T92" s="1" t="s">
+    </row>
+    <row r="93" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A93" s="1" t="s">
         <v>441</v>
       </c>
-    </row>
-    <row r="93" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A93" s="1" t="s">
+      <c r="B93" s="1" t="s">
         <v>442</v>
       </c>
-      <c r="B93" s="1" t="s">
-        <v>443</v>
-      </c>
       <c r="C93" s="1" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D93" s="1" t="s">
         <v>65</v>
@@ -6641,48 +6646,48 @@
         <v>79</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="G93" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="I93" s="1" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="K93" s="1" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="L93" s="1" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="M93" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="N93" s="1" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="O93" s="1" t="s">
         <v>56</v>
       </c>
       <c r="P93" s="1" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="R93" s="1" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="T93" s="1" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="94" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A94" s="1" t="s">
         <v>444</v>
       </c>
-    </row>
-    <row r="94" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A94" s="1" t="s">
+      <c r="B94" s="1" t="s">
         <v>445</v>
       </c>
-      <c r="B94" s="1" t="s">
+      <c r="C94" s="1" t="s">
         <v>446</v>
-      </c>
-      <c r="C94" s="1" t="s">
-        <v>447</v>
       </c>
       <c r="D94" s="1" t="s">
         <v>65</v>
@@ -6691,48 +6696,48 @@
         <v>79</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="G94" s="1" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="I94" s="1" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="K94" s="1" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="L94" s="1" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="M94" s="1" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="N94" s="1" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="O94" s="1" t="s">
         <v>56</v>
       </c>
       <c r="P94" s="1" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="R94" s="1" t="s">
+        <v>448</v>
+      </c>
+      <c r="T94" s="1" t="s">
         <v>449</v>
       </c>
-      <c r="T94" s="1" t="s">
+    </row>
+    <row r="95" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A95" s="1" t="s">
         <v>450</v>
       </c>
-    </row>
-    <row r="95" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A95" s="1" t="s">
+      <c r="B95" s="1" t="s">
         <v>451</v>
       </c>
-      <c r="B95" s="1" t="s">
-        <v>452</v>
-      </c>
       <c r="C95" s="1" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="D95" s="1" t="s">
         <v>65</v>
@@ -6741,37 +6746,37 @@
         <v>79</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="G95" s="1" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="I95" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="K95" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="L95" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="M95" s="1" t="s">
         <v>423</v>
       </c>
-      <c r="K95" s="1" t="s">
-        <v>423</v>
-      </c>
-      <c r="L95" s="1" t="s">
-        <v>423</v>
-      </c>
-      <c r="M95" s="1" t="s">
-        <v>424</v>
-      </c>
       <c r="N95" s="1" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="O95" s="1" t="s">
         <v>56</v>
       </c>
       <c r="P95" s="1" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="R95" s="1" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="T95" s="1" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
   </sheetData>
@@ -6783,414 +6788,414 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:A81"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="125.625" customWidth="1"/>
+    <col min="1" max="1" width="125.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
         <v>357</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
         <v>358</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
         <v>359</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A10" s="2" t="s">
         <v>361</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A14" s="2" t="s">
         <v>363</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A15" s="2" t="s">
         <v>364</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A15" s="2" t="s">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A16" s="2" t="s">
         <v>365</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A16" s="2" t="s">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A17" s="2" t="s">
         <v>366</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" s="2" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:1" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A21" s="2" t="s">
         <v>368</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" s="2" t="s">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A22" s="2" t="s">
         <v>369</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A22" s="2" t="s">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A23" s="2" t="s">
         <v>370</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A23" s="2" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A27" s="2" t="s">
         <v>372</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A27" s="2" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A31" s="2" t="s">
         <v>374</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A31" s="2" t="s">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A32" s="2" t="s">
         <v>375</v>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A32" s="2" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A36" s="2" t="s">
         <v>377</v>
       </c>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A36" s="2" t="s">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A37" s="2" t="s">
         <v>378</v>
       </c>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A37" s="2" t="s">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A38" s="2" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A39" s="2" t="s">
         <v>379</v>
       </c>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A38" s="2" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A39" s="2" t="s">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A40" s="2" t="s">
         <v>380</v>
       </c>
     </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A40" s="2" t="s">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A41" s="2" t="s">
         <v>381</v>
       </c>
     </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A41" s="2" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A45" s="2" t="s">
         <v>383</v>
       </c>
     </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A45" s="2" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A48" s="2" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A49" s="2" t="s">
         <v>385</v>
       </c>
     </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A49" s="2" t="s">
+    <row r="50" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A50" s="2" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A50" s="2" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A52" s="2" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A53" s="2" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A54" s="2" t="s">
         <v>388</v>
       </c>
     </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A54" s="2" t="s">
+    <row r="55" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A55" s="2" t="s">
         <v>389</v>
       </c>
     </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A55" s="2" t="s">
+    <row r="56" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A56" s="2" t="s">
         <v>390</v>
       </c>
     </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A56" s="2" t="s">
+    <row r="57" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A57" s="2" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A58" s="2" t="s">
         <v>391</v>
       </c>
     </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A57" s="2" t="s">
+    <row r="59" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A59" s="2" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A60" s="2" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A61" s="2" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A62" s="2" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A63" s="2" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A64" s="2" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A65" s="2" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A66" s="2" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A67" s="2" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A68" s="2" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A69" s="2" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A70" s="2" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A71" s="2" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A72" s="2" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A73" s="2" t="s">
         <v>414</v>
       </c>
     </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A58" s="2" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A59" s="2" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A60" s="2" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A61" s="2" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="62" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A62" s="2" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A63" s="2" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A64" s="2" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A65" s="2" t="s">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A66" s="2" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A67" s="2" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A68" s="2" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A69" s="2" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A70" s="2" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A71" s="2" t="s">
+    <row r="74" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A74" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A75" s="2" t="s">
         <v>404</v>
       </c>
     </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A72" s="2" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A73" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="74" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A74" s="2" t="s">
+    <row r="76" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A76" s="2" t="s">
         <v>416</v>
       </c>
     </row>
-    <row r="75" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A75" s="2" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="76" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A76" s="2" t="s">
+    <row r="77" spans="1:1" ht="32.4" x14ac:dyDescent="0.3">
+      <c r="A77" s="2" t="s">
         <v>417</v>
       </c>
     </row>
-    <row r="77" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A77" s="2" t="s">
+    <row r="78" spans="1:1" ht="32.4" x14ac:dyDescent="0.3">
+      <c r="A78" s="2" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A79" s="2" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A80" s="2" t="s">
         <v>418</v>
       </c>
     </row>
-    <row r="78" spans="1:1" ht="33" x14ac:dyDescent="0.25">
-      <c r="A78" s="2" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="79" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A79" s="2" t="s">
-        <v>455</v>
-      </c>
-    </row>
-    <row r="80" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A80" s="2" t="s">
+    <row r="81" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A81" s="2" t="s">
         <v>419</v>
-      </c>
-    </row>
-    <row r="81" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A81" s="2" t="s">
-        <v>420</v>
       </c>
     </row>
   </sheetData>

--- a/config/Excel/Status.xlsx
+++ b/config/Excel/Status.xlsx
@@ -5,23 +5,36 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alway\AppData\Local\Temp\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyGame\Idle-RPG\codex\config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{963113B6-683A-48FA-ACAC-241FD304F571}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40918CFA-4F79-4F41-ACF3-D7068622663B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Status" sheetId="1" r:id="rId1"/>
     <sheet name="欄位定義" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="964" uniqueCount="457">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="964" uniqueCount="458">
   <si>
     <t>狀態ID</t>
   </si>
@@ -1394,6 +1407,9 @@
   <si>
     <t>新版技能【暴風亂舞】：化身暴風，期間自動施放雙刀亂舞、可以普攻及施放技能。</t>
     <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>ground-domain-earth-10</t>
   </si>
 </sst>
 </file>
@@ -2372,9 +2388,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:T95"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="18" max="18" width="12.375" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2436,7 +2455,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>20</v>
       </c>
@@ -2480,7 +2499,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>28</v>
       </c>
@@ -2527,7 +2546,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>33</v>
       </c>
@@ -2574,7 +2593,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>37</v>
       </c>
@@ -2621,7 +2640,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>42</v>
       </c>
@@ -2668,7 +2687,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>46</v>
       </c>
@@ -2718,7 +2737,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>52</v>
       </c>
@@ -2762,7 +2781,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>58</v>
       </c>
@@ -2806,7 +2825,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>62</v>
       </c>
@@ -2850,7 +2869,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>67</v>
       </c>
@@ -2897,7 +2916,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>72</v>
       </c>
@@ -2944,7 +2963,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>76</v>
       </c>
@@ -2988,7 +3007,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>81</v>
       </c>
@@ -3032,7 +3051,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>84</v>
       </c>
@@ -3076,7 +3095,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>88</v>
       </c>
@@ -3120,7 +3139,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="17" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>92</v>
       </c>
@@ -3164,7 +3183,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>96</v>
       </c>
@@ -3208,7 +3227,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="19" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>100</v>
       </c>
@@ -3252,7 +3271,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="20" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>104</v>
       </c>
@@ -3296,7 +3315,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="21" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>108</v>
       </c>
@@ -3340,7 +3359,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="22" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>112</v>
       </c>
@@ -3384,7 +3403,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="23" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>116</v>
       </c>
@@ -3428,7 +3447,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="24" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>120</v>
       </c>
@@ -3475,7 +3494,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="25" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>125</v>
       </c>
@@ -3519,7 +3538,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="26" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>129</v>
       </c>
@@ -3566,7 +3585,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="27" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>134</v>
       </c>
@@ -3613,7 +3632,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="28" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>138</v>
       </c>
@@ -3657,7 +3676,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="29" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>141</v>
       </c>
@@ -3704,7 +3723,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="30" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>144</v>
       </c>
@@ -3748,7 +3767,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="31" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>146</v>
       </c>
@@ -3792,7 +3811,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="32" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>148</v>
       </c>
@@ -3836,7 +3855,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="33" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>152</v>
       </c>
@@ -3880,7 +3899,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="34" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>155</v>
       </c>
@@ -3933,7 +3952,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="35" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>158</v>
       </c>
@@ -3977,7 +3996,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="36" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>161</v>
       </c>
@@ -4021,7 +4040,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="37" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>164</v>
       </c>
@@ -4065,7 +4084,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="38" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>168</v>
       </c>
@@ -4109,7 +4128,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="39" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>172</v>
       </c>
@@ -4156,7 +4175,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="40" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>175</v>
       </c>
@@ -4203,7 +4222,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="41" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>179</v>
       </c>
@@ -4247,7 +4266,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="42" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>185</v>
       </c>
@@ -4297,7 +4316,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="43" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>188</v>
       </c>
@@ -4344,7 +4363,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="44" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>191</v>
       </c>
@@ -4391,7 +4410,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="45" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>195</v>
       </c>
@@ -4438,7 +4457,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="46" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>200</v>
       </c>
@@ -4482,7 +4501,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="47" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>203</v>
       </c>
@@ -4529,7 +4548,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="48" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>207</v>
       </c>
@@ -4576,7 +4595,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="49" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>210</v>
       </c>
@@ -4623,7 +4642,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="50" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>214</v>
       </c>
@@ -4670,7 +4689,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="51" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>218</v>
       </c>
@@ -4717,7 +4736,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="52" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>223</v>
       </c>
@@ -4767,7 +4786,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="53" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>227</v>
       </c>
@@ -4814,7 +4833,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="54" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>231</v>
       </c>
@@ -4861,7 +4880,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="55" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>235</v>
       </c>
@@ -4908,7 +4927,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="56" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>238</v>
       </c>
@@ -4955,7 +4974,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="57" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>242</v>
       </c>
@@ -5002,7 +5021,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="58" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>245</v>
       </c>
@@ -5049,7 +5068,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="59" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>249</v>
       </c>
@@ -5099,7 +5118,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="60" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>252</v>
       </c>
@@ -5146,7 +5165,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="61" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>255</v>
       </c>
@@ -5196,7 +5215,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="62" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>259</v>
       </c>
@@ -5240,7 +5259,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="63" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>262</v>
       </c>
@@ -5287,7 +5306,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="64" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>266</v>
       </c>
@@ -5331,7 +5350,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="65" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>269</v>
       </c>
@@ -5375,7 +5394,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="66" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>273</v>
       </c>
@@ -5419,7 +5438,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="67" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>276</v>
       </c>
@@ -5463,7 +5482,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="68" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>280</v>
       </c>
@@ -5507,7 +5526,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="69" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>284</v>
       </c>
@@ -5554,7 +5573,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="70" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>288</v>
       </c>
@@ -5601,7 +5620,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="71" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>292</v>
       </c>
@@ -5648,7 +5667,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="72" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>296</v>
       </c>
@@ -5692,7 +5711,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="73" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>299</v>
       </c>
@@ -5736,7 +5755,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="74" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>303</v>
       </c>
@@ -5780,7 +5799,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="75" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>306</v>
       </c>
@@ -5824,7 +5843,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="76" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>310</v>
       </c>
@@ -5868,7 +5887,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="77" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>314</v>
       </c>
@@ -5915,7 +5934,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="78" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>318</v>
       </c>
@@ -5962,7 +5981,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="79" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>321</v>
       </c>
@@ -6009,7 +6028,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="80" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>324</v>
       </c>
@@ -6056,7 +6075,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="81" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>328</v>
       </c>
@@ -6103,7 +6122,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="82" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>332</v>
       </c>
@@ -6147,7 +6166,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="83" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>335</v>
       </c>
@@ -6194,7 +6213,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="84" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>338</v>
       </c>
@@ -6241,7 +6260,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="85" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>341</v>
       </c>
@@ -6288,7 +6307,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="86" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>345</v>
       </c>
@@ -6335,7 +6354,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="87" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>348</v>
       </c>
@@ -6382,7 +6401,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="88" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>352</v>
       </c>
@@ -6429,7 +6448,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="89" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
         <v>420</v>
       </c>
@@ -6479,7 +6498,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="90" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
         <v>427</v>
       </c>
@@ -6529,7 +6548,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="91" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
         <v>432</v>
       </c>
@@ -6579,7 +6598,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="92" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
         <v>436</v>
       </c>
@@ -6629,7 +6648,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="93" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
         <v>441</v>
       </c>
@@ -6673,13 +6692,13 @@
         <v>424</v>
       </c>
       <c r="R93" s="1" t="s">
-        <v>439</v>
+        <v>457</v>
       </c>
       <c r="T93" s="1" t="s">
         <v>443</v>
       </c>
     </row>
-    <row r="94" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
         <v>444</v>
       </c>
@@ -6729,7 +6748,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="95" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
         <v>450</v>
       </c>
@@ -6788,412 +6807,412 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:A81"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="125.6640625" customWidth="1"/>
+    <col min="1" max="1" width="125.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>356</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>357</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>413</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>358</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>359</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>413</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>360</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>361</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>413</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>362</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>363</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>364</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>365</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>366</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>413</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="20" spans="1:1" ht="32.4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>367</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>368</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>369</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>370</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>413</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>371</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>372</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>413</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
         <v>373</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>374</v>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>375</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
         <v>413</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
         <v>376</v>
       </c>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
         <v>377</v>
       </c>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
         <v>378</v>
       </c>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
         <v>413</v>
       </c>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
         <v>379</v>
       </c>
     </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
         <v>380</v>
       </c>
     </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
         <v>381</v>
       </c>
     </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
         <v>413</v>
       </c>
     </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
         <v>382</v>
       </c>
     </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
         <v>383</v>
       </c>
     </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
         <v>413</v>
       </c>
     </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
         <v>384</v>
       </c>
     </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
         <v>385</v>
       </c>
     </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
         <v>413</v>
       </c>
     </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
         <v>387</v>
       </c>
     </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
         <v>388</v>
       </c>
     </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
         <v>389</v>
       </c>
     </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
         <v>390</v>
       </c>
     </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
         <v>413</v>
       </c>
     </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
         <v>391</v>
       </c>
     </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
         <v>392</v>
       </c>
     </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
         <v>393</v>
       </c>
     </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
         <v>394</v>
       </c>
     </row>
-    <row r="62" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
         <v>395</v>
       </c>
     </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
         <v>396</v>
       </c>
     </row>
-    <row r="64" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
         <v>398</v>
       </c>
     </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
         <v>413</v>
       </c>
     </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
         <v>399</v>
       </c>
     </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
         <v>400</v>
       </c>
     </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
         <v>401</v>
       </c>
     </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
         <v>402</v>
       </c>
     </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
         <v>403</v>
       </c>
     </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
         <v>413</v>
       </c>
     </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
         <v>414</v>
       </c>
     </row>
-    <row r="74" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
         <v>415</v>
       </c>
     </row>
-    <row r="75" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
         <v>404</v>
       </c>
     </row>
-    <row r="76" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
         <v>416</v>
       </c>
     </row>
-    <row r="77" spans="1:1" ht="32.4" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
         <v>417</v>
       </c>
     </row>
-    <row r="78" spans="1:1" ht="32.4" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
         <v>453</v>
       </c>
     </row>
-    <row r="79" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
         <v>454</v>
       </c>
     </row>
-    <row r="80" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
         <v>418</v>
       </c>
     </row>
-    <row r="81" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
         <v>419</v>
       </c>

--- a/config/Excel/Status.xlsx
+++ b/config/Excel/Status.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyGame\Idle-RPG\codex\config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40918CFA-4F79-4F41-ACF3-D7068622663B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D76DF7F2-2196-4660-A6CF-D3BF2A03231E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="33420" yWindow="2730" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Status" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="964" uniqueCount="458">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="964" uniqueCount="459">
   <si>
     <t>狀態ID</t>
   </si>
@@ -1381,9 +1381,6 @@
   </si>
   <si>
     <t>ground-domain-ice</t>
-  </si>
-  <si>
-    <t>超神進化【水牢天瀑】：圍在你周圍的水牢，持續期間跟著你移動；持續特效依水牢半徑縮放（牢內敵人身上的【水牢】與攻擊下降另計）。</t>
   </si>
   <si>
     <t>sgAbyssDomain</t>
@@ -1410,6 +1407,14 @@
   </si>
   <si>
     <t>ground-domain-earth-10</t>
+  </si>
+  <si>
+    <t>field-water-prison-dome</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>超神進化【水牢天瀑】：周圍的水牢罩子（半徑依技能範圍，跟著玩家移動）；期間受到的遠程傷害降低，圈內敵人攻擊下降且受到傷害提高，水牢結束時撤除。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -4169,10 +4174,10 @@
         <v>1</v>
       </c>
       <c r="R39" s="1" t="s">
+        <v>454</v>
+      </c>
+      <c r="T39" s="1" t="s">
         <v>455</v>
-      </c>
-      <c r="T39" s="1" t="s">
-        <v>456</v>
       </c>
     </row>
     <row r="40" spans="1:20" x14ac:dyDescent="0.25">
@@ -6383,7 +6388,7 @@
         <v>0</v>
       </c>
       <c r="L87">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="M87">
         <v>6</v>
@@ -6692,7 +6697,7 @@
         <v>424</v>
       </c>
       <c r="R93" s="1" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="T93" s="1" t="s">
         <v>443</v>
@@ -6742,18 +6747,18 @@
         <v>424</v>
       </c>
       <c r="R94" s="1" t="s">
-        <v>448</v>
+        <v>457</v>
       </c>
       <c r="T94" s="1" t="s">
-        <v>449</v>
+        <v>458</v>
       </c>
     </row>
     <row r="95" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
+        <v>449</v>
+      </c>
+      <c r="B95" s="1" t="s">
         <v>450</v>
-      </c>
-      <c r="B95" s="1" t="s">
-        <v>451</v>
       </c>
       <c r="C95" s="1" t="s">
         <v>350</v>
@@ -6765,7 +6770,7 @@
         <v>79</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="G95" s="1" t="s">
         <v>221</v>
@@ -6795,7 +6800,7 @@
         <v>448</v>
       </c>
       <c r="T95" s="1" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
   </sheetData>
@@ -7199,12 +7204,12 @@
     </row>
     <row r="78" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="79" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
     </row>
     <row r="80" spans="1:1" x14ac:dyDescent="0.25">

--- a/config/Excel/Status.xlsx
+++ b/config/Excel/Status.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyGame\Idle-RPG\codex\config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D76DF7F2-2196-4660-A6CF-D3BF2A03231E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA6066D4-F9DB-4DE4-A68E-54CB0AADE936}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="33420" yWindow="2730" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1389,9 +1389,6 @@
     <t>海淵葬界</t>
   </si>
   <si>
-    <t>超神進化【海淵葬界】：永久展開的水之領域，跟著你移動；持續特效依領域半徑縮放。持續時間只是讓它一直掛著：領域在不在由超神進化與技能列裝配決定，卸下或換掉超神就移除。</t>
-  </si>
-  <si>
     <t>　代表一個範圍的狀態（以玩家為中心的領域：殺神領域、火神降臨、海淵葬界…）例外：持續特效依領域的實際半徑縮放並跟著玩家走，範圍變大畫面就跟著變大；</t>
   </si>
   <si>
@@ -1414,6 +1411,10 @@
   </si>
   <si>
     <t>超神進化【水牢天瀑】：周圍的水牢罩子（半徑依技能範圍，跟著玩家移動）；期間受到的遠程傷害降低，圈內敵人攻擊下降且受到傷害提高，水牢結束時撤除。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>超神進化【海淵葬界】：永久展開的寒冰領域，跟著你移動；持續特效依領域半徑縮放。持續時間只是讓它一直掛著：領域在不在由超神進化與技能列裝配決定，卸下或換掉超神就移除。</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -4174,10 +4175,10 @@
         <v>1</v>
       </c>
       <c r="R39" s="1" t="s">
+        <v>453</v>
+      </c>
+      <c r="T39" s="1" t="s">
         <v>454</v>
-      </c>
-      <c r="T39" s="1" t="s">
-        <v>455</v>
       </c>
     </row>
     <row r="40" spans="1:20" x14ac:dyDescent="0.25">
@@ -6697,7 +6698,7 @@
         <v>424</v>
       </c>
       <c r="R93" s="1" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="T93" s="1" t="s">
         <v>443</v>
@@ -6747,10 +6748,10 @@
         <v>424</v>
       </c>
       <c r="R94" s="1" t="s">
+        <v>456</v>
+      </c>
+      <c r="T94" s="1" t="s">
         <v>457</v>
-      </c>
-      <c r="T94" s="1" t="s">
-        <v>458</v>
       </c>
     </row>
     <row r="95" spans="1:20" x14ac:dyDescent="0.25">
@@ -6800,7 +6801,7 @@
         <v>448</v>
       </c>
       <c r="T95" s="1" t="s">
-        <v>451</v>
+        <v>458</v>
       </c>
     </row>
   </sheetData>
@@ -7204,12 +7205,12 @@
     </row>
     <row r="78" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="79" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="80" spans="1:1" x14ac:dyDescent="0.25">

--- a/config/Excel/Status.xlsx
+++ b/config/Excel/Status.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyGame\Idle-RPG\codex\config\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\AppData\Local\Temp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA6066D4-F9DB-4DE4-A68E-54CB0AADE936}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF1F7C16-358A-490A-881A-B463092C17E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="33420" yWindow="2730" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Status" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="964" uniqueCount="459">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="964" uniqueCount="460">
   <si>
     <t>狀態ID</t>
   </si>
@@ -1017,9 +1017,6 @@
     <t>🗿</t>
   </si>
   <si>
-    <t>超神進化【超重岩之術】：被壓縮的巨岩之力封住的敵人。行動限制本身由「暈眩」承擔（因此完整沿用 BOSS 控場免疫、韌性折減與控場遞減），本狀態只負責「受到的土系傷害額外提高」（效果值＝提高%）。</t>
-  </si>
-  <si>
     <t>sgStiffen</t>
   </si>
   <si>
@@ -1354,9 +1351,6 @@
   </si>
   <si>
     <t>ground-domain-earth</t>
-  </si>
-  <si>
-    <t>超神進化【超重岩之術】：岩甲護盾存在期間展開的領域，進入的敵人被石化；持續特效依領域半徑縮放、跟著你移動。持續到岩甲護盾結束（實際秒數由岩甲術給）。</t>
   </si>
   <si>
     <t>sgGravityDomain</t>
@@ -1415,6 +1409,18 @@
   </si>
   <si>
     <t>超神進化【海淵葬界】：永久展開的寒冰領域，跟著你移動；持續特效依領域半徑縮放。持續時間只是讓它一直掛著：領域在不在由超神進化與技能列裝配決定，卸下或換掉超神就移除。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>超神進化【超重岩之術】：石化期間無法行動且屬性標籤轉為地。行動限制沿用暈眩、BOSS免控、韌性與控場遞減；石化標記及轉地與實際暈眩時間一致，結束後恢復原屬性。不再附加地系易傷。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>4</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>超神進化【超重岩之術】：施放時石化24米內敵人，之後4秒每0.5秒升起4道岩柱。領域跟隨玩家、按24米半徑顯示；持續固定4秒，不依岩甲護盾時間，也不對新進入者重複石化。</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -3949,10 +3955,10 @@
         <v>1</v>
       </c>
       <c r="Q34" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="S34" s="1" t="s">
         <v>405</v>
-      </c>
-      <c r="S34" s="1" t="s">
-        <v>406</v>
       </c>
       <c r="T34" t="s">
         <v>157</v>
@@ -4175,10 +4181,10 @@
         <v>1</v>
       </c>
       <c r="R39" s="1" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="T39" s="1" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
     </row>
     <row r="40" spans="1:20" x14ac:dyDescent="0.25">
@@ -4222,7 +4228,7 @@
         <v>1</v>
       </c>
       <c r="R40" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="T40" t="s">
         <v>178</v>
@@ -4316,7 +4322,7 @@
         <v>1</v>
       </c>
       <c r="S42" s="1" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="T42" t="s">
         <v>187</v>
@@ -4786,7 +4792,7 @@
         <v>1</v>
       </c>
       <c r="S52" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="T52" t="s">
         <v>226</v>
@@ -5118,7 +5124,7 @@
         <v>1</v>
       </c>
       <c r="R59" s="1" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="T59" t="s">
         <v>251</v>
@@ -5215,7 +5221,7 @@
         <v>1</v>
       </c>
       <c r="R61" s="1" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="T61" t="s">
         <v>258</v>
@@ -5667,7 +5673,7 @@
         <v>1</v>
       </c>
       <c r="R71" s="1" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="T71" t="s">
         <v>295</v>
@@ -5934,7 +5940,7 @@
         <v>1</v>
       </c>
       <c r="R77" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="T77" t="s">
         <v>317</v>
@@ -6063,10 +6069,10 @@
         <v>0</v>
       </c>
       <c r="L80">
-        <v>400</v>
+        <v>1</v>
       </c>
       <c r="M80">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N80">
         <v>0</v>
@@ -6078,18 +6084,18 @@
         <v>1</v>
       </c>
       <c r="T80" t="s">
-        <v>327</v>
+        <v>457</v>
       </c>
     </row>
     <row r="81" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
+        <v>327</v>
+      </c>
+      <c r="B81" t="s">
         <v>328</v>
       </c>
-      <c r="B81" t="s">
+      <c r="C81" t="s">
         <v>329</v>
-      </c>
-      <c r="C81" t="s">
-        <v>330</v>
       </c>
       <c r="D81" t="s">
         <v>23</v>
@@ -6098,7 +6104,7 @@
         <v>79</v>
       </c>
       <c r="F81" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="G81" t="s">
         <v>198</v>
@@ -6125,15 +6131,15 @@
         <v>1</v>
       </c>
       <c r="T81" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="82" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
+        <v>331</v>
+      </c>
+      <c r="B82" t="s">
         <v>332</v>
-      </c>
-      <c r="B82" t="s">
-        <v>333</v>
       </c>
       <c r="C82" t="s">
         <v>22</v>
@@ -6169,15 +6175,15 @@
         <v>1</v>
       </c>
       <c r="T82" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="83" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
+        <v>334</v>
+      </c>
+      <c r="B83" t="s">
         <v>335</v>
-      </c>
-      <c r="B83" t="s">
-        <v>336</v>
       </c>
       <c r="C83" t="s">
         <v>44</v>
@@ -6216,15 +6222,15 @@
         <v>1</v>
       </c>
       <c r="T83" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="84" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
+        <v>337</v>
+      </c>
+      <c r="B84" t="s">
         <v>338</v>
-      </c>
-      <c r="B84" t="s">
-        <v>339</v>
       </c>
       <c r="C84" t="s">
         <v>212</v>
@@ -6236,7 +6242,7 @@
         <v>79</v>
       </c>
       <c r="F84" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="G84" t="s">
         <v>31</v>
@@ -6263,18 +6269,18 @@
         <v>1</v>
       </c>
       <c r="T84" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="85" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
+        <v>340</v>
+      </c>
+      <c r="B85" t="s">
         <v>341</v>
       </c>
-      <c r="B85" t="s">
+      <c r="C85" t="s">
         <v>342</v>
-      </c>
-      <c r="C85" t="s">
-        <v>343</v>
       </c>
       <c r="D85" t="s">
         <v>65</v>
@@ -6283,7 +6289,7 @@
         <v>79</v>
       </c>
       <c r="F85" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="G85" t="s">
         <v>123</v>
@@ -6310,15 +6316,15 @@
         <v>100</v>
       </c>
       <c r="T85" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="86" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
+        <v>344</v>
+      </c>
+      <c r="B86" t="s">
         <v>345</v>
-      </c>
-      <c r="B86" t="s">
-        <v>346</v>
       </c>
       <c r="C86" t="s">
         <v>86</v>
@@ -6330,7 +6336,7 @@
         <v>79</v>
       </c>
       <c r="F86" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="G86" t="s">
         <v>123</v>
@@ -6357,18 +6363,18 @@
         <v>1</v>
       </c>
       <c r="T86" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="87" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
+        <v>347</v>
+      </c>
+      <c r="B87" t="s">
         <v>348</v>
       </c>
-      <c r="B87" t="s">
+      <c r="C87" t="s">
         <v>349</v>
-      </c>
-      <c r="C87" t="s">
-        <v>350</v>
       </c>
       <c r="D87" t="s">
         <v>23</v>
@@ -6377,7 +6383,7 @@
         <v>79</v>
       </c>
       <c r="F87" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="G87" t="s">
         <v>221</v>
@@ -6404,18 +6410,18 @@
         <v>1</v>
       </c>
       <c r="T87" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="88" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
+        <v>351</v>
+      </c>
+      <c r="B88" t="s">
         <v>352</v>
       </c>
-      <c r="B88" t="s">
+      <c r="C88" t="s">
         <v>353</v>
-      </c>
-      <c r="C88" t="s">
-        <v>354</v>
       </c>
       <c r="D88" t="s">
         <v>23</v>
@@ -6424,7 +6430,7 @@
         <v>79</v>
       </c>
       <c r="F88" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="G88" t="s">
         <v>240</v>
@@ -6451,15 +6457,15 @@
         <v>1</v>
       </c>
       <c r="T88" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="89" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
+        <v>419</v>
+      </c>
+      <c r="B89" s="1" t="s">
         <v>420</v>
-      </c>
-      <c r="B89" s="1" t="s">
-        <v>421</v>
       </c>
       <c r="C89" s="1" t="s">
         <v>282</v>
@@ -6471,48 +6477,48 @@
         <v>79</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="G89" s="1" t="s">
         <v>40</v>
       </c>
       <c r="I89" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="K89" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="L89" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="M89" s="1" t="s">
         <v>422</v>
       </c>
-      <c r="K89" s="1" t="s">
-        <v>422</v>
-      </c>
-      <c r="L89" s="1" t="s">
-        <v>422</v>
-      </c>
-      <c r="M89" s="1" t="s">
-        <v>423</v>
-      </c>
       <c r="N89" s="1" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="O89" s="1" t="s">
         <v>56</v>
       </c>
       <c r="P89" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="R89" s="1" t="s">
         <v>424</v>
       </c>
-      <c r="R89" s="1" t="s">
+      <c r="T89" s="1" t="s">
         <v>425</v>
-      </c>
-      <c r="T89" s="1" t="s">
-        <v>426</v>
       </c>
     </row>
     <row r="90" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="B90" s="1" t="s">
         <v>427</v>
       </c>
-      <c r="B90" s="1" t="s">
+      <c r="C90" s="1" t="s">
         <v>428</v>
-      </c>
-      <c r="C90" s="1" t="s">
-        <v>429</v>
       </c>
       <c r="D90" s="1" t="s">
         <v>65</v>
@@ -6521,45 +6527,45 @@
         <v>79</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="G90" s="1" t="s">
         <v>33</v>
       </c>
       <c r="I90" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="K90" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="L90" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="M90" s="1" t="s">
         <v>422</v>
       </c>
-      <c r="K90" s="1" t="s">
-        <v>422</v>
-      </c>
-      <c r="L90" s="1" t="s">
-        <v>422</v>
-      </c>
-      <c r="M90" s="1" t="s">
-        <v>423</v>
-      </c>
       <c r="N90" s="1" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="O90" s="1" t="s">
         <v>56</v>
       </c>
       <c r="P90" s="1" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="R90" s="1" t="s">
+        <v>429</v>
+      </c>
+      <c r="T90" s="1" t="s">
         <v>430</v>
-      </c>
-      <c r="T90" s="1" t="s">
-        <v>431</v>
       </c>
     </row>
     <row r="91" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="B91" s="1" t="s">
         <v>432</v>
-      </c>
-      <c r="B91" s="1" t="s">
-        <v>433</v>
       </c>
       <c r="C91" s="1" t="s">
         <v>30</v>
@@ -6571,45 +6577,45 @@
         <v>79</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="G91" s="1" t="s">
         <v>31</v>
       </c>
       <c r="I91" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="K91" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="L91" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="M91" s="1" t="s">
         <v>422</v>
       </c>
-      <c r="K91" s="1" t="s">
-        <v>422</v>
-      </c>
-      <c r="L91" s="1" t="s">
-        <v>422</v>
-      </c>
-      <c r="M91" s="1" t="s">
-        <v>423</v>
-      </c>
       <c r="N91" s="1" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="O91" s="1" t="s">
         <v>56</v>
       </c>
       <c r="P91" s="1" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="R91" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="T91" s="1" t="s">
         <v>434</v>
-      </c>
-      <c r="T91" s="1" t="s">
-        <v>435</v>
       </c>
     </row>
     <row r="92" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="B92" s="1" t="s">
         <v>436</v>
-      </c>
-      <c r="B92" s="1" t="s">
-        <v>437</v>
       </c>
       <c r="C92" s="1" t="s">
         <v>326</v>
@@ -6621,48 +6627,48 @@
         <v>79</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="G92" s="1" t="s">
         <v>198</v>
       </c>
       <c r="I92" s="1" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="K92" s="1" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="L92" s="1" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="M92" s="1" t="s">
-        <v>438</v>
+        <v>458</v>
       </c>
       <c r="N92" s="1" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="O92" s="1" t="s">
         <v>56</v>
       </c>
       <c r="P92" s="1" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="R92" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="T92" s="1" t="s">
-        <v>440</v>
+        <v>459</v>
       </c>
     </row>
     <row r="93" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="D93" s="1" t="s">
         <v>65</v>
@@ -6671,48 +6677,48 @@
         <v>79</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="G93" s="1" t="s">
         <v>198</v>
       </c>
       <c r="I93" s="1" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="K93" s="1" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="L93" s="1" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="M93" s="1" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="N93" s="1" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="O93" s="1" t="s">
         <v>56</v>
       </c>
       <c r="P93" s="1" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="R93" s="1" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="T93" s="1" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
     </row>
     <row r="94" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="B94" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="C94" s="1" t="s">
         <v>444</v>
-      </c>
-      <c r="B94" s="1" t="s">
-        <v>445</v>
-      </c>
-      <c r="C94" s="1" t="s">
-        <v>446</v>
       </c>
       <c r="D94" s="1" t="s">
         <v>65</v>
@@ -6721,48 +6727,48 @@
         <v>79</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="G94" s="1" t="s">
         <v>221</v>
       </c>
       <c r="I94" s="1" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="K94" s="1" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="L94" s="1" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="M94" s="1" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="N94" s="1" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="O94" s="1" t="s">
         <v>56</v>
       </c>
       <c r="P94" s="1" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="R94" s="1" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="T94" s="1" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
     </row>
     <row r="95" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="D95" s="1" t="s">
         <v>65</v>
@@ -6771,42 +6777,43 @@
         <v>79</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="G95" s="1" t="s">
         <v>221</v>
       </c>
       <c r="I95" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="K95" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="L95" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="M95" s="1" t="s">
         <v>422</v>
       </c>
-      <c r="K95" s="1" t="s">
-        <v>422</v>
-      </c>
-      <c r="L95" s="1" t="s">
-        <v>422</v>
-      </c>
-      <c r="M95" s="1" t="s">
-        <v>423</v>
-      </c>
       <c r="N95" s="1" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="O95" s="1" t="s">
         <v>56</v>
       </c>
       <c r="P95" s="1" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="R95" s="1" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="T95" s="1" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -6825,32 +6832,32 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
@@ -6860,17 +6867,17 @@
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
@@ -6880,32 +6887,32 @@
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
@@ -6915,27 +6922,27 @@
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
@@ -6945,17 +6952,17 @@
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
@@ -6965,22 +6972,22 @@
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
@@ -6990,42 +6997,42 @@
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.25">
@@ -7035,17 +7042,17 @@
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.25">
@@ -7055,22 +7062,22 @@
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.25">
@@ -7080,147 +7087,147 @@
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="54" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="56" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="59" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="60" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="61" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="62" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="63" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="64" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="66" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="67" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="68" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="69" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="70" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="71" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="72" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="73" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
     </row>
     <row r="74" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="75" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="76" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="77" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="78" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
     </row>
     <row r="79" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
     </row>
     <row r="80" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="81" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
   </sheetData>

--- a/config/Excel/Status.xlsx
+++ b/config/Excel/Status.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\AppData\Local\Temp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF1F7C16-358A-490A-881A-B463092C17E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C0D384D-958B-4D46-A756-64C045628C81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3090" yWindow="2310" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Status" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="964" uniqueCount="460">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1041" uniqueCount="486">
   <si>
     <t>狀態ID</t>
   </si>
@@ -1422,6 +1422,84 @@
   <si>
     <t>超神進化【超重岩之術】：施放時石化24米內敵人，之後4秒每0.5秒升起4道岩柱。領域跟隨玩家、按24米半徑顯示；持續固定4秒，不依岩甲護盾時間，也不對新進入者重複石化。</t>
     <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>eInvuln</t>
+  </si>
+  <si>
+    <t>無敵護罩</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>en-gold-dome</t>
+  </si>
+  <si>
+    <t>敵人專用（高級敵人技能【護盾】【庇護光環】【不死鳥】）：身上罩著金色光罩，期間免疫所有傷害。這是畫面標記，免疫本身由敵人技能引擎結算；持續時間由技能給。</t>
+  </si>
+  <si>
+    <t>eEnrage</t>
+  </si>
+  <si>
+    <t>狂暴</t>
+  </si>
+  <si>
+    <t>en-burst-blood</t>
+  </si>
+  <si>
+    <t>en-aura-enrage</t>
+  </si>
+  <si>
+    <t>敵人專用（高級敵人技能【狂暴】）：生命低於門檻後進入，攻擊力與攻速大幅提高，直到死亡為止。這是畫面標記，數值由敵人技能引擎結算。</t>
+  </si>
+  <si>
+    <t>eRage</t>
+  </si>
+  <si>
+    <t>怒意</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>en-rage-burst</t>
+  </si>
+  <si>
+    <t>en-aura-rage</t>
+  </si>
+  <si>
+    <t>敵人專用（高級敵人技能【血祭】【復仇】）：攻擊力提高的怒氣狀態（血祭＝限時、復仇＝每死一個同伴疊一次並持續到死亡）。這是畫面標記，數值由敵人技能引擎結算。</t>
+  </si>
+  <si>
+    <t>eRegen</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>en-burst-holy</t>
+  </si>
+  <si>
+    <t>敵人專用（高級敵人技能【再生】）：每隔一段時間回復最大生命的一個比例，直到死亡為止。這是畫面標記，回復由敵人技能引擎結算；每次回復播「作用特效」。</t>
+  </si>
+  <si>
+    <t>eCurse</t>
+  </si>
+  <si>
+    <t>衰弱詛咒</t>
+  </si>
+  <si>
+    <t>🧿</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>en-curse-dark</t>
+  </si>
+  <si>
+    <t>敵人專用（高級敵人技能【衰弱詛咒】）：被詛咒的玩家攻擊力與防禦力降低（降幅由「攻擊」「防禦」減益狀態結算）。這是畫面標記，用來顯示詛咒的上身特效與剩餘時間。</t>
   </si>
 </sst>
 </file>
@@ -2399,7 +2477,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:T95"/>
+  <dimension ref="A1:T100"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="18" max="18" width="12.375" customWidth="1"/>
@@ -6808,6 +6886,247 @@
       </c>
       <c r="T95" s="1" t="s">
         <v>456</v>
+      </c>
+    </row>
+    <row r="96" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A96" s="1" t="s">
+        <v>460</v>
+      </c>
+      <c r="B96" s="1" t="s">
+        <v>461</v>
+      </c>
+      <c r="C96" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="D96" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="E96" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="F96" s="1" t="s">
+        <v>460</v>
+      </c>
+      <c r="I96" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="K96" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="L96" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="M96" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="N96" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="O96" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="P96" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="R96" s="1" t="s">
+        <v>463</v>
+      </c>
+      <c r="T96" s="1" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="97" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A97" s="1" t="s">
+        <v>465</v>
+      </c>
+      <c r="B97" s="1" t="s">
+        <v>466</v>
+      </c>
+      <c r="C97" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="D97" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="E97" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="F97" s="1" t="s">
+        <v>465</v>
+      </c>
+      <c r="I97" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="K97" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="L97" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="M97" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="N97" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="O97" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="P97" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="Q97" s="1" t="s">
+        <v>467</v>
+      </c>
+      <c r="R97" s="1" t="s">
+        <v>468</v>
+      </c>
+      <c r="T97" s="1" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="98" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A98" s="1" t="s">
+        <v>470</v>
+      </c>
+      <c r="B98" s="1" t="s">
+        <v>471</v>
+      </c>
+      <c r="C98" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D98" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="E98" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="F98" s="1" t="s">
+        <v>470</v>
+      </c>
+      <c r="I98" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="K98" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="L98" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="M98" s="1" t="s">
+        <v>472</v>
+      </c>
+      <c r="N98" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="O98" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="P98" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="Q98" s="1" t="s">
+        <v>473</v>
+      </c>
+      <c r="R98" s="1" t="s">
+        <v>474</v>
+      </c>
+      <c r="T98" s="1" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="99" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A99" s="1" t="s">
+        <v>476</v>
+      </c>
+      <c r="B99" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C99" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="D99" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="E99" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="F99" s="1" t="s">
+        <v>476</v>
+      </c>
+      <c r="I99" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="K99" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="L99" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="M99" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="N99" s="1" t="s">
+        <v>477</v>
+      </c>
+      <c r="O99" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="P99" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="S99" s="1" t="s">
+        <v>478</v>
+      </c>
+      <c r="T99" s="1" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="100" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A100" s="1" t="s">
+        <v>480</v>
+      </c>
+      <c r="B100" s="1" t="s">
+        <v>481</v>
+      </c>
+      <c r="C100" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="D100" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E100" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="F100" s="1" t="s">
+        <v>480</v>
+      </c>
+      <c r="I100" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="K100" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="L100" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="M100" s="1" t="s">
+        <v>483</v>
+      </c>
+      <c r="N100" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="O100" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="P100" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="Q100" s="1" t="s">
+        <v>484</v>
+      </c>
+      <c r="T100" s="1" t="s">
+        <v>485</v>
       </c>
     </row>
   </sheetData>

--- a/config/Excel/Status.xlsx
+++ b/config/Excel/Status.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\AppData\Local\Temp\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\AppData\Local\Temp\potential-remove-baseline-20261018\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C0D384D-958B-4D46-A756-64C045628C81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B0E3818-6910-4E84-8531-C3B33A332005}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3090" yWindow="2310" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1041" uniqueCount="486">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="999" uniqueCount="467">
   <si>
     <t>狀態ID</t>
   </si>
@@ -375,69 +375,18 @@
     <t>allDmgUp</t>
   </si>
   <si>
-    <t>時空凝滯·所有傷害</t>
-  </si>
-  <si>
     <t>🌌</t>
   </si>
   <si>
-    <t>潛力【時空凝滯】：所有傷害提高。</t>
-  </si>
-  <si>
-    <t>velocitySurge</t>
-  </si>
-  <si>
-    <t>極速之力·攻速</t>
-  </si>
-  <si>
     <t>💨</t>
   </si>
   <si>
-    <t>潛力【極速之力】：攻速提高。</t>
-  </si>
-  <si>
-    <t>lightningOverload</t>
-  </si>
-  <si>
-    <t>雷霆過載·雷電傷害</t>
-  </si>
-  <si>
-    <t>🌩️</t>
-  </si>
-  <si>
     <t>lightning</t>
   </si>
   <si>
-    <t>潛力【雷霆過載】：雷電傷害提高。</t>
-  </si>
-  <si>
-    <t>chronoCdr</t>
-  </si>
-  <si>
-    <t>時間坍縮·冷卻縮減</t>
-  </si>
-  <si>
-    <t>⏱️</t>
-  </si>
-  <si>
-    <t>潛力【時間坍縮】：冷卻縮減。</t>
-  </si>
-  <si>
-    <t>sacredInvert</t>
-  </si>
-  <si>
-    <t>聖療逆轉·回復/溢傷</t>
-  </si>
-  <si>
-    <t>🕊️</t>
-  </si>
-  <si>
     <t>light</t>
   </si>
   <si>
-    <t>潛力【聖療逆轉】：回復與溢傷轉換。</t>
-  </si>
-  <si>
     <t>legendaryDarkUp</t>
   </si>
   <si>
@@ -478,18 +427,6 @@
   </si>
   <si>
     <t>目標防禦力下降（舊存檔融合技快照相容保留，新設計改用穿透提升）。</t>
-  </si>
-  <si>
-    <t>enemyAspdDown</t>
-  </si>
-  <si>
-    <t>時間結界·攻速</t>
-  </si>
-  <si>
-    <t>⏳</t>
-  </si>
-  <si>
-    <t>潛力【時間結界】：目標攻擊速度下降。</t>
   </si>
   <si>
     <t>sgBleed</t>
@@ -1500,6 +1437,14 @@
   </si>
   <si>
     <t>敵人專用（高級敵人技能【衰弱詛咒】）：被詛咒的玩家攻擊力與防禦力降低（降幅由「攻擊」「防禦」減益狀態結算）。這是畫面標記，用來顯示詛咒的上身特效與剩餘時間。</t>
+  </si>
+  <si>
+    <t>所有傷害提高</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>符文真言增益：所有傷害提高。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -2477,7 +2422,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:T100"/>
+  <dimension ref="A1:T95"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="18" max="18" width="12.375" customWidth="1"/>
@@ -3454,10 +3399,10 @@
         <v>112</v>
       </c>
       <c r="B22" t="s">
+        <v>465</v>
+      </c>
+      <c r="C22" t="s">
         <v>113</v>
-      </c>
-      <c r="C22" t="s">
-        <v>114</v>
       </c>
       <c r="D22" t="s">
         <v>65</v>
@@ -3490,18 +3435,18 @@
         <v>1</v>
       </c>
       <c r="T22" t="s">
-        <v>115</v>
+        <v>466</v>
       </c>
     </row>
     <row r="23" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B23" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C23" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D23" t="s">
         <v>65</v>
@@ -3510,7 +3455,10 @@
         <v>79</v>
       </c>
       <c r="F23" t="s">
-        <v>116</v>
+        <v>117</v>
+      </c>
+      <c r="G23" t="s">
+        <v>40</v>
       </c>
       <c r="I23">
         <v>0</v>
@@ -3534,18 +3482,18 @@
         <v>1</v>
       </c>
       <c r="T23" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="24" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B24" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C24" t="s">
-        <v>122</v>
+        <v>74</v>
       </c>
       <c r="D24" t="s">
         <v>65</v>
@@ -3554,10 +3502,7 @@
         <v>79</v>
       </c>
       <c r="F24" t="s">
-        <v>120</v>
-      </c>
-      <c r="G24" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="I24">
         <v>0</v>
@@ -3581,18 +3526,18 @@
         <v>1</v>
       </c>
       <c r="T24" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="25" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
+        <v>124</v>
+      </c>
+      <c r="B25" t="s">
         <v>125</v>
       </c>
-      <c r="B25" t="s">
+      <c r="C25" t="s">
         <v>126</v>
-      </c>
-      <c r="C25" t="s">
-        <v>127</v>
       </c>
       <c r="D25" t="s">
         <v>65</v>
@@ -3601,7 +3546,10 @@
         <v>79</v>
       </c>
       <c r="F25" t="s">
-        <v>125</v>
+        <v>124</v>
+      </c>
+      <c r="G25" t="s">
+        <v>116</v>
       </c>
       <c r="I25">
         <v>0</v>
@@ -3625,30 +3573,27 @@
         <v>1</v>
       </c>
       <c r="T25" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
     </row>
     <row r="26" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B26" t="s">
-        <v>130</v>
+        <v>77</v>
       </c>
       <c r="C26" t="s">
-        <v>131</v>
+        <v>78</v>
       </c>
       <c r="D26" t="s">
-        <v>65</v>
+        <v>23</v>
       </c>
       <c r="E26" t="s">
         <v>79</v>
       </c>
       <c r="F26" t="s">
-        <v>129</v>
-      </c>
-      <c r="G26" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="I26">
         <v>0</v>
@@ -3657,10 +3602,10 @@
         <v>0</v>
       </c>
       <c r="L26">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="M26">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N26">
         <v>0</v>
@@ -3672,30 +3617,27 @@
         <v>1</v>
       </c>
       <c r="T26" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
     </row>
     <row r="27" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="B27" t="s">
-        <v>135</v>
+        <v>82</v>
       </c>
       <c r="C27" t="s">
-        <v>136</v>
+        <v>74</v>
       </c>
       <c r="D27" t="s">
-        <v>65</v>
+        <v>23</v>
       </c>
       <c r="E27" t="s">
         <v>79</v>
       </c>
       <c r="F27" t="s">
-        <v>134</v>
-      </c>
-      <c r="G27" t="s">
-        <v>40</v>
+        <v>129</v>
       </c>
       <c r="I27">
         <v>0</v>
@@ -3707,7 +3649,7 @@
         <v>0</v>
       </c>
       <c r="M27">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N27">
         <v>0</v>
@@ -3719,30 +3661,30 @@
         <v>1</v>
       </c>
       <c r="T27" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
     </row>
     <row r="28" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="B28" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="C28" t="s">
-        <v>74</v>
+        <v>22</v>
       </c>
       <c r="D28" t="s">
-        <v>65</v>
+        <v>23</v>
       </c>
       <c r="E28" t="s">
-        <v>79</v>
-      </c>
-      <c r="F28" t="s">
-        <v>138</v>
+        <v>24</v>
+      </c>
+      <c r="H28" t="s">
+        <v>25</v>
       </c>
       <c r="I28">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="K28">
         <v>0</v>
@@ -3754,42 +3696,42 @@
         <v>5</v>
       </c>
       <c r="N28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O28" t="s">
-        <v>56</v>
+        <v>26</v>
       </c>
       <c r="P28">
         <v>1</v>
       </c>
       <c r="T28" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
     </row>
     <row r="29" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="B29" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="C29" t="s">
-        <v>143</v>
+        <v>35</v>
       </c>
       <c r="D29" t="s">
-        <v>65</v>
+        <v>23</v>
       </c>
       <c r="E29" t="s">
-        <v>79</v>
-      </c>
-      <c r="F29" t="s">
-        <v>141</v>
+        <v>24</v>
       </c>
       <c r="G29" t="s">
-        <v>132</v>
+        <v>33</v>
+      </c>
+      <c r="H29" t="s">
+        <v>25</v>
       </c>
       <c r="I29">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="K29">
         <v>0</v>
@@ -3798,54 +3740,60 @@
         <v>0</v>
       </c>
       <c r="M29">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N29">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="O29" t="s">
-        <v>56</v>
+        <v>26</v>
       </c>
       <c r="P29">
         <v>1</v>
       </c>
+      <c r="Q29" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="S29" s="1" t="s">
+        <v>384</v>
+      </c>
       <c r="T29" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
     </row>
     <row r="30" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="B30" t="s">
-        <v>77</v>
+        <v>138</v>
       </c>
       <c r="C30" t="s">
-        <v>78</v>
+        <v>110</v>
       </c>
       <c r="D30" t="s">
         <v>23</v>
       </c>
       <c r="E30" t="s">
-        <v>79</v>
-      </c>
-      <c r="F30" t="s">
-        <v>144</v>
+        <v>24</v>
+      </c>
+      <c r="H30" t="s">
+        <v>49</v>
       </c>
       <c r="I30">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="K30">
         <v>0</v>
       </c>
       <c r="L30">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="M30">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="N30">
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="O30" t="s">
         <v>56</v>
@@ -3854,27 +3802,27 @@
         <v>1</v>
       </c>
       <c r="T30" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
     </row>
     <row r="31" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="B31" t="s">
-        <v>82</v>
+        <v>141</v>
       </c>
       <c r="C31" t="s">
-        <v>74</v>
+        <v>114</v>
       </c>
       <c r="D31" t="s">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="E31" t="s">
         <v>79</v>
       </c>
       <c r="F31" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="I31">
         <v>0</v>
@@ -3883,10 +3831,10 @@
         <v>0</v>
       </c>
       <c r="L31">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M31">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N31">
         <v>0</v>
@@ -3898,27 +3846,27 @@
         <v>1</v>
       </c>
       <c r="T31" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
     </row>
     <row r="32" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="B32" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="C32" t="s">
-        <v>150</v>
+        <v>30</v>
       </c>
       <c r="D32" t="s">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="E32" t="s">
         <v>79</v>
       </c>
       <c r="F32" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="I32">
         <v>0</v>
@@ -3927,10 +3875,10 @@
         <v>0</v>
       </c>
       <c r="L32">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M32">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N32">
         <v>0</v>
@@ -3942,77 +3890,74 @@
         <v>1</v>
       </c>
       <c r="T32" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
     </row>
     <row r="33" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="B33" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="C33" t="s">
-        <v>22</v>
+        <v>94</v>
       </c>
       <c r="D33" t="s">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="E33" t="s">
-        <v>24</v>
-      </c>
-      <c r="H33" t="s">
-        <v>25</v>
+        <v>79</v>
+      </c>
+      <c r="F33" t="s">
+        <v>149</v>
       </c>
       <c r="I33">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K33">
         <v>0</v>
       </c>
       <c r="L33">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="M33">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N33">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O33" t="s">
-        <v>26</v>
+        <v>56</v>
       </c>
       <c r="P33">
         <v>1</v>
       </c>
       <c r="T33" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
     </row>
     <row r="34" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="B34" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="C34" t="s">
-        <v>35</v>
+        <v>153</v>
       </c>
       <c r="D34" t="s">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="E34" t="s">
-        <v>24</v>
-      </c>
-      <c r="G34" t="s">
-        <v>33</v>
-      </c>
-      <c r="H34" t="s">
-        <v>25</v>
+        <v>79</v>
+      </c>
+      <c r="F34" t="s">
+        <v>151</v>
       </c>
       <c r="I34">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K34">
         <v>0</v>
@@ -4021,60 +3966,57 @@
         <v>0</v>
       </c>
       <c r="M34">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N34">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="O34" t="s">
-        <v>26</v>
+        <v>56</v>
       </c>
       <c r="P34">
         <v>1</v>
       </c>
-      <c r="Q34" s="1" t="s">
-        <v>404</v>
-      </c>
-      <c r="S34" s="1" t="s">
-        <v>405</v>
-      </c>
-      <c r="T34" t="s">
-        <v>157</v>
+      <c r="R34" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="T34" s="1" t="s">
+        <v>431</v>
       </c>
     </row>
     <row r="35" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="B35" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="C35" t="s">
-        <v>110</v>
+        <v>156</v>
       </c>
       <c r="D35" t="s">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="E35" t="s">
-        <v>24</v>
-      </c>
-      <c r="H35" t="s">
-        <v>49</v>
+        <v>79</v>
+      </c>
+      <c r="F35" t="s">
+        <v>154</v>
       </c>
       <c r="I35">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="K35">
         <v>0</v>
       </c>
       <c r="L35">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M35">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="N35">
-        <v>0.35</v>
+        <v>0</v>
       </c>
       <c r="O35" t="s">
         <v>56</v>
@@ -4082,22 +4024,25 @@
       <c r="P35">
         <v>1</v>
       </c>
+      <c r="R35" s="1" t="s">
+        <v>386</v>
+      </c>
       <c r="T35" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
     </row>
     <row r="36" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="B36" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="C36" t="s">
-        <v>118</v>
+        <v>160</v>
       </c>
       <c r="D36" t="s">
-        <v>65</v>
+        <v>23</v>
       </c>
       <c r="E36" t="s">
         <v>79</v>
@@ -4112,19 +4057,19 @@
         <v>0</v>
       </c>
       <c r="L36">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="M36">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N36">
         <v>0</v>
       </c>
       <c r="O36" t="s">
-        <v>56</v>
+        <v>162</v>
       </c>
       <c r="P36">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T36" t="s">
         <v>163</v>
@@ -4141,48 +4086,54 @@
         <v>30</v>
       </c>
       <c r="D37" t="s">
-        <v>65</v>
+        <v>23</v>
       </c>
       <c r="E37" t="s">
-        <v>79</v>
-      </c>
-      <c r="F37" t="s">
+        <v>24</v>
+      </c>
+      <c r="G37" t="s">
+        <v>31</v>
+      </c>
+      <c r="H37" t="s">
+        <v>25</v>
+      </c>
+      <c r="I37">
+        <v>20</v>
+      </c>
+      <c r="K37">
+        <v>0</v>
+      </c>
+      <c r="L37">
+        <v>0</v>
+      </c>
+      <c r="M37">
+        <v>5</v>
+      </c>
+      <c r="N37">
+        <v>0.5</v>
+      </c>
+      <c r="O37" t="s">
+        <v>26</v>
+      </c>
+      <c r="P37">
+        <v>1</v>
+      </c>
+      <c r="S37" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="T37" t="s">
         <v>166</v>
-      </c>
-      <c r="I37">
-        <v>0</v>
-      </c>
-      <c r="K37">
-        <v>0</v>
-      </c>
-      <c r="L37">
-        <v>50</v>
-      </c>
-      <c r="M37">
-        <v>6</v>
-      </c>
-      <c r="N37">
-        <v>0</v>
-      </c>
-      <c r="O37" t="s">
-        <v>56</v>
-      </c>
-      <c r="P37">
-        <v>1</v>
-      </c>
-      <c r="T37" t="s">
-        <v>167</v>
       </c>
     </row>
     <row r="38" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
+        <v>167</v>
+      </c>
+      <c r="B38" t="s">
         <v>168</v>
       </c>
-      <c r="B38" t="s">
-        <v>169</v>
-      </c>
       <c r="C38" t="s">
-        <v>94</v>
+        <v>30</v>
       </c>
       <c r="D38" t="s">
         <v>65</v>
@@ -4191,7 +4142,10 @@
         <v>79</v>
       </c>
       <c r="F38" t="s">
-        <v>170</v>
+        <v>167</v>
+      </c>
+      <c r="G38" t="s">
+        <v>31</v>
       </c>
       <c r="I38">
         <v>0</v>
@@ -4200,10 +4154,10 @@
         <v>0</v>
       </c>
       <c r="L38">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="M38">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N38">
         <v>0</v>
@@ -4215,18 +4169,18 @@
         <v>1</v>
       </c>
       <c r="T38" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="39" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
+        <v>170</v>
+      </c>
+      <c r="B39" t="s">
+        <v>171</v>
+      </c>
+      <c r="C39" t="s">
         <v>172</v>
-      </c>
-      <c r="B39" t="s">
-        <v>173</v>
-      </c>
-      <c r="C39" t="s">
-        <v>174</v>
       </c>
       <c r="D39" t="s">
         <v>65</v>
@@ -4235,7 +4189,10 @@
         <v>79</v>
       </c>
       <c r="F39" t="s">
-        <v>172</v>
+        <v>170</v>
+      </c>
+      <c r="G39" t="s">
+        <v>31</v>
       </c>
       <c r="I39">
         <v>0</v>
@@ -4247,7 +4204,7 @@
         <v>0</v>
       </c>
       <c r="M39">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N39">
         <v>0</v>
@@ -4258,22 +4215,19 @@
       <c r="P39">
         <v>1</v>
       </c>
-      <c r="R39" s="1" t="s">
-        <v>451</v>
-      </c>
-      <c r="T39" s="1" t="s">
-        <v>452</v>
+      <c r="T39" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="40" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
+        <v>174</v>
+      </c>
+      <c r="B40" t="s">
         <v>175</v>
       </c>
-      <c r="B40" t="s">
+      <c r="C40" t="s">
         <v>176</v>
-      </c>
-      <c r="C40" t="s">
-        <v>177</v>
       </c>
       <c r="D40" t="s">
         <v>65</v>
@@ -4282,7 +4236,10 @@
         <v>79</v>
       </c>
       <c r="F40" t="s">
-        <v>175</v>
+        <v>174</v>
+      </c>
+      <c r="G40" t="s">
+        <v>177</v>
       </c>
       <c r="I40">
         <v>0</v>
@@ -4291,10 +4248,10 @@
         <v>0</v>
       </c>
       <c r="L40">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="M40">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="N40">
         <v>0</v>
@@ -4304,9 +4261,6 @@
       </c>
       <c r="P40">
         <v>1</v>
-      </c>
-      <c r="R40" s="1" t="s">
-        <v>407</v>
       </c>
       <c r="T40" t="s">
         <v>178</v>
@@ -4320,16 +4274,16 @@
         <v>180</v>
       </c>
       <c r="C41" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="D41" t="s">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="E41" t="s">
         <v>79</v>
       </c>
       <c r="F41" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="I41">
         <v>0</v>
@@ -4338,98 +4292,95 @@
         <v>0</v>
       </c>
       <c r="L41">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="M41">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N41">
         <v>0</v>
       </c>
       <c r="O41" t="s">
-        <v>183</v>
+        <v>56</v>
       </c>
       <c r="P41">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T41" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
     </row>
     <row r="42" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="B42" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="C42" t="s">
-        <v>30</v>
+        <v>184</v>
       </c>
       <c r="D42" t="s">
         <v>23</v>
       </c>
       <c r="E42" t="s">
-        <v>24</v>
+        <v>79</v>
+      </c>
+      <c r="F42" t="s">
+        <v>182</v>
       </c>
       <c r="G42" t="s">
-        <v>31</v>
-      </c>
-      <c r="H42" t="s">
-        <v>25</v>
+        <v>177</v>
       </c>
       <c r="I42">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="K42">
         <v>0</v>
       </c>
       <c r="L42">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M42">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="N42">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="O42" t="s">
-        <v>26</v>
+        <v>56</v>
       </c>
       <c r="P42">
         <v>1</v>
       </c>
-      <c r="S42" s="1" t="s">
-        <v>408</v>
-      </c>
       <c r="T42" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="43" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="B43" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C43" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="D43" t="s">
-        <v>65</v>
+        <v>23</v>
       </c>
       <c r="E43" t="s">
-        <v>79</v>
-      </c>
-      <c r="F43" t="s">
-        <v>188</v>
+        <v>24</v>
       </c>
       <c r="G43" t="s">
-        <v>31</v>
+        <v>33</v>
+      </c>
+      <c r="H43" t="s">
+        <v>25</v>
       </c>
       <c r="I43">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="K43">
         <v>0</v>
@@ -4438,10 +4389,10 @@
         <v>0</v>
       </c>
       <c r="M43">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N43">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="O43" t="s">
         <v>56</v>
@@ -4450,33 +4401,33 @@
         <v>1</v>
       </c>
       <c r="T43" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="44" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
+        <v>189</v>
+      </c>
+      <c r="B44" t="s">
+        <v>190</v>
+      </c>
+      <c r="C44" t="s">
         <v>191</v>
       </c>
-      <c r="B44" t="s">
-        <v>192</v>
-      </c>
-      <c r="C44" t="s">
-        <v>193</v>
-      </c>
       <c r="D44" t="s">
-        <v>65</v>
+        <v>23</v>
       </c>
       <c r="E44" t="s">
-        <v>79</v>
-      </c>
-      <c r="F44" t="s">
-        <v>191</v>
+        <v>24</v>
       </c>
       <c r="G44" t="s">
         <v>31</v>
       </c>
+      <c r="H44" t="s">
+        <v>25</v>
+      </c>
       <c r="I44">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="K44">
         <v>0</v>
@@ -4485,10 +4436,10 @@
         <v>0</v>
       </c>
       <c r="M44">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N44">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="O44" t="s">
         <v>56</v>
@@ -4497,18 +4448,18 @@
         <v>1</v>
       </c>
       <c r="T44" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
     </row>
     <row r="45" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
+        <v>193</v>
+      </c>
+      <c r="B45" t="s">
+        <v>194</v>
+      </c>
+      <c r="C45" t="s">
         <v>195</v>
-      </c>
-      <c r="B45" t="s">
-        <v>196</v>
-      </c>
-      <c r="C45" t="s">
-        <v>197</v>
       </c>
       <c r="D45" t="s">
         <v>65</v>
@@ -4517,10 +4468,10 @@
         <v>79</v>
       </c>
       <c r="F45" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="G45" t="s">
-        <v>198</v>
+        <v>115</v>
       </c>
       <c r="I45">
         <v>0</v>
@@ -4532,7 +4483,7 @@
         <v>0</v>
       </c>
       <c r="M45">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="N45">
         <v>0</v>
@@ -4544,26 +4495,29 @@
         <v>1</v>
       </c>
       <c r="T45" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
     </row>
     <row r="46" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="B46" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="C46" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="D46" t="s">
-        <v>65</v>
+        <v>23</v>
       </c>
       <c r="E46" t="s">
         <v>79</v>
       </c>
       <c r="F46" t="s">
+        <v>197</v>
+      </c>
+      <c r="G46" t="s">
         <v>200</v>
       </c>
       <c r="I46">
@@ -4573,95 +4527,98 @@
         <v>0</v>
       </c>
       <c r="L46">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M46">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N46">
         <v>0</v>
       </c>
       <c r="O46" t="s">
-        <v>56</v>
+        <v>162</v>
       </c>
       <c r="P46">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T46" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="47" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
+        <v>202</v>
+      </c>
+      <c r="B47" t="s">
         <v>203</v>
       </c>
-      <c r="B47" t="s">
+      <c r="C47" t="s">
         <v>204</v>
-      </c>
-      <c r="C47" t="s">
-        <v>205</v>
       </c>
       <c r="D47" t="s">
         <v>23</v>
       </c>
       <c r="E47" t="s">
-        <v>79</v>
-      </c>
-      <c r="F47" t="s">
-        <v>203</v>
+        <v>24</v>
       </c>
       <c r="G47" t="s">
-        <v>198</v>
+        <v>200</v>
+      </c>
+      <c r="H47" t="s">
+        <v>25</v>
       </c>
       <c r="I47">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="K47">
         <v>0</v>
       </c>
       <c r="L47">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="M47">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="N47">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="O47" t="s">
-        <v>56</v>
+        <v>26</v>
       </c>
       <c r="P47">
         <v>1</v>
       </c>
+      <c r="S47" s="1" t="s">
+        <v>388</v>
+      </c>
       <c r="T47" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="48" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
+        <v>206</v>
+      </c>
+      <c r="B48" t="s">
         <v>207</v>
       </c>
-      <c r="B48" t="s">
+      <c r="C48" t="s">
         <v>208</v>
-      </c>
-      <c r="C48" t="s">
-        <v>35</v>
       </c>
       <c r="D48" t="s">
         <v>23</v>
       </c>
       <c r="E48" t="s">
-        <v>24</v>
+        <v>79</v>
+      </c>
+      <c r="F48" t="s">
+        <v>206</v>
       </c>
       <c r="G48" t="s">
-        <v>33</v>
-      </c>
-      <c r="H48" t="s">
-        <v>25</v>
+        <v>200</v>
       </c>
       <c r="I48">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K48">
         <v>0</v>
@@ -4670,10 +4627,10 @@
         <v>0</v>
       </c>
       <c r="M48">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N48">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="O48" t="s">
         <v>56</v>
@@ -4699,28 +4656,28 @@
         <v>23</v>
       </c>
       <c r="E49" t="s">
-        <v>24</v>
+        <v>79</v>
+      </c>
+      <c r="F49" t="s">
+        <v>210</v>
       </c>
       <c r="G49" t="s">
-        <v>31</v>
-      </c>
-      <c r="H49" t="s">
-        <v>25</v>
+        <v>200</v>
       </c>
       <c r="I49">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="K49">
         <v>0</v>
       </c>
       <c r="L49">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M49">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="N49">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="O49" t="s">
         <v>56</v>
@@ -4740,7 +4697,7 @@
         <v>215</v>
       </c>
       <c r="C50" t="s">
-        <v>216</v>
+        <v>199</v>
       </c>
       <c r="D50" t="s">
         <v>65</v>
@@ -4752,7 +4709,7 @@
         <v>214</v>
       </c>
       <c r="G50" t="s">
-        <v>123</v>
+        <v>200</v>
       </c>
       <c r="I50">
         <v>0</v>
@@ -4761,7 +4718,7 @@
         <v>0</v>
       </c>
       <c r="L50">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="M50">
         <v>6</v>
@@ -4776,18 +4733,18 @@
         <v>1</v>
       </c>
       <c r="T50" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="51" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
+        <v>217</v>
+      </c>
+      <c r="B51" t="s">
         <v>218</v>
       </c>
-      <c r="B51" t="s">
-        <v>219</v>
-      </c>
       <c r="C51" t="s">
-        <v>220</v>
+        <v>114</v>
       </c>
       <c r="D51" t="s">
         <v>23</v>
@@ -4796,10 +4753,10 @@
         <v>79</v>
       </c>
       <c r="F51" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="G51" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="I51">
         <v>0</v>
@@ -4808,33 +4765,33 @@
         <v>0</v>
       </c>
       <c r="L51">
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="M51">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N51">
         <v>0</v>
       </c>
       <c r="O51" t="s">
-        <v>183</v>
+        <v>162</v>
       </c>
       <c r="P51">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T51" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
     </row>
     <row r="52" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="B52" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C52" t="s">
-        <v>225</v>
+        <v>114</v>
       </c>
       <c r="D52" t="s">
         <v>23</v>
@@ -4843,7 +4800,7 @@
         <v>24</v>
       </c>
       <c r="G52" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="H52" t="s">
         <v>25</v>
@@ -4858,7 +4815,7 @@
         <v>0</v>
       </c>
       <c r="M52">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N52">
         <v>0.5</v>
@@ -4869,22 +4826,19 @@
       <c r="P52">
         <v>1</v>
       </c>
-      <c r="S52" s="1" t="s">
-        <v>409</v>
-      </c>
       <c r="T52" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
     </row>
     <row r="53" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="B53" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="C53" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="D53" t="s">
         <v>23</v>
@@ -4893,10 +4847,10 @@
         <v>79</v>
       </c>
       <c r="F53" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="G53" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="I53">
         <v>0</v>
@@ -4905,7 +4859,7 @@
         <v>0</v>
       </c>
       <c r="L53">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="M53">
         <v>3</v>
@@ -4920,30 +4874,30 @@
         <v>1</v>
       </c>
       <c r="T53" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
     </row>
     <row r="54" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="B54" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="C54" t="s">
-        <v>233</v>
+        <v>153</v>
       </c>
       <c r="D54" t="s">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="E54" t="s">
         <v>79</v>
       </c>
       <c r="F54" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="G54" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="I54">
         <v>0</v>
@@ -4952,10 +4906,10 @@
         <v>0</v>
       </c>
       <c r="L54">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="M54">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="N54">
         <v>0</v>
@@ -4966,19 +4920,22 @@
       <c r="P54">
         <v>1</v>
       </c>
+      <c r="R54" s="1" t="s">
+        <v>389</v>
+      </c>
       <c r="T54" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
     </row>
     <row r="55" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="B55" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="C55" t="s">
-        <v>220</v>
+        <v>90</v>
       </c>
       <c r="D55" t="s">
         <v>65</v>
@@ -4987,10 +4944,10 @@
         <v>79</v>
       </c>
       <c r="F55" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="G55" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="I55">
         <v>0</v>
@@ -4999,7 +4956,7 @@
         <v>0</v>
       </c>
       <c r="L55">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="M55">
         <v>6</v>
@@ -5014,30 +4971,30 @@
         <v>1</v>
       </c>
       <c r="T55" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
     </row>
     <row r="56" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="B56" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="C56" t="s">
-        <v>118</v>
+        <v>236</v>
       </c>
       <c r="D56" t="s">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="E56" t="s">
         <v>79</v>
       </c>
       <c r="F56" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="G56" t="s">
-        <v>240</v>
+        <v>219</v>
       </c>
       <c r="I56">
         <v>0</v>
@@ -5046,80 +5003,80 @@
         <v>0</v>
       </c>
       <c r="L56">
-        <v>80</v>
+        <v>99</v>
       </c>
       <c r="M56">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N56">
         <v>0</v>
       </c>
       <c r="O56" t="s">
-        <v>183</v>
+        <v>56</v>
       </c>
       <c r="P56">
-        <v>6</v>
+        <v>1</v>
+      </c>
+      <c r="R56" s="1" t="s">
+        <v>390</v>
       </c>
       <c r="T56" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
     </row>
     <row r="57" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="B57" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="C57" t="s">
-        <v>118</v>
+        <v>39</v>
       </c>
       <c r="D57" t="s">
         <v>23</v>
       </c>
       <c r="E57" t="s">
-        <v>24</v>
-      </c>
-      <c r="G57" t="s">
+        <v>79</v>
+      </c>
+      <c r="F57" t="s">
+        <v>238</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="K57">
+        <v>0</v>
+      </c>
+      <c r="L57">
+        <v>4</v>
+      </c>
+      <c r="M57">
+        <v>5</v>
+      </c>
+      <c r="N57">
+        <v>0</v>
+      </c>
+      <c r="O57" t="s">
+        <v>162</v>
+      </c>
+      <c r="P57">
+        <v>10</v>
+      </c>
+      <c r="T57" t="s">
         <v>240</v>
-      </c>
-      <c r="H57" t="s">
-        <v>25</v>
-      </c>
-      <c r="I57">
-        <v>50</v>
-      </c>
-      <c r="K57">
-        <v>0</v>
-      </c>
-      <c r="L57">
-        <v>0</v>
-      </c>
-      <c r="M57">
-        <v>4</v>
-      </c>
-      <c r="N57">
-        <v>0.5</v>
-      </c>
-      <c r="O57" t="s">
-        <v>26</v>
-      </c>
-      <c r="P57">
-        <v>1</v>
-      </c>
-      <c r="T57" t="s">
-        <v>244</v>
       </c>
     </row>
     <row r="58" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="B58" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="C58" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="D58" t="s">
         <v>23</v>
@@ -5128,10 +5085,10 @@
         <v>79</v>
       </c>
       <c r="F58" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="G58" t="s">
-        <v>240</v>
+        <v>40</v>
       </c>
       <c r="I58">
         <v>0</v>
@@ -5140,83 +5097,77 @@
         <v>0</v>
       </c>
       <c r="L58">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="M58">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="N58">
         <v>0</v>
       </c>
       <c r="O58" t="s">
-        <v>56</v>
+        <v>162</v>
       </c>
       <c r="P58">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="T58" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
     </row>
     <row r="59" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="B59" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="C59" t="s">
-        <v>174</v>
+        <v>22</v>
       </c>
       <c r="D59" t="s">
-        <v>65</v>
+        <v>23</v>
       </c>
       <c r="E59" t="s">
-        <v>79</v>
-      </c>
-      <c r="F59" t="s">
-        <v>249</v>
-      </c>
-      <c r="G59" t="s">
-        <v>240</v>
+        <v>24</v>
+      </c>
+      <c r="H59" t="s">
+        <v>25</v>
       </c>
       <c r="I59">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="K59">
         <v>0</v>
       </c>
       <c r="L59">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M59">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="N59">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="O59" t="s">
-        <v>56</v>
+        <v>26</v>
       </c>
       <c r="P59">
         <v>1</v>
       </c>
-      <c r="R59" s="1" t="s">
-        <v>410</v>
-      </c>
       <c r="T59" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
     </row>
     <row r="60" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="B60" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="C60" t="s">
-        <v>90</v>
+        <v>250</v>
       </c>
       <c r="D60" t="s">
         <v>65</v>
@@ -5225,10 +5176,7 @@
         <v>79</v>
       </c>
       <c r="F60" t="s">
-        <v>252</v>
-      </c>
-      <c r="G60" t="s">
-        <v>240</v>
+        <v>248</v>
       </c>
       <c r="I60">
         <v>0</v>
@@ -5237,10 +5185,10 @@
         <v>0</v>
       </c>
       <c r="L60">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="M60">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="N60">
         <v>0</v>
@@ -5252,18 +5200,18 @@
         <v>1</v>
       </c>
       <c r="T60" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
     </row>
     <row r="61" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="B61" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="C61" t="s">
-        <v>257</v>
+        <v>35</v>
       </c>
       <c r="D61" t="s">
         <v>65</v>
@@ -5272,10 +5220,7 @@
         <v>79</v>
       </c>
       <c r="F61" t="s">
-        <v>255</v>
-      </c>
-      <c r="G61" t="s">
-        <v>240</v>
+        <v>252</v>
       </c>
       <c r="I61">
         <v>0</v>
@@ -5284,45 +5229,42 @@
         <v>0</v>
       </c>
       <c r="L61">
-        <v>99</v>
+        <v>25</v>
       </c>
       <c r="M61">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="N61">
         <v>0</v>
       </c>
       <c r="O61" t="s">
-        <v>56</v>
+        <v>162</v>
       </c>
       <c r="P61">
-        <v>1</v>
-      </c>
-      <c r="R61" s="1" t="s">
-        <v>411</v>
+        <v>20</v>
       </c>
       <c r="T61" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
     </row>
     <row r="62" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="B62" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="C62" t="s">
-        <v>39</v>
+        <v>257</v>
       </c>
       <c r="D62" t="s">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="E62" t="s">
         <v>79</v>
       </c>
       <c r="F62" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="I62">
         <v>0</v>
@@ -5331,7 +5273,7 @@
         <v>0</v>
       </c>
       <c r="L62">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M62">
         <v>5</v>
@@ -5340,36 +5282,33 @@
         <v>0</v>
       </c>
       <c r="O62" t="s">
-        <v>183</v>
+        <v>56</v>
       </c>
       <c r="P62">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T62" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
     </row>
     <row r="63" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="B63" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="C63" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="D63" t="s">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="E63" t="s">
         <v>79</v>
       </c>
       <c r="F63" t="s">
-        <v>262</v>
-      </c>
-      <c r="G63" t="s">
-        <v>40</v>
+        <v>259</v>
       </c>
       <c r="I63">
         <v>0</v>
@@ -5378,33 +5317,33 @@
         <v>0</v>
       </c>
       <c r="L63">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M63">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="N63">
         <v>0</v>
       </c>
       <c r="O63" t="s">
-        <v>183</v>
+        <v>162</v>
       </c>
       <c r="P63">
         <v>100</v>
       </c>
       <c r="T63" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
     </row>
     <row r="64" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="B64" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="C64" t="s">
-        <v>22</v>
+        <v>265</v>
       </c>
       <c r="D64" t="s">
         <v>23</v>
@@ -5412,11 +5351,14 @@
       <c r="E64" t="s">
         <v>24</v>
       </c>
+      <c r="G64" t="s">
+        <v>33</v>
+      </c>
       <c r="H64" t="s">
         <v>25</v>
       </c>
       <c r="I64">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="K64">
         <v>0</v>
@@ -5425,74 +5367,77 @@
         <v>0</v>
       </c>
       <c r="M64">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N64">
         <v>0.5</v>
       </c>
       <c r="O64" t="s">
-        <v>26</v>
+        <v>162</v>
       </c>
       <c r="P64">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T64" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="65" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
+        <v>267</v>
+      </c>
+      <c r="B65" t="s">
+        <v>268</v>
+      </c>
+      <c r="C65" t="s">
         <v>269</v>
       </c>
-      <c r="B65" t="s">
+      <c r="D65" t="s">
+        <v>23</v>
+      </c>
+      <c r="E65" t="s">
+        <v>24</v>
+      </c>
+      <c r="G65" t="s">
+        <v>31</v>
+      </c>
+      <c r="H65" t="s">
+        <v>25</v>
+      </c>
+      <c r="I65">
+        <v>10</v>
+      </c>
+      <c r="K65">
+        <v>0</v>
+      </c>
+      <c r="L65">
+        <v>0</v>
+      </c>
+      <c r="M65">
+        <v>6</v>
+      </c>
+      <c r="N65">
+        <v>0.5</v>
+      </c>
+      <c r="O65" t="s">
+        <v>162</v>
+      </c>
+      <c r="P65">
+        <v>20</v>
+      </c>
+      <c r="T65" t="s">
         <v>270</v>
-      </c>
-      <c r="C65" t="s">
-        <v>271</v>
-      </c>
-      <c r="D65" t="s">
-        <v>65</v>
-      </c>
-      <c r="E65" t="s">
-        <v>79</v>
-      </c>
-      <c r="F65" t="s">
-        <v>269</v>
-      </c>
-      <c r="I65">
-        <v>0</v>
-      </c>
-      <c r="K65">
-        <v>0</v>
-      </c>
-      <c r="L65">
-        <v>30</v>
-      </c>
-      <c r="M65">
-        <v>2</v>
-      </c>
-      <c r="N65">
-        <v>0</v>
-      </c>
-      <c r="O65" t="s">
-        <v>56</v>
-      </c>
-      <c r="P65">
-        <v>1</v>
-      </c>
-      <c r="T65" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="66" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
+        <v>271</v>
+      </c>
+      <c r="B66" t="s">
+        <v>272</v>
+      </c>
+      <c r="C66" t="s">
         <v>273</v>
-      </c>
-      <c r="B66" t="s">
-        <v>274</v>
-      </c>
-      <c r="C66" t="s">
-        <v>35</v>
       </c>
       <c r="D66" t="s">
         <v>65</v>
@@ -5501,7 +5446,7 @@
         <v>79</v>
       </c>
       <c r="F66" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="I66">
         <v>0</v>
@@ -5510,42 +5455,45 @@
         <v>0</v>
       </c>
       <c r="L66">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="M66">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="N66">
         <v>0</v>
       </c>
       <c r="O66" t="s">
-        <v>183</v>
+        <v>56</v>
       </c>
       <c r="P66">
-        <v>20</v>
+        <v>1</v>
+      </c>
+      <c r="R66" s="1" t="s">
+        <v>385</v>
       </c>
       <c r="T66" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="67" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
+        <v>275</v>
+      </c>
+      <c r="B67" t="s">
         <v>276</v>
       </c>
-      <c r="B67" t="s">
-        <v>277</v>
-      </c>
       <c r="C67" t="s">
-        <v>278</v>
+        <v>250</v>
       </c>
       <c r="D67" t="s">
-        <v>65</v>
+        <v>23</v>
       </c>
       <c r="E67" t="s">
         <v>79</v>
       </c>
       <c r="F67" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="I67">
         <v>0</v>
@@ -5557,7 +5505,7 @@
         <v>0</v>
       </c>
       <c r="M67">
-        <v>5</v>
+        <v>0.6</v>
       </c>
       <c r="N67">
         <v>0</v>
@@ -5569,18 +5517,18 @@
         <v>1</v>
       </c>
       <c r="T67" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
     </row>
     <row r="68" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
+        <v>278</v>
+      </c>
+      <c r="B68" t="s">
+        <v>279</v>
+      </c>
+      <c r="C68" t="s">
         <v>280</v>
-      </c>
-      <c r="B68" t="s">
-        <v>281</v>
-      </c>
-      <c r="C68" t="s">
-        <v>282</v>
       </c>
       <c r="D68" t="s">
         <v>65</v>
@@ -5589,7 +5537,7 @@
         <v>79</v>
       </c>
       <c r="F68" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="I68">
         <v>0</v>
@@ -5598,7 +5546,7 @@
         <v>0</v>
       </c>
       <c r="L68">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="M68">
         <v>6</v>
@@ -5607,118 +5555,112 @@
         <v>0</v>
       </c>
       <c r="O68" t="s">
-        <v>183</v>
+        <v>56</v>
       </c>
       <c r="P68">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="T68" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
     </row>
     <row r="69" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
+        <v>282</v>
+      </c>
+      <c r="B69" t="s">
+        <v>283</v>
+      </c>
+      <c r="C69" t="s">
+        <v>22</v>
+      </c>
+      <c r="D69" t="s">
+        <v>65</v>
+      </c>
+      <c r="E69" t="s">
+        <v>79</v>
+      </c>
+      <c r="F69" t="s">
+        <v>282</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="K69">
+        <v>0</v>
+      </c>
+      <c r="L69">
+        <v>1</v>
+      </c>
+      <c r="M69">
+        <v>4</v>
+      </c>
+      <c r="N69">
+        <v>0</v>
+      </c>
+      <c r="O69" t="s">
+        <v>162</v>
+      </c>
+      <c r="P69">
+        <v>50</v>
+      </c>
+      <c r="T69" t="s">
         <v>284</v>
-      </c>
-      <c r="B69" t="s">
-        <v>285</v>
-      </c>
-      <c r="C69" t="s">
-        <v>286</v>
-      </c>
-      <c r="D69" t="s">
-        <v>23</v>
-      </c>
-      <c r="E69" t="s">
-        <v>24</v>
-      </c>
-      <c r="G69" t="s">
-        <v>33</v>
-      </c>
-      <c r="H69" t="s">
-        <v>25</v>
-      </c>
-      <c r="I69">
-        <v>100</v>
-      </c>
-      <c r="K69">
-        <v>0</v>
-      </c>
-      <c r="L69">
-        <v>0</v>
-      </c>
-      <c r="M69">
-        <v>6</v>
-      </c>
-      <c r="N69">
-        <v>0.5</v>
-      </c>
-      <c r="O69" t="s">
-        <v>183</v>
-      </c>
-      <c r="P69">
-        <v>10</v>
-      </c>
-      <c r="T69" t="s">
-        <v>287</v>
       </c>
     </row>
     <row r="70" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
+        <v>285</v>
+      </c>
+      <c r="B70" t="s">
+        <v>286</v>
+      </c>
+      <c r="C70" t="s">
+        <v>287</v>
+      </c>
+      <c r="D70" t="s">
+        <v>65</v>
+      </c>
+      <c r="E70" t="s">
+        <v>79</v>
+      </c>
+      <c r="F70" t="s">
+        <v>285</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="K70">
+        <v>0</v>
+      </c>
+      <c r="L70">
+        <v>5</v>
+      </c>
+      <c r="M70">
+        <v>4</v>
+      </c>
+      <c r="N70">
+        <v>0</v>
+      </c>
+      <c r="O70" t="s">
+        <v>162</v>
+      </c>
+      <c r="P70">
+        <v>10</v>
+      </c>
+      <c r="T70" t="s">
         <v>288</v>
-      </c>
-      <c r="B70" t="s">
-        <v>289</v>
-      </c>
-      <c r="C70" t="s">
-        <v>290</v>
-      </c>
-      <c r="D70" t="s">
-        <v>23</v>
-      </c>
-      <c r="E70" t="s">
-        <v>24</v>
-      </c>
-      <c r="G70" t="s">
-        <v>31</v>
-      </c>
-      <c r="H70" t="s">
-        <v>25</v>
-      </c>
-      <c r="I70">
-        <v>10</v>
-      </c>
-      <c r="K70">
-        <v>0</v>
-      </c>
-      <c r="L70">
-        <v>0</v>
-      </c>
-      <c r="M70">
-        <v>6</v>
-      </c>
-      <c r="N70">
-        <v>0.5</v>
-      </c>
-      <c r="O70" t="s">
-        <v>183</v>
-      </c>
-      <c r="P70">
-        <v>20</v>
-      </c>
-      <c r="T70" t="s">
-        <v>291</v>
       </c>
     </row>
     <row r="71" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="B71" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="C71" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="D71" t="s">
         <v>65</v>
@@ -5727,54 +5669,51 @@
         <v>79</v>
       </c>
       <c r="F71" t="s">
+        <v>289</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="K71">
+        <v>0</v>
+      </c>
+      <c r="L71">
+        <v>4</v>
+      </c>
+      <c r="M71">
+        <v>99999</v>
+      </c>
+      <c r="N71">
+        <v>0</v>
+      </c>
+      <c r="O71" t="s">
+        <v>162</v>
+      </c>
+      <c r="P71">
+        <v>100</v>
+      </c>
+      <c r="T71" t="s">
         <v>292</v>
-      </c>
-      <c r="I71">
-        <v>0</v>
-      </c>
-      <c r="K71">
-        <v>0</v>
-      </c>
-      <c r="L71">
-        <v>100</v>
-      </c>
-      <c r="M71">
-        <v>10</v>
-      </c>
-      <c r="N71">
-        <v>0</v>
-      </c>
-      <c r="O71" t="s">
-        <v>56</v>
-      </c>
-      <c r="P71">
-        <v>1</v>
-      </c>
-      <c r="R71" s="1" t="s">
-        <v>406</v>
-      </c>
-      <c r="T71" t="s">
-        <v>295</v>
       </c>
     </row>
     <row r="72" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="B72" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="C72" t="s">
-        <v>271</v>
+        <v>295</v>
       </c>
       <c r="D72" t="s">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="E72" t="s">
         <v>79</v>
       </c>
       <c r="F72" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="I72">
         <v>0</v>
@@ -5783,10 +5722,10 @@
         <v>0</v>
       </c>
       <c r="L72">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="M72">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="N72">
         <v>0</v>
@@ -5797,19 +5736,22 @@
       <c r="P72">
         <v>1</v>
       </c>
+      <c r="R72" s="1" t="s">
+        <v>386</v>
+      </c>
       <c r="T72" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
     </row>
     <row r="73" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="B73" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="C73" t="s">
-        <v>301</v>
+        <v>172</v>
       </c>
       <c r="D73" t="s">
         <v>65</v>
@@ -5818,7 +5760,10 @@
         <v>79</v>
       </c>
       <c r="F73" t="s">
-        <v>299</v>
+        <v>297</v>
+      </c>
+      <c r="G73" t="s">
+        <v>31</v>
       </c>
       <c r="I73">
         <v>0</v>
@@ -5827,10 +5772,10 @@
         <v>0</v>
       </c>
       <c r="L73">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="M73">
-        <v>6</v>
+        <v>60</v>
       </c>
       <c r="N73">
         <v>0</v>
@@ -5842,27 +5787,30 @@
         <v>1</v>
       </c>
       <c r="T73" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
     </row>
     <row r="74" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="B74" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="C74" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="D74" t="s">
-        <v>65</v>
+        <v>23</v>
       </c>
       <c r="E74" t="s">
         <v>79</v>
       </c>
       <c r="F74" t="s">
-        <v>303</v>
+        <v>300</v>
+      </c>
+      <c r="G74" t="s">
+        <v>31</v>
       </c>
       <c r="I74">
         <v>0</v>
@@ -5871,7 +5819,7 @@
         <v>0</v>
       </c>
       <c r="L74">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="M74">
         <v>4</v>
@@ -5880,33 +5828,36 @@
         <v>0</v>
       </c>
       <c r="O74" t="s">
-        <v>183</v>
+        <v>56</v>
       </c>
       <c r="P74">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="T74" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
     </row>
     <row r="75" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="B75" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="C75" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="D75" t="s">
-        <v>65</v>
+        <v>23</v>
       </c>
       <c r="E75" t="s">
         <v>79</v>
       </c>
       <c r="F75" t="s">
-        <v>306</v>
+        <v>303</v>
+      </c>
+      <c r="G75" t="s">
+        <v>177</v>
       </c>
       <c r="I75">
         <v>0</v>
@@ -5915,42 +5866,45 @@
         <v>0</v>
       </c>
       <c r="L75">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M75">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N75">
         <v>0</v>
       </c>
       <c r="O75" t="s">
-        <v>183</v>
+        <v>56</v>
       </c>
       <c r="P75">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T75" t="s">
-        <v>309</v>
+        <v>436</v>
       </c>
     </row>
     <row r="76" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="B76" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="C76" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="D76" t="s">
-        <v>65</v>
+        <v>23</v>
       </c>
       <c r="E76" t="s">
         <v>79</v>
       </c>
       <c r="F76" t="s">
-        <v>310</v>
+        <v>306</v>
+      </c>
+      <c r="G76" t="s">
+        <v>177</v>
       </c>
       <c r="I76">
         <v>0</v>
@@ -5959,95 +5913,92 @@
         <v>0</v>
       </c>
       <c r="L76">
-        <v>4</v>
+        <v>65</v>
       </c>
       <c r="M76">
-        <v>99999</v>
+        <v>5</v>
       </c>
       <c r="N76">
         <v>0</v>
       </c>
       <c r="O76" t="s">
-        <v>183</v>
+        <v>56</v>
       </c>
       <c r="P76">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="T76" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
     </row>
     <row r="77" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="B77" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="C77" t="s">
-        <v>316</v>
+        <v>22</v>
       </c>
       <c r="D77" t="s">
-        <v>65</v>
+        <v>23</v>
       </c>
       <c r="E77" t="s">
-        <v>79</v>
-      </c>
-      <c r="F77" t="s">
-        <v>314</v>
+        <v>24</v>
+      </c>
+      <c r="H77" t="s">
+        <v>25</v>
       </c>
       <c r="I77">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="K77">
         <v>0</v>
       </c>
       <c r="L77">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="M77">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="N77">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="O77" t="s">
-        <v>56</v>
+        <v>26</v>
       </c>
       <c r="P77">
         <v>1</v>
       </c>
-      <c r="R77" s="1" t="s">
-        <v>407</v>
-      </c>
       <c r="T77" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
     </row>
     <row r="78" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="B78" t="s">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="C78" t="s">
-        <v>193</v>
+        <v>44</v>
       </c>
       <c r="D78" t="s">
-        <v>65</v>
+        <v>23</v>
       </c>
       <c r="E78" t="s">
-        <v>79</v>
-      </c>
-      <c r="F78" t="s">
-        <v>318</v>
+        <v>24</v>
       </c>
       <c r="G78" t="s">
-        <v>31</v>
+        <v>33</v>
+      </c>
+      <c r="H78" t="s">
+        <v>25</v>
       </c>
       <c r="I78">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="K78">
         <v>0</v>
@@ -6056,30 +6007,30 @@
         <v>0</v>
       </c>
       <c r="M78">
-        <v>60</v>
+        <v>8</v>
       </c>
       <c r="N78">
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="O78" t="s">
-        <v>56</v>
+        <v>26</v>
       </c>
       <c r="P78">
         <v>1</v>
       </c>
       <c r="T78" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
     </row>
     <row r="79" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="B79" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="C79" t="s">
-        <v>30</v>
+        <v>191</v>
       </c>
       <c r="D79" t="s">
         <v>23</v>
@@ -6088,7 +6039,7 @@
         <v>79</v>
       </c>
       <c r="F79" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="G79" t="s">
         <v>31</v>
@@ -6100,10 +6051,10 @@
         <v>0</v>
       </c>
       <c r="L79">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="M79">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="N79">
         <v>0</v>
@@ -6115,30 +6066,30 @@
         <v>1</v>
       </c>
       <c r="T79" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
     </row>
     <row r="80" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="B80" t="s">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="C80" t="s">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="D80" t="s">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="E80" t="s">
         <v>79</v>
       </c>
       <c r="F80" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="G80" t="s">
-        <v>198</v>
+        <v>115</v>
       </c>
       <c r="I80">
         <v>0</v>
@@ -6147,33 +6098,33 @@
         <v>0</v>
       </c>
       <c r="L80">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M80">
-        <v>2</v>
+        <v>99999</v>
       </c>
       <c r="N80">
         <v>0</v>
       </c>
       <c r="O80" t="s">
-        <v>56</v>
+        <v>162</v>
       </c>
       <c r="P80">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="T80" t="s">
-        <v>457</v>
+        <v>322</v>
       </c>
     </row>
     <row r="81" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="B81" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="C81" t="s">
-        <v>329</v>
+        <v>86</v>
       </c>
       <c r="D81" t="s">
         <v>23</v>
@@ -6182,10 +6133,10 @@
         <v>79</v>
       </c>
       <c r="F81" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="G81" t="s">
-        <v>198</v>
+        <v>115</v>
       </c>
       <c r="I81">
         <v>0</v>
@@ -6194,10 +6145,10 @@
         <v>0</v>
       </c>
       <c r="L81">
-        <v>65</v>
+        <v>25</v>
       </c>
       <c r="M81">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="N81">
         <v>0</v>
@@ -6209,344 +6160,362 @@
         <v>1</v>
       </c>
       <c r="T81" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
     </row>
     <row r="82" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="B82" t="s">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="C82" t="s">
-        <v>22</v>
+        <v>328</v>
       </c>
       <c r="D82" t="s">
         <v>23</v>
       </c>
       <c r="E82" t="s">
-        <v>24</v>
-      </c>
-      <c r="H82" t="s">
-        <v>25</v>
+        <v>79</v>
+      </c>
+      <c r="F82" t="s">
+        <v>326</v>
+      </c>
+      <c r="G82" t="s">
+        <v>200</v>
       </c>
       <c r="I82">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="K82">
         <v>0</v>
       </c>
       <c r="L82">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M82">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N82">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="O82" t="s">
-        <v>26</v>
+        <v>56</v>
       </c>
       <c r="P82">
         <v>1</v>
       </c>
       <c r="T82" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
     </row>
     <row r="83" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="B83" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="C83" t="s">
-        <v>44</v>
+        <v>332</v>
       </c>
       <c r="D83" t="s">
         <v>23</v>
       </c>
       <c r="E83" t="s">
-        <v>24</v>
+        <v>79</v>
+      </c>
+      <c r="F83" t="s">
+        <v>330</v>
       </c>
       <c r="G83" t="s">
+        <v>219</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="K83">
+        <v>0</v>
+      </c>
+      <c r="L83">
+        <v>25</v>
+      </c>
+      <c r="M83">
+        <v>4</v>
+      </c>
+      <c r="N83">
+        <v>0</v>
+      </c>
+      <c r="O83" t="s">
+        <v>56</v>
+      </c>
+      <c r="P83">
+        <v>1</v>
+      </c>
+      <c r="T83" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="84" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A84" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="B84" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="C84" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="D84" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="E84" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="F84" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="G84" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="I84" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="K84" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="L84" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="M84" s="1" t="s">
+        <v>401</v>
+      </c>
+      <c r="N84" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="O84" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="P84" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="R84" s="1" t="s">
+        <v>403</v>
+      </c>
+      <c r="T84" s="1" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="85" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A85" s="1" t="s">
+        <v>405</v>
+      </c>
+      <c r="B85" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="C85" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="D85" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="E85" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="F85" s="1" t="s">
+        <v>405</v>
+      </c>
+      <c r="G85" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="H83" t="s">
-        <v>25</v>
-      </c>
-      <c r="I83">
-        <v>200</v>
-      </c>
-      <c r="K83">
-        <v>0</v>
-      </c>
-      <c r="L83">
-        <v>0</v>
-      </c>
-      <c r="M83">
-        <v>8</v>
-      </c>
-      <c r="N83">
-        <v>0.35</v>
-      </c>
-      <c r="O83" t="s">
-        <v>26</v>
-      </c>
-      <c r="P83">
-        <v>1</v>
-      </c>
-      <c r="T83" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="84" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A84" t="s">
-        <v>337</v>
-      </c>
-      <c r="B84" t="s">
-        <v>338</v>
-      </c>
-      <c r="C84" t="s">
-        <v>212</v>
-      </c>
-      <c r="D84" t="s">
-        <v>23</v>
-      </c>
-      <c r="E84" t="s">
+      <c r="I85" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="K85" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="L85" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="M85" s="1" t="s">
+        <v>401</v>
+      </c>
+      <c r="N85" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="O85" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="P85" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="R85" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="T85" s="1" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="86" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A86" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="B86" s="1" t="s">
+        <v>411</v>
+      </c>
+      <c r="C86" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D86" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="E86" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="F84" t="s">
-        <v>337</v>
-      </c>
-      <c r="G84" t="s">
+      <c r="F86" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="G86" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="I84">
-        <v>0</v>
-      </c>
-      <c r="K84">
-        <v>0</v>
-      </c>
-      <c r="L84">
-        <v>1</v>
-      </c>
-      <c r="M84">
-        <v>8</v>
-      </c>
-      <c r="N84">
-        <v>0</v>
-      </c>
-      <c r="O84" t="s">
+      <c r="I86" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="K86" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="L86" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="M86" s="1" t="s">
+        <v>401</v>
+      </c>
+      <c r="N86" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="O86" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="P84">
-        <v>1</v>
-      </c>
-      <c r="T84" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="85" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A85" t="s">
-        <v>340</v>
-      </c>
-      <c r="B85" t="s">
-        <v>341</v>
-      </c>
-      <c r="C85" t="s">
-        <v>342</v>
-      </c>
-      <c r="D85" t="s">
+      <c r="P86" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="R86" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="T86" s="1" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="87" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A87" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="B87" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="C87" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="D87" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="E85" t="s">
+      <c r="E87" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="F85" t="s">
-        <v>340</v>
-      </c>
-      <c r="G85" t="s">
-        <v>123</v>
-      </c>
-      <c r="I85">
-        <v>0</v>
-      </c>
-      <c r="K85">
-        <v>0</v>
-      </c>
-      <c r="L85">
-        <v>2</v>
-      </c>
-      <c r="M85">
-        <v>99999</v>
-      </c>
-      <c r="N85">
-        <v>0</v>
-      </c>
-      <c r="O85" t="s">
-        <v>183</v>
-      </c>
-      <c r="P85">
-        <v>100</v>
-      </c>
-      <c r="T85" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="86" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A86" t="s">
-        <v>344</v>
-      </c>
-      <c r="B86" t="s">
-        <v>345</v>
-      </c>
-      <c r="C86" t="s">
-        <v>86</v>
-      </c>
-      <c r="D86" t="s">
-        <v>23</v>
-      </c>
-      <c r="E86" t="s">
+      <c r="F87" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="G87" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="I87" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="K87" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="L87" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="M87" s="1" t="s">
+        <v>437</v>
+      </c>
+      <c r="N87" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="O87" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="P87" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="R87" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="T87" s="1" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="88" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A88" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="B88" s="1" t="s">
+        <v>419</v>
+      </c>
+      <c r="C88" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="D88" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="E88" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="F86" t="s">
-        <v>344</v>
-      </c>
-      <c r="G86" t="s">
-        <v>123</v>
-      </c>
-      <c r="I86">
-        <v>0</v>
-      </c>
-      <c r="K86">
-        <v>0</v>
-      </c>
-      <c r="L86">
-        <v>25</v>
-      </c>
-      <c r="M86">
-        <v>8</v>
-      </c>
-      <c r="N86">
-        <v>0</v>
-      </c>
-      <c r="O86" t="s">
+      <c r="F88" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="G88" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="I88" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="K88" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="L88" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="M88" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="N88" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="O88" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="P86">
-        <v>1</v>
-      </c>
-      <c r="T86" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="87" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A87" t="s">
-        <v>347</v>
-      </c>
-      <c r="B87" t="s">
-        <v>348</v>
-      </c>
-      <c r="C87" t="s">
-        <v>349</v>
-      </c>
-      <c r="D87" t="s">
-        <v>23</v>
-      </c>
-      <c r="E87" t="s">
-        <v>79</v>
-      </c>
-      <c r="F87" t="s">
-        <v>347</v>
-      </c>
-      <c r="G87" t="s">
-        <v>221</v>
-      </c>
-      <c r="I87">
-        <v>0</v>
-      </c>
-      <c r="K87">
-        <v>0</v>
-      </c>
-      <c r="L87">
-        <v>50</v>
-      </c>
-      <c r="M87">
-        <v>6</v>
-      </c>
-      <c r="N87">
-        <v>0</v>
-      </c>
-      <c r="O87" t="s">
-        <v>56</v>
-      </c>
-      <c r="P87">
-        <v>1</v>
-      </c>
-      <c r="T87" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="88" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A88" t="s">
-        <v>351</v>
-      </c>
-      <c r="B88" t="s">
-        <v>352</v>
-      </c>
-      <c r="C88" t="s">
-        <v>353</v>
-      </c>
-      <c r="D88" t="s">
-        <v>23</v>
-      </c>
-      <c r="E88" t="s">
-        <v>79</v>
-      </c>
-      <c r="F88" t="s">
-        <v>351</v>
-      </c>
-      <c r="G88" t="s">
-        <v>240</v>
-      </c>
-      <c r="I88">
-        <v>0</v>
-      </c>
-      <c r="K88">
-        <v>0</v>
-      </c>
-      <c r="L88">
-        <v>25</v>
-      </c>
-      <c r="M88">
-        <v>4</v>
-      </c>
-      <c r="N88">
-        <v>0</v>
-      </c>
-      <c r="O88" t="s">
-        <v>56</v>
-      </c>
-      <c r="P88">
-        <v>1</v>
-      </c>
-      <c r="T88" t="s">
-        <v>354</v>
+      <c r="P88" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="R88" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="T88" s="1" t="s">
+        <v>420</v>
       </c>
     </row>
     <row r="89" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>282</v>
+        <v>423</v>
       </c>
       <c r="D89" s="1" t="s">
         <v>65</v>
@@ -6555,37 +6524,37 @@
         <v>79</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="G89" s="1" t="s">
-        <v>40</v>
+        <v>200</v>
       </c>
       <c r="I89" s="1" t="s">
-        <v>421</v>
+        <v>400</v>
       </c>
       <c r="K89" s="1" t="s">
-        <v>421</v>
+        <v>400</v>
       </c>
       <c r="L89" s="1" t="s">
-        <v>421</v>
+        <v>400</v>
       </c>
       <c r="M89" s="1" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="N89" s="1" t="s">
-        <v>421</v>
+        <v>400</v>
       </c>
       <c r="O89" s="1" t="s">
         <v>56</v>
       </c>
       <c r="P89" s="1" t="s">
-        <v>423</v>
+        <v>402</v>
       </c>
       <c r="R89" s="1" t="s">
-        <v>424</v>
+        <v>433</v>
       </c>
       <c r="T89" s="1" t="s">
-        <v>425</v>
+        <v>434</v>
       </c>
     </row>
     <row r="90" spans="1:20" x14ac:dyDescent="0.25">
@@ -6596,7 +6565,7 @@
         <v>427</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>428</v>
+        <v>328</v>
       </c>
       <c r="D90" s="1" t="s">
         <v>65</v>
@@ -6608,45 +6577,45 @@
         <v>426</v>
       </c>
       <c r="G90" s="1" t="s">
-        <v>33</v>
+        <v>200</v>
       </c>
       <c r="I90" s="1" t="s">
-        <v>421</v>
+        <v>400</v>
       </c>
       <c r="K90" s="1" t="s">
-        <v>421</v>
+        <v>400</v>
       </c>
       <c r="L90" s="1" t="s">
-        <v>421</v>
+        <v>400</v>
       </c>
       <c r="M90" s="1" t="s">
-        <v>422</v>
+        <v>401</v>
       </c>
       <c r="N90" s="1" t="s">
-        <v>421</v>
+        <v>400</v>
       </c>
       <c r="O90" s="1" t="s">
         <v>56</v>
       </c>
       <c r="P90" s="1" t="s">
-        <v>423</v>
+        <v>402</v>
       </c>
       <c r="R90" s="1" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
       <c r="T90" s="1" t="s">
-        <v>430</v>
+        <v>435</v>
       </c>
     </row>
     <row r="91" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
-        <v>431</v>
+        <v>439</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>432</v>
+        <v>440</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>30</v>
+        <v>74</v>
       </c>
       <c r="D91" s="1" t="s">
         <v>65</v>
@@ -6655,48 +6624,45 @@
         <v>79</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>431</v>
-      </c>
-      <c r="G91" s="1" t="s">
-        <v>31</v>
+        <v>439</v>
       </c>
       <c r="I91" s="1" t="s">
-        <v>421</v>
+        <v>400</v>
       </c>
       <c r="K91" s="1" t="s">
-        <v>421</v>
+        <v>400</v>
       </c>
       <c r="L91" s="1" t="s">
-        <v>421</v>
+        <v>400</v>
       </c>
       <c r="M91" s="1" t="s">
-        <v>422</v>
+        <v>441</v>
       </c>
       <c r="N91" s="1" t="s">
-        <v>421</v>
+        <v>400</v>
       </c>
       <c r="O91" s="1" t="s">
         <v>56</v>
       </c>
       <c r="P91" s="1" t="s">
-        <v>423</v>
+        <v>402</v>
       </c>
       <c r="R91" s="1" t="s">
-        <v>433</v>
+        <v>442</v>
       </c>
       <c r="T91" s="1" t="s">
-        <v>434</v>
+        <v>443</v>
       </c>
     </row>
     <row r="92" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
-        <v>435</v>
+        <v>444</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>436</v>
+        <v>445</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>326</v>
+        <v>280</v>
       </c>
       <c r="D92" s="1" t="s">
         <v>65</v>
@@ -6705,48 +6671,48 @@
         <v>79</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>435</v>
-      </c>
-      <c r="G92" s="1" t="s">
-        <v>198</v>
+        <v>444</v>
       </c>
       <c r="I92" s="1" t="s">
-        <v>421</v>
+        <v>400</v>
       </c>
       <c r="K92" s="1" t="s">
-        <v>421</v>
+        <v>400</v>
       </c>
       <c r="L92" s="1" t="s">
-        <v>421</v>
+        <v>400</v>
       </c>
       <c r="M92" s="1" t="s">
-        <v>458</v>
+        <v>401</v>
       </c>
       <c r="N92" s="1" t="s">
-        <v>421</v>
+        <v>400</v>
       </c>
       <c r="O92" s="1" t="s">
         <v>56</v>
       </c>
       <c r="P92" s="1" t="s">
-        <v>423</v>
+        <v>402</v>
+      </c>
+      <c r="Q92" s="1" t="s">
+        <v>446</v>
       </c>
       <c r="R92" s="1" t="s">
-        <v>438</v>
+        <v>447</v>
       </c>
       <c r="T92" s="1" t="s">
-        <v>459</v>
+        <v>448</v>
       </c>
     </row>
     <row r="93" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
-        <v>439</v>
+        <v>449</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>440</v>
+        <v>450</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>329</v>
+        <v>30</v>
       </c>
       <c r="D93" s="1" t="s">
         <v>65</v>
@@ -6755,48 +6721,48 @@
         <v>79</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>439</v>
-      </c>
-      <c r="G93" s="1" t="s">
-        <v>198</v>
+        <v>449</v>
       </c>
       <c r="I93" s="1" t="s">
-        <v>421</v>
+        <v>400</v>
       </c>
       <c r="K93" s="1" t="s">
-        <v>421</v>
+        <v>400</v>
       </c>
       <c r="L93" s="1" t="s">
-        <v>421</v>
+        <v>400</v>
       </c>
       <c r="M93" s="1" t="s">
-        <v>437</v>
+        <v>451</v>
       </c>
       <c r="N93" s="1" t="s">
-        <v>421</v>
+        <v>400</v>
       </c>
       <c r="O93" s="1" t="s">
         <v>56</v>
       </c>
       <c r="P93" s="1" t="s">
-        <v>423</v>
+        <v>402</v>
+      </c>
+      <c r="Q93" s="1" t="s">
+        <v>452</v>
       </c>
       <c r="R93" s="1" t="s">
         <v>453</v>
       </c>
       <c r="T93" s="1" t="s">
-        <v>441</v>
+        <v>454</v>
       </c>
     </row>
     <row r="94" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
-        <v>442</v>
+        <v>455</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>443</v>
+        <v>68</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>444</v>
+        <v>69</v>
       </c>
       <c r="D94" s="1" t="s">
         <v>65</v>
@@ -6805,328 +6771,81 @@
         <v>79</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>442</v>
-      </c>
-      <c r="G94" s="1" t="s">
-        <v>221</v>
+        <v>455</v>
       </c>
       <c r="I94" s="1" t="s">
-        <v>421</v>
+        <v>400</v>
       </c>
       <c r="K94" s="1" t="s">
-        <v>421</v>
+        <v>400</v>
       </c>
       <c r="L94" s="1" t="s">
-        <v>421</v>
+        <v>400</v>
       </c>
       <c r="M94" s="1" t="s">
-        <v>445</v>
+        <v>401</v>
       </c>
       <c r="N94" s="1" t="s">
-        <v>421</v>
+        <v>456</v>
       </c>
       <c r="O94" s="1" t="s">
         <v>56</v>
       </c>
       <c r="P94" s="1" t="s">
-        <v>423</v>
-      </c>
-      <c r="R94" s="1" t="s">
-        <v>454</v>
+        <v>402</v>
+      </c>
+      <c r="S94" s="1" t="s">
+        <v>457</v>
       </c>
       <c r="T94" s="1" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
     </row>
     <row r="95" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
-        <v>447</v>
+        <v>459</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>448</v>
+        <v>460</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>349</v>
+        <v>461</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>65</v>
+        <v>23</v>
       </c>
       <c r="E95" s="1" t="s">
         <v>79</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>447</v>
-      </c>
-      <c r="G95" s="1" t="s">
-        <v>221</v>
+        <v>459</v>
       </c>
       <c r="I95" s="1" t="s">
-        <v>421</v>
+        <v>400</v>
       </c>
       <c r="K95" s="1" t="s">
-        <v>421</v>
+        <v>400</v>
       </c>
       <c r="L95" s="1" t="s">
-        <v>421</v>
+        <v>400</v>
       </c>
       <c r="M95" s="1" t="s">
-        <v>422</v>
+        <v>462</v>
       </c>
       <c r="N95" s="1" t="s">
-        <v>421</v>
+        <v>400</v>
       </c>
       <c r="O95" s="1" t="s">
         <v>56</v>
       </c>
       <c r="P95" s="1" t="s">
-        <v>423</v>
-      </c>
-      <c r="R95" s="1" t="s">
-        <v>446</v>
+        <v>402</v>
+      </c>
+      <c r="Q95" s="1" t="s">
+        <v>463</v>
       </c>
       <c r="T95" s="1" t="s">
-        <v>456</v>
-      </c>
-    </row>
-    <row r="96" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A96" s="1" t="s">
-        <v>460</v>
-      </c>
-      <c r="B96" s="1" t="s">
-        <v>461</v>
-      </c>
-      <c r="C96" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="D96" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="E96" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="F96" s="1" t="s">
-        <v>460</v>
-      </c>
-      <c r="I96" s="1" t="s">
-        <v>421</v>
-      </c>
-      <c r="K96" s="1" t="s">
-        <v>421</v>
-      </c>
-      <c r="L96" s="1" t="s">
-        <v>421</v>
-      </c>
-      <c r="M96" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="N96" s="1" t="s">
-        <v>421</v>
-      </c>
-      <c r="O96" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="P96" s="1" t="s">
-        <v>423</v>
-      </c>
-      <c r="R96" s="1" t="s">
-        <v>463</v>
-      </c>
-      <c r="T96" s="1" t="s">
         <v>464</v>
-      </c>
-    </row>
-    <row r="97" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A97" s="1" t="s">
-        <v>465</v>
-      </c>
-      <c r="B97" s="1" t="s">
-        <v>466</v>
-      </c>
-      <c r="C97" s="1" t="s">
-        <v>301</v>
-      </c>
-      <c r="D97" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="E97" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="F97" s="1" t="s">
-        <v>465</v>
-      </c>
-      <c r="I97" s="1" t="s">
-        <v>421</v>
-      </c>
-      <c r="K97" s="1" t="s">
-        <v>421</v>
-      </c>
-      <c r="L97" s="1" t="s">
-        <v>421</v>
-      </c>
-      <c r="M97" s="1" t="s">
-        <v>422</v>
-      </c>
-      <c r="N97" s="1" t="s">
-        <v>421</v>
-      </c>
-      <c r="O97" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="P97" s="1" t="s">
-        <v>423</v>
-      </c>
-      <c r="Q97" s="1" t="s">
-        <v>467</v>
-      </c>
-      <c r="R97" s="1" t="s">
-        <v>468</v>
-      </c>
-      <c r="T97" s="1" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="98" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A98" s="1" t="s">
-        <v>470</v>
-      </c>
-      <c r="B98" s="1" t="s">
-        <v>471</v>
-      </c>
-      <c r="C98" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D98" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="E98" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="F98" s="1" t="s">
-        <v>470</v>
-      </c>
-      <c r="I98" s="1" t="s">
-        <v>421</v>
-      </c>
-      <c r="K98" s="1" t="s">
-        <v>421</v>
-      </c>
-      <c r="L98" s="1" t="s">
-        <v>421</v>
-      </c>
-      <c r="M98" s="1" t="s">
-        <v>472</v>
-      </c>
-      <c r="N98" s="1" t="s">
-        <v>421</v>
-      </c>
-      <c r="O98" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="P98" s="1" t="s">
-        <v>423</v>
-      </c>
-      <c r="Q98" s="1" t="s">
-        <v>473</v>
-      </c>
-      <c r="R98" s="1" t="s">
-        <v>474</v>
-      </c>
-      <c r="T98" s="1" t="s">
-        <v>475</v>
-      </c>
-    </row>
-    <row r="99" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A99" s="1" t="s">
-        <v>476</v>
-      </c>
-      <c r="B99" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="C99" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="D99" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="E99" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="F99" s="1" t="s">
-        <v>476</v>
-      </c>
-      <c r="I99" s="1" t="s">
-        <v>421</v>
-      </c>
-      <c r="K99" s="1" t="s">
-        <v>421</v>
-      </c>
-      <c r="L99" s="1" t="s">
-        <v>421</v>
-      </c>
-      <c r="M99" s="1" t="s">
-        <v>422</v>
-      </c>
-      <c r="N99" s="1" t="s">
-        <v>477</v>
-      </c>
-      <c r="O99" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="P99" s="1" t="s">
-        <v>423</v>
-      </c>
-      <c r="S99" s="1" t="s">
-        <v>478</v>
-      </c>
-      <c r="T99" s="1" t="s">
-        <v>479</v>
-      </c>
-    </row>
-    <row r="100" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A100" s="1" t="s">
-        <v>480</v>
-      </c>
-      <c r="B100" s="1" t="s">
-        <v>481</v>
-      </c>
-      <c r="C100" s="1" t="s">
-        <v>482</v>
-      </c>
-      <c r="D100" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E100" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="F100" s="1" t="s">
-        <v>480</v>
-      </c>
-      <c r="I100" s="1" t="s">
-        <v>421</v>
-      </c>
-      <c r="K100" s="1" t="s">
-        <v>421</v>
-      </c>
-      <c r="L100" s="1" t="s">
-        <v>421</v>
-      </c>
-      <c r="M100" s="1" t="s">
-        <v>483</v>
-      </c>
-      <c r="N100" s="1" t="s">
-        <v>421</v>
-      </c>
-      <c r="O100" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="P100" s="1" t="s">
-        <v>423</v>
-      </c>
-      <c r="Q100" s="1" t="s">
-        <v>484</v>
-      </c>
-      <c r="T100" s="1" t="s">
-        <v>485</v>
       </c>
     </row>
   </sheetData>
@@ -7151,32 +6870,32 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>355</v>
+        <v>334</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>356</v>
+        <v>335</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>412</v>
+        <v>391</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>357</v>
+        <v>336</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>358</v>
+        <v>337</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>412</v>
+        <v>391</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
@@ -7186,17 +6905,17 @@
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>359</v>
+        <v>338</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>360</v>
+        <v>339</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>412</v>
+        <v>391</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
@@ -7206,32 +6925,32 @@
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>361</v>
+        <v>340</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>362</v>
+        <v>341</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>363</v>
+        <v>342</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>364</v>
+        <v>343</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>365</v>
+        <v>344</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>412</v>
+        <v>391</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
@@ -7241,27 +6960,27 @@
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>366</v>
+        <v>345</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>367</v>
+        <v>346</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>368</v>
+        <v>347</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>369</v>
+        <v>348</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>412</v>
+        <v>391</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
@@ -7271,17 +6990,17 @@
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>370</v>
+        <v>349</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>371</v>
+        <v>350</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>412</v>
+        <v>391</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
@@ -7291,22 +7010,22 @@
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>372</v>
+        <v>351</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>373</v>
+        <v>352</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>374</v>
+        <v>353</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>412</v>
+        <v>391</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
@@ -7316,42 +7035,42 @@
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>375</v>
+        <v>354</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>376</v>
+        <v>355</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>377</v>
+        <v>356</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>412</v>
+        <v>391</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>378</v>
+        <v>357</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>379</v>
+        <v>358</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>380</v>
+        <v>359</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>412</v>
+        <v>391</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.25">
@@ -7361,17 +7080,17 @@
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>381</v>
+        <v>360</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>382</v>
+        <v>361</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>412</v>
+        <v>391</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.25">
@@ -7381,22 +7100,22 @@
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>383</v>
+        <v>362</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>384</v>
+        <v>363</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>385</v>
+        <v>364</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>412</v>
+        <v>391</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.25">
@@ -7406,147 +7125,147 @@
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>386</v>
+        <v>365</v>
       </c>
     </row>
     <row r="54" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>387</v>
+        <v>366</v>
       </c>
     </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>388</v>
+        <v>367</v>
       </c>
     </row>
     <row r="56" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>389</v>
+        <v>368</v>
       </c>
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
-        <v>412</v>
+        <v>391</v>
       </c>
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
-        <v>390</v>
+        <v>369</v>
       </c>
     </row>
     <row r="59" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
-        <v>391</v>
+        <v>370</v>
       </c>
     </row>
     <row r="60" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
-        <v>392</v>
+        <v>371</v>
       </c>
     </row>
     <row r="61" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
-        <v>393</v>
+        <v>372</v>
       </c>
     </row>
     <row r="62" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
-        <v>394</v>
+        <v>373</v>
       </c>
     </row>
     <row r="63" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
-        <v>395</v>
+        <v>374</v>
       </c>
     </row>
     <row r="64" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
-        <v>396</v>
+        <v>375</v>
       </c>
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
-        <v>397</v>
+        <v>376</v>
       </c>
     </row>
     <row r="66" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
-        <v>412</v>
+        <v>391</v>
       </c>
     </row>
     <row r="67" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
-        <v>398</v>
+        <v>377</v>
       </c>
     </row>
     <row r="68" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
-        <v>399</v>
+        <v>378</v>
       </c>
     </row>
     <row r="69" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
-        <v>400</v>
+        <v>379</v>
       </c>
     </row>
     <row r="70" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
-        <v>401</v>
+        <v>380</v>
       </c>
     </row>
     <row r="71" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
-        <v>402</v>
+        <v>381</v>
       </c>
     </row>
     <row r="72" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
-        <v>412</v>
+        <v>391</v>
       </c>
     </row>
     <row r="73" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
-        <v>413</v>
+        <v>392</v>
       </c>
     </row>
     <row r="74" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
-        <v>414</v>
+        <v>393</v>
       </c>
     </row>
     <row r="75" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
-        <v>403</v>
+        <v>382</v>
       </c>
     </row>
     <row r="76" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
-        <v>415</v>
+        <v>394</v>
       </c>
     </row>
     <row r="77" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
-        <v>416</v>
+        <v>395</v>
       </c>
     </row>
     <row r="78" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
-        <v>449</v>
+        <v>428</v>
       </c>
     </row>
     <row r="79" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
-        <v>450</v>
+        <v>429</v>
       </c>
     </row>
     <row r="80" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
-        <v>417</v>
+        <v>396</v>
       </c>
     </row>
     <row r="81" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
-        <v>418</v>
+        <v>397</v>
       </c>
     </row>
   </sheetData>

--- a/config/Excel/Status.xlsx
+++ b/config/Excel/Status.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\AppData\Local\Temp\potential-remove-baseline-20261018\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyGame\Idle-RPG\codex\config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B0E3818-6910-4E84-8531-C3B33A332005}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33E3C268-951D-45DA-AD38-5D15206B85E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3090" yWindow="2310" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -846,9 +846,6 @@
     <t>🎇</t>
   </si>
   <si>
-    <t>超神進化【火之神樂】：雙刀亂舞每命中 1 次疊 1 層，每跳量＝單層量 × 層數（引擎以 dps 覆寫）。</t>
-  </si>
-  <si>
     <t>sgDeathDefer</t>
   </si>
   <si>
@@ -1444,6 +1441,10 @@
   </si>
   <si>
     <t>符文真言增益：所有傷害提高。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>超神進化【火之神樂】：雙刀亂舞每命中 1 次疊 1 層，每跳量＝單層量 × 層數（引擎以 dps 覆寫）；狀態生效期間將敵人屬性改為火屬性，結束後恢復。</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -3399,7 +3400,7 @@
         <v>112</v>
       </c>
       <c r="B22" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="C22" t="s">
         <v>113</v>
@@ -3435,7 +3436,7 @@
         <v>1</v>
       </c>
       <c r="T22" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="23" spans="1:20" x14ac:dyDescent="0.25">
@@ -3752,10 +3753,10 @@
         <v>1</v>
       </c>
       <c r="Q29" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="S29" s="1" t="s">
         <v>383</v>
-      </c>
-      <c r="S29" s="1" t="s">
-        <v>384</v>
       </c>
       <c r="T29" t="s">
         <v>136</v>
@@ -3978,10 +3979,10 @@
         <v>1</v>
       </c>
       <c r="R34" s="1" t="s">
+        <v>429</v>
+      </c>
+      <c r="T34" s="1" t="s">
         <v>430</v>
-      </c>
-      <c r="T34" s="1" t="s">
-        <v>431</v>
       </c>
     </row>
     <row r="35" spans="1:20" x14ac:dyDescent="0.25">
@@ -4025,7 +4026,7 @@
         <v>1</v>
       </c>
       <c r="R35" s="1" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="T35" t="s">
         <v>157</v>
@@ -4119,7 +4120,7 @@
         <v>1</v>
       </c>
       <c r="S37" s="1" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="T37" t="s">
         <v>166</v>
@@ -4589,7 +4590,7 @@
         <v>1</v>
       </c>
       <c r="S47" s="1" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="T47" t="s">
         <v>205</v>
@@ -4921,7 +4922,7 @@
         <v>1</v>
       </c>
       <c r="R54" s="1" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="T54" t="s">
         <v>230</v>
@@ -5018,7 +5019,7 @@
         <v>1</v>
       </c>
       <c r="R56" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="T56" t="s">
         <v>237</v>
@@ -5426,18 +5427,18 @@
         <v>20</v>
       </c>
       <c r="T65" t="s">
-        <v>270</v>
+        <v>466</v>
       </c>
     </row>
     <row r="66" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
+        <v>270</v>
+      </c>
+      <c r="B66" t="s">
         <v>271</v>
       </c>
-      <c r="B66" t="s">
+      <c r="C66" t="s">
         <v>272</v>
-      </c>
-      <c r="C66" t="s">
-        <v>273</v>
       </c>
       <c r="D66" t="s">
         <v>65</v>
@@ -5446,7 +5447,7 @@
         <v>79</v>
       </c>
       <c r="F66" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="I66">
         <v>0</v>
@@ -5470,18 +5471,18 @@
         <v>1</v>
       </c>
       <c r="R66" s="1" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="T66" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="67" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
+        <v>274</v>
+      </c>
+      <c r="B67" t="s">
         <v>275</v>
-      </c>
-      <c r="B67" t="s">
-        <v>276</v>
       </c>
       <c r="C67" t="s">
         <v>250</v>
@@ -5493,7 +5494,7 @@
         <v>79</v>
       </c>
       <c r="F67" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="I67">
         <v>0</v>
@@ -5517,18 +5518,18 @@
         <v>1</v>
       </c>
       <c r="T67" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="68" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
+        <v>277</v>
+      </c>
+      <c r="B68" t="s">
         <v>278</v>
       </c>
-      <c r="B68" t="s">
+      <c r="C68" t="s">
         <v>279</v>
-      </c>
-      <c r="C68" t="s">
-        <v>280</v>
       </c>
       <c r="D68" t="s">
         <v>65</v>
@@ -5537,7 +5538,7 @@
         <v>79</v>
       </c>
       <c r="F68" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="I68">
         <v>0</v>
@@ -5561,15 +5562,15 @@
         <v>1</v>
       </c>
       <c r="T68" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="69" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
+        <v>281</v>
+      </c>
+      <c r="B69" t="s">
         <v>282</v>
-      </c>
-      <c r="B69" t="s">
-        <v>283</v>
       </c>
       <c r="C69" t="s">
         <v>22</v>
@@ -5581,7 +5582,7 @@
         <v>79</v>
       </c>
       <c r="F69" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="I69">
         <v>0</v>
@@ -5605,18 +5606,18 @@
         <v>50</v>
       </c>
       <c r="T69" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="70" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
+        <v>284</v>
+      </c>
+      <c r="B70" t="s">
         <v>285</v>
       </c>
-      <c r="B70" t="s">
+      <c r="C70" t="s">
         <v>286</v>
-      </c>
-      <c r="C70" t="s">
-        <v>287</v>
       </c>
       <c r="D70" t="s">
         <v>65</v>
@@ -5625,7 +5626,7 @@
         <v>79</v>
       </c>
       <c r="F70" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="I70">
         <v>0</v>
@@ -5649,18 +5650,18 @@
         <v>10</v>
       </c>
       <c r="T70" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="71" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
+        <v>288</v>
+      </c>
+      <c r="B71" t="s">
         <v>289</v>
       </c>
-      <c r="B71" t="s">
+      <c r="C71" t="s">
         <v>290</v>
-      </c>
-      <c r="C71" t="s">
-        <v>291</v>
       </c>
       <c r="D71" t="s">
         <v>65</v>
@@ -5669,7 +5670,7 @@
         <v>79</v>
       </c>
       <c r="F71" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="I71">
         <v>0</v>
@@ -5693,18 +5694,18 @@
         <v>100</v>
       </c>
       <c r="T71" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="72" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
+        <v>292</v>
+      </c>
+      <c r="B72" t="s">
         <v>293</v>
       </c>
-      <c r="B72" t="s">
+      <c r="C72" t="s">
         <v>294</v>
-      </c>
-      <c r="C72" t="s">
-        <v>295</v>
       </c>
       <c r="D72" t="s">
         <v>65</v>
@@ -5713,7 +5714,7 @@
         <v>79</v>
       </c>
       <c r="F72" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="I72">
         <v>0</v>
@@ -5737,18 +5738,18 @@
         <v>1</v>
       </c>
       <c r="R72" s="1" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="T72" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="73" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
+        <v>296</v>
+      </c>
+      <c r="B73" t="s">
         <v>297</v>
-      </c>
-      <c r="B73" t="s">
-        <v>298</v>
       </c>
       <c r="C73" t="s">
         <v>172</v>
@@ -5760,7 +5761,7 @@
         <v>79</v>
       </c>
       <c r="F73" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="G73" t="s">
         <v>31</v>
@@ -5787,15 +5788,15 @@
         <v>1</v>
       </c>
       <c r="T73" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="74" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
+        <v>299</v>
+      </c>
+      <c r="B74" t="s">
         <v>300</v>
-      </c>
-      <c r="B74" t="s">
-        <v>301</v>
       </c>
       <c r="C74" t="s">
         <v>30</v>
@@ -5807,7 +5808,7 @@
         <v>79</v>
       </c>
       <c r="F74" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="G74" t="s">
         <v>31</v>
@@ -5834,18 +5835,18 @@
         <v>1</v>
       </c>
       <c r="T74" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="75" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
+        <v>302</v>
+      </c>
+      <c r="B75" t="s">
         <v>303</v>
       </c>
-      <c r="B75" t="s">
+      <c r="C75" t="s">
         <v>304</v>
-      </c>
-      <c r="C75" t="s">
-        <v>305</v>
       </c>
       <c r="D75" t="s">
         <v>23</v>
@@ -5854,7 +5855,7 @@
         <v>79</v>
       </c>
       <c r="F75" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="G75" t="s">
         <v>177</v>
@@ -5881,18 +5882,18 @@
         <v>1</v>
       </c>
       <c r="T75" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="76" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
+        <v>305</v>
+      </c>
+      <c r="B76" t="s">
         <v>306</v>
       </c>
-      <c r="B76" t="s">
+      <c r="C76" t="s">
         <v>307</v>
-      </c>
-      <c r="C76" t="s">
-        <v>308</v>
       </c>
       <c r="D76" t="s">
         <v>23</v>
@@ -5901,7 +5902,7 @@
         <v>79</v>
       </c>
       <c r="F76" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="G76" t="s">
         <v>177</v>
@@ -5928,15 +5929,15 @@
         <v>1</v>
       </c>
       <c r="T76" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="77" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
+        <v>309</v>
+      </c>
+      <c r="B77" t="s">
         <v>310</v>
-      </c>
-      <c r="B77" t="s">
-        <v>311</v>
       </c>
       <c r="C77" t="s">
         <v>22</v>
@@ -5972,15 +5973,15 @@
         <v>1</v>
       </c>
       <c r="T77" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="78" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
+        <v>312</v>
+      </c>
+      <c r="B78" t="s">
         <v>313</v>
-      </c>
-      <c r="B78" t="s">
-        <v>314</v>
       </c>
       <c r="C78" t="s">
         <v>44</v>
@@ -6019,15 +6020,15 @@
         <v>1</v>
       </c>
       <c r="T78" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="79" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
+        <v>315</v>
+      </c>
+      <c r="B79" t="s">
         <v>316</v>
-      </c>
-      <c r="B79" t="s">
-        <v>317</v>
       </c>
       <c r="C79" t="s">
         <v>191</v>
@@ -6039,7 +6040,7 @@
         <v>79</v>
       </c>
       <c r="F79" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="G79" t="s">
         <v>31</v>
@@ -6066,18 +6067,18 @@
         <v>1</v>
       </c>
       <c r="T79" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="80" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
+        <v>318</v>
+      </c>
+      <c r="B80" t="s">
         <v>319</v>
       </c>
-      <c r="B80" t="s">
+      <c r="C80" t="s">
         <v>320</v>
-      </c>
-      <c r="C80" t="s">
-        <v>321</v>
       </c>
       <c r="D80" t="s">
         <v>65</v>
@@ -6086,7 +6087,7 @@
         <v>79</v>
       </c>
       <c r="F80" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="G80" t="s">
         <v>115</v>
@@ -6113,15 +6114,15 @@
         <v>100</v>
       </c>
       <c r="T80" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="81" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
+        <v>322</v>
+      </c>
+      <c r="B81" t="s">
         <v>323</v>
-      </c>
-      <c r="B81" t="s">
-        <v>324</v>
       </c>
       <c r="C81" t="s">
         <v>86</v>
@@ -6133,7 +6134,7 @@
         <v>79</v>
       </c>
       <c r="F81" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="G81" t="s">
         <v>115</v>
@@ -6160,18 +6161,18 @@
         <v>1</v>
       </c>
       <c r="T81" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="82" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
+        <v>325</v>
+      </c>
+      <c r="B82" t="s">
         <v>326</v>
       </c>
-      <c r="B82" t="s">
+      <c r="C82" t="s">
         <v>327</v>
-      </c>
-      <c r="C82" t="s">
-        <v>328</v>
       </c>
       <c r="D82" t="s">
         <v>23</v>
@@ -6180,7 +6181,7 @@
         <v>79</v>
       </c>
       <c r="F82" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="G82" t="s">
         <v>200</v>
@@ -6207,18 +6208,18 @@
         <v>1</v>
       </c>
       <c r="T82" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="83" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
+        <v>329</v>
+      </c>
+      <c r="B83" t="s">
         <v>330</v>
       </c>
-      <c r="B83" t="s">
+      <c r="C83" t="s">
         <v>331</v>
-      </c>
-      <c r="C83" t="s">
-        <v>332</v>
       </c>
       <c r="D83" t="s">
         <v>23</v>
@@ -6227,7 +6228,7 @@
         <v>79</v>
       </c>
       <c r="F83" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="G83" t="s">
         <v>219</v>
@@ -6254,15 +6255,15 @@
         <v>1</v>
       </c>
       <c r="T83" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="84" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="B84" s="1" t="s">
         <v>398</v>
-      </c>
-      <c r="B84" s="1" t="s">
-        <v>399</v>
       </c>
       <c r="C84" s="1" t="s">
         <v>261</v>
@@ -6274,48 +6275,48 @@
         <v>79</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="G84" s="1" t="s">
         <v>40</v>
       </c>
       <c r="I84" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="K84" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="L84" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="M84" s="1" t="s">
         <v>400</v>
       </c>
-      <c r="K84" s="1" t="s">
-        <v>400</v>
-      </c>
-      <c r="L84" s="1" t="s">
-        <v>400</v>
-      </c>
-      <c r="M84" s="1" t="s">
-        <v>401</v>
-      </c>
       <c r="N84" s="1" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="O84" s="1" t="s">
         <v>56</v>
       </c>
       <c r="P84" s="1" t="s">
+        <v>401</v>
+      </c>
+      <c r="R84" s="1" t="s">
         <v>402</v>
       </c>
-      <c r="R84" s="1" t="s">
+      <c r="T84" s="1" t="s">
         <v>403</v>
-      </c>
-      <c r="T84" s="1" t="s">
-        <v>404</v>
       </c>
     </row>
     <row r="85" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="B85" s="1" t="s">
         <v>405</v>
       </c>
-      <c r="B85" s="1" t="s">
+      <c r="C85" s="1" t="s">
         <v>406</v>
-      </c>
-      <c r="C85" s="1" t="s">
-        <v>407</v>
       </c>
       <c r="D85" s="1" t="s">
         <v>65</v>
@@ -6324,45 +6325,45 @@
         <v>79</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="G85" s="1" t="s">
         <v>33</v>
       </c>
       <c r="I85" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="K85" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="L85" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="M85" s="1" t="s">
         <v>400</v>
       </c>
-      <c r="K85" s="1" t="s">
-        <v>400</v>
-      </c>
-      <c r="L85" s="1" t="s">
-        <v>400</v>
-      </c>
-      <c r="M85" s="1" t="s">
-        <v>401</v>
-      </c>
       <c r="N85" s="1" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="O85" s="1" t="s">
         <v>56</v>
       </c>
       <c r="P85" s="1" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="R85" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="T85" s="1" t="s">
         <v>408</v>
-      </c>
-      <c r="T85" s="1" t="s">
-        <v>409</v>
       </c>
     </row>
     <row r="86" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="B86" s="1" t="s">
         <v>410</v>
-      </c>
-      <c r="B86" s="1" t="s">
-        <v>411</v>
       </c>
       <c r="C86" s="1" t="s">
         <v>30</v>
@@ -6374,48 +6375,48 @@
         <v>79</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="G86" s="1" t="s">
         <v>31</v>
       </c>
       <c r="I86" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="K86" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="L86" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="M86" s="1" t="s">
         <v>400</v>
       </c>
-      <c r="K86" s="1" t="s">
-        <v>400</v>
-      </c>
-      <c r="L86" s="1" t="s">
-        <v>400</v>
-      </c>
-      <c r="M86" s="1" t="s">
-        <v>401</v>
-      </c>
       <c r="N86" s="1" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="O86" s="1" t="s">
         <v>56</v>
       </c>
       <c r="P86" s="1" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="R86" s="1" t="s">
+        <v>411</v>
+      </c>
+      <c r="T86" s="1" t="s">
         <v>412</v>
-      </c>
-      <c r="T86" s="1" t="s">
-        <v>413</v>
       </c>
     </row>
     <row r="87" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="B87" s="1" t="s">
         <v>414</v>
       </c>
-      <c r="B87" s="1" t="s">
-        <v>415</v>
-      </c>
       <c r="C87" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="D87" s="1" t="s">
         <v>65</v>
@@ -6424,48 +6425,48 @@
         <v>79</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="G87" s="1" t="s">
         <v>177</v>
       </c>
       <c r="I87" s="1" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="K87" s="1" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="L87" s="1" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="M87" s="1" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="N87" s="1" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="O87" s="1" t="s">
         <v>56</v>
       </c>
       <c r="P87" s="1" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="R87" s="1" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="T87" s="1" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="88" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="B88" s="1" t="s">
         <v>418</v>
       </c>
-      <c r="B88" s="1" t="s">
-        <v>419</v>
-      </c>
       <c r="C88" s="1" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="D88" s="1" t="s">
         <v>65</v>
@@ -6474,48 +6475,48 @@
         <v>79</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="G88" s="1" t="s">
         <v>177</v>
       </c>
       <c r="I88" s="1" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="K88" s="1" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="L88" s="1" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="M88" s="1" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="N88" s="1" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="O88" s="1" t="s">
         <v>56</v>
       </c>
       <c r="P88" s="1" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="R88" s="1" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="T88" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
     </row>
     <row r="89" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="B89" s="1" t="s">
         <v>421</v>
       </c>
-      <c r="B89" s="1" t="s">
+      <c r="C89" s="1" t="s">
         <v>422</v>
-      </c>
-      <c r="C89" s="1" t="s">
-        <v>423</v>
       </c>
       <c r="D89" s="1" t="s">
         <v>65</v>
@@ -6524,48 +6525,48 @@
         <v>79</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="G89" s="1" t="s">
         <v>200</v>
       </c>
       <c r="I89" s="1" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="K89" s="1" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="L89" s="1" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="M89" s="1" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="N89" s="1" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="O89" s="1" t="s">
         <v>56</v>
       </c>
       <c r="P89" s="1" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="R89" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="T89" s="1" t="s">
         <v>433</v>
-      </c>
-      <c r="T89" s="1" t="s">
-        <v>434</v>
       </c>
     </row>
     <row r="90" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="B90" s="1" t="s">
         <v>426</v>
       </c>
-      <c r="B90" s="1" t="s">
-        <v>427</v>
-      </c>
       <c r="C90" s="1" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="D90" s="1" t="s">
         <v>65</v>
@@ -6574,45 +6575,45 @@
         <v>79</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="G90" s="1" t="s">
         <v>200</v>
       </c>
       <c r="I90" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="K90" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="L90" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="M90" s="1" t="s">
         <v>400</v>
       </c>
-      <c r="K90" s="1" t="s">
-        <v>400</v>
-      </c>
-      <c r="L90" s="1" t="s">
-        <v>400</v>
-      </c>
-      <c r="M90" s="1" t="s">
-        <v>401</v>
-      </c>
       <c r="N90" s="1" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="O90" s="1" t="s">
         <v>56</v>
       </c>
       <c r="P90" s="1" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="R90" s="1" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="T90" s="1" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="91" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
+        <v>438</v>
+      </c>
+      <c r="B91" s="1" t="s">
         <v>439</v>
-      </c>
-      <c r="B91" s="1" t="s">
-        <v>440</v>
       </c>
       <c r="C91" s="1" t="s">
         <v>74</v>
@@ -6624,45 +6625,45 @@
         <v>79</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="I91" s="1" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="K91" s="1" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="L91" s="1" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="M91" s="1" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="N91" s="1" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="O91" s="1" t="s">
         <v>56</v>
       </c>
       <c r="P91" s="1" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="R91" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="T91" s="1" t="s">
         <v>442</v>
-      </c>
-      <c r="T91" s="1" t="s">
-        <v>443</v>
       </c>
     </row>
     <row r="92" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="B92" s="1" t="s">
         <v>444</v>
       </c>
-      <c r="B92" s="1" t="s">
-        <v>445</v>
-      </c>
       <c r="C92" s="1" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="D92" s="1" t="s">
         <v>65</v>
@@ -6671,45 +6672,45 @@
         <v>79</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="I92" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="K92" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="L92" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="M92" s="1" t="s">
         <v>400</v>
       </c>
-      <c r="K92" s="1" t="s">
-        <v>400</v>
-      </c>
-      <c r="L92" s="1" t="s">
-        <v>400</v>
-      </c>
-      <c r="M92" s="1" t="s">
-        <v>401</v>
-      </c>
       <c r="N92" s="1" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="O92" s="1" t="s">
         <v>56</v>
       </c>
       <c r="P92" s="1" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="Q92" s="1" t="s">
+        <v>445</v>
+      </c>
+      <c r="R92" s="1" t="s">
         <v>446</v>
       </c>
-      <c r="R92" s="1" t="s">
+      <c r="T92" s="1" t="s">
         <v>447</v>
-      </c>
-      <c r="T92" s="1" t="s">
-        <v>448</v>
       </c>
     </row>
     <row r="93" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
+        <v>448</v>
+      </c>
+      <c r="B93" s="1" t="s">
         <v>449</v>
-      </c>
-      <c r="B93" s="1" t="s">
-        <v>450</v>
       </c>
       <c r="C93" s="1" t="s">
         <v>30</v>
@@ -6721,42 +6722,42 @@
         <v>79</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="I93" s="1" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="K93" s="1" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="L93" s="1" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="M93" s="1" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="N93" s="1" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="O93" s="1" t="s">
         <v>56</v>
       </c>
       <c r="P93" s="1" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="Q93" s="1" t="s">
+        <v>451</v>
+      </c>
+      <c r="R93" s="1" t="s">
         <v>452</v>
       </c>
-      <c r="R93" s="1" t="s">
+      <c r="T93" s="1" t="s">
         <v>453</v>
-      </c>
-      <c r="T93" s="1" t="s">
-        <v>454</v>
       </c>
     </row>
     <row r="94" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="B94" s="1" t="s">
         <v>68</v>
@@ -6771,45 +6772,45 @@
         <v>79</v>
       </c>
       <c r="F94" s="1" t="s">
+        <v>454</v>
+      </c>
+      <c r="I94" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="K94" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="L94" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="M94" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="N94" s="1" t="s">
         <v>455</v>
-      </c>
-      <c r="I94" s="1" t="s">
-        <v>400</v>
-      </c>
-      <c r="K94" s="1" t="s">
-        <v>400</v>
-      </c>
-      <c r="L94" s="1" t="s">
-        <v>400</v>
-      </c>
-      <c r="M94" s="1" t="s">
-        <v>401</v>
-      </c>
-      <c r="N94" s="1" t="s">
-        <v>456</v>
       </c>
       <c r="O94" s="1" t="s">
         <v>56</v>
       </c>
       <c r="P94" s="1" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="S94" s="1" t="s">
+        <v>456</v>
+      </c>
+      <c r="T94" s="1" t="s">
         <v>457</v>
-      </c>
-      <c r="T94" s="1" t="s">
-        <v>458</v>
       </c>
     </row>
     <row r="95" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
+        <v>458</v>
+      </c>
+      <c r="B95" s="1" t="s">
         <v>459</v>
       </c>
-      <c r="B95" s="1" t="s">
+      <c r="C95" s="1" t="s">
         <v>460</v>
-      </c>
-      <c r="C95" s="1" t="s">
-        <v>461</v>
       </c>
       <c r="D95" s="1" t="s">
         <v>23</v>
@@ -6818,34 +6819,34 @@
         <v>79</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="I95" s="1" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="K95" s="1" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="L95" s="1" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="M95" s="1" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="N95" s="1" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="O95" s="1" t="s">
         <v>56</v>
       </c>
       <c r="P95" s="1" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="Q95" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="T95" s="1" t="s">
         <v>463</v>
-      </c>
-      <c r="T95" s="1" t="s">
-        <v>464</v>
       </c>
     </row>
   </sheetData>
@@ -6870,32 +6871,32 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
@@ -6905,17 +6906,17 @@
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
@@ -6925,32 +6926,32 @@
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
@@ -6960,27 +6961,27 @@
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
@@ -6990,17 +6991,17 @@
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
@@ -7010,22 +7011,22 @@
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
@@ -7035,42 +7036,42 @@
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.25">
@@ -7080,17 +7081,17 @@
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.25">
@@ -7100,22 +7101,22 @@
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.25">
@@ -7125,147 +7126,147 @@
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="54" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="56" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="59" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="60" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="61" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="62" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="63" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="64" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="66" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="67" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="68" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="69" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="70" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="71" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="72" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="73" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="74" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="75" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="76" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="77" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="78" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="79" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="80" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="81" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
   </sheetData>

--- a/config/Excel/Status.xlsx
+++ b/config/Excel/Status.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyGame\Idle-RPG\codex\config\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\AppData\Local\Temp\idle-rage-asura-20261019\stage\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33E3C268-951D-45DA-AD38-5D15206B85E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BBA10FF-E52B-40A8-9EA9-D5C5E43AB779}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3090" yWindow="2310" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -921,9 +921,6 @@
     <t>👊</t>
   </si>
   <si>
-    <t>超神進化【阿修羅霸王拳】：每隔一段時間自動發動，短暫期間內你造成的所有傷害大幅提高。</t>
-  </si>
-  <si>
     <t>sgStarfall</t>
   </si>
   <si>
@@ -1445,6 +1442,10 @@
   </si>
   <si>
     <t>超神進化【火之神樂】：雙刀亂舞每命中 1 次疊 1 層，每跳量＝單層量 × 層數（引擎以 dps 覆寫）；狀態生效期間將敵人屬性改為火屬性，結束後恢復。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>超神進化【阿修羅霸王拳】：每隔一段時間自動發動，作用期間你造成的所有傷害提高、連擊觸發率提升至 100%；連擊次數仍依目前連擊數，每擊殺 1 個敵人延長同一狀態的持續時間。</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -3400,7 +3401,7 @@
         <v>112</v>
       </c>
       <c r="B22" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="C22" t="s">
         <v>113</v>
@@ -3436,7 +3437,7 @@
         <v>1</v>
       </c>
       <c r="T22" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="23" spans="1:20" x14ac:dyDescent="0.25">
@@ -3753,10 +3754,10 @@
         <v>1</v>
       </c>
       <c r="Q29" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="S29" s="1" t="s">
         <v>382</v>
-      </c>
-      <c r="S29" s="1" t="s">
-        <v>383</v>
       </c>
       <c r="T29" t="s">
         <v>136</v>
@@ -3979,10 +3980,10 @@
         <v>1</v>
       </c>
       <c r="R34" s="1" t="s">
+        <v>428</v>
+      </c>
+      <c r="T34" s="1" t="s">
         <v>429</v>
-      </c>
-      <c r="T34" s="1" t="s">
-        <v>430</v>
       </c>
     </row>
     <row r="35" spans="1:20" x14ac:dyDescent="0.25">
@@ -4026,7 +4027,7 @@
         <v>1</v>
       </c>
       <c r="R35" s="1" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="T35" t="s">
         <v>157</v>
@@ -4120,7 +4121,7 @@
         <v>1</v>
       </c>
       <c r="S37" s="1" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="T37" t="s">
         <v>166</v>
@@ -4590,7 +4591,7 @@
         <v>1</v>
       </c>
       <c r="S47" s="1" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="T47" t="s">
         <v>205</v>
@@ -4922,7 +4923,7 @@
         <v>1</v>
       </c>
       <c r="R54" s="1" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="T54" t="s">
         <v>230</v>
@@ -5019,7 +5020,7 @@
         <v>1</v>
       </c>
       <c r="R56" s="1" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="T56" t="s">
         <v>237</v>
@@ -5427,7 +5428,7 @@
         <v>20</v>
       </c>
       <c r="T65" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="66" spans="1:20" x14ac:dyDescent="0.25">
@@ -5471,7 +5472,7 @@
         <v>1</v>
       </c>
       <c r="R66" s="1" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="T66" t="s">
         <v>273</v>
@@ -5738,18 +5739,18 @@
         <v>1</v>
       </c>
       <c r="R72" s="1" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="T72" t="s">
-        <v>295</v>
+        <v>466</v>
       </c>
     </row>
     <row r="73" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
+        <v>295</v>
+      </c>
+      <c r="B73" t="s">
         <v>296</v>
-      </c>
-      <c r="B73" t="s">
-        <v>297</v>
       </c>
       <c r="C73" t="s">
         <v>172</v>
@@ -5761,7 +5762,7 @@
         <v>79</v>
       </c>
       <c r="F73" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="G73" t="s">
         <v>31</v>
@@ -5788,15 +5789,15 @@
         <v>1</v>
       </c>
       <c r="T73" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="74" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
+        <v>298</v>
+      </c>
+      <c r="B74" t="s">
         <v>299</v>
-      </c>
-      <c r="B74" t="s">
-        <v>300</v>
       </c>
       <c r="C74" t="s">
         <v>30</v>
@@ -5808,7 +5809,7 @@
         <v>79</v>
       </c>
       <c r="F74" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="G74" t="s">
         <v>31</v>
@@ -5835,18 +5836,18 @@
         <v>1</v>
       </c>
       <c r="T74" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="75" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
+        <v>301</v>
+      </c>
+      <c r="B75" t="s">
         <v>302</v>
       </c>
-      <c r="B75" t="s">
+      <c r="C75" t="s">
         <v>303</v>
-      </c>
-      <c r="C75" t="s">
-        <v>304</v>
       </c>
       <c r="D75" t="s">
         <v>23</v>
@@ -5855,7 +5856,7 @@
         <v>79</v>
       </c>
       <c r="F75" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="G75" t="s">
         <v>177</v>
@@ -5882,18 +5883,18 @@
         <v>1</v>
       </c>
       <c r="T75" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="76" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
+        <v>304</v>
+      </c>
+      <c r="B76" t="s">
         <v>305</v>
       </c>
-      <c r="B76" t="s">
+      <c r="C76" t="s">
         <v>306</v>
-      </c>
-      <c r="C76" t="s">
-        <v>307</v>
       </c>
       <c r="D76" t="s">
         <v>23</v>
@@ -5902,7 +5903,7 @@
         <v>79</v>
       </c>
       <c r="F76" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="G76" t="s">
         <v>177</v>
@@ -5929,15 +5930,15 @@
         <v>1</v>
       </c>
       <c r="T76" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="77" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
+        <v>308</v>
+      </c>
+      <c r="B77" t="s">
         <v>309</v>
-      </c>
-      <c r="B77" t="s">
-        <v>310</v>
       </c>
       <c r="C77" t="s">
         <v>22</v>
@@ -5973,15 +5974,15 @@
         <v>1</v>
       </c>
       <c r="T77" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="78" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
+        <v>311</v>
+      </c>
+      <c r="B78" t="s">
         <v>312</v>
-      </c>
-      <c r="B78" t="s">
-        <v>313</v>
       </c>
       <c r="C78" t="s">
         <v>44</v>
@@ -6020,15 +6021,15 @@
         <v>1</v>
       </c>
       <c r="T78" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="79" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
+        <v>314</v>
+      </c>
+      <c r="B79" t="s">
         <v>315</v>
-      </c>
-      <c r="B79" t="s">
-        <v>316</v>
       </c>
       <c r="C79" t="s">
         <v>191</v>
@@ -6040,7 +6041,7 @@
         <v>79</v>
       </c>
       <c r="F79" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="G79" t="s">
         <v>31</v>
@@ -6067,18 +6068,18 @@
         <v>1</v>
       </c>
       <c r="T79" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="80" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
+        <v>317</v>
+      </c>
+      <c r="B80" t="s">
         <v>318</v>
       </c>
-      <c r="B80" t="s">
+      <c r="C80" t="s">
         <v>319</v>
-      </c>
-      <c r="C80" t="s">
-        <v>320</v>
       </c>
       <c r="D80" t="s">
         <v>65</v>
@@ -6087,7 +6088,7 @@
         <v>79</v>
       </c>
       <c r="F80" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="G80" t="s">
         <v>115</v>
@@ -6114,15 +6115,15 @@
         <v>100</v>
       </c>
       <c r="T80" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="81" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
+        <v>321</v>
+      </c>
+      <c r="B81" t="s">
         <v>322</v>
-      </c>
-      <c r="B81" t="s">
-        <v>323</v>
       </c>
       <c r="C81" t="s">
         <v>86</v>
@@ -6134,7 +6135,7 @@
         <v>79</v>
       </c>
       <c r="F81" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="G81" t="s">
         <v>115</v>
@@ -6161,18 +6162,18 @@
         <v>1</v>
       </c>
       <c r="T81" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="82" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
+        <v>324</v>
+      </c>
+      <c r="B82" t="s">
         <v>325</v>
       </c>
-      <c r="B82" t="s">
+      <c r="C82" t="s">
         <v>326</v>
-      </c>
-      <c r="C82" t="s">
-        <v>327</v>
       </c>
       <c r="D82" t="s">
         <v>23</v>
@@ -6181,7 +6182,7 @@
         <v>79</v>
       </c>
       <c r="F82" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="G82" t="s">
         <v>200</v>
@@ -6208,18 +6209,18 @@
         <v>1</v>
       </c>
       <c r="T82" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="83" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
+        <v>328</v>
+      </c>
+      <c r="B83" t="s">
         <v>329</v>
       </c>
-      <c r="B83" t="s">
+      <c r="C83" t="s">
         <v>330</v>
-      </c>
-      <c r="C83" t="s">
-        <v>331</v>
       </c>
       <c r="D83" t="s">
         <v>23</v>
@@ -6228,7 +6229,7 @@
         <v>79</v>
       </c>
       <c r="F83" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="G83" t="s">
         <v>219</v>
@@ -6255,15 +6256,15 @@
         <v>1</v>
       </c>
       <c r="T83" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="84" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="B84" s="1" t="s">
         <v>397</v>
-      </c>
-      <c r="B84" s="1" t="s">
-        <v>398</v>
       </c>
       <c r="C84" s="1" t="s">
         <v>261</v>
@@ -6275,48 +6276,48 @@
         <v>79</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="G84" s="1" t="s">
         <v>40</v>
       </c>
       <c r="I84" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="K84" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="L84" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="M84" s="1" t="s">
         <v>399</v>
       </c>
-      <c r="K84" s="1" t="s">
-        <v>399</v>
-      </c>
-      <c r="L84" s="1" t="s">
-        <v>399</v>
-      </c>
-      <c r="M84" s="1" t="s">
-        <v>400</v>
-      </c>
       <c r="N84" s="1" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="O84" s="1" t="s">
         <v>56</v>
       </c>
       <c r="P84" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="R84" s="1" t="s">
         <v>401</v>
       </c>
-      <c r="R84" s="1" t="s">
+      <c r="T84" s="1" t="s">
         <v>402</v>
-      </c>
-      <c r="T84" s="1" t="s">
-        <v>403</v>
       </c>
     </row>
     <row r="85" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
+        <v>403</v>
+      </c>
+      <c r="B85" s="1" t="s">
         <v>404</v>
       </c>
-      <c r="B85" s="1" t="s">
+      <c r="C85" s="1" t="s">
         <v>405</v>
-      </c>
-      <c r="C85" s="1" t="s">
-        <v>406</v>
       </c>
       <c r="D85" s="1" t="s">
         <v>65</v>
@@ -6325,45 +6326,45 @@
         <v>79</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="G85" s="1" t="s">
         <v>33</v>
       </c>
       <c r="I85" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="K85" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="L85" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="M85" s="1" t="s">
         <v>399</v>
       </c>
-      <c r="K85" s="1" t="s">
-        <v>399</v>
-      </c>
-      <c r="L85" s="1" t="s">
-        <v>399</v>
-      </c>
-      <c r="M85" s="1" t="s">
-        <v>400</v>
-      </c>
       <c r="N85" s="1" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="O85" s="1" t="s">
         <v>56</v>
       </c>
       <c r="P85" s="1" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="R85" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="T85" s="1" t="s">
         <v>407</v>
-      </c>
-      <c r="T85" s="1" t="s">
-        <v>408</v>
       </c>
     </row>
     <row r="86" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="B86" s="1" t="s">
         <v>409</v>
-      </c>
-      <c r="B86" s="1" t="s">
-        <v>410</v>
       </c>
       <c r="C86" s="1" t="s">
         <v>30</v>
@@ -6375,48 +6376,48 @@
         <v>79</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="G86" s="1" t="s">
         <v>31</v>
       </c>
       <c r="I86" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="K86" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="L86" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="M86" s="1" t="s">
         <v>399</v>
       </c>
-      <c r="K86" s="1" t="s">
-        <v>399</v>
-      </c>
-      <c r="L86" s="1" t="s">
-        <v>399</v>
-      </c>
-      <c r="M86" s="1" t="s">
-        <v>400</v>
-      </c>
       <c r="N86" s="1" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="O86" s="1" t="s">
         <v>56</v>
       </c>
       <c r="P86" s="1" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="R86" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="T86" s="1" t="s">
         <v>411</v>
-      </c>
-      <c r="T86" s="1" t="s">
-        <v>412</v>
       </c>
     </row>
     <row r="87" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="B87" s="1" t="s">
         <v>413</v>
       </c>
-      <c r="B87" s="1" t="s">
-        <v>414</v>
-      </c>
       <c r="C87" s="1" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D87" s="1" t="s">
         <v>65</v>
@@ -6425,48 +6426,48 @@
         <v>79</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="G87" s="1" t="s">
         <v>177</v>
       </c>
       <c r="I87" s="1" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="K87" s="1" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="L87" s="1" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="M87" s="1" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="N87" s="1" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="O87" s="1" t="s">
         <v>56</v>
       </c>
       <c r="P87" s="1" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="R87" s="1" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="T87" s="1" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
     </row>
     <row r="88" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="B88" s="1" t="s">
         <v>417</v>
       </c>
-      <c r="B88" s="1" t="s">
-        <v>418</v>
-      </c>
       <c r="C88" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="D88" s="1" t="s">
         <v>65</v>
@@ -6475,48 +6476,48 @@
         <v>79</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="G88" s="1" t="s">
         <v>177</v>
       </c>
       <c r="I88" s="1" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="K88" s="1" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="L88" s="1" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="M88" s="1" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="N88" s="1" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="O88" s="1" t="s">
         <v>56</v>
       </c>
       <c r="P88" s="1" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="R88" s="1" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="T88" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="89" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
+        <v>419</v>
+      </c>
+      <c r="B89" s="1" t="s">
         <v>420</v>
       </c>
-      <c r="B89" s="1" t="s">
+      <c r="C89" s="1" t="s">
         <v>421</v>
-      </c>
-      <c r="C89" s="1" t="s">
-        <v>422</v>
       </c>
       <c r="D89" s="1" t="s">
         <v>65</v>
@@ -6525,48 +6526,48 @@
         <v>79</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="G89" s="1" t="s">
         <v>200</v>
       </c>
       <c r="I89" s="1" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="K89" s="1" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="L89" s="1" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="M89" s="1" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="N89" s="1" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="O89" s="1" t="s">
         <v>56</v>
       </c>
       <c r="P89" s="1" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="R89" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="T89" s="1" t="s">
         <v>432</v>
-      </c>
-      <c r="T89" s="1" t="s">
-        <v>433</v>
       </c>
     </row>
     <row r="90" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="B90" s="1" t="s">
         <v>425</v>
       </c>
-      <c r="B90" s="1" t="s">
-        <v>426</v>
-      </c>
       <c r="C90" s="1" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="D90" s="1" t="s">
         <v>65</v>
@@ -6575,45 +6576,45 @@
         <v>79</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="G90" s="1" t="s">
         <v>200</v>
       </c>
       <c r="I90" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="K90" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="L90" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="M90" s="1" t="s">
         <v>399</v>
       </c>
-      <c r="K90" s="1" t="s">
-        <v>399</v>
-      </c>
-      <c r="L90" s="1" t="s">
-        <v>399</v>
-      </c>
-      <c r="M90" s="1" t="s">
-        <v>400</v>
-      </c>
       <c r="N90" s="1" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="O90" s="1" t="s">
         <v>56</v>
       </c>
       <c r="P90" s="1" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="R90" s="1" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="T90" s="1" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="91" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
+        <v>437</v>
+      </c>
+      <c r="B91" s="1" t="s">
         <v>438</v>
-      </c>
-      <c r="B91" s="1" t="s">
-        <v>439</v>
       </c>
       <c r="C91" s="1" t="s">
         <v>74</v>
@@ -6625,42 +6626,42 @@
         <v>79</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="I91" s="1" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="K91" s="1" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="L91" s="1" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="M91" s="1" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="N91" s="1" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="O91" s="1" t="s">
         <v>56</v>
       </c>
       <c r="P91" s="1" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="R91" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="T91" s="1" t="s">
         <v>441</v>
-      </c>
-      <c r="T91" s="1" t="s">
-        <v>442</v>
       </c>
     </row>
     <row r="92" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="B92" s="1" t="s">
         <v>443</v>
-      </c>
-      <c r="B92" s="1" t="s">
-        <v>444</v>
       </c>
       <c r="C92" s="1" t="s">
         <v>279</v>
@@ -6672,45 +6673,45 @@
         <v>79</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="I92" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="K92" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="L92" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="M92" s="1" t="s">
         <v>399</v>
       </c>
-      <c r="K92" s="1" t="s">
-        <v>399</v>
-      </c>
-      <c r="L92" s="1" t="s">
-        <v>399</v>
-      </c>
-      <c r="M92" s="1" t="s">
-        <v>400</v>
-      </c>
       <c r="N92" s="1" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="O92" s="1" t="s">
         <v>56</v>
       </c>
       <c r="P92" s="1" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="Q92" s="1" t="s">
+        <v>444</v>
+      </c>
+      <c r="R92" s="1" t="s">
         <v>445</v>
       </c>
-      <c r="R92" s="1" t="s">
+      <c r="T92" s="1" t="s">
         <v>446</v>
-      </c>
-      <c r="T92" s="1" t="s">
-        <v>447</v>
       </c>
     </row>
     <row r="93" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="B93" s="1" t="s">
         <v>448</v>
-      </c>
-      <c r="B93" s="1" t="s">
-        <v>449</v>
       </c>
       <c r="C93" s="1" t="s">
         <v>30</v>
@@ -6722,42 +6723,42 @@
         <v>79</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="I93" s="1" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="K93" s="1" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="L93" s="1" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="M93" s="1" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="N93" s="1" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="O93" s="1" t="s">
         <v>56</v>
       </c>
       <c r="P93" s="1" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="Q93" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="R93" s="1" t="s">
         <v>451</v>
       </c>
-      <c r="R93" s="1" t="s">
+      <c r="T93" s="1" t="s">
         <v>452</v>
-      </c>
-      <c r="T93" s="1" t="s">
-        <v>453</v>
       </c>
     </row>
     <row r="94" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="B94" s="1" t="s">
         <v>68</v>
@@ -6772,45 +6773,45 @@
         <v>79</v>
       </c>
       <c r="F94" s="1" t="s">
+        <v>453</v>
+      </c>
+      <c r="I94" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="K94" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="L94" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="M94" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="N94" s="1" t="s">
         <v>454</v>
-      </c>
-      <c r="I94" s="1" t="s">
-        <v>399</v>
-      </c>
-      <c r="K94" s="1" t="s">
-        <v>399</v>
-      </c>
-      <c r="L94" s="1" t="s">
-        <v>399</v>
-      </c>
-      <c r="M94" s="1" t="s">
-        <v>400</v>
-      </c>
-      <c r="N94" s="1" t="s">
-        <v>455</v>
       </c>
       <c r="O94" s="1" t="s">
         <v>56</v>
       </c>
       <c r="P94" s="1" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="S94" s="1" t="s">
+        <v>455</v>
+      </c>
+      <c r="T94" s="1" t="s">
         <v>456</v>
-      </c>
-      <c r="T94" s="1" t="s">
-        <v>457</v>
       </c>
     </row>
     <row r="95" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
+        <v>457</v>
+      </c>
+      <c r="B95" s="1" t="s">
         <v>458</v>
       </c>
-      <c r="B95" s="1" t="s">
+      <c r="C95" s="1" t="s">
         <v>459</v>
-      </c>
-      <c r="C95" s="1" t="s">
-        <v>460</v>
       </c>
       <c r="D95" s="1" t="s">
         <v>23</v>
@@ -6819,34 +6820,34 @@
         <v>79</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="I95" s="1" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="K95" s="1" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="L95" s="1" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="M95" s="1" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="N95" s="1" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="O95" s="1" t="s">
         <v>56</v>
       </c>
       <c r="P95" s="1" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="Q95" s="1" t="s">
+        <v>461</v>
+      </c>
+      <c r="T95" s="1" t="s">
         <v>462</v>
-      </c>
-      <c r="T95" s="1" t="s">
-        <v>463</v>
       </c>
     </row>
   </sheetData>
@@ -6871,32 +6872,32 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
@@ -6906,17 +6907,17 @@
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
@@ -6926,32 +6927,32 @@
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
@@ -6961,27 +6962,27 @@
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
@@ -6991,17 +6992,17 @@
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
@@ -7011,22 +7012,22 @@
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
@@ -7036,42 +7037,42 @@
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.25">
@@ -7081,17 +7082,17 @@
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.25">
@@ -7101,22 +7102,22 @@
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.25">
@@ -7126,147 +7127,147 @@
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="54" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="56" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="59" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="60" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="61" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="62" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="63" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="64" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="66" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="67" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="68" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="69" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="70" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="71" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="72" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="73" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="74" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="75" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="76" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="77" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="78" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="79" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="80" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="81" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
   </sheetData>

--- a/config/Excel/Status.xlsx
+++ b/config/Excel/Status.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\AppData\Local\Temp\idle-rage-asura-20261019\stage\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\AppData\Local\Temp\idle-fireamp-cap-20261019\stage\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BBA10FF-E52B-40A8-9EA9-D5C5E43AB779}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DDAA2EE-8EE3-4BFD-8950-5B98FA4038CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3090" yWindow="2310" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="999" uniqueCount="467">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1008" uniqueCount="475">
   <si>
     <t>狀態ID</t>
   </si>
@@ -543,9 +543,6 @@
     <t>火焰增幅</t>
   </si>
   <si>
-    <t>新版技能【火焰增幅】：火屬性傷害提升（層數由引擎累加成單一數值，故用後蓋前並重置時間）。</t>
-  </si>
-  <si>
     <t>sgFirehunt</t>
   </si>
   <si>
@@ -934,9 +931,6 @@
   </si>
   <si>
     <t>爆燃</t>
-  </si>
-  <si>
-    <t>傳奇特效【爆燃】：火龍捲每造成 1 段傷害就疊 1 層，使該敵人受到的燃燒傷害提高（效果值＝目前的總提高%）。設計文檔未設層數上限，因此比照【火焰增幅】由引擎累加成單一數值後「後蓋前」，不使用狀態表的疊層規則。</t>
   </si>
   <si>
     <t>sgPetrify</t>
@@ -1446,6 +1440,46 @@
   </si>
   <si>
     <t>超神進化【阿修羅霸王拳】：每隔一段時間自動發動，作用期間你造成的所有傷害提高、連擊觸發率提升至 100%；連擊次數仍依目前連擊數，每擊殺 1 個敵人延長同一狀態的持續時間。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>stack</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>新版技能【火焰增幅】：範圍內每次燃燒作用疊一層火屬性傷害提升，最多 50 層，每次觸發重置時間；與傳奇烈火狩各自計算層數。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>傳奇特效【爆燃】：火龍捲每造成 1 段傷害就疊 1 層，使該敵人受到的燃燒傷害提高（效果值＝目前的總提高%）。設計文檔未設層數上限，因此由引擎累加成單一數值後「後蓋前」，不使用狀態表的疊層規則。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>sgFirehuntAmp</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>烈火狩</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>🔥</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>buff</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>stat</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>fire</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>傳奇【烈火狩】：火狩持續期間按節拍疊加火屬性傷害提升，最多 50 層，滿層只刷新時間；火狩全部消失後到期，與火焰增幅各自計算層數。</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -2424,7 +2458,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:T95"/>
+  <dimension ref="A1:T96"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="18" max="18" width="12.375" customWidth="1"/>
@@ -3401,7 +3435,7 @@
         <v>112</v>
       </c>
       <c r="B22" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="C22" t="s">
         <v>113</v>
@@ -3437,7 +3471,7 @@
         <v>1</v>
       </c>
       <c r="T22" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
     </row>
     <row r="23" spans="1:20" x14ac:dyDescent="0.25">
@@ -3754,10 +3788,10 @@
         <v>1</v>
       </c>
       <c r="Q29" s="1" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="S29" s="1" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="T29" t="s">
         <v>136</v>
@@ -3980,10 +4014,10 @@
         <v>1</v>
       </c>
       <c r="R34" s="1" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="T34" s="1" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
     </row>
     <row r="35" spans="1:20" x14ac:dyDescent="0.25">
@@ -4027,7 +4061,7 @@
         <v>1</v>
       </c>
       <c r="R35" s="1" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="T35" t="s">
         <v>157</v>
@@ -4121,7 +4155,7 @@
         <v>1</v>
       </c>
       <c r="S37" s="1" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="T37" t="s">
         <v>166</v>
@@ -4165,24 +4199,24 @@
         <v>0</v>
       </c>
       <c r="O38" t="s">
-        <v>56</v>
+        <v>465</v>
       </c>
       <c r="P38">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="T38" t="s">
-        <v>169</v>
+        <v>466</v>
       </c>
     </row>
     <row r="39" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
+        <v>169</v>
+      </c>
+      <c r="B39" t="s">
         <v>170</v>
       </c>
-      <c r="B39" t="s">
+      <c r="C39" t="s">
         <v>171</v>
-      </c>
-      <c r="C39" t="s">
-        <v>172</v>
       </c>
       <c r="D39" t="s">
         <v>65</v>
@@ -4191,7 +4225,7 @@
         <v>79</v>
       </c>
       <c r="F39" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="G39" t="s">
         <v>31</v>
@@ -4218,18 +4252,18 @@
         <v>1</v>
       </c>
       <c r="T39" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="40" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
+        <v>173</v>
+      </c>
+      <c r="B40" t="s">
         <v>174</v>
       </c>
-      <c r="B40" t="s">
+      <c r="C40" t="s">
         <v>175</v>
-      </c>
-      <c r="C40" t="s">
-        <v>176</v>
       </c>
       <c r="D40" t="s">
         <v>65</v>
@@ -4238,10 +4272,10 @@
         <v>79</v>
       </c>
       <c r="F40" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="G40" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I40">
         <v>0</v>
@@ -4265,18 +4299,18 @@
         <v>1</v>
       </c>
       <c r="T40" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="41" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
+        <v>178</v>
+      </c>
+      <c r="B41" t="s">
         <v>179</v>
       </c>
-      <c r="B41" t="s">
-        <v>180</v>
-      </c>
       <c r="C41" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D41" t="s">
         <v>65</v>
@@ -4285,7 +4319,7 @@
         <v>79</v>
       </c>
       <c r="F41" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="I41">
         <v>0</v>
@@ -4309,18 +4343,18 @@
         <v>1</v>
       </c>
       <c r="T41" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="42" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
+        <v>181</v>
+      </c>
+      <c r="B42" t="s">
         <v>182</v>
       </c>
-      <c r="B42" t="s">
+      <c r="C42" t="s">
         <v>183</v>
-      </c>
-      <c r="C42" t="s">
-        <v>184</v>
       </c>
       <c r="D42" t="s">
         <v>23</v>
@@ -4329,10 +4363,10 @@
         <v>79</v>
       </c>
       <c r="F42" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G42" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I42">
         <v>0</v>
@@ -4356,15 +4390,15 @@
         <v>1</v>
       </c>
       <c r="T42" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="43" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
+        <v>185</v>
+      </c>
+      <c r="B43" t="s">
         <v>186</v>
-      </c>
-      <c r="B43" t="s">
-        <v>187</v>
       </c>
       <c r="C43" t="s">
         <v>35</v>
@@ -4403,18 +4437,18 @@
         <v>1</v>
       </c>
       <c r="T43" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="44" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
+        <v>188</v>
+      </c>
+      <c r="B44" t="s">
         <v>189</v>
       </c>
-      <c r="B44" t="s">
+      <c r="C44" t="s">
         <v>190</v>
-      </c>
-      <c r="C44" t="s">
-        <v>191</v>
       </c>
       <c r="D44" t="s">
         <v>23</v>
@@ -4450,18 +4484,18 @@
         <v>1</v>
       </c>
       <c r="T44" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="45" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
+        <v>192</v>
+      </c>
+      <c r="B45" t="s">
         <v>193</v>
       </c>
-      <c r="B45" t="s">
+      <c r="C45" t="s">
         <v>194</v>
-      </c>
-      <c r="C45" t="s">
-        <v>195</v>
       </c>
       <c r="D45" t="s">
         <v>65</v>
@@ -4470,7 +4504,7 @@
         <v>79</v>
       </c>
       <c r="F45" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="G45" t="s">
         <v>115</v>
@@ -4497,18 +4531,18 @@
         <v>1</v>
       </c>
       <c r="T45" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="46" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
+        <v>196</v>
+      </c>
+      <c r="B46" t="s">
         <v>197</v>
       </c>
-      <c r="B46" t="s">
+      <c r="C46" t="s">
         <v>198</v>
-      </c>
-      <c r="C46" t="s">
-        <v>199</v>
       </c>
       <c r="D46" t="s">
         <v>23</v>
@@ -4517,10 +4551,10 @@
         <v>79</v>
       </c>
       <c r="F46" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="G46" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="I46">
         <v>0</v>
@@ -4544,18 +4578,18 @@
         <v>5</v>
       </c>
       <c r="T46" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="47" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
+        <v>201</v>
+      </c>
+      <c r="B47" t="s">
         <v>202</v>
       </c>
-      <c r="B47" t="s">
+      <c r="C47" t="s">
         <v>203</v>
-      </c>
-      <c r="C47" t="s">
-        <v>204</v>
       </c>
       <c r="D47" t="s">
         <v>23</v>
@@ -4564,7 +4598,7 @@
         <v>24</v>
       </c>
       <c r="G47" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="H47" t="s">
         <v>25</v>
@@ -4591,21 +4625,21 @@
         <v>1</v>
       </c>
       <c r="S47" s="1" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="T47" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="48" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
+        <v>205</v>
+      </c>
+      <c r="B48" t="s">
         <v>206</v>
       </c>
-      <c r="B48" t="s">
+      <c r="C48" t="s">
         <v>207</v>
-      </c>
-      <c r="C48" t="s">
-        <v>208</v>
       </c>
       <c r="D48" t="s">
         <v>23</v>
@@ -4614,10 +4648,10 @@
         <v>79</v>
       </c>
       <c r="F48" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="G48" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="I48">
         <v>0</v>
@@ -4641,18 +4675,18 @@
         <v>1</v>
       </c>
       <c r="T48" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="49" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
+        <v>209</v>
+      </c>
+      <c r="B49" t="s">
         <v>210</v>
       </c>
-      <c r="B49" t="s">
+      <c r="C49" t="s">
         <v>211</v>
-      </c>
-      <c r="C49" t="s">
-        <v>212</v>
       </c>
       <c r="D49" t="s">
         <v>23</v>
@@ -4661,10 +4695,10 @@
         <v>79</v>
       </c>
       <c r="F49" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="G49" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="I49">
         <v>0</v>
@@ -4688,18 +4722,18 @@
         <v>1</v>
       </c>
       <c r="T49" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="50" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
+        <v>213</v>
+      </c>
+      <c r="B50" t="s">
         <v>214</v>
       </c>
-      <c r="B50" t="s">
-        <v>215</v>
-      </c>
       <c r="C50" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D50" t="s">
         <v>65</v>
@@ -4708,10 +4742,10 @@
         <v>79</v>
       </c>
       <c r="F50" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="G50" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="I50">
         <v>0</v>
@@ -4735,15 +4769,15 @@
         <v>1</v>
       </c>
       <c r="T50" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="51" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
+        <v>216</v>
+      </c>
+      <c r="B51" t="s">
         <v>217</v>
-      </c>
-      <c r="B51" t="s">
-        <v>218</v>
       </c>
       <c r="C51" t="s">
         <v>114</v>
@@ -4755,10 +4789,10 @@
         <v>79</v>
       </c>
       <c r="F51" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="G51" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I51">
         <v>0</v>
@@ -4782,15 +4816,15 @@
         <v>6</v>
       </c>
       <c r="T51" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="52" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
+        <v>220</v>
+      </c>
+      <c r="B52" t="s">
         <v>221</v>
-      </c>
-      <c r="B52" t="s">
-        <v>222</v>
       </c>
       <c r="C52" t="s">
         <v>114</v>
@@ -4802,7 +4836,7 @@
         <v>24</v>
       </c>
       <c r="G52" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H52" t="s">
         <v>25</v>
@@ -4829,18 +4863,18 @@
         <v>1</v>
       </c>
       <c r="T52" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="53" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
+        <v>223</v>
+      </c>
+      <c r="B53" t="s">
         <v>224</v>
       </c>
-      <c r="B53" t="s">
+      <c r="C53" t="s">
         <v>225</v>
-      </c>
-      <c r="C53" t="s">
-        <v>226</v>
       </c>
       <c r="D53" t="s">
         <v>23</v>
@@ -4849,10 +4883,10 @@
         <v>79</v>
       </c>
       <c r="F53" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="G53" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I53">
         <v>0</v>
@@ -4876,15 +4910,15 @@
         <v>1</v>
       </c>
       <c r="T53" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="54" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
+        <v>227</v>
+      </c>
+      <c r="B54" t="s">
         <v>228</v>
-      </c>
-      <c r="B54" t="s">
-        <v>229</v>
       </c>
       <c r="C54" t="s">
         <v>153</v>
@@ -4896,10 +4930,10 @@
         <v>79</v>
       </c>
       <c r="F54" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="G54" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I54">
         <v>0</v>
@@ -4923,18 +4957,18 @@
         <v>1</v>
       </c>
       <c r="R54" s="1" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="T54" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="55" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
+        <v>230</v>
+      </c>
+      <c r="B55" t="s">
         <v>231</v>
-      </c>
-      <c r="B55" t="s">
-        <v>232</v>
       </c>
       <c r="C55" t="s">
         <v>90</v>
@@ -4946,10 +4980,10 @@
         <v>79</v>
       </c>
       <c r="F55" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="G55" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I55">
         <v>0</v>
@@ -4973,18 +5007,18 @@
         <v>1</v>
       </c>
       <c r="T55" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="56" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
+        <v>233</v>
+      </c>
+      <c r="B56" t="s">
         <v>234</v>
       </c>
-      <c r="B56" t="s">
+      <c r="C56" t="s">
         <v>235</v>
-      </c>
-      <c r="C56" t="s">
-        <v>236</v>
       </c>
       <c r="D56" t="s">
         <v>65</v>
@@ -4993,10 +5027,10 @@
         <v>79</v>
       </c>
       <c r="F56" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="G56" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I56">
         <v>0</v>
@@ -5020,18 +5054,18 @@
         <v>1</v>
       </c>
       <c r="R56" s="1" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="T56" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="57" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
+        <v>237</v>
+      </c>
+      <c r="B57" t="s">
         <v>238</v>
-      </c>
-      <c r="B57" t="s">
-        <v>239</v>
       </c>
       <c r="C57" t="s">
         <v>39</v>
@@ -5043,7 +5077,7 @@
         <v>79</v>
       </c>
       <c r="F57" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="I57">
         <v>0</v>
@@ -5067,18 +5101,18 @@
         <v>10</v>
       </c>
       <c r="T57" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="58" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
+        <v>240</v>
+      </c>
+      <c r="B58" t="s">
         <v>241</v>
       </c>
-      <c r="B58" t="s">
+      <c r="C58" t="s">
         <v>242</v>
-      </c>
-      <c r="C58" t="s">
-        <v>243</v>
       </c>
       <c r="D58" t="s">
         <v>23</v>
@@ -5087,7 +5121,7 @@
         <v>79</v>
       </c>
       <c r="F58" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="G58" t="s">
         <v>40</v>
@@ -5114,15 +5148,15 @@
         <v>100</v>
       </c>
       <c r="T58" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="59" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
+        <v>244</v>
+      </c>
+      <c r="B59" t="s">
         <v>245</v>
-      </c>
-      <c r="B59" t="s">
-        <v>246</v>
       </c>
       <c r="C59" t="s">
         <v>22</v>
@@ -5158,18 +5192,18 @@
         <v>1</v>
       </c>
       <c r="T59" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="60" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
+        <v>247</v>
+      </c>
+      <c r="B60" t="s">
         <v>248</v>
       </c>
-      <c r="B60" t="s">
+      <c r="C60" t="s">
         <v>249</v>
-      </c>
-      <c r="C60" t="s">
-        <v>250</v>
       </c>
       <c r="D60" t="s">
         <v>65</v>
@@ -5178,7 +5212,7 @@
         <v>79</v>
       </c>
       <c r="F60" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="I60">
         <v>0</v>
@@ -5202,15 +5236,15 @@
         <v>1</v>
       </c>
       <c r="T60" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="61" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
+        <v>251</v>
+      </c>
+      <c r="B61" t="s">
         <v>252</v>
-      </c>
-      <c r="B61" t="s">
-        <v>253</v>
       </c>
       <c r="C61" t="s">
         <v>35</v>
@@ -5222,7 +5256,7 @@
         <v>79</v>
       </c>
       <c r="F61" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="I61">
         <v>0</v>
@@ -5246,18 +5280,18 @@
         <v>20</v>
       </c>
       <c r="T61" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="62" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
+        <v>254</v>
+      </c>
+      <c r="B62" t="s">
         <v>255</v>
       </c>
-      <c r="B62" t="s">
+      <c r="C62" t="s">
         <v>256</v>
-      </c>
-      <c r="C62" t="s">
-        <v>257</v>
       </c>
       <c r="D62" t="s">
         <v>65</v>
@@ -5266,7 +5300,7 @@
         <v>79</v>
       </c>
       <c r="F62" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="I62">
         <v>0</v>
@@ -5290,18 +5324,18 @@
         <v>1</v>
       </c>
       <c r="T62" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="63" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
+        <v>258</v>
+      </c>
+      <c r="B63" t="s">
         <v>259</v>
       </c>
-      <c r="B63" t="s">
+      <c r="C63" t="s">
         <v>260</v>
-      </c>
-      <c r="C63" t="s">
-        <v>261</v>
       </c>
       <c r="D63" t="s">
         <v>65</v>
@@ -5310,7 +5344,7 @@
         <v>79</v>
       </c>
       <c r="F63" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="I63">
         <v>0</v>
@@ -5334,18 +5368,18 @@
         <v>100</v>
       </c>
       <c r="T63" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="64" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
+        <v>262</v>
+      </c>
+      <c r="B64" t="s">
         <v>263</v>
       </c>
-      <c r="B64" t="s">
+      <c r="C64" t="s">
         <v>264</v>
-      </c>
-      <c r="C64" t="s">
-        <v>265</v>
       </c>
       <c r="D64" t="s">
         <v>23</v>
@@ -5381,18 +5415,18 @@
         <v>10</v>
       </c>
       <c r="T64" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="65" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
+        <v>266</v>
+      </c>
+      <c r="B65" t="s">
         <v>267</v>
       </c>
-      <c r="B65" t="s">
+      <c r="C65" t="s">
         <v>268</v>
-      </c>
-      <c r="C65" t="s">
-        <v>269</v>
       </c>
       <c r="D65" t="s">
         <v>23</v>
@@ -5428,18 +5462,18 @@
         <v>20</v>
       </c>
       <c r="T65" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
     </row>
     <row r="66" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
+        <v>269</v>
+      </c>
+      <c r="B66" t="s">
         <v>270</v>
       </c>
-      <c r="B66" t="s">
+      <c r="C66" t="s">
         <v>271</v>
-      </c>
-      <c r="C66" t="s">
-        <v>272</v>
       </c>
       <c r="D66" t="s">
         <v>65</v>
@@ -5448,7 +5482,7 @@
         <v>79</v>
       </c>
       <c r="F66" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="I66">
         <v>0</v>
@@ -5472,21 +5506,21 @@
         <v>1</v>
       </c>
       <c r="R66" s="1" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="T66" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="67" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
+        <v>273</v>
+      </c>
+      <c r="B67" t="s">
         <v>274</v>
       </c>
-      <c r="B67" t="s">
-        <v>275</v>
-      </c>
       <c r="C67" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="D67" t="s">
         <v>23</v>
@@ -5495,7 +5529,7 @@
         <v>79</v>
       </c>
       <c r="F67" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="I67">
         <v>0</v>
@@ -5519,18 +5553,18 @@
         <v>1</v>
       </c>
       <c r="T67" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="68" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
+        <v>276</v>
+      </c>
+      <c r="B68" t="s">
         <v>277</v>
       </c>
-      <c r="B68" t="s">
+      <c r="C68" t="s">
         <v>278</v>
-      </c>
-      <c r="C68" t="s">
-        <v>279</v>
       </c>
       <c r="D68" t="s">
         <v>65</v>
@@ -5539,7 +5573,7 @@
         <v>79</v>
       </c>
       <c r="F68" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="I68">
         <v>0</v>
@@ -5563,15 +5597,15 @@
         <v>1</v>
       </c>
       <c r="T68" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="69" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
+        <v>280</v>
+      </c>
+      <c r="B69" t="s">
         <v>281</v>
-      </c>
-      <c r="B69" t="s">
-        <v>282</v>
       </c>
       <c r="C69" t="s">
         <v>22</v>
@@ -5583,7 +5617,7 @@
         <v>79</v>
       </c>
       <c r="F69" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="I69">
         <v>0</v>
@@ -5607,18 +5641,18 @@
         <v>50</v>
       </c>
       <c r="T69" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="70" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
+        <v>283</v>
+      </c>
+      <c r="B70" t="s">
         <v>284</v>
       </c>
-      <c r="B70" t="s">
+      <c r="C70" t="s">
         <v>285</v>
-      </c>
-      <c r="C70" t="s">
-        <v>286</v>
       </c>
       <c r="D70" t="s">
         <v>65</v>
@@ -5627,7 +5661,7 @@
         <v>79</v>
       </c>
       <c r="F70" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="I70">
         <v>0</v>
@@ -5651,18 +5685,18 @@
         <v>10</v>
       </c>
       <c r="T70" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="71" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
+        <v>287</v>
+      </c>
+      <c r="B71" t="s">
         <v>288</v>
       </c>
-      <c r="B71" t="s">
+      <c r="C71" t="s">
         <v>289</v>
-      </c>
-      <c r="C71" t="s">
-        <v>290</v>
       </c>
       <c r="D71" t="s">
         <v>65</v>
@@ -5671,7 +5705,7 @@
         <v>79</v>
       </c>
       <c r="F71" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="I71">
         <v>0</v>
@@ -5695,18 +5729,18 @@
         <v>100</v>
       </c>
       <c r="T71" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="72" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
+        <v>291</v>
+      </c>
+      <c r="B72" t="s">
         <v>292</v>
       </c>
-      <c r="B72" t="s">
+      <c r="C72" t="s">
         <v>293</v>
-      </c>
-      <c r="C72" t="s">
-        <v>294</v>
       </c>
       <c r="D72" t="s">
         <v>65</v>
@@ -5715,7 +5749,7 @@
         <v>79</v>
       </c>
       <c r="F72" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="I72">
         <v>0</v>
@@ -5739,21 +5773,21 @@
         <v>1</v>
       </c>
       <c r="R72" s="1" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="T72" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
     </row>
     <row r="73" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
+        <v>294</v>
+      </c>
+      <c r="B73" t="s">
         <v>295</v>
       </c>
-      <c r="B73" t="s">
-        <v>296</v>
-      </c>
       <c r="C73" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D73" t="s">
         <v>65</v>
@@ -5762,7 +5796,7 @@
         <v>79</v>
       </c>
       <c r="F73" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="G73" t="s">
         <v>31</v>
@@ -5789,15 +5823,15 @@
         <v>1</v>
       </c>
       <c r="T73" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="74" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
+        <v>297</v>
+      </c>
+      <c r="B74" t="s">
         <v>298</v>
-      </c>
-      <c r="B74" t="s">
-        <v>299</v>
       </c>
       <c r="C74" t="s">
         <v>30</v>
@@ -5809,7 +5843,7 @@
         <v>79</v>
       </c>
       <c r="F74" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="G74" t="s">
         <v>31</v>
@@ -5836,18 +5870,18 @@
         <v>1</v>
       </c>
       <c r="T74" t="s">
-        <v>300</v>
+        <v>467</v>
       </c>
     </row>
     <row r="75" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
+        <v>299</v>
+      </c>
+      <c r="B75" t="s">
+        <v>300</v>
+      </c>
+      <c r="C75" t="s">
         <v>301</v>
-      </c>
-      <c r="B75" t="s">
-        <v>302</v>
-      </c>
-      <c r="C75" t="s">
-        <v>303</v>
       </c>
       <c r="D75" t="s">
         <v>23</v>
@@ -5856,10 +5890,10 @@
         <v>79</v>
       </c>
       <c r="F75" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="G75" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I75">
         <v>0</v>
@@ -5883,18 +5917,18 @@
         <v>1</v>
       </c>
       <c r="T75" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
     </row>
     <row r="76" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
+        <v>302</v>
+      </c>
+      <c r="B76" t="s">
+        <v>303</v>
+      </c>
+      <c r="C76" t="s">
         <v>304</v>
-      </c>
-      <c r="B76" t="s">
-        <v>305</v>
-      </c>
-      <c r="C76" t="s">
-        <v>306</v>
       </c>
       <c r="D76" t="s">
         <v>23</v>
@@ -5903,10 +5937,10 @@
         <v>79</v>
       </c>
       <c r="F76" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="G76" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I76">
         <v>0</v>
@@ -5930,15 +5964,15 @@
         <v>1</v>
       </c>
       <c r="T76" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
     </row>
     <row r="77" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="B77" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="C77" t="s">
         <v>22</v>
@@ -5974,15 +6008,15 @@
         <v>1</v>
       </c>
       <c r="T77" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
     </row>
     <row r="78" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="B78" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="C78" t="s">
         <v>44</v>
@@ -6021,18 +6055,18 @@
         <v>1</v>
       </c>
       <c r="T78" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
     </row>
     <row r="79" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="B79" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="C79" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D79" t="s">
         <v>23</v>
@@ -6041,7 +6075,7 @@
         <v>79</v>
       </c>
       <c r="F79" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="G79" t="s">
         <v>31</v>
@@ -6068,18 +6102,18 @@
         <v>1</v>
       </c>
       <c r="T79" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
     </row>
     <row r="80" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
+        <v>315</v>
+      </c>
+      <c r="B80" t="s">
+        <v>316</v>
+      </c>
+      <c r="C80" t="s">
         <v>317</v>
-      </c>
-      <c r="B80" t="s">
-        <v>318</v>
-      </c>
-      <c r="C80" t="s">
-        <v>319</v>
       </c>
       <c r="D80" t="s">
         <v>65</v>
@@ -6088,7 +6122,7 @@
         <v>79</v>
       </c>
       <c r="F80" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="G80" t="s">
         <v>115</v>
@@ -6115,15 +6149,15 @@
         <v>100</v>
       </c>
       <c r="T80" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
     </row>
     <row r="81" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="B81" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="C81" t="s">
         <v>86</v>
@@ -6135,7 +6169,7 @@
         <v>79</v>
       </c>
       <c r="F81" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="G81" t="s">
         <v>115</v>
@@ -6162,18 +6196,18 @@
         <v>1</v>
       </c>
       <c r="T81" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
     </row>
     <row r="82" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
+        <v>322</v>
+      </c>
+      <c r="B82" t="s">
+        <v>323</v>
+      </c>
+      <c r="C82" t="s">
         <v>324</v>
-      </c>
-      <c r="B82" t="s">
-        <v>325</v>
-      </c>
-      <c r="C82" t="s">
-        <v>326</v>
       </c>
       <c r="D82" t="s">
         <v>23</v>
@@ -6182,10 +6216,10 @@
         <v>79</v>
       </c>
       <c r="F82" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="G82" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="I82">
         <v>0</v>
@@ -6209,18 +6243,18 @@
         <v>1</v>
       </c>
       <c r="T82" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
     </row>
     <row r="83" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
+        <v>326</v>
+      </c>
+      <c r="B83" t="s">
+        <v>327</v>
+      </c>
+      <c r="C83" t="s">
         <v>328</v>
-      </c>
-      <c r="B83" t="s">
-        <v>329</v>
-      </c>
-      <c r="C83" t="s">
-        <v>330</v>
       </c>
       <c r="D83" t="s">
         <v>23</v>
@@ -6229,10 +6263,10 @@
         <v>79</v>
       </c>
       <c r="F83" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="G83" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I83">
         <v>0</v>
@@ -6256,18 +6290,18 @@
         <v>1</v>
       </c>
       <c r="T83" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
     </row>
     <row r="84" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D84" s="1" t="s">
         <v>65</v>
@@ -6276,48 +6310,48 @@
         <v>79</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="G84" s="1" t="s">
         <v>40</v>
       </c>
       <c r="I84" s="1" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="K84" s="1" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="L84" s="1" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="M84" s="1" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="N84" s="1" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="O84" s="1" t="s">
         <v>56</v>
       </c>
       <c r="P84" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="R84" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="T84" s="1" t="s">
         <v>400</v>
-      </c>
-      <c r="R84" s="1" t="s">
-        <v>401</v>
-      </c>
-      <c r="T84" s="1" t="s">
-        <v>402</v>
       </c>
     </row>
     <row r="85" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
+        <v>401</v>
+      </c>
+      <c r="B85" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="C85" s="1" t="s">
         <v>403</v>
-      </c>
-      <c r="B85" s="1" t="s">
-        <v>404</v>
-      </c>
-      <c r="C85" s="1" t="s">
-        <v>405</v>
       </c>
       <c r="D85" s="1" t="s">
         <v>65</v>
@@ -6326,45 +6360,45 @@
         <v>79</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="G85" s="1" t="s">
         <v>33</v>
       </c>
       <c r="I85" s="1" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="K85" s="1" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="L85" s="1" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="M85" s="1" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="N85" s="1" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="O85" s="1" t="s">
         <v>56</v>
       </c>
       <c r="P85" s="1" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="R85" s="1" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="T85" s="1" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
     </row>
     <row r="86" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="C86" s="1" t="s">
         <v>30</v>
@@ -6376,48 +6410,48 @@
         <v>79</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="G86" s="1" t="s">
         <v>31</v>
       </c>
       <c r="I86" s="1" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="K86" s="1" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="L86" s="1" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="M86" s="1" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="N86" s="1" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="O86" s="1" t="s">
         <v>56</v>
       </c>
       <c r="P86" s="1" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="R86" s="1" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="T86" s="1" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
     </row>
     <row r="87" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="D87" s="1" t="s">
         <v>65</v>
@@ -6426,48 +6460,48 @@
         <v>79</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="G87" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I87" s="1" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="K87" s="1" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="L87" s="1" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="M87" s="1" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="N87" s="1" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="O87" s="1" t="s">
         <v>56</v>
       </c>
       <c r="P87" s="1" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="R87" s="1" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="T87" s="1" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
     </row>
     <row r="88" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="D88" s="1" t="s">
         <v>65</v>
@@ -6476,48 +6510,48 @@
         <v>79</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="G88" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I88" s="1" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="K88" s="1" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="L88" s="1" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="M88" s="1" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="N88" s="1" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="O88" s="1" t="s">
         <v>56</v>
       </c>
       <c r="P88" s="1" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="R88" s="1" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="T88" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
     </row>
     <row r="89" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="B89" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="C89" s="1" t="s">
         <v>419</v>
-      </c>
-      <c r="B89" s="1" t="s">
-        <v>420</v>
-      </c>
-      <c r="C89" s="1" t="s">
-        <v>421</v>
       </c>
       <c r="D89" s="1" t="s">
         <v>65</v>
@@ -6526,48 +6560,48 @@
         <v>79</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="G89" s="1" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="I89" s="1" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="K89" s="1" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="L89" s="1" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="M89" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="N89" s="1" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="O89" s="1" t="s">
         <v>56</v>
       </c>
       <c r="P89" s="1" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="R89" s="1" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="T89" s="1" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
     </row>
     <row r="90" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="D90" s="1" t="s">
         <v>65</v>
@@ -6576,45 +6610,45 @@
         <v>79</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="G90" s="1" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="I90" s="1" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="K90" s="1" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="L90" s="1" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="M90" s="1" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="N90" s="1" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="O90" s="1" t="s">
         <v>56</v>
       </c>
       <c r="P90" s="1" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="R90" s="1" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="T90" s="1" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
     </row>
     <row r="91" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="C91" s="1" t="s">
         <v>74</v>
@@ -6626,45 +6660,45 @@
         <v>79</v>
       </c>
       <c r="F91" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="I91" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="K91" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="L91" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="M91" s="1" t="s">
         <v>437</v>
       </c>
-      <c r="I91" s="1" t="s">
-        <v>398</v>
-      </c>
-      <c r="K91" s="1" t="s">
-        <v>398</v>
-      </c>
-      <c r="L91" s="1" t="s">
-        <v>398</v>
-      </c>
-      <c r="M91" s="1" t="s">
-        <v>439</v>
-      </c>
       <c r="N91" s="1" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="O91" s="1" t="s">
         <v>56</v>
       </c>
       <c r="P91" s="1" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="R91" s="1" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="T91" s="1" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="92" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D92" s="1" t="s">
         <v>65</v>
@@ -6673,45 +6707,45 @@
         <v>79</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="I92" s="1" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="K92" s="1" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="L92" s="1" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="M92" s="1" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="N92" s="1" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="O92" s="1" t="s">
         <v>56</v>
       </c>
       <c r="P92" s="1" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="Q92" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="R92" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="T92" s="1" t="s">
         <v>444</v>
-      </c>
-      <c r="R92" s="1" t="s">
-        <v>445</v>
-      </c>
-      <c r="T92" s="1" t="s">
-        <v>446</v>
       </c>
     </row>
     <row r="93" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="C93" s="1" t="s">
         <v>30</v>
@@ -6723,42 +6757,42 @@
         <v>79</v>
       </c>
       <c r="F93" s="1" t="s">
+        <v>445</v>
+      </c>
+      <c r="I93" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="K93" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="L93" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="M93" s="1" t="s">
         <v>447</v>
       </c>
-      <c r="I93" s="1" t="s">
-        <v>398</v>
-      </c>
-      <c r="K93" s="1" t="s">
-        <v>398</v>
-      </c>
-      <c r="L93" s="1" t="s">
-        <v>398</v>
-      </c>
-      <c r="M93" s="1" t="s">
-        <v>449</v>
-      </c>
       <c r="N93" s="1" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="O93" s="1" t="s">
         <v>56</v>
       </c>
       <c r="P93" s="1" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="Q93" s="1" t="s">
+        <v>448</v>
+      </c>
+      <c r="R93" s="1" t="s">
+        <v>449</v>
+      </c>
+      <c r="T93" s="1" t="s">
         <v>450</v>
-      </c>
-      <c r="R93" s="1" t="s">
-        <v>451</v>
-      </c>
-      <c r="T93" s="1" t="s">
-        <v>452</v>
       </c>
     </row>
     <row r="94" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B94" s="1" t="s">
         <v>68</v>
@@ -6773,45 +6807,45 @@
         <v>79</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="I94" s="1" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="K94" s="1" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="L94" s="1" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="M94" s="1" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="N94" s="1" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="O94" s="1" t="s">
         <v>56</v>
       </c>
       <c r="P94" s="1" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="S94" s="1" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="T94" s="1" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
     </row>
     <row r="95" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
+        <v>455</v>
+      </c>
+      <c r="B95" s="1" t="s">
+        <v>456</v>
+      </c>
+      <c r="C95" s="1" t="s">
         <v>457</v>
-      </c>
-      <c r="B95" s="1" t="s">
-        <v>458</v>
-      </c>
-      <c r="C95" s="1" t="s">
-        <v>459</v>
       </c>
       <c r="D95" s="1" t="s">
         <v>23</v>
@@ -6820,34 +6854,81 @@
         <v>79</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="I95" s="1" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="K95" s="1" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="L95" s="1" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="M95" s="1" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="N95" s="1" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="O95" s="1" t="s">
         <v>56</v>
       </c>
       <c r="P95" s="1" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="Q95" s="1" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="T95" s="1" t="s">
-        <v>462</v>
+        <v>460</v>
+      </c>
+    </row>
+    <row r="96" spans="1:20" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>468</v>
+      </c>
+      <c r="B96" t="s">
+        <v>469</v>
+      </c>
+      <c r="C96" t="s">
+        <v>470</v>
+      </c>
+      <c r="D96" t="s">
+        <v>471</v>
+      </c>
+      <c r="E96" t="s">
+        <v>472</v>
+      </c>
+      <c r="F96" t="s">
+        <v>468</v>
+      </c>
+      <c r="G96" t="s">
+        <v>473</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="K96">
+        <v>0</v>
+      </c>
+      <c r="L96">
+        <v>2</v>
+      </c>
+      <c r="M96">
+        <v>1</v>
+      </c>
+      <c r="N96">
+        <v>0</v>
+      </c>
+      <c r="O96" t="s">
+        <v>465</v>
+      </c>
+      <c r="P96">
+        <v>50</v>
+      </c>
+      <c r="T96" t="s">
+        <v>474</v>
       </c>
     </row>
   </sheetData>
@@ -6872,32 +6953,32 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
@@ -6907,17 +6988,17 @@
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
@@ -6927,32 +7008,32 @@
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
@@ -6962,27 +7043,27 @@
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
@@ -6992,17 +7073,17 @@
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
@@ -7012,22 +7093,22 @@
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
@@ -7037,42 +7118,42 @@
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.25">
@@ -7082,17 +7163,17 @@
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.25">
@@ -7102,22 +7183,22 @@
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.25">
@@ -7127,147 +7208,147 @@
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
     </row>
     <row r="54" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
     </row>
     <row r="56" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="59" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="60" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
     </row>
     <row r="61" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
     </row>
     <row r="62" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
     </row>
     <row r="63" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
     </row>
     <row r="64" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
     </row>
     <row r="66" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
     </row>
     <row r="67" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
     </row>
     <row r="68" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
     </row>
     <row r="69" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
     </row>
     <row r="70" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
     </row>
     <row r="71" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
     </row>
     <row r="72" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
     </row>
     <row r="73" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
     </row>
     <row r="74" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
     </row>
     <row r="75" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
     </row>
     <row r="76" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
     </row>
     <row r="77" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
     </row>
     <row r="78" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
     </row>
     <row r="79" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
     </row>
     <row r="80" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
     </row>
     <row r="81" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
     </row>
   </sheetData>

--- a/config/Excel/Status.xlsx
+++ b/config/Excel/Status.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\AppData\Local\Temp\idle-fireamp-cap-20261019\stage\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\AppData\Local\Temp\idle-infinite-burn-20261019\stage\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DDAA2EE-8EE3-4BFD-8950-5B98FA4038CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38C871F0-F3CB-4AC3-849C-5D5BA519388B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3090" yWindow="2310" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -534,9 +534,6 @@
     <t>烈焰燃燒</t>
   </si>
   <si>
-    <t>新版技能【火球術／火柱】：火屬性持續傷害；每跳量與間隔由技能各階決定（引擎以 dps 覆寫）。</t>
-  </si>
-  <si>
     <t>sgFireAmp</t>
   </si>
   <si>
@@ -1480,6 +1477,10 @@
   </si>
   <si>
     <t>傳奇【烈火狩】：火狩持續期間按節拍疊加火屬性傷害提升，最多 50 層，滿層只刷新時間；火狩全部消失後到期，與火焰增幅各自計算層數。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>新版技能【火球術／火柱／無限星環】：火屬性持續傷害；每跳量與間隔由技能各階決定（引擎以 dps 覆寫）。</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -3435,7 +3436,7 @@
         <v>112</v>
       </c>
       <c r="B22" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="C22" t="s">
         <v>113</v>
@@ -3471,7 +3472,7 @@
         <v>1</v>
       </c>
       <c r="T22" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="23" spans="1:20" x14ac:dyDescent="0.25">
@@ -3788,10 +3789,10 @@
         <v>1</v>
       </c>
       <c r="Q29" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="S29" s="1" t="s">
         <v>379</v>
-      </c>
-      <c r="S29" s="1" t="s">
-        <v>380</v>
       </c>
       <c r="T29" t="s">
         <v>136</v>
@@ -4014,10 +4015,10 @@
         <v>1</v>
       </c>
       <c r="R34" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="T34" s="1" t="s">
         <v>426</v>
-      </c>
-      <c r="T34" s="1" t="s">
-        <v>427</v>
       </c>
     </row>
     <row r="35" spans="1:20" x14ac:dyDescent="0.25">
@@ -4061,7 +4062,7 @@
         <v>1</v>
       </c>
       <c r="R35" s="1" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="T35" t="s">
         <v>157</v>
@@ -4155,18 +4156,18 @@
         <v>1</v>
       </c>
       <c r="S37" s="1" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="T37" t="s">
-        <v>166</v>
+        <v>474</v>
       </c>
     </row>
     <row r="38" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
+        <v>166</v>
+      </c>
+      <c r="B38" t="s">
         <v>167</v>
-      </c>
-      <c r="B38" t="s">
-        <v>168</v>
       </c>
       <c r="C38" t="s">
         <v>30</v>
@@ -4178,7 +4179,7 @@
         <v>79</v>
       </c>
       <c r="F38" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G38" t="s">
         <v>31</v>
@@ -4199,24 +4200,24 @@
         <v>0</v>
       </c>
       <c r="O38" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="P38">
         <v>50</v>
       </c>
       <c r="T38" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="39" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
+        <v>168</v>
+      </c>
+      <c r="B39" t="s">
         <v>169</v>
       </c>
-      <c r="B39" t="s">
+      <c r="C39" t="s">
         <v>170</v>
-      </c>
-      <c r="C39" t="s">
-        <v>171</v>
       </c>
       <c r="D39" t="s">
         <v>65</v>
@@ -4225,7 +4226,7 @@
         <v>79</v>
       </c>
       <c r="F39" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="G39" t="s">
         <v>31</v>
@@ -4252,18 +4253,18 @@
         <v>1</v>
       </c>
       <c r="T39" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="40" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
+        <v>172</v>
+      </c>
+      <c r="B40" t="s">
         <v>173</v>
       </c>
-      <c r="B40" t="s">
+      <c r="C40" t="s">
         <v>174</v>
-      </c>
-      <c r="C40" t="s">
-        <v>175</v>
       </c>
       <c r="D40" t="s">
         <v>65</v>
@@ -4272,10 +4273,10 @@
         <v>79</v>
       </c>
       <c r="F40" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="G40" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I40">
         <v>0</v>
@@ -4299,18 +4300,18 @@
         <v>1</v>
       </c>
       <c r="T40" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="41" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
+        <v>177</v>
+      </c>
+      <c r="B41" t="s">
         <v>178</v>
       </c>
-      <c r="B41" t="s">
-        <v>179</v>
-      </c>
       <c r="C41" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D41" t="s">
         <v>65</v>
@@ -4319,7 +4320,7 @@
         <v>79</v>
       </c>
       <c r="F41" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="I41">
         <v>0</v>
@@ -4343,18 +4344,18 @@
         <v>1</v>
       </c>
       <c r="T41" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="42" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
+        <v>180</v>
+      </c>
+      <c r="B42" t="s">
         <v>181</v>
       </c>
-      <c r="B42" t="s">
+      <c r="C42" t="s">
         <v>182</v>
-      </c>
-      <c r="C42" t="s">
-        <v>183</v>
       </c>
       <c r="D42" t="s">
         <v>23</v>
@@ -4363,10 +4364,10 @@
         <v>79</v>
       </c>
       <c r="F42" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="G42" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I42">
         <v>0</v>
@@ -4390,15 +4391,15 @@
         <v>1</v>
       </c>
       <c r="T42" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="43" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
+        <v>184</v>
+      </c>
+      <c r="B43" t="s">
         <v>185</v>
-      </c>
-      <c r="B43" t="s">
-        <v>186</v>
       </c>
       <c r="C43" t="s">
         <v>35</v>
@@ -4437,18 +4438,18 @@
         <v>1</v>
       </c>
       <c r="T43" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="44" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
+        <v>187</v>
+      </c>
+      <c r="B44" t="s">
         <v>188</v>
       </c>
-      <c r="B44" t="s">
+      <c r="C44" t="s">
         <v>189</v>
-      </c>
-      <c r="C44" t="s">
-        <v>190</v>
       </c>
       <c r="D44" t="s">
         <v>23</v>
@@ -4484,18 +4485,18 @@
         <v>1</v>
       </c>
       <c r="T44" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="45" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
+        <v>191</v>
+      </c>
+      <c r="B45" t="s">
         <v>192</v>
       </c>
-      <c r="B45" t="s">
+      <c r="C45" t="s">
         <v>193</v>
-      </c>
-      <c r="C45" t="s">
-        <v>194</v>
       </c>
       <c r="D45" t="s">
         <v>65</v>
@@ -4504,7 +4505,7 @@
         <v>79</v>
       </c>
       <c r="F45" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="G45" t="s">
         <v>115</v>
@@ -4531,18 +4532,18 @@
         <v>1</v>
       </c>
       <c r="T45" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="46" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
+        <v>195</v>
+      </c>
+      <c r="B46" t="s">
         <v>196</v>
       </c>
-      <c r="B46" t="s">
+      <c r="C46" t="s">
         <v>197</v>
-      </c>
-      <c r="C46" t="s">
-        <v>198</v>
       </c>
       <c r="D46" t="s">
         <v>23</v>
@@ -4551,10 +4552,10 @@
         <v>79</v>
       </c>
       <c r="F46" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G46" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="I46">
         <v>0</v>
@@ -4578,18 +4579,18 @@
         <v>5</v>
       </c>
       <c r="T46" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="47" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
+        <v>200</v>
+      </c>
+      <c r="B47" t="s">
         <v>201</v>
       </c>
-      <c r="B47" t="s">
+      <c r="C47" t="s">
         <v>202</v>
-      </c>
-      <c r="C47" t="s">
-        <v>203</v>
       </c>
       <c r="D47" t="s">
         <v>23</v>
@@ -4598,7 +4599,7 @@
         <v>24</v>
       </c>
       <c r="G47" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="H47" t="s">
         <v>25</v>
@@ -4625,21 +4626,21 @@
         <v>1</v>
       </c>
       <c r="S47" s="1" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="T47" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="48" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
+        <v>204</v>
+      </c>
+      <c r="B48" t="s">
         <v>205</v>
       </c>
-      <c r="B48" t="s">
+      <c r="C48" t="s">
         <v>206</v>
-      </c>
-      <c r="C48" t="s">
-        <v>207</v>
       </c>
       <c r="D48" t="s">
         <v>23</v>
@@ -4648,10 +4649,10 @@
         <v>79</v>
       </c>
       <c r="F48" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="G48" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="I48">
         <v>0</v>
@@ -4675,18 +4676,18 @@
         <v>1</v>
       </c>
       <c r="T48" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="49" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
+        <v>208</v>
+      </c>
+      <c r="B49" t="s">
         <v>209</v>
       </c>
-      <c r="B49" t="s">
+      <c r="C49" t="s">
         <v>210</v>
-      </c>
-      <c r="C49" t="s">
-        <v>211</v>
       </c>
       <c r="D49" t="s">
         <v>23</v>
@@ -4695,10 +4696,10 @@
         <v>79</v>
       </c>
       <c r="F49" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="G49" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="I49">
         <v>0</v>
@@ -4722,18 +4723,18 @@
         <v>1</v>
       </c>
       <c r="T49" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="50" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
+        <v>212</v>
+      </c>
+      <c r="B50" t="s">
         <v>213</v>
       </c>
-      <c r="B50" t="s">
-        <v>214</v>
-      </c>
       <c r="C50" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D50" t="s">
         <v>65</v>
@@ -4742,10 +4743,10 @@
         <v>79</v>
       </c>
       <c r="F50" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="G50" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="I50">
         <v>0</v>
@@ -4769,15 +4770,15 @@
         <v>1</v>
       </c>
       <c r="T50" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="51" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
+        <v>215</v>
+      </c>
+      <c r="B51" t="s">
         <v>216</v>
-      </c>
-      <c r="B51" t="s">
-        <v>217</v>
       </c>
       <c r="C51" t="s">
         <v>114</v>
@@ -4789,10 +4790,10 @@
         <v>79</v>
       </c>
       <c r="F51" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="G51" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="I51">
         <v>0</v>
@@ -4816,15 +4817,15 @@
         <v>6</v>
       </c>
       <c r="T51" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="52" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
+        <v>219</v>
+      </c>
+      <c r="B52" t="s">
         <v>220</v>
-      </c>
-      <c r="B52" t="s">
-        <v>221</v>
       </c>
       <c r="C52" t="s">
         <v>114</v>
@@ -4836,7 +4837,7 @@
         <v>24</v>
       </c>
       <c r="G52" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H52" t="s">
         <v>25</v>
@@ -4863,18 +4864,18 @@
         <v>1</v>
       </c>
       <c r="T52" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="53" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
+        <v>222</v>
+      </c>
+      <c r="B53" t="s">
         <v>223</v>
       </c>
-      <c r="B53" t="s">
+      <c r="C53" t="s">
         <v>224</v>
-      </c>
-      <c r="C53" t="s">
-        <v>225</v>
       </c>
       <c r="D53" t="s">
         <v>23</v>
@@ -4883,10 +4884,10 @@
         <v>79</v>
       </c>
       <c r="F53" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="G53" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="I53">
         <v>0</v>
@@ -4910,15 +4911,15 @@
         <v>1</v>
       </c>
       <c r="T53" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="54" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
+        <v>226</v>
+      </c>
+      <c r="B54" t="s">
         <v>227</v>
-      </c>
-      <c r="B54" t="s">
-        <v>228</v>
       </c>
       <c r="C54" t="s">
         <v>153</v>
@@ -4930,10 +4931,10 @@
         <v>79</v>
       </c>
       <c r="F54" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G54" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="I54">
         <v>0</v>
@@ -4957,18 +4958,18 @@
         <v>1</v>
       </c>
       <c r="R54" s="1" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="T54" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="55" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
+        <v>229</v>
+      </c>
+      <c r="B55" t="s">
         <v>230</v>
-      </c>
-      <c r="B55" t="s">
-        <v>231</v>
       </c>
       <c r="C55" t="s">
         <v>90</v>
@@ -4980,10 +4981,10 @@
         <v>79</v>
       </c>
       <c r="F55" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G55" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="I55">
         <v>0</v>
@@ -5007,18 +5008,18 @@
         <v>1</v>
       </c>
       <c r="T55" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="56" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
+        <v>232</v>
+      </c>
+      <c r="B56" t="s">
         <v>233</v>
       </c>
-      <c r="B56" t="s">
+      <c r="C56" t="s">
         <v>234</v>
-      </c>
-      <c r="C56" t="s">
-        <v>235</v>
       </c>
       <c r="D56" t="s">
         <v>65</v>
@@ -5027,10 +5028,10 @@
         <v>79</v>
       </c>
       <c r="F56" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="G56" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="I56">
         <v>0</v>
@@ -5054,18 +5055,18 @@
         <v>1</v>
       </c>
       <c r="R56" s="1" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="T56" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="57" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
+        <v>236</v>
+      </c>
+      <c r="B57" t="s">
         <v>237</v>
-      </c>
-      <c r="B57" t="s">
-        <v>238</v>
       </c>
       <c r="C57" t="s">
         <v>39</v>
@@ -5077,7 +5078,7 @@
         <v>79</v>
       </c>
       <c r="F57" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="I57">
         <v>0</v>
@@ -5101,18 +5102,18 @@
         <v>10</v>
       </c>
       <c r="T57" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="58" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
+        <v>239</v>
+      </c>
+      <c r="B58" t="s">
         <v>240</v>
       </c>
-      <c r="B58" t="s">
+      <c r="C58" t="s">
         <v>241</v>
-      </c>
-      <c r="C58" t="s">
-        <v>242</v>
       </c>
       <c r="D58" t="s">
         <v>23</v>
@@ -5121,7 +5122,7 @@
         <v>79</v>
       </c>
       <c r="F58" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="G58" t="s">
         <v>40</v>
@@ -5148,15 +5149,15 @@
         <v>100</v>
       </c>
       <c r="T58" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="59" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
+        <v>243</v>
+      </c>
+      <c r="B59" t="s">
         <v>244</v>
-      </c>
-      <c r="B59" t="s">
-        <v>245</v>
       </c>
       <c r="C59" t="s">
         <v>22</v>
@@ -5192,18 +5193,18 @@
         <v>1</v>
       </c>
       <c r="T59" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="60" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
+        <v>246</v>
+      </c>
+      <c r="B60" t="s">
         <v>247</v>
       </c>
-      <c r="B60" t="s">
+      <c r="C60" t="s">
         <v>248</v>
-      </c>
-      <c r="C60" t="s">
-        <v>249</v>
       </c>
       <c r="D60" t="s">
         <v>65</v>
@@ -5212,7 +5213,7 @@
         <v>79</v>
       </c>
       <c r="F60" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="I60">
         <v>0</v>
@@ -5236,15 +5237,15 @@
         <v>1</v>
       </c>
       <c r="T60" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="61" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
+        <v>250</v>
+      </c>
+      <c r="B61" t="s">
         <v>251</v>
-      </c>
-      <c r="B61" t="s">
-        <v>252</v>
       </c>
       <c r="C61" t="s">
         <v>35</v>
@@ -5256,7 +5257,7 @@
         <v>79</v>
       </c>
       <c r="F61" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="I61">
         <v>0</v>
@@ -5280,18 +5281,18 @@
         <v>20</v>
       </c>
       <c r="T61" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="62" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
+        <v>253</v>
+      </c>
+      <c r="B62" t="s">
         <v>254</v>
       </c>
-      <c r="B62" t="s">
+      <c r="C62" t="s">
         <v>255</v>
-      </c>
-      <c r="C62" t="s">
-        <v>256</v>
       </c>
       <c r="D62" t="s">
         <v>65</v>
@@ -5300,7 +5301,7 @@
         <v>79</v>
       </c>
       <c r="F62" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="I62">
         <v>0</v>
@@ -5324,18 +5325,18 @@
         <v>1</v>
       </c>
       <c r="T62" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="63" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
+        <v>257</v>
+      </c>
+      <c r="B63" t="s">
         <v>258</v>
       </c>
-      <c r="B63" t="s">
+      <c r="C63" t="s">
         <v>259</v>
-      </c>
-      <c r="C63" t="s">
-        <v>260</v>
       </c>
       <c r="D63" t="s">
         <v>65</v>
@@ -5344,7 +5345,7 @@
         <v>79</v>
       </c>
       <c r="F63" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="I63">
         <v>0</v>
@@ -5368,18 +5369,18 @@
         <v>100</v>
       </c>
       <c r="T63" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="64" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
+        <v>261</v>
+      </c>
+      <c r="B64" t="s">
         <v>262</v>
       </c>
-      <c r="B64" t="s">
+      <c r="C64" t="s">
         <v>263</v>
-      </c>
-      <c r="C64" t="s">
-        <v>264</v>
       </c>
       <c r="D64" t="s">
         <v>23</v>
@@ -5415,18 +5416,18 @@
         <v>10</v>
       </c>
       <c r="T64" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="65" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
+        <v>265</v>
+      </c>
+      <c r="B65" t="s">
         <v>266</v>
       </c>
-      <c r="B65" t="s">
+      <c r="C65" t="s">
         <v>267</v>
-      </c>
-      <c r="C65" t="s">
-        <v>268</v>
       </c>
       <c r="D65" t="s">
         <v>23</v>
@@ -5462,18 +5463,18 @@
         <v>20</v>
       </c>
       <c r="T65" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
     </row>
     <row r="66" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
+        <v>268</v>
+      </c>
+      <c r="B66" t="s">
         <v>269</v>
       </c>
-      <c r="B66" t="s">
+      <c r="C66" t="s">
         <v>270</v>
-      </c>
-      <c r="C66" t="s">
-        <v>271</v>
       </c>
       <c r="D66" t="s">
         <v>65</v>
@@ -5482,7 +5483,7 @@
         <v>79</v>
       </c>
       <c r="F66" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="I66">
         <v>0</v>
@@ -5506,21 +5507,21 @@
         <v>1</v>
       </c>
       <c r="R66" s="1" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="T66" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="67" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
+        <v>272</v>
+      </c>
+      <c r="B67" t="s">
         <v>273</v>
       </c>
-      <c r="B67" t="s">
-        <v>274</v>
-      </c>
       <c r="C67" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="D67" t="s">
         <v>23</v>
@@ -5529,7 +5530,7 @@
         <v>79</v>
       </c>
       <c r="F67" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="I67">
         <v>0</v>
@@ -5553,18 +5554,18 @@
         <v>1</v>
       </c>
       <c r="T67" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="68" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
+        <v>275</v>
+      </c>
+      <c r="B68" t="s">
         <v>276</v>
       </c>
-      <c r="B68" t="s">
+      <c r="C68" t="s">
         <v>277</v>
-      </c>
-      <c r="C68" t="s">
-        <v>278</v>
       </c>
       <c r="D68" t="s">
         <v>65</v>
@@ -5573,7 +5574,7 @@
         <v>79</v>
       </c>
       <c r="F68" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="I68">
         <v>0</v>
@@ -5597,15 +5598,15 @@
         <v>1</v>
       </c>
       <c r="T68" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="69" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
+        <v>279</v>
+      </c>
+      <c r="B69" t="s">
         <v>280</v>
-      </c>
-      <c r="B69" t="s">
-        <v>281</v>
       </c>
       <c r="C69" t="s">
         <v>22</v>
@@ -5617,7 +5618,7 @@
         <v>79</v>
       </c>
       <c r="F69" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="I69">
         <v>0</v>
@@ -5641,18 +5642,18 @@
         <v>50</v>
       </c>
       <c r="T69" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="70" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
+        <v>282</v>
+      </c>
+      <c r="B70" t="s">
         <v>283</v>
       </c>
-      <c r="B70" t="s">
+      <c r="C70" t="s">
         <v>284</v>
-      </c>
-      <c r="C70" t="s">
-        <v>285</v>
       </c>
       <c r="D70" t="s">
         <v>65</v>
@@ -5661,7 +5662,7 @@
         <v>79</v>
       </c>
       <c r="F70" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="I70">
         <v>0</v>
@@ -5685,18 +5686,18 @@
         <v>10</v>
       </c>
       <c r="T70" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="71" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
+        <v>286</v>
+      </c>
+      <c r="B71" t="s">
         <v>287</v>
       </c>
-      <c r="B71" t="s">
+      <c r="C71" t="s">
         <v>288</v>
-      </c>
-      <c r="C71" t="s">
-        <v>289</v>
       </c>
       <c r="D71" t="s">
         <v>65</v>
@@ -5705,7 +5706,7 @@
         <v>79</v>
       </c>
       <c r="F71" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="I71">
         <v>0</v>
@@ -5729,18 +5730,18 @@
         <v>100</v>
       </c>
       <c r="T71" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="72" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
+        <v>290</v>
+      </c>
+      <c r="B72" t="s">
         <v>291</v>
       </c>
-      <c r="B72" t="s">
+      <c r="C72" t="s">
         <v>292</v>
-      </c>
-      <c r="C72" t="s">
-        <v>293</v>
       </c>
       <c r="D72" t="s">
         <v>65</v>
@@ -5749,7 +5750,7 @@
         <v>79</v>
       </c>
       <c r="F72" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="I72">
         <v>0</v>
@@ -5773,21 +5774,21 @@
         <v>1</v>
       </c>
       <c r="R72" s="1" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="T72" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="73" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
+        <v>293</v>
+      </c>
+      <c r="B73" t="s">
         <v>294</v>
       </c>
-      <c r="B73" t="s">
-        <v>295</v>
-      </c>
       <c r="C73" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D73" t="s">
         <v>65</v>
@@ -5796,7 +5797,7 @@
         <v>79</v>
       </c>
       <c r="F73" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="G73" t="s">
         <v>31</v>
@@ -5823,15 +5824,15 @@
         <v>1</v>
       </c>
       <c r="T73" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="74" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
+        <v>296</v>
+      </c>
+      <c r="B74" t="s">
         <v>297</v>
-      </c>
-      <c r="B74" t="s">
-        <v>298</v>
       </c>
       <c r="C74" t="s">
         <v>30</v>
@@ -5843,7 +5844,7 @@
         <v>79</v>
       </c>
       <c r="F74" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="G74" t="s">
         <v>31</v>
@@ -5870,18 +5871,18 @@
         <v>1</v>
       </c>
       <c r="T74" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="75" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
+        <v>298</v>
+      </c>
+      <c r="B75" t="s">
         <v>299</v>
       </c>
-      <c r="B75" t="s">
+      <c r="C75" t="s">
         <v>300</v>
-      </c>
-      <c r="C75" t="s">
-        <v>301</v>
       </c>
       <c r="D75" t="s">
         <v>23</v>
@@ -5890,10 +5891,10 @@
         <v>79</v>
       </c>
       <c r="F75" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="G75" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I75">
         <v>0</v>
@@ -5917,18 +5918,18 @@
         <v>1</v>
       </c>
       <c r="T75" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="76" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
+        <v>301</v>
+      </c>
+      <c r="B76" t="s">
         <v>302</v>
       </c>
-      <c r="B76" t="s">
+      <c r="C76" t="s">
         <v>303</v>
-      </c>
-      <c r="C76" t="s">
-        <v>304</v>
       </c>
       <c r="D76" t="s">
         <v>23</v>
@@ -5937,10 +5938,10 @@
         <v>79</v>
       </c>
       <c r="F76" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="G76" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I76">
         <v>0</v>
@@ -5964,15 +5965,15 @@
         <v>1</v>
       </c>
       <c r="T76" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="77" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
+        <v>305</v>
+      </c>
+      <c r="B77" t="s">
         <v>306</v>
-      </c>
-      <c r="B77" t="s">
-        <v>307</v>
       </c>
       <c r="C77" t="s">
         <v>22</v>
@@ -6008,15 +6009,15 @@
         <v>1</v>
       </c>
       <c r="T77" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="78" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
+        <v>308</v>
+      </c>
+      <c r="B78" t="s">
         <v>309</v>
-      </c>
-      <c r="B78" t="s">
-        <v>310</v>
       </c>
       <c r="C78" t="s">
         <v>44</v>
@@ -6055,18 +6056,18 @@
         <v>1</v>
       </c>
       <c r="T78" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="79" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
+        <v>311</v>
+      </c>
+      <c r="B79" t="s">
         <v>312</v>
       </c>
-      <c r="B79" t="s">
-        <v>313</v>
-      </c>
       <c r="C79" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D79" t="s">
         <v>23</v>
@@ -6075,7 +6076,7 @@
         <v>79</v>
       </c>
       <c r="F79" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="G79" t="s">
         <v>31</v>
@@ -6102,18 +6103,18 @@
         <v>1</v>
       </c>
       <c r="T79" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="80" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
+        <v>314</v>
+      </c>
+      <c r="B80" t="s">
         <v>315</v>
       </c>
-      <c r="B80" t="s">
+      <c r="C80" t="s">
         <v>316</v>
-      </c>
-      <c r="C80" t="s">
-        <v>317</v>
       </c>
       <c r="D80" t="s">
         <v>65</v>
@@ -6122,7 +6123,7 @@
         <v>79</v>
       </c>
       <c r="F80" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="G80" t="s">
         <v>115</v>
@@ -6149,15 +6150,15 @@
         <v>100</v>
       </c>
       <c r="T80" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="81" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
+        <v>318</v>
+      </c>
+      <c r="B81" t="s">
         <v>319</v>
-      </c>
-      <c r="B81" t="s">
-        <v>320</v>
       </c>
       <c r="C81" t="s">
         <v>86</v>
@@ -6169,7 +6170,7 @@
         <v>79</v>
       </c>
       <c r="F81" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="G81" t="s">
         <v>115</v>
@@ -6196,18 +6197,18 @@
         <v>1</v>
       </c>
       <c r="T81" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="82" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
+        <v>321</v>
+      </c>
+      <c r="B82" t="s">
         <v>322</v>
       </c>
-      <c r="B82" t="s">
+      <c r="C82" t="s">
         <v>323</v>
-      </c>
-      <c r="C82" t="s">
-        <v>324</v>
       </c>
       <c r="D82" t="s">
         <v>23</v>
@@ -6216,10 +6217,10 @@
         <v>79</v>
       </c>
       <c r="F82" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="G82" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="I82">
         <v>0</v>
@@ -6243,18 +6244,18 @@
         <v>1</v>
       </c>
       <c r="T82" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="83" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
+        <v>325</v>
+      </c>
+      <c r="B83" t="s">
         <v>326</v>
       </c>
-      <c r="B83" t="s">
+      <c r="C83" t="s">
         <v>327</v>
-      </c>
-      <c r="C83" t="s">
-        <v>328</v>
       </c>
       <c r="D83" t="s">
         <v>23</v>
@@ -6263,10 +6264,10 @@
         <v>79</v>
       </c>
       <c r="F83" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="G83" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="I83">
         <v>0</v>
@@ -6290,18 +6291,18 @@
         <v>1</v>
       </c>
       <c r="T83" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="84" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="B84" s="1" t="s">
         <v>394</v>
       </c>
-      <c r="B84" s="1" t="s">
-        <v>395</v>
-      </c>
       <c r="C84" s="1" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D84" s="1" t="s">
         <v>65</v>
@@ -6310,48 +6311,48 @@
         <v>79</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="G84" s="1" t="s">
         <v>40</v>
       </c>
       <c r="I84" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="K84" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="L84" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="M84" s="1" t="s">
         <v>396</v>
       </c>
-      <c r="K84" s="1" t="s">
-        <v>396</v>
-      </c>
-      <c r="L84" s="1" t="s">
-        <v>396</v>
-      </c>
-      <c r="M84" s="1" t="s">
-        <v>397</v>
-      </c>
       <c r="N84" s="1" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="O84" s="1" t="s">
         <v>56</v>
       </c>
       <c r="P84" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="R84" s="1" t="s">
         <v>398</v>
       </c>
-      <c r="R84" s="1" t="s">
+      <c r="T84" s="1" t="s">
         <v>399</v>
-      </c>
-      <c r="T84" s="1" t="s">
-        <v>400</v>
       </c>
     </row>
     <row r="85" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="B85" s="1" t="s">
         <v>401</v>
       </c>
-      <c r="B85" s="1" t="s">
+      <c r="C85" s="1" t="s">
         <v>402</v>
-      </c>
-      <c r="C85" s="1" t="s">
-        <v>403</v>
       </c>
       <c r="D85" s="1" t="s">
         <v>65</v>
@@ -6360,45 +6361,45 @@
         <v>79</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="G85" s="1" t="s">
         <v>33</v>
       </c>
       <c r="I85" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="K85" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="L85" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="M85" s="1" t="s">
         <v>396</v>
       </c>
-      <c r="K85" s="1" t="s">
-        <v>396</v>
-      </c>
-      <c r="L85" s="1" t="s">
-        <v>396</v>
-      </c>
-      <c r="M85" s="1" t="s">
-        <v>397</v>
-      </c>
       <c r="N85" s="1" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="O85" s="1" t="s">
         <v>56</v>
       </c>
       <c r="P85" s="1" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="R85" s="1" t="s">
+        <v>403</v>
+      </c>
+      <c r="T85" s="1" t="s">
         <v>404</v>
-      </c>
-      <c r="T85" s="1" t="s">
-        <v>405</v>
       </c>
     </row>
     <row r="86" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
+        <v>405</v>
+      </c>
+      <c r="B86" s="1" t="s">
         <v>406</v>
-      </c>
-      <c r="B86" s="1" t="s">
-        <v>407</v>
       </c>
       <c r="C86" s="1" t="s">
         <v>30</v>
@@ -6410,48 +6411,48 @@
         <v>79</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="G86" s="1" t="s">
         <v>31</v>
       </c>
       <c r="I86" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="K86" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="L86" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="M86" s="1" t="s">
         <v>396</v>
       </c>
-      <c r="K86" s="1" t="s">
-        <v>396</v>
-      </c>
-      <c r="L86" s="1" t="s">
-        <v>396</v>
-      </c>
-      <c r="M86" s="1" t="s">
-        <v>397</v>
-      </c>
       <c r="N86" s="1" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="O86" s="1" t="s">
         <v>56</v>
       </c>
       <c r="P86" s="1" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="R86" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="T86" s="1" t="s">
         <v>408</v>
-      </c>
-      <c r="T86" s="1" t="s">
-        <v>409</v>
       </c>
     </row>
     <row r="87" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="B87" s="1" t="s">
         <v>410</v>
       </c>
-      <c r="B87" s="1" t="s">
-        <v>411</v>
-      </c>
       <c r="C87" s="1" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="D87" s="1" t="s">
         <v>65</v>
@@ -6460,48 +6461,48 @@
         <v>79</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="G87" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I87" s="1" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="K87" s="1" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="L87" s="1" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="M87" s="1" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="N87" s="1" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="O87" s="1" t="s">
         <v>56</v>
       </c>
       <c r="P87" s="1" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="R87" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="T87" s="1" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="88" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="B88" s="1" t="s">
         <v>414</v>
       </c>
-      <c r="B88" s="1" t="s">
-        <v>415</v>
-      </c>
       <c r="C88" s="1" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D88" s="1" t="s">
         <v>65</v>
@@ -6510,48 +6511,48 @@
         <v>79</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="G88" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I88" s="1" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="K88" s="1" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="L88" s="1" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="M88" s="1" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="N88" s="1" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="O88" s="1" t="s">
         <v>56</v>
       </c>
       <c r="P88" s="1" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="R88" s="1" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="T88" s="1" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="89" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="B89" s="1" t="s">
         <v>417</v>
       </c>
-      <c r="B89" s="1" t="s">
+      <c r="C89" s="1" t="s">
         <v>418</v>
-      </c>
-      <c r="C89" s="1" t="s">
-        <v>419</v>
       </c>
       <c r="D89" s="1" t="s">
         <v>65</v>
@@ -6560,48 +6561,48 @@
         <v>79</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="G89" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="I89" s="1" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="K89" s="1" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="L89" s="1" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="M89" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="N89" s="1" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="O89" s="1" t="s">
         <v>56</v>
       </c>
       <c r="P89" s="1" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="R89" s="1" t="s">
+        <v>428</v>
+      </c>
+      <c r="T89" s="1" t="s">
         <v>429</v>
-      </c>
-      <c r="T89" s="1" t="s">
-        <v>430</v>
       </c>
     </row>
     <row r="90" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="B90" s="1" t="s">
         <v>422</v>
       </c>
-      <c r="B90" s="1" t="s">
-        <v>423</v>
-      </c>
       <c r="C90" s="1" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="D90" s="1" t="s">
         <v>65</v>
@@ -6610,45 +6611,45 @@
         <v>79</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="G90" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="I90" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="K90" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="L90" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="M90" s="1" t="s">
         <v>396</v>
       </c>
-      <c r="K90" s="1" t="s">
-        <v>396</v>
-      </c>
-      <c r="L90" s="1" t="s">
-        <v>396</v>
-      </c>
-      <c r="M90" s="1" t="s">
-        <v>397</v>
-      </c>
       <c r="N90" s="1" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="O90" s="1" t="s">
         <v>56</v>
       </c>
       <c r="P90" s="1" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="R90" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="T90" s="1" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="91" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="B91" s="1" t="s">
         <v>435</v>
-      </c>
-      <c r="B91" s="1" t="s">
-        <v>436</v>
       </c>
       <c r="C91" s="1" t="s">
         <v>74</v>
@@ -6660,45 +6661,45 @@
         <v>79</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="I91" s="1" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="K91" s="1" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="L91" s="1" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="M91" s="1" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="N91" s="1" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="O91" s="1" t="s">
         <v>56</v>
       </c>
       <c r="P91" s="1" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="R91" s="1" t="s">
+        <v>437</v>
+      </c>
+      <c r="T91" s="1" t="s">
         <v>438</v>
-      </c>
-      <c r="T91" s="1" t="s">
-        <v>439</v>
       </c>
     </row>
     <row r="92" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
+        <v>439</v>
+      </c>
+      <c r="B92" s="1" t="s">
         <v>440</v>
       </c>
-      <c r="B92" s="1" t="s">
-        <v>441</v>
-      </c>
       <c r="C92" s="1" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D92" s="1" t="s">
         <v>65</v>
@@ -6707,45 +6708,45 @@
         <v>79</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="I92" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="K92" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="L92" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="M92" s="1" t="s">
         <v>396</v>
       </c>
-      <c r="K92" s="1" t="s">
-        <v>396</v>
-      </c>
-      <c r="L92" s="1" t="s">
-        <v>396</v>
-      </c>
-      <c r="M92" s="1" t="s">
-        <v>397</v>
-      </c>
       <c r="N92" s="1" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="O92" s="1" t="s">
         <v>56</v>
       </c>
       <c r="P92" s="1" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="Q92" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="R92" s="1" t="s">
         <v>442</v>
       </c>
-      <c r="R92" s="1" t="s">
+      <c r="T92" s="1" t="s">
         <v>443</v>
-      </c>
-      <c r="T92" s="1" t="s">
-        <v>444</v>
       </c>
     </row>
     <row r="93" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
+        <v>444</v>
+      </c>
+      <c r="B93" s="1" t="s">
         <v>445</v>
-      </c>
-      <c r="B93" s="1" t="s">
-        <v>446</v>
       </c>
       <c r="C93" s="1" t="s">
         <v>30</v>
@@ -6757,42 +6758,42 @@
         <v>79</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="I93" s="1" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="K93" s="1" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="L93" s="1" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="M93" s="1" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="N93" s="1" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="O93" s="1" t="s">
         <v>56</v>
       </c>
       <c r="P93" s="1" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="Q93" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="R93" s="1" t="s">
         <v>448</v>
       </c>
-      <c r="R93" s="1" t="s">
+      <c r="T93" s="1" t="s">
         <v>449</v>
-      </c>
-      <c r="T93" s="1" t="s">
-        <v>450</v>
       </c>
     </row>
     <row r="94" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B94" s="1" t="s">
         <v>68</v>
@@ -6807,45 +6808,45 @@
         <v>79</v>
       </c>
       <c r="F94" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="I94" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="K94" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="L94" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="M94" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="N94" s="1" t="s">
         <v>451</v>
-      </c>
-      <c r="I94" s="1" t="s">
-        <v>396</v>
-      </c>
-      <c r="K94" s="1" t="s">
-        <v>396</v>
-      </c>
-      <c r="L94" s="1" t="s">
-        <v>396</v>
-      </c>
-      <c r="M94" s="1" t="s">
-        <v>397</v>
-      </c>
-      <c r="N94" s="1" t="s">
-        <v>452</v>
       </c>
       <c r="O94" s="1" t="s">
         <v>56</v>
       </c>
       <c r="P94" s="1" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="S94" s="1" t="s">
+        <v>452</v>
+      </c>
+      <c r="T94" s="1" t="s">
         <v>453</v>
-      </c>
-      <c r="T94" s="1" t="s">
-        <v>454</v>
       </c>
     </row>
     <row r="95" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
+        <v>454</v>
+      </c>
+      <c r="B95" s="1" t="s">
         <v>455</v>
       </c>
-      <c r="B95" s="1" t="s">
+      <c r="C95" s="1" t="s">
         <v>456</v>
-      </c>
-      <c r="C95" s="1" t="s">
-        <v>457</v>
       </c>
       <c r="D95" s="1" t="s">
         <v>23</v>
@@ -6854,57 +6855,57 @@
         <v>79</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="I95" s="1" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="K95" s="1" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="L95" s="1" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="M95" s="1" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="N95" s="1" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="O95" s="1" t="s">
         <v>56</v>
       </c>
       <c r="P95" s="1" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="Q95" s="1" t="s">
+        <v>458</v>
+      </c>
+      <c r="T95" s="1" t="s">
         <v>459</v>
-      </c>
-      <c r="T95" s="1" t="s">
-        <v>460</v>
       </c>
     </row>
     <row r="96" spans="1:20" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
+        <v>467</v>
+      </c>
+      <c r="B96" t="s">
         <v>468</v>
       </c>
-      <c r="B96" t="s">
+      <c r="C96" t="s">
         <v>469</v>
       </c>
-      <c r="C96" t="s">
+      <c r="D96" t="s">
         <v>470</v>
       </c>
-      <c r="D96" t="s">
+      <c r="E96" t="s">
         <v>471</v>
       </c>
-      <c r="E96" t="s">
+      <c r="F96" t="s">
+        <v>467</v>
+      </c>
+      <c r="G96" t="s">
         <v>472</v>
-      </c>
-      <c r="F96" t="s">
-        <v>468</v>
-      </c>
-      <c r="G96" t="s">
-        <v>473</v>
       </c>
       <c r="I96">
         <v>0</v>
@@ -6922,13 +6923,13 @@
         <v>0</v>
       </c>
       <c r="O96" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="P96">
         <v>50</v>
       </c>
       <c r="T96" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
     </row>
   </sheetData>
@@ -6953,32 +6954,32 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
@@ -6988,17 +6989,17 @@
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
@@ -7008,32 +7009,32 @@
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
@@ -7043,27 +7044,27 @@
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
@@ -7073,17 +7074,17 @@
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
@@ -7093,22 +7094,22 @@
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
@@ -7118,42 +7119,42 @@
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.25">
@@ -7163,17 +7164,17 @@
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.25">
@@ -7183,22 +7184,22 @@
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.25">
@@ -7208,147 +7209,147 @@
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="54" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="56" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="59" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="60" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="61" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="62" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="63" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="64" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="66" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="67" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="68" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="69" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="70" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="71" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="72" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="73" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="74" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="75" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="76" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="77" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="78" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="79" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="80" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="81" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
   </sheetData>

--- a/config/Excel/Status.xlsx
+++ b/config/Excel/Status.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\AppData\Local\Temp\idle-infinite-burn-20261019\stage\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alway\.codex\visualizations\2026\10\19\01a154b8-8fd9-7253-8f40-4499a22fa170\earthguard-task\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38C871F0-F3CB-4AC3-849C-5D5BA519388B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD4D48C0-CFDF-4750-AB92-C6080A8D0521}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3090" yWindow="2310" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Status" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1008" uniqueCount="475">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1016" uniqueCount="478">
   <si>
     <t>狀態ID</t>
   </si>
@@ -1482,6 +1482,15 @@
   <si>
     <t>新版技能【火球術／火柱／無限星環】：火屬性持續傷害；每跳量與間隔由技能各階決定（引擎以 dps 覆寫）。</t>
     <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>sgRebirthGuard</t>
+  </si>
+  <si>
+    <t>天地共生減傷</t>
+  </si>
+  <si>
+    <t>天地共生復活後受到的傷害降低；不滅意志擊殺可延長持續時間。</t>
   </si>
 </sst>
 </file>
@@ -2459,13 +2468,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:T96"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:T97"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="18" max="18" width="12.375" customWidth="1"/>
+    <col min="18" max="18" width="12.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2527,7 +2536,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>20</v>
       </c>
@@ -2571,7 +2580,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>28</v>
       </c>
@@ -2618,7 +2627,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>33</v>
       </c>
@@ -2665,7 +2674,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>37</v>
       </c>
@@ -2712,7 +2721,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>42</v>
       </c>
@@ -2759,7 +2768,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>46</v>
       </c>
@@ -2809,7 +2818,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>52</v>
       </c>
@@ -2853,7 +2862,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>58</v>
       </c>
@@ -2897,7 +2906,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>62</v>
       </c>
@@ -2941,7 +2950,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>67</v>
       </c>
@@ -2988,7 +2997,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>72</v>
       </c>
@@ -3035,7 +3044,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>76</v>
       </c>
@@ -3079,7 +3088,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>81</v>
       </c>
@@ -3123,7 +3132,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>84</v>
       </c>
@@ -3167,7 +3176,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>88</v>
       </c>
@@ -3211,7 +3220,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="17" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>92</v>
       </c>
@@ -3255,7 +3264,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>96</v>
       </c>
@@ -3299,7 +3308,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="19" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>100</v>
       </c>
@@ -3343,7 +3352,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="20" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>104</v>
       </c>
@@ -3387,7 +3396,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="21" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>108</v>
       </c>
@@ -3431,7 +3440,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="22" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>112</v>
       </c>
@@ -3475,7 +3484,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="23" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>117</v>
       </c>
@@ -3522,7 +3531,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="24" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>121</v>
       </c>
@@ -3566,7 +3575,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="25" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>124</v>
       </c>
@@ -3613,7 +3622,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="26" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>127</v>
       </c>
@@ -3657,7 +3666,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="27" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>129</v>
       </c>
@@ -3701,7 +3710,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="28" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>131</v>
       </c>
@@ -3745,7 +3754,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="29" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>134</v>
       </c>
@@ -3798,7 +3807,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="30" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>137</v>
       </c>
@@ -3842,7 +3851,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="31" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>140</v>
       </c>
@@ -3886,7 +3895,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="32" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>143</v>
       </c>
@@ -3930,7 +3939,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="33" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>147</v>
       </c>
@@ -3974,7 +3983,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="34" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>151</v>
       </c>
@@ -4021,7 +4030,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="35" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>154</v>
       </c>
@@ -4068,7 +4077,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="36" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>158</v>
       </c>
@@ -4112,7 +4121,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="37" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>164</v>
       </c>
@@ -4162,7 +4171,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="38" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>166</v>
       </c>
@@ -4209,7 +4218,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="39" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>168</v>
       </c>
@@ -4256,7 +4265,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="40" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>172</v>
       </c>
@@ -4303,7 +4312,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="41" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>177</v>
       </c>
@@ -4347,7 +4356,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="42" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>180</v>
       </c>
@@ -4394,7 +4403,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="43" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>184</v>
       </c>
@@ -4441,7 +4450,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="44" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>187</v>
       </c>
@@ -4488,7 +4497,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="45" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>191</v>
       </c>
@@ -4535,7 +4544,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="46" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>195</v>
       </c>
@@ -4582,7 +4591,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="47" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>200</v>
       </c>
@@ -4632,7 +4641,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="48" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>204</v>
       </c>
@@ -4679,7 +4688,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="49" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>208</v>
       </c>
@@ -4726,7 +4735,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="50" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>212</v>
       </c>
@@ -4773,7 +4782,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="51" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>215</v>
       </c>
@@ -4820,7 +4829,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="52" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>219</v>
       </c>
@@ -4867,7 +4876,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="53" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>222</v>
       </c>
@@ -4914,7 +4923,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="54" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>226</v>
       </c>
@@ -4964,7 +4973,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="55" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>229</v>
       </c>
@@ -5011,7 +5020,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="56" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>232</v>
       </c>
@@ -5061,7 +5070,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="57" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>236</v>
       </c>
@@ -5105,7 +5114,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="58" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>239</v>
       </c>
@@ -5152,7 +5161,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="59" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>243</v>
       </c>
@@ -5196,7 +5205,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="60" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>246</v>
       </c>
@@ -5240,7 +5249,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="61" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>250</v>
       </c>
@@ -5284,7 +5293,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="62" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>253</v>
       </c>
@@ -5328,7 +5337,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="63" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>257</v>
       </c>
@@ -5372,7 +5381,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="64" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>261</v>
       </c>
@@ -5419,7 +5428,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="65" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>265</v>
       </c>
@@ -5466,7 +5475,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="66" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>268</v>
       </c>
@@ -5513,7 +5522,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="67" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>272</v>
       </c>
@@ -5557,7 +5566,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="68" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>275</v>
       </c>
@@ -5601,7 +5610,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="69" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>279</v>
       </c>
@@ -5645,7 +5654,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="70" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>282</v>
       </c>
@@ -5689,7 +5698,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="71" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>286</v>
       </c>
@@ -5733,7 +5742,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="72" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>290</v>
       </c>
@@ -5780,7 +5789,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="73" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>293</v>
       </c>
@@ -5827,7 +5836,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="74" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>296</v>
       </c>
@@ -5874,7 +5883,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="75" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>298</v>
       </c>
@@ -5921,7 +5930,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="76" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>301</v>
       </c>
@@ -5968,7 +5977,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="77" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>305</v>
       </c>
@@ -6012,7 +6021,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="78" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>308</v>
       </c>
@@ -6059,7 +6068,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="79" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>311</v>
       </c>
@@ -6106,7 +6115,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="80" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>314</v>
       </c>
@@ -6153,7 +6162,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="81" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>318</v>
       </c>
@@ -6200,7 +6209,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="82" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>321</v>
       </c>
@@ -6247,7 +6256,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="83" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>325</v>
       </c>
@@ -6294,7 +6303,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="84" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A84" s="1" t="s">
         <v>393</v>
       </c>
@@ -6344,7 +6353,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="85" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A85" s="1" t="s">
         <v>400</v>
       </c>
@@ -6394,7 +6403,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="86" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A86" s="1" t="s">
         <v>405</v>
       </c>
@@ -6444,7 +6453,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="87" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A87" s="1" t="s">
         <v>409</v>
       </c>
@@ -6494,7 +6503,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="88" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A88" s="1" t="s">
         <v>413</v>
       </c>
@@ -6544,7 +6553,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="89" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A89" s="1" t="s">
         <v>416</v>
       </c>
@@ -6594,7 +6603,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="90" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A90" s="1" t="s">
         <v>421</v>
       </c>
@@ -6644,7 +6653,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="91" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A91" s="1" t="s">
         <v>434</v>
       </c>
@@ -6691,7 +6700,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="92" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A92" s="1" t="s">
         <v>439</v>
       </c>
@@ -6741,7 +6750,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="93" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A93" s="1" t="s">
         <v>444</v>
       </c>
@@ -6791,7 +6800,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="94" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A94" s="1" t="s">
         <v>450</v>
       </c>
@@ -6838,7 +6847,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="95" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A95" s="1" t="s">
         <v>454</v>
       </c>
@@ -6885,7 +6894,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="96" spans="1:20" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:20" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>467</v>
       </c>
@@ -6930,6 +6939,50 @@
       </c>
       <c r="T96" t="s">
         <v>473</v>
+      </c>
+    </row>
+    <row r="97" spans="1:20" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A97" t="s">
+        <v>475</v>
+      </c>
+      <c r="B97" t="s">
+        <v>476</v>
+      </c>
+      <c r="C97" t="s">
+        <v>74</v>
+      </c>
+      <c r="D97" t="s">
+        <v>65</v>
+      </c>
+      <c r="E97" t="s">
+        <v>79</v>
+      </c>
+      <c r="F97" t="s">
+        <v>475</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="K97">
+        <v>0</v>
+      </c>
+      <c r="L97">
+        <v>50</v>
+      </c>
+      <c r="M97">
+        <v>5</v>
+      </c>
+      <c r="N97">
+        <v>0</v>
+      </c>
+      <c r="O97" t="s">
+        <v>56</v>
+      </c>
+      <c r="P97">
+        <v>1</v>
+      </c>
+      <c r="T97" t="s">
+        <v>477</v>
       </c>
     </row>
   </sheetData>
@@ -6942,412 +6995,412 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:A81"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="125.625" customWidth="1"/>
+    <col min="1" max="1" width="125.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>329</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>331</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>332</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>333</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>334</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>335</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
         <v>336</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
         <v>337</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
         <v>338</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
         <v>339</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:1" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
         <v>341</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
         <v>342</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
         <v>343</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
         <v>344</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
         <v>345</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
         <v>346</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
         <v>347</v>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
         <v>348</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
         <v>349</v>
       </c>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
         <v>350</v>
       </c>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
         <v>351</v>
       </c>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
         <v>352</v>
       </c>
     </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
         <v>353</v>
       </c>
     </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
         <v>354</v>
       </c>
     </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
         <v>355</v>
       </c>
     </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
         <v>356</v>
       </c>
     </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A48" s="2" t="s">
         <v>357</v>
       </c>
     </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A49" s="2" t="s">
         <v>358</v>
       </c>
     </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
         <v>359</v>
       </c>
     </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A52" s="2" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A53" s="2" t="s">
         <v>360</v>
       </c>
     </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="s">
         <v>361</v>
       </c>
     </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A55" s="2" t="s">
         <v>362</v>
       </c>
     </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A56" s="2" t="s">
         <v>363</v>
       </c>
     </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A57" s="2" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A58" s="2" t="s">
         <v>364</v>
       </c>
     </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A59" s="2" t="s">
         <v>365</v>
       </c>
     </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A60" s="2" t="s">
         <v>366</v>
       </c>
     </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A61" s="2" t="s">
         <v>367</v>
       </c>
     </row>
-    <row r="62" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A62" s="2" t="s">
         <v>368</v>
       </c>
     </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A63" s="2" t="s">
         <v>369</v>
       </c>
     </row>
-    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A64" s="2" t="s">
         <v>370</v>
       </c>
     </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A65" s="2" t="s">
         <v>371</v>
       </c>
     </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A66" s="2" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A67" s="2" t="s">
         <v>372</v>
       </c>
     </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A68" s="2" t="s">
         <v>373</v>
       </c>
     </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A69" s="2" t="s">
         <v>374</v>
       </c>
     </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A70" s="2" t="s">
         <v>375</v>
       </c>
     </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A71" s="2" t="s">
         <v>376</v>
       </c>
     </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A72" s="2" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A73" s="2" t="s">
         <v>387</v>
       </c>
     </row>
-    <row r="74" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A74" s="2" t="s">
         <v>388</v>
       </c>
     </row>
-    <row r="75" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A75" s="2" t="s">
         <v>377</v>
       </c>
     </row>
-    <row r="76" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A76" s="2" t="s">
         <v>389</v>
       </c>
     </row>
-    <row r="77" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:1" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A77" s="2" t="s">
         <v>390</v>
       </c>
     </row>
-    <row r="78" spans="1:1" ht="33" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:1" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A78" s="2" t="s">
         <v>423</v>
       </c>
     </row>
-    <row r="79" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A79" s="2" t="s">
         <v>424</v>
       </c>
     </row>
-    <row r="80" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A80" s="2" t="s">
         <v>391</v>
       </c>
     </row>
-    <row r="81" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A81" s="2" t="s">
         <v>392</v>
       </c>

--- a/config/Excel/Status.xlsx
+++ b/config/Excel/Status.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alway\.codex\visualizations\2026\10\19\01a154b8-8fd9-7253-8f40-4499a22fa170\earthguard-task\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyGame\Idle-RPG\codex\config\param-patches\archive\2026-10-20T07-49-18-678Z-33ab5330-ee8d-48d1-9e5c-d6c1c8344d69\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD4D48C0-CFDF-4750-AB92-C6080A8D0521}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4F85197-DD98-4D0A-9B77-D4DEB9E9663A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3090" yWindow="2310" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Status" sheetId="1" r:id="rId1"/>
@@ -711,9 +711,6 @@
     <t>🍃</t>
   </si>
   <si>
-    <t>新版技能【狂風碎裂】：被風刃命中的敵人移動速度下降（效果值＝下降%）。同類型緩速依「取代」規則後蓋前並重新計時。</t>
-  </si>
-  <si>
     <t>sgStormBarrier</t>
   </si>
   <si>
@@ -1491,6 +1488,10 @@
   </si>
   <si>
     <t>天地共生復活後受到的傷害降低；不滅意志擊殺可延長持續時間。</t>
+  </si>
+  <si>
+    <t>新版技能【狂風碎裂】：被風刃命中的敵人移動速度與攻速下降（共用效果值＝各自下降%）。同類型緩速依「取代」規則後蓋前並重新計時。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -2083,7 +2084,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2092,6 +2093,9 @@
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="42">
@@ -2469,12 +2473,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:T97"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="18" max="18" width="12.33203125" customWidth="1"/>
+    <col min="18" max="18" width="12.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2536,7 +2540,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>20</v>
       </c>
@@ -2580,7 +2584,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>28</v>
       </c>
@@ -2627,7 +2631,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>33</v>
       </c>
@@ -2674,7 +2678,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>37</v>
       </c>
@@ -2721,7 +2725,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>42</v>
       </c>
@@ -2768,7 +2772,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>46</v>
       </c>
@@ -2818,7 +2822,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>52</v>
       </c>
@@ -2862,7 +2866,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>58</v>
       </c>
@@ -2906,7 +2910,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>62</v>
       </c>
@@ -2950,7 +2954,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>67</v>
       </c>
@@ -2997,7 +3001,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>72</v>
       </c>
@@ -3044,7 +3048,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>76</v>
       </c>
@@ -3088,7 +3092,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>81</v>
       </c>
@@ -3132,7 +3136,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>84</v>
       </c>
@@ -3176,7 +3180,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>88</v>
       </c>
@@ -3220,7 +3224,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="17" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>92</v>
       </c>
@@ -3264,7 +3268,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>96</v>
       </c>
@@ -3308,7 +3312,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="19" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>100</v>
       </c>
@@ -3352,7 +3356,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="20" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>104</v>
       </c>
@@ -3396,7 +3400,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="21" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>108</v>
       </c>
@@ -3440,12 +3444,12 @@
         <v>111</v>
       </c>
     </row>
-    <row r="22" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>112</v>
       </c>
       <c r="B22" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="C22" t="s">
         <v>113</v>
@@ -3481,10 +3485,10 @@
         <v>1</v>
       </c>
       <c r="T22" t="s">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="23" spans="1:20" x14ac:dyDescent="0.3">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="23" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>117</v>
       </c>
@@ -3531,7 +3535,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="24" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>121</v>
       </c>
@@ -3575,7 +3579,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="25" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>124</v>
       </c>
@@ -3622,7 +3626,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="26" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>127</v>
       </c>
@@ -3666,7 +3670,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="27" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>129</v>
       </c>
@@ -3710,7 +3714,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="28" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>131</v>
       </c>
@@ -3754,7 +3758,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="29" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>134</v>
       </c>
@@ -3798,16 +3802,16 @@
         <v>1</v>
       </c>
       <c r="Q29" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="S29" s="1" t="s">
         <v>378</v>
-      </c>
-      <c r="S29" s="1" t="s">
-        <v>379</v>
       </c>
       <c r="T29" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="30" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>137</v>
       </c>
@@ -3851,7 +3855,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="31" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>140</v>
       </c>
@@ -3895,7 +3899,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="32" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>143</v>
       </c>
@@ -3939,7 +3943,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="33" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>147</v>
       </c>
@@ -3983,7 +3987,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="34" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>151</v>
       </c>
@@ -4024,13 +4028,13 @@
         <v>1</v>
       </c>
       <c r="R34" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="T34" s="1" t="s">
         <v>425</v>
       </c>
-      <c r="T34" s="1" t="s">
-        <v>426</v>
-      </c>
-    </row>
-    <row r="35" spans="1:20" x14ac:dyDescent="0.3">
+    </row>
+    <row r="35" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>154</v>
       </c>
@@ -4071,13 +4075,13 @@
         <v>1</v>
       </c>
       <c r="R35" s="1" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="T35" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="36" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>158</v>
       </c>
@@ -4121,7 +4125,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="37" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>164</v>
       </c>
@@ -4165,13 +4169,13 @@
         <v>1</v>
       </c>
       <c r="S37" s="1" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="T37" t="s">
-        <v>474</v>
-      </c>
-    </row>
-    <row r="38" spans="1:20" x14ac:dyDescent="0.3">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="38" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>166</v>
       </c>
@@ -4209,16 +4213,16 @@
         <v>0</v>
       </c>
       <c r="O38" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="P38">
         <v>50</v>
       </c>
       <c r="T38" t="s">
-        <v>465</v>
-      </c>
-    </row>
-    <row r="39" spans="1:20" x14ac:dyDescent="0.3">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="39" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>168</v>
       </c>
@@ -4265,7 +4269,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="40" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>172</v>
       </c>
@@ -4312,7 +4316,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="41" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>177</v>
       </c>
@@ -4356,7 +4360,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="42" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>180</v>
       </c>
@@ -4403,7 +4407,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="43" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>184</v>
       </c>
@@ -4450,7 +4454,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="44" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>187</v>
       </c>
@@ -4497,7 +4501,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="45" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>191</v>
       </c>
@@ -4544,7 +4548,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="46" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>195</v>
       </c>
@@ -4591,7 +4595,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="47" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>200</v>
       </c>
@@ -4635,13 +4639,13 @@
         <v>1</v>
       </c>
       <c r="S47" s="1" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="T47" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="48" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>204</v>
       </c>
@@ -4688,7 +4692,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="49" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>208</v>
       </c>
@@ -4735,7 +4739,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="50" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>212</v>
       </c>
@@ -4782,7 +4786,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="51" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>215</v>
       </c>
@@ -4829,7 +4833,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="52" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>219</v>
       </c>
@@ -4876,7 +4880,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="53" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>222</v>
       </c>
@@ -4905,7 +4909,7 @@
         <v>0</v>
       </c>
       <c r="L53">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="M53">
         <v>3</v>
@@ -4919,16 +4923,16 @@
       <c r="P53">
         <v>1</v>
       </c>
-      <c r="T53" t="s">
+      <c r="T53" s="3" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="54" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="54" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A54" t="s">
+      <c r="B54" t="s">
         <v>226</v>
-      </c>
-      <c r="B54" t="s">
-        <v>227</v>
       </c>
       <c r="C54" t="s">
         <v>153</v>
@@ -4940,7 +4944,7 @@
         <v>79</v>
       </c>
       <c r="F54" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="G54" t="s">
         <v>217</v>
@@ -4967,18 +4971,18 @@
         <v>1</v>
       </c>
       <c r="R54" s="1" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="T54" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="55" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
         <v>228</v>
       </c>
-    </row>
-    <row r="55" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A55" t="s">
+      <c r="B55" t="s">
         <v>229</v>
-      </c>
-      <c r="B55" t="s">
-        <v>230</v>
       </c>
       <c r="C55" t="s">
         <v>90</v>
@@ -4990,7 +4994,7 @@
         <v>79</v>
       </c>
       <c r="F55" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="G55" t="s">
         <v>217</v>
@@ -5017,18 +5021,18 @@
         <v>1</v>
       </c>
       <c r="T55" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="56" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="56" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A56" t="s">
+      <c r="B56" t="s">
         <v>232</v>
       </c>
-      <c r="B56" t="s">
+      <c r="C56" t="s">
         <v>233</v>
-      </c>
-      <c r="C56" t="s">
-        <v>234</v>
       </c>
       <c r="D56" t="s">
         <v>65</v>
@@ -5037,7 +5041,7 @@
         <v>79</v>
       </c>
       <c r="F56" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="G56" t="s">
         <v>217</v>
@@ -5064,18 +5068,18 @@
         <v>1</v>
       </c>
       <c r="R56" s="1" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="T56" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="57" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
         <v>235</v>
       </c>
-    </row>
-    <row r="57" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A57" t="s">
+      <c r="B57" t="s">
         <v>236</v>
-      </c>
-      <c r="B57" t="s">
-        <v>237</v>
       </c>
       <c r="C57" t="s">
         <v>39</v>
@@ -5087,7 +5091,7 @@
         <v>79</v>
       </c>
       <c r="F57" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="I57">
         <v>0</v>
@@ -5111,18 +5115,18 @@
         <v>10</v>
       </c>
       <c r="T57" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="58" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
         <v>238</v>
       </c>
-    </row>
-    <row r="58" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A58" t="s">
+      <c r="B58" t="s">
         <v>239</v>
       </c>
-      <c r="B58" t="s">
+      <c r="C58" t="s">
         <v>240</v>
-      </c>
-      <c r="C58" t="s">
-        <v>241</v>
       </c>
       <c r="D58" t="s">
         <v>23</v>
@@ -5131,7 +5135,7 @@
         <v>79</v>
       </c>
       <c r="F58" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="G58" t="s">
         <v>40</v>
@@ -5158,15 +5162,15 @@
         <v>100</v>
       </c>
       <c r="T58" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="59" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
         <v>242</v>
       </c>
-    </row>
-    <row r="59" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A59" t="s">
+      <c r="B59" t="s">
         <v>243</v>
-      </c>
-      <c r="B59" t="s">
-        <v>244</v>
       </c>
       <c r="C59" t="s">
         <v>22</v>
@@ -5202,18 +5206,18 @@
         <v>1</v>
       </c>
       <c r="T59" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="60" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
         <v>245</v>
       </c>
-    </row>
-    <row r="60" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A60" t="s">
+      <c r="B60" t="s">
         <v>246</v>
       </c>
-      <c r="B60" t="s">
+      <c r="C60" t="s">
         <v>247</v>
-      </c>
-      <c r="C60" t="s">
-        <v>248</v>
       </c>
       <c r="D60" t="s">
         <v>65</v>
@@ -5222,7 +5226,7 @@
         <v>79</v>
       </c>
       <c r="F60" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="I60">
         <v>0</v>
@@ -5246,15 +5250,15 @@
         <v>1</v>
       </c>
       <c r="T60" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="61" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
         <v>249</v>
       </c>
-    </row>
-    <row r="61" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A61" t="s">
+      <c r="B61" t="s">
         <v>250</v>
-      </c>
-      <c r="B61" t="s">
-        <v>251</v>
       </c>
       <c r="C61" t="s">
         <v>35</v>
@@ -5266,7 +5270,7 @@
         <v>79</v>
       </c>
       <c r="F61" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="I61">
         <v>0</v>
@@ -5290,18 +5294,18 @@
         <v>20</v>
       </c>
       <c r="T61" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="62" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
         <v>252</v>
       </c>
-    </row>
-    <row r="62" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A62" t="s">
+      <c r="B62" t="s">
         <v>253</v>
       </c>
-      <c r="B62" t="s">
+      <c r="C62" t="s">
         <v>254</v>
-      </c>
-      <c r="C62" t="s">
-        <v>255</v>
       </c>
       <c r="D62" t="s">
         <v>65</v>
@@ -5310,7 +5314,7 @@
         <v>79</v>
       </c>
       <c r="F62" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="I62">
         <v>0</v>
@@ -5334,18 +5338,18 @@
         <v>1</v>
       </c>
       <c r="T62" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="63" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="63" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A63" t="s">
+      <c r="B63" t="s">
         <v>257</v>
       </c>
-      <c r="B63" t="s">
+      <c r="C63" t="s">
         <v>258</v>
-      </c>
-      <c r="C63" t="s">
-        <v>259</v>
       </c>
       <c r="D63" t="s">
         <v>65</v>
@@ -5354,7 +5358,7 @@
         <v>79</v>
       </c>
       <c r="F63" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="I63">
         <v>0</v>
@@ -5378,18 +5382,18 @@
         <v>100</v>
       </c>
       <c r="T63" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="64" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
         <v>260</v>
       </c>
-    </row>
-    <row r="64" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A64" t="s">
+      <c r="B64" t="s">
         <v>261</v>
       </c>
-      <c r="B64" t="s">
+      <c r="C64" t="s">
         <v>262</v>
-      </c>
-      <c r="C64" t="s">
-        <v>263</v>
       </c>
       <c r="D64" t="s">
         <v>23</v>
@@ -5425,18 +5429,18 @@
         <v>10</v>
       </c>
       <c r="T64" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="65" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
         <v>264</v>
       </c>
-    </row>
-    <row r="65" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A65" t="s">
+      <c r="B65" t="s">
         <v>265</v>
       </c>
-      <c r="B65" t="s">
+      <c r="C65" t="s">
         <v>266</v>
-      </c>
-      <c r="C65" t="s">
-        <v>267</v>
       </c>
       <c r="D65" t="s">
         <v>23</v>
@@ -5472,18 +5476,18 @@
         <v>20</v>
       </c>
       <c r="T65" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="66" spans="1:20" x14ac:dyDescent="0.3">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="66" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
+        <v>267</v>
+      </c>
+      <c r="B66" t="s">
         <v>268</v>
       </c>
-      <c r="B66" t="s">
+      <c r="C66" t="s">
         <v>269</v>
-      </c>
-      <c r="C66" t="s">
-        <v>270</v>
       </c>
       <c r="D66" t="s">
         <v>65</v>
@@ -5492,7 +5496,7 @@
         <v>79</v>
       </c>
       <c r="F66" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="I66">
         <v>0</v>
@@ -5516,21 +5520,21 @@
         <v>1</v>
       </c>
       <c r="R66" s="1" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="T66" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="67" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
         <v>271</v>
       </c>
-    </row>
-    <row r="67" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A67" t="s">
+      <c r="B67" t="s">
         <v>272</v>
       </c>
-      <c r="B67" t="s">
-        <v>273</v>
-      </c>
       <c r="C67" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D67" t="s">
         <v>23</v>
@@ -5539,7 +5543,7 @@
         <v>79</v>
       </c>
       <c r="F67" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="I67">
         <v>0</v>
@@ -5563,18 +5567,18 @@
         <v>1</v>
       </c>
       <c r="T67" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="68" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
         <v>274</v>
       </c>
-    </row>
-    <row r="68" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A68" t="s">
+      <c r="B68" t="s">
         <v>275</v>
       </c>
-      <c r="B68" t="s">
+      <c r="C68" t="s">
         <v>276</v>
-      </c>
-      <c r="C68" t="s">
-        <v>277</v>
       </c>
       <c r="D68" t="s">
         <v>65</v>
@@ -5583,7 +5587,7 @@
         <v>79</v>
       </c>
       <c r="F68" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="I68">
         <v>0</v>
@@ -5607,15 +5611,15 @@
         <v>1</v>
       </c>
       <c r="T68" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="69" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
         <v>278</v>
       </c>
-    </row>
-    <row r="69" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A69" t="s">
+      <c r="B69" t="s">
         <v>279</v>
-      </c>
-      <c r="B69" t="s">
-        <v>280</v>
       </c>
       <c r="C69" t="s">
         <v>22</v>
@@ -5627,7 +5631,7 @@
         <v>79</v>
       </c>
       <c r="F69" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="I69">
         <v>0</v>
@@ -5651,18 +5655,18 @@
         <v>50</v>
       </c>
       <c r="T69" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="70" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="70" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A70" t="s">
+      <c r="B70" t="s">
         <v>282</v>
       </c>
-      <c r="B70" t="s">
+      <c r="C70" t="s">
         <v>283</v>
-      </c>
-      <c r="C70" t="s">
-        <v>284</v>
       </c>
       <c r="D70" t="s">
         <v>65</v>
@@ -5671,7 +5675,7 @@
         <v>79</v>
       </c>
       <c r="F70" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="I70">
         <v>0</v>
@@ -5695,18 +5699,18 @@
         <v>10</v>
       </c>
       <c r="T70" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="71" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
         <v>285</v>
       </c>
-    </row>
-    <row r="71" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A71" t="s">
+      <c r="B71" t="s">
         <v>286</v>
       </c>
-      <c r="B71" t="s">
+      <c r="C71" t="s">
         <v>287</v>
-      </c>
-      <c r="C71" t="s">
-        <v>288</v>
       </c>
       <c r="D71" t="s">
         <v>65</v>
@@ -5715,7 +5719,7 @@
         <v>79</v>
       </c>
       <c r="F71" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="I71">
         <v>0</v>
@@ -5739,18 +5743,18 @@
         <v>100</v>
       </c>
       <c r="T71" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="72" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
         <v>289</v>
       </c>
-    </row>
-    <row r="72" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A72" t="s">
+      <c r="B72" t="s">
         <v>290</v>
       </c>
-      <c r="B72" t="s">
+      <c r="C72" t="s">
         <v>291</v>
-      </c>
-      <c r="C72" t="s">
-        <v>292</v>
       </c>
       <c r="D72" t="s">
         <v>65</v>
@@ -5759,7 +5763,7 @@
         <v>79</v>
       </c>
       <c r="F72" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="I72">
         <v>0</v>
@@ -5783,18 +5787,18 @@
         <v>1</v>
       </c>
       <c r="R72" s="1" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="T72" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="73" spans="1:20" x14ac:dyDescent="0.3">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="73" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
+        <v>292</v>
+      </c>
+      <c r="B73" t="s">
         <v>293</v>
-      </c>
-      <c r="B73" t="s">
-        <v>294</v>
       </c>
       <c r="C73" t="s">
         <v>170</v>
@@ -5806,7 +5810,7 @@
         <v>79</v>
       </c>
       <c r="F73" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="G73" t="s">
         <v>31</v>
@@ -5833,15 +5837,15 @@
         <v>1</v>
       </c>
       <c r="T73" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="74" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
         <v>295</v>
       </c>
-    </row>
-    <row r="74" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A74" t="s">
+      <c r="B74" t="s">
         <v>296</v>
-      </c>
-      <c r="B74" t="s">
-        <v>297</v>
       </c>
       <c r="C74" t="s">
         <v>30</v>
@@ -5853,7 +5857,7 @@
         <v>79</v>
       </c>
       <c r="F74" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="G74" t="s">
         <v>31</v>
@@ -5880,18 +5884,18 @@
         <v>1</v>
       </c>
       <c r="T74" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="75" spans="1:20" x14ac:dyDescent="0.3">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="75" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
+        <v>297</v>
+      </c>
+      <c r="B75" t="s">
         <v>298</v>
       </c>
-      <c r="B75" t="s">
+      <c r="C75" t="s">
         <v>299</v>
-      </c>
-      <c r="C75" t="s">
-        <v>300</v>
       </c>
       <c r="D75" t="s">
         <v>23</v>
@@ -5900,7 +5904,7 @@
         <v>79</v>
       </c>
       <c r="F75" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="G75" t="s">
         <v>175</v>
@@ -5927,18 +5931,18 @@
         <v>1</v>
       </c>
       <c r="T75" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="76" spans="1:20" x14ac:dyDescent="0.3">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="76" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
+        <v>300</v>
+      </c>
+      <c r="B76" t="s">
         <v>301</v>
       </c>
-      <c r="B76" t="s">
+      <c r="C76" t="s">
         <v>302</v>
-      </c>
-      <c r="C76" t="s">
-        <v>303</v>
       </c>
       <c r="D76" t="s">
         <v>23</v>
@@ -5947,7 +5951,7 @@
         <v>79</v>
       </c>
       <c r="F76" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="G76" t="s">
         <v>175</v>
@@ -5974,15 +5978,15 @@
         <v>1</v>
       </c>
       <c r="T76" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="77" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
         <v>304</v>
       </c>
-    </row>
-    <row r="77" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A77" t="s">
+      <c r="B77" t="s">
         <v>305</v>
-      </c>
-      <c r="B77" t="s">
-        <v>306</v>
       </c>
       <c r="C77" t="s">
         <v>22</v>
@@ -6018,15 +6022,15 @@
         <v>1</v>
       </c>
       <c r="T77" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="78" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
         <v>307</v>
       </c>
-    </row>
-    <row r="78" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A78" t="s">
+      <c r="B78" t="s">
         <v>308</v>
-      </c>
-      <c r="B78" t="s">
-        <v>309</v>
       </c>
       <c r="C78" t="s">
         <v>44</v>
@@ -6065,15 +6069,15 @@
         <v>1</v>
       </c>
       <c r="T78" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="79" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
         <v>310</v>
       </c>
-    </row>
-    <row r="79" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A79" t="s">
+      <c r="B79" t="s">
         <v>311</v>
-      </c>
-      <c r="B79" t="s">
-        <v>312</v>
       </c>
       <c r="C79" t="s">
         <v>189</v>
@@ -6085,7 +6089,7 @@
         <v>79</v>
       </c>
       <c r="F79" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="G79" t="s">
         <v>31</v>
@@ -6112,18 +6116,18 @@
         <v>1</v>
       </c>
       <c r="T79" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="80" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
         <v>313</v>
       </c>
-    </row>
-    <row r="80" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A80" t="s">
+      <c r="B80" t="s">
         <v>314</v>
       </c>
-      <c r="B80" t="s">
+      <c r="C80" t="s">
         <v>315</v>
-      </c>
-      <c r="C80" t="s">
-        <v>316</v>
       </c>
       <c r="D80" t="s">
         <v>65</v>
@@ -6132,7 +6136,7 @@
         <v>79</v>
       </c>
       <c r="F80" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="G80" t="s">
         <v>115</v>
@@ -6159,15 +6163,15 @@
         <v>100</v>
       </c>
       <c r="T80" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="81" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
         <v>317</v>
       </c>
-    </row>
-    <row r="81" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A81" t="s">
+      <c r="B81" t="s">
         <v>318</v>
-      </c>
-      <c r="B81" t="s">
-        <v>319</v>
       </c>
       <c r="C81" t="s">
         <v>86</v>
@@ -6179,7 +6183,7 @@
         <v>79</v>
       </c>
       <c r="F81" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="G81" t="s">
         <v>115</v>
@@ -6206,18 +6210,18 @@
         <v>1</v>
       </c>
       <c r="T81" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="82" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
         <v>320</v>
       </c>
-    </row>
-    <row r="82" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A82" t="s">
+      <c r="B82" t="s">
         <v>321</v>
       </c>
-      <c r="B82" t="s">
+      <c r="C82" t="s">
         <v>322</v>
-      </c>
-      <c r="C82" t="s">
-        <v>323</v>
       </c>
       <c r="D82" t="s">
         <v>23</v>
@@ -6226,7 +6230,7 @@
         <v>79</v>
       </c>
       <c r="F82" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="G82" t="s">
         <v>198</v>
@@ -6253,18 +6257,18 @@
         <v>1</v>
       </c>
       <c r="T82" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="83" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
         <v>324</v>
       </c>
-    </row>
-    <row r="83" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A83" t="s">
+      <c r="B83" t="s">
         <v>325</v>
       </c>
-      <c r="B83" t="s">
+      <c r="C83" t="s">
         <v>326</v>
-      </c>
-      <c r="C83" t="s">
-        <v>327</v>
       </c>
       <c r="D83" t="s">
         <v>23</v>
@@ -6273,7 +6277,7 @@
         <v>79</v>
       </c>
       <c r="F83" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="G83" t="s">
         <v>217</v>
@@ -6300,18 +6304,18 @@
         <v>1</v>
       </c>
       <c r="T83" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="84" spans="1:20" x14ac:dyDescent="0.3">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="84" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="B84" s="1" t="s">
         <v>393</v>
       </c>
-      <c r="B84" s="1" t="s">
-        <v>394</v>
-      </c>
       <c r="C84" s="1" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="D84" s="1" t="s">
         <v>65</v>
@@ -6320,48 +6324,48 @@
         <v>79</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="G84" s="1" t="s">
         <v>40</v>
       </c>
       <c r="I84" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="K84" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="L84" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="M84" s="1" t="s">
         <v>395</v>
       </c>
-      <c r="K84" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="L84" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="M84" s="1" t="s">
-        <v>396</v>
-      </c>
       <c r="N84" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="O84" s="1" t="s">
         <v>56</v>
       </c>
       <c r="P84" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="R84" s="1" t="s">
         <v>397</v>
       </c>
-      <c r="R84" s="1" t="s">
+      <c r="T84" s="1" t="s">
         <v>398</v>
       </c>
-      <c r="T84" s="1" t="s">
+    </row>
+    <row r="85" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A85" s="1" t="s">
         <v>399</v>
       </c>
-    </row>
-    <row r="85" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A85" s="1" t="s">
+      <c r="B85" s="1" t="s">
         <v>400</v>
       </c>
-      <c r="B85" s="1" t="s">
+      <c r="C85" s="1" t="s">
         <v>401</v>
-      </c>
-      <c r="C85" s="1" t="s">
-        <v>402</v>
       </c>
       <c r="D85" s="1" t="s">
         <v>65</v>
@@ -6370,45 +6374,45 @@
         <v>79</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="G85" s="1" t="s">
         <v>33</v>
       </c>
       <c r="I85" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="K85" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="L85" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="M85" s="1" t="s">
         <v>395</v>
       </c>
-      <c r="K85" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="L85" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="M85" s="1" t="s">
-        <v>396</v>
-      </c>
       <c r="N85" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="O85" s="1" t="s">
         <v>56</v>
       </c>
       <c r="P85" s="1" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="R85" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="T85" s="1" t="s">
         <v>403</v>
       </c>
-      <c r="T85" s="1" t="s">
+    </row>
+    <row r="86" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A86" s="1" t="s">
         <v>404</v>
       </c>
-    </row>
-    <row r="86" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A86" s="1" t="s">
+      <c r="B86" s="1" t="s">
         <v>405</v>
-      </c>
-      <c r="B86" s="1" t="s">
-        <v>406</v>
       </c>
       <c r="C86" s="1" t="s">
         <v>30</v>
@@ -6420,48 +6424,48 @@
         <v>79</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="G86" s="1" t="s">
         <v>31</v>
       </c>
       <c r="I86" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="K86" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="L86" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="M86" s="1" t="s">
         <v>395</v>
       </c>
-      <c r="K86" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="L86" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="M86" s="1" t="s">
-        <v>396</v>
-      </c>
       <c r="N86" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="O86" s="1" t="s">
         <v>56</v>
       </c>
       <c r="P86" s="1" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="R86" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="T86" s="1" t="s">
         <v>407</v>
       </c>
-      <c r="T86" s="1" t="s">
+    </row>
+    <row r="87" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A87" s="1" t="s">
         <v>408</v>
       </c>
-    </row>
-    <row r="87" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A87" s="1" t="s">
+      <c r="B87" s="1" t="s">
         <v>409</v>
       </c>
-      <c r="B87" s="1" t="s">
-        <v>410</v>
-      </c>
       <c r="C87" s="1" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="D87" s="1" t="s">
         <v>65</v>
@@ -6470,48 +6474,48 @@
         <v>79</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="G87" s="1" t="s">
         <v>175</v>
       </c>
       <c r="I87" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="K87" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="L87" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="M87" s="1" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="N87" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="O87" s="1" t="s">
         <v>56</v>
       </c>
       <c r="P87" s="1" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="R87" s="1" t="s">
+        <v>411</v>
+      </c>
+      <c r="T87" s="1" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="88" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A88" s="1" t="s">
         <v>412</v>
       </c>
-      <c r="T87" s="1" t="s">
-        <v>433</v>
-      </c>
-    </row>
-    <row r="88" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A88" s="1" t="s">
+      <c r="B88" s="1" t="s">
         <v>413</v>
       </c>
-      <c r="B88" s="1" t="s">
-        <v>414</v>
-      </c>
       <c r="C88" s="1" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="D88" s="1" t="s">
         <v>65</v>
@@ -6520,48 +6524,48 @@
         <v>79</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="G88" s="1" t="s">
         <v>175</v>
       </c>
       <c r="I88" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="K88" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="L88" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="M88" s="1" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="N88" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="O88" s="1" t="s">
         <v>56</v>
       </c>
       <c r="P88" s="1" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="R88" s="1" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="T88" s="1" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="89" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A89" s="1" t="s">
         <v>415</v>
       </c>
-    </row>
-    <row r="89" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A89" s="1" t="s">
+      <c r="B89" s="1" t="s">
         <v>416</v>
       </c>
-      <c r="B89" s="1" t="s">
+      <c r="C89" s="1" t="s">
         <v>417</v>
-      </c>
-      <c r="C89" s="1" t="s">
-        <v>418</v>
       </c>
       <c r="D89" s="1" t="s">
         <v>65</v>
@@ -6570,48 +6574,48 @@
         <v>79</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="G89" s="1" t="s">
         <v>198</v>
       </c>
       <c r="I89" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="K89" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="L89" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="M89" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="N89" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="O89" s="1" t="s">
         <v>56</v>
       </c>
       <c r="P89" s="1" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="R89" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="T89" s="1" t="s">
         <v>428</v>
       </c>
-      <c r="T89" s="1" t="s">
-        <v>429</v>
-      </c>
-    </row>
-    <row r="90" spans="1:20" x14ac:dyDescent="0.3">
+    </row>
+    <row r="90" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="B90" s="1" t="s">
         <v>421</v>
       </c>
-      <c r="B90" s="1" t="s">
-        <v>422</v>
-      </c>
       <c r="C90" s="1" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="D90" s="1" t="s">
         <v>65</v>
@@ -6620,45 +6624,45 @@
         <v>79</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="G90" s="1" t="s">
         <v>198</v>
       </c>
       <c r="I90" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="K90" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="L90" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="M90" s="1" t="s">
         <v>395</v>
       </c>
-      <c r="K90" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="L90" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="M90" s="1" t="s">
-        <v>396</v>
-      </c>
       <c r="N90" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="O90" s="1" t="s">
         <v>56</v>
       </c>
       <c r="P90" s="1" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="R90" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="T90" s="1" t="s">
-        <v>430</v>
-      </c>
-    </row>
-    <row r="91" spans="1:20" x14ac:dyDescent="0.3">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="91" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="B91" s="1" t="s">
         <v>434</v>
-      </c>
-      <c r="B91" s="1" t="s">
-        <v>435</v>
       </c>
       <c r="C91" s="1" t="s">
         <v>74</v>
@@ -6670,45 +6674,45 @@
         <v>79</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="I91" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="K91" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="L91" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="M91" s="1" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="N91" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="O91" s="1" t="s">
         <v>56</v>
       </c>
       <c r="P91" s="1" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="R91" s="1" t="s">
+        <v>436</v>
+      </c>
+      <c r="T91" s="1" t="s">
         <v>437</v>
       </c>
-      <c r="T91" s="1" t="s">
+    </row>
+    <row r="92" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A92" s="1" t="s">
         <v>438</v>
       </c>
-    </row>
-    <row r="92" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A92" s="1" t="s">
+      <c r="B92" s="1" t="s">
         <v>439</v>
       </c>
-      <c r="B92" s="1" t="s">
-        <v>440</v>
-      </c>
       <c r="C92" s="1" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D92" s="1" t="s">
         <v>65</v>
@@ -6717,45 +6721,45 @@
         <v>79</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="I92" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="K92" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="L92" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="M92" s="1" t="s">
         <v>395</v>
       </c>
-      <c r="K92" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="L92" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="M92" s="1" t="s">
-        <v>396</v>
-      </c>
       <c r="N92" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="O92" s="1" t="s">
         <v>56</v>
       </c>
       <c r="P92" s="1" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="Q92" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="R92" s="1" t="s">
         <v>441</v>
       </c>
-      <c r="R92" s="1" t="s">
+      <c r="T92" s="1" t="s">
         <v>442</v>
       </c>
-      <c r="T92" s="1" t="s">
+    </row>
+    <row r="93" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A93" s="1" t="s">
         <v>443</v>
       </c>
-    </row>
-    <row r="93" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A93" s="1" t="s">
+      <c r="B93" s="1" t="s">
         <v>444</v>
-      </c>
-      <c r="B93" s="1" t="s">
-        <v>445</v>
       </c>
       <c r="C93" s="1" t="s">
         <v>30</v>
@@ -6767,42 +6771,42 @@
         <v>79</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="I93" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="K93" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="L93" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="M93" s="1" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="N93" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="O93" s="1" t="s">
         <v>56</v>
       </c>
       <c r="P93" s="1" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="Q93" s="1" t="s">
+        <v>446</v>
+      </c>
+      <c r="R93" s="1" t="s">
         <v>447</v>
       </c>
-      <c r="R93" s="1" t="s">
+      <c r="T93" s="1" t="s">
         <v>448</v>
       </c>
-      <c r="T93" s="1" t="s">
+    </row>
+    <row r="94" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A94" s="1" t="s">
         <v>449</v>
-      </c>
-    </row>
-    <row r="94" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A94" s="1" t="s">
-        <v>450</v>
       </c>
       <c r="B94" s="1" t="s">
         <v>68</v>
@@ -6817,45 +6821,45 @@
         <v>79</v>
       </c>
       <c r="F94" s="1" t="s">
+        <v>449</v>
+      </c>
+      <c r="I94" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="K94" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="L94" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="M94" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="N94" s="1" t="s">
         <v>450</v>
-      </c>
-      <c r="I94" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="K94" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="L94" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="M94" s="1" t="s">
-        <v>396</v>
-      </c>
-      <c r="N94" s="1" t="s">
-        <v>451</v>
       </c>
       <c r="O94" s="1" t="s">
         <v>56</v>
       </c>
       <c r="P94" s="1" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="S94" s="1" t="s">
+        <v>451</v>
+      </c>
+      <c r="T94" s="1" t="s">
         <v>452</v>
       </c>
-      <c r="T94" s="1" t="s">
+    </row>
+    <row r="95" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A95" s="1" t="s">
         <v>453</v>
       </c>
-    </row>
-    <row r="95" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A95" s="1" t="s">
+      <c r="B95" s="1" t="s">
         <v>454</v>
       </c>
-      <c r="B95" s="1" t="s">
+      <c r="C95" s="1" t="s">
         <v>455</v>
-      </c>
-      <c r="C95" s="1" t="s">
-        <v>456</v>
       </c>
       <c r="D95" s="1" t="s">
         <v>23</v>
@@ -6864,57 +6868,57 @@
         <v>79</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="I95" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="K95" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="L95" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="M95" s="1" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="N95" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="O95" s="1" t="s">
         <v>56</v>
       </c>
       <c r="P95" s="1" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="Q95" s="1" t="s">
+        <v>457</v>
+      </c>
+      <c r="T95" s="1" t="s">
         <v>458</v>
       </c>
-      <c r="T95" s="1" t="s">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="96" spans="1:20" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="96" spans="1:20" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
+        <v>466</v>
+      </c>
+      <c r="B96" t="s">
         <v>467</v>
       </c>
-      <c r="B96" t="s">
+      <c r="C96" t="s">
         <v>468</v>
       </c>
-      <c r="C96" t="s">
+      <c r="D96" t="s">
         <v>469</v>
       </c>
-      <c r="D96" t="s">
+      <c r="E96" t="s">
         <v>470</v>
       </c>
-      <c r="E96" t="s">
+      <c r="F96" t="s">
+        <v>466</v>
+      </c>
+      <c r="G96" t="s">
         <v>471</v>
-      </c>
-      <c r="F96" t="s">
-        <v>467</v>
-      </c>
-      <c r="G96" t="s">
-        <v>472</v>
       </c>
       <c r="I96">
         <v>0</v>
@@ -6932,21 +6936,21 @@
         <v>0</v>
       </c>
       <c r="O96" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="P96">
         <v>50</v>
       </c>
       <c r="T96" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="97" spans="1:20" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="97" spans="1:20" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
+        <v>474</v>
+      </c>
+      <c r="B97" t="s">
         <v>475</v>
-      </c>
-      <c r="B97" t="s">
-        <v>476</v>
       </c>
       <c r="C97" t="s">
         <v>74</v>
@@ -6958,7 +6962,7 @@
         <v>79</v>
       </c>
       <c r="F97" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="I97">
         <v>0</v>
@@ -6982,7 +6986,7 @@
         <v>1</v>
       </c>
       <c r="T97" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
     </row>
   </sheetData>
@@ -6995,414 +6999,414 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:A81"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="125.6640625" customWidth="1"/>
+    <col min="1" max="1" width="125.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
         <v>329</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
         <v>331</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A6" s="2" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
         <v>333</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A10" s="2" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
         <v>335</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A14" s="2" t="s">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
         <v>336</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A15" s="2" t="s">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
         <v>337</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A16" s="2" t="s">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
         <v>338</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A17" s="2" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="20" spans="1:1" ht="32.4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A21" s="2" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A21" s="2" t="s">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A22" s="2" t="s">
         <v>341</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A22" s="2" t="s">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A23" s="2" t="s">
         <v>342</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A23" s="2" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A27" s="2" t="s">
         <v>344</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A27" s="2" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A31" s="2" t="s">
         <v>346</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A31" s="2" t="s">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A32" s="2" t="s">
         <v>347</v>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A32" s="2" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A36" s="2" t="s">
         <v>349</v>
       </c>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A36" s="2" t="s">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A37" s="2" t="s">
         <v>350</v>
       </c>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A37" s="2" t="s">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A38" s="2" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A39" s="2" t="s">
         <v>351</v>
       </c>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A38" s="2" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A39" s="2" t="s">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A40" s="2" t="s">
         <v>352</v>
       </c>
     </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A40" s="2" t="s">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A41" s="2" t="s">
         <v>353</v>
       </c>
     </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A41" s="2" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.3">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A45" s="2" t="s">
         <v>355</v>
       </c>
     </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A45" s="2" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.3">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A49" s="2" t="s">
         <v>357</v>
       </c>
     </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A49" s="2" t="s">
+    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A50" s="2" t="s">
         <v>358</v>
       </c>
     </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A50" s="2" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.3">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A54" s="2" t="s">
         <v>360</v>
       </c>
     </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A54" s="2" t="s">
+    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A55" s="2" t="s">
         <v>361</v>
       </c>
     </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A55" s="2" t="s">
+    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A56" s="2" t="s">
         <v>362</v>
       </c>
     </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A56" s="2" t="s">
+    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A57" s="2" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A58" s="2" t="s">
         <v>363</v>
       </c>
     </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A57" s="2" t="s">
+    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A59" s="2" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A60" s="2" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A61" s="2" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A62" s="2" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A63" s="2" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A64" s="2" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A65" s="2" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A66" s="2" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A67" s="2" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A68" s="2" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A69" s="2" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A70" s="2" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A71" s="2" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A72" s="2" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A73" s="2" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A58" s="2" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A59" s="2" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A60" s="2" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A61" s="2" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="62" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A62" s="2" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A63" s="2" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="64" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A64" s="2" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A65" s="2" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A66" s="2" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A67" s="2" t="s">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A68" s="2" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A69" s="2" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A70" s="2" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A71" s="2" t="s">
+    <row r="74" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A74" s="2" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A75" s="2" t="s">
         <v>376</v>
       </c>
     </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A72" s="2" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A73" s="2" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="74" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A74" s="2" t="s">
+    <row r="76" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A76" s="2" t="s">
         <v>388</v>
       </c>
     </row>
-    <row r="75" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A75" s="2" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="76" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A76" s="2" t="s">
+    <row r="77" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A77" s="2" t="s">
         <v>389</v>
       </c>
     </row>
-    <row r="77" spans="1:1" ht="32.4" x14ac:dyDescent="0.3">
-      <c r="A77" s="2" t="s">
+    <row r="78" spans="1:1" ht="33" x14ac:dyDescent="0.25">
+      <c r="A78" s="2" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A79" s="2" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A80" s="2" t="s">
         <v>390</v>
       </c>
     </row>
-    <row r="78" spans="1:1" ht="32.4" x14ac:dyDescent="0.3">
-      <c r="A78" s="2" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="79" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A79" s="2" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="80" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A80" s="2" t="s">
+    <row r="81" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A81" s="2" t="s">
         <v>391</v>
-      </c>
-    </row>
-    <row r="81" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A81" s="2" t="s">
-        <v>392</v>
       </c>
     </row>
   </sheetData>

--- a/config/Excel/Status.xlsx
+++ b/config/Excel/Status.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyGame\Idle-RPG\codex\config\param-patches\archive\2026-10-20T07-49-18-678Z-33ab5330-ee8d-48d1-9e5c-d6c1c8344d69\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\AppData\Local\Temp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4F85197-DD98-4D0A-9B77-D4DEB9E9663A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D8D3AF8-42C0-448E-ACB0-F4BF0CE0998D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3090" yWindow="2310" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1016" uniqueCount="478">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1031" uniqueCount="484">
   <si>
     <t>狀態ID</t>
   </si>
@@ -745,9 +745,6 @@
   </si>
   <si>
     <t>千瘡百孔</t>
-  </si>
-  <si>
-    <t>傳奇特效【千瘡百孔】：每次突刺命中疊 1 層，每層使該敵人受到的傷害提高（效果值＝單層提高%）；層數上限由特效參數決定。</t>
   </si>
   <si>
     <t>sgSoulRend</t>
@@ -1473,10 +1470,6 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>傳奇【烈火狩】：火狩持續期間按節拍疊加火屬性傷害提升，最多 50 層，滿層只刷新時間；火狩全部消失後到期，與火焰增幅各自計算層數。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>新版技能【火球術／火柱／無限星環】：火屬性持續傷害；每跳量與間隔由技能各階決定（引擎以 dps 覆寫）。</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -1491,6 +1484,32 @@
   </si>
   <si>
     <t>新版技能【狂風碎裂】：被風刃命中的敵人移動速度與攻速下降（共用效果值＝各自下降%）。同類型緩速依「取代」規則後蓋前並重新計時。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>傳奇特效【千瘡百孔】：每次突刺命中疊 1 層，每層使該敵人受到的「突刺」傷害提高（效果值＝單層提高%；只放大突刺技能自己的傷害，普攻與其他技能不吃）；層數上限由特效參數決定。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>sgThrustWound</t>
+  </si>
+  <si>
+    <t>重傷</t>
+  </si>
+  <si>
+    <t>🩹</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>傳奇特效【貫日之刺】：突刺命中時機率使敵人重傷（效果值＝受到的傷害提高%）。沒有附加條件，狀態在身上就算數，走 skill2VulnACfg 的同一個 totalDmgPct；不疊層，重複命中只刷新時間。</t>
+  </si>
+  <si>
+    <t>傳奇【烈火狩】：火狩持續期間按節拍疊加火屬性傷害提升，最多 20 層，滿層只刷新時間；火狩全部消失後到期，與火焰增幅各自計算層數。</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -2084,7 +2103,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2093,9 +2112,6 @@
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="42">
@@ -2472,7 +2488,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:T97"/>
+  <dimension ref="A1:T98"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="18" max="18" width="12.375" customWidth="1"/>
@@ -3449,7 +3465,7 @@
         <v>112</v>
       </c>
       <c r="B22" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="C22" t="s">
         <v>113</v>
@@ -3485,7 +3501,7 @@
         <v>1</v>
       </c>
       <c r="T22" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
     </row>
     <row r="23" spans="1:20" x14ac:dyDescent="0.25">
@@ -3802,10 +3818,10 @@
         <v>1</v>
       </c>
       <c r="Q29" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="S29" s="1" t="s">
         <v>377</v>
-      </c>
-      <c r="S29" s="1" t="s">
-        <v>378</v>
       </c>
       <c r="T29" t="s">
         <v>136</v>
@@ -4028,10 +4044,10 @@
         <v>1</v>
       </c>
       <c r="R34" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="T34" s="1" t="s">
         <v>424</v>
-      </c>
-      <c r="T34" s="1" t="s">
-        <v>425</v>
       </c>
     </row>
     <row r="35" spans="1:20" x14ac:dyDescent="0.25">
@@ -4075,7 +4091,7 @@
         <v>1</v>
       </c>
       <c r="R35" s="1" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="T35" t="s">
         <v>157</v>
@@ -4169,10 +4185,10 @@
         <v>1</v>
       </c>
       <c r="S37" s="1" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="T37" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
     </row>
     <row r="38" spans="1:20" x14ac:dyDescent="0.25">
@@ -4213,13 +4229,13 @@
         <v>0</v>
       </c>
       <c r="O38" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="P38">
         <v>50</v>
       </c>
       <c r="T38" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="39" spans="1:20" x14ac:dyDescent="0.25">
@@ -4639,7 +4655,7 @@
         <v>1</v>
       </c>
       <c r="S47" s="1" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="T47" t="s">
         <v>203</v>
@@ -4923,8 +4939,8 @@
       <c r="P53">
         <v>1</v>
       </c>
-      <c r="T53" s="3" t="s">
-        <v>477</v>
+      <c r="T53" t="s">
+        <v>475</v>
       </c>
     </row>
     <row r="54" spans="1:20" x14ac:dyDescent="0.25">
@@ -4971,7 +4987,7 @@
         <v>1</v>
       </c>
       <c r="R54" s="1" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="T54" t="s">
         <v>227</v>
@@ -5068,7 +5084,7 @@
         <v>1</v>
       </c>
       <c r="R56" s="1" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="T56" t="s">
         <v>234</v>
@@ -5114,154 +5130,154 @@
       <c r="P57">
         <v>10</v>
       </c>
-      <c r="T57" t="s">
-        <v>237</v>
+      <c r="T57" s="1" t="s">
+        <v>476</v>
       </c>
     </row>
     <row r="58" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A58" t="s">
-        <v>238</v>
-      </c>
-      <c r="B58" t="s">
-        <v>239</v>
-      </c>
-      <c r="C58" t="s">
-        <v>240</v>
-      </c>
-      <c r="D58" t="s">
+      <c r="A58" s="1" t="s">
+        <v>477</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>478</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>479</v>
+      </c>
+      <c r="D58" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E58" t="s">
+      <c r="E58" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="F58" t="s">
-        <v>238</v>
-      </c>
-      <c r="G58" t="s">
-        <v>40</v>
-      </c>
-      <c r="I58">
-        <v>0</v>
-      </c>
-      <c r="K58">
-        <v>0</v>
-      </c>
-      <c r="L58">
-        <v>1</v>
-      </c>
-      <c r="M58">
-        <v>30</v>
-      </c>
-      <c r="N58">
-        <v>0</v>
-      </c>
-      <c r="O58" t="s">
-        <v>162</v>
-      </c>
-      <c r="P58">
-        <v>100</v>
-      </c>
-      <c r="T58" t="s">
-        <v>241</v>
+      <c r="F58" s="1" t="s">
+        <v>477</v>
+      </c>
+      <c r="I58" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="K58" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="L58" s="1" t="s">
+        <v>480</v>
+      </c>
+      <c r="M58" s="1" t="s">
+        <v>481</v>
+      </c>
+      <c r="N58" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="O58" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="P58" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="T58" s="1" t="s">
+        <v>482</v>
       </c>
     </row>
     <row r="59" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="B59" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="C59" t="s">
-        <v>22</v>
+        <v>239</v>
       </c>
       <c r="D59" t="s">
         <v>23</v>
       </c>
       <c r="E59" t="s">
-        <v>24</v>
-      </c>
-      <c r="H59" t="s">
-        <v>25</v>
+        <v>79</v>
+      </c>
+      <c r="F59" t="s">
+        <v>237</v>
+      </c>
+      <c r="G59" t="s">
+        <v>40</v>
       </c>
       <c r="I59">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="K59">
         <v>0</v>
       </c>
       <c r="L59">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M59">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="N59">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="O59" t="s">
-        <v>26</v>
+        <v>162</v>
       </c>
       <c r="P59">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="T59" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
     </row>
     <row r="60" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="B60" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="C60" t="s">
-        <v>247</v>
+        <v>22</v>
       </c>
       <c r="D60" t="s">
-        <v>65</v>
+        <v>23</v>
       </c>
       <c r="E60" t="s">
-        <v>79</v>
-      </c>
-      <c r="F60" t="s">
-        <v>245</v>
+        <v>24</v>
+      </c>
+      <c r="H60" t="s">
+        <v>25</v>
       </c>
       <c r="I60">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="K60">
         <v>0</v>
       </c>
       <c r="L60">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="M60">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="N60">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="O60" t="s">
-        <v>56</v>
+        <v>26</v>
       </c>
       <c r="P60">
         <v>1</v>
       </c>
       <c r="T60" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
     </row>
     <row r="61" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="B61" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="C61" t="s">
-        <v>35</v>
+        <v>246</v>
       </c>
       <c r="D61" t="s">
         <v>65</v>
@@ -5270,7 +5286,7 @@
         <v>79</v>
       </c>
       <c r="F61" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="I61">
         <v>0</v>
@@ -5279,33 +5295,33 @@
         <v>0</v>
       </c>
       <c r="L61">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="M61">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="N61">
         <v>0</v>
       </c>
       <c r="O61" t="s">
-        <v>162</v>
+        <v>56</v>
       </c>
       <c r="P61">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="T61" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
     </row>
     <row r="62" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="B62" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="C62" t="s">
-        <v>254</v>
+        <v>35</v>
       </c>
       <c r="D62" t="s">
         <v>65</v>
@@ -5314,7 +5330,7 @@
         <v>79</v>
       </c>
       <c r="F62" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="I62">
         <v>0</v>
@@ -5323,33 +5339,33 @@
         <v>0</v>
       </c>
       <c r="L62">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="M62">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="N62">
         <v>0</v>
       </c>
       <c r="O62" t="s">
-        <v>56</v>
+        <v>162</v>
       </c>
       <c r="P62">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="T62" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
     </row>
     <row r="63" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="B63" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="C63" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="D63" t="s">
         <v>65</v>
@@ -5358,7 +5374,7 @@
         <v>79</v>
       </c>
       <c r="F63" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="I63">
         <v>0</v>
@@ -5367,80 +5383,77 @@
         <v>0</v>
       </c>
       <c r="L63">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M63">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N63">
         <v>0</v>
       </c>
       <c r="O63" t="s">
-        <v>162</v>
+        <v>56</v>
       </c>
       <c r="P63">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="T63" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
     </row>
     <row r="64" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="B64" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="C64" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="D64" t="s">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="E64" t="s">
-        <v>24</v>
-      </c>
-      <c r="G64" t="s">
-        <v>33</v>
-      </c>
-      <c r="H64" t="s">
-        <v>25</v>
+        <v>79</v>
+      </c>
+      <c r="F64" t="s">
+        <v>255</v>
       </c>
       <c r="I64">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K64">
         <v>0</v>
       </c>
       <c r="L64">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M64">
         <v>6</v>
       </c>
       <c r="N64">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="O64" t="s">
         <v>162</v>
       </c>
       <c r="P64">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T64" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
     </row>
     <row r="65" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="B65" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="C65" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="D65" t="s">
         <v>23</v>
@@ -5449,13 +5462,13 @@
         <v>24</v>
       </c>
       <c r="G65" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H65" t="s">
         <v>25</v>
       </c>
       <c r="I65">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="K65">
         <v>0</v>
@@ -5473,77 +5486,77 @@
         <v>162</v>
       </c>
       <c r="P65">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T65" t="s">
-        <v>461</v>
+        <v>262</v>
       </c>
     </row>
     <row r="66" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="B66" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="C66" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="D66" t="s">
-        <v>65</v>
+        <v>23</v>
       </c>
       <c r="E66" t="s">
-        <v>79</v>
-      </c>
-      <c r="F66" t="s">
-        <v>267</v>
+        <v>24</v>
+      </c>
+      <c r="G66" t="s">
+        <v>31</v>
+      </c>
+      <c r="H66" t="s">
+        <v>25</v>
       </c>
       <c r="I66">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K66">
         <v>0</v>
       </c>
       <c r="L66">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M66">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="N66">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="O66" t="s">
-        <v>56</v>
+        <v>162</v>
       </c>
       <c r="P66">
-        <v>1</v>
-      </c>
-      <c r="R66" s="1" t="s">
-        <v>379</v>
+        <v>20</v>
       </c>
       <c r="T66" t="s">
-        <v>270</v>
+        <v>460</v>
       </c>
     </row>
     <row r="67" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="B67" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="C67" t="s">
-        <v>247</v>
+        <v>268</v>
       </c>
       <c r="D67" t="s">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="E67" t="s">
         <v>79</v>
       </c>
       <c r="F67" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="I67">
         <v>0</v>
@@ -5552,10 +5565,10 @@
         <v>0</v>
       </c>
       <c r="L67">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M67">
-        <v>0.6</v>
+        <v>10</v>
       </c>
       <c r="N67">
         <v>0</v>
@@ -5566,28 +5579,31 @@
       <c r="P67">
         <v>1</v>
       </c>
+      <c r="R67" s="1" t="s">
+        <v>378</v>
+      </c>
       <c r="T67" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
     </row>
     <row r="68" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="B68" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="C68" t="s">
-        <v>276</v>
+        <v>246</v>
       </c>
       <c r="D68" t="s">
-        <v>65</v>
+        <v>23</v>
       </c>
       <c r="E68" t="s">
         <v>79</v>
       </c>
       <c r="F68" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="I68">
         <v>0</v>
@@ -5596,10 +5612,10 @@
         <v>0</v>
       </c>
       <c r="L68">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="M68">
-        <v>6</v>
+        <v>0.6</v>
       </c>
       <c r="N68">
         <v>0</v>
@@ -5611,18 +5627,18 @@
         <v>1</v>
       </c>
       <c r="T68" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
     </row>
     <row r="69" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="B69" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="C69" t="s">
-        <v>22</v>
+        <v>275</v>
       </c>
       <c r="D69" t="s">
         <v>65</v>
@@ -5631,7 +5647,7 @@
         <v>79</v>
       </c>
       <c r="F69" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="I69">
         <v>0</v>
@@ -5640,33 +5656,33 @@
         <v>0</v>
       </c>
       <c r="L69">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="M69">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N69">
         <v>0</v>
       </c>
       <c r="O69" t="s">
-        <v>162</v>
+        <v>56</v>
       </c>
       <c r="P69">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="T69" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
     </row>
     <row r="70" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="B70" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="C70" t="s">
-        <v>283</v>
+        <v>22</v>
       </c>
       <c r="D70" t="s">
         <v>65</v>
@@ -5675,7 +5691,7 @@
         <v>79</v>
       </c>
       <c r="F70" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="I70">
         <v>0</v>
@@ -5684,7 +5700,7 @@
         <v>0</v>
       </c>
       <c r="L70">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M70">
         <v>4</v>
@@ -5696,21 +5712,21 @@
         <v>162</v>
       </c>
       <c r="P70">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T70" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
     </row>
     <row r="71" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="B71" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="C71" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="D71" t="s">
         <v>65</v>
@@ -5719,7 +5735,7 @@
         <v>79</v>
       </c>
       <c r="F71" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="I71">
         <v>0</v>
@@ -5728,10 +5744,10 @@
         <v>0</v>
       </c>
       <c r="L71">
+        <v>5</v>
+      </c>
+      <c r="M71">
         <v>4</v>
-      </c>
-      <c r="M71">
-        <v>99999</v>
       </c>
       <c r="N71">
         <v>0</v>
@@ -5740,21 +5756,21 @@
         <v>162</v>
       </c>
       <c r="P71">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T71" t="s">
-        <v>288</v>
+        <v>283</v>
       </c>
     </row>
     <row r="72" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="B72" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="C72" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="D72" t="s">
         <v>65</v>
@@ -5763,7 +5779,7 @@
         <v>79</v>
       </c>
       <c r="F72" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="I72">
         <v>0</v>
@@ -5772,36 +5788,33 @@
         <v>0</v>
       </c>
       <c r="L72">
-        <v>500</v>
+        <v>4</v>
       </c>
       <c r="M72">
-        <v>1</v>
+        <v>99999</v>
       </c>
       <c r="N72">
         <v>0</v>
       </c>
       <c r="O72" t="s">
-        <v>56</v>
+        <v>162</v>
       </c>
       <c r="P72">
-        <v>1</v>
-      </c>
-      <c r="R72" s="1" t="s">
-        <v>380</v>
+        <v>100</v>
       </c>
       <c r="T72" t="s">
-        <v>462</v>
+        <v>287</v>
       </c>
     </row>
     <row r="73" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="B73" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="C73" t="s">
-        <v>170</v>
+        <v>290</v>
       </c>
       <c r="D73" t="s">
         <v>65</v>
@@ -5810,10 +5823,7 @@
         <v>79</v>
       </c>
       <c r="F73" t="s">
-        <v>292</v>
-      </c>
-      <c r="G73" t="s">
-        <v>31</v>
+        <v>288</v>
       </c>
       <c r="I73">
         <v>0</v>
@@ -5822,10 +5832,10 @@
         <v>0</v>
       </c>
       <c r="L73">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="M73">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="N73">
         <v>0</v>
@@ -5836,28 +5846,31 @@
       <c r="P73">
         <v>1</v>
       </c>
+      <c r="R73" s="1" t="s">
+        <v>379</v>
+      </c>
       <c r="T73" t="s">
-        <v>294</v>
+        <v>461</v>
       </c>
     </row>
     <row r="74" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="B74" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="C74" t="s">
-        <v>30</v>
+        <v>170</v>
       </c>
       <c r="D74" t="s">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="E74" t="s">
         <v>79</v>
       </c>
       <c r="F74" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="G74" t="s">
         <v>31</v>
@@ -5869,10 +5882,10 @@
         <v>0</v>
       </c>
       <c r="L74">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M74">
-        <v>4</v>
+        <v>60</v>
       </c>
       <c r="N74">
         <v>0</v>
@@ -5884,18 +5897,18 @@
         <v>1</v>
       </c>
       <c r="T74" t="s">
-        <v>465</v>
+        <v>293</v>
       </c>
     </row>
     <row r="75" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="B75" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="C75" t="s">
-        <v>299</v>
+        <v>30</v>
       </c>
       <c r="D75" t="s">
         <v>23</v>
@@ -5904,10 +5917,10 @@
         <v>79</v>
       </c>
       <c r="F75" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="G75" t="s">
-        <v>175</v>
+        <v>31</v>
       </c>
       <c r="I75">
         <v>0</v>
@@ -5916,10 +5929,10 @@
         <v>0</v>
       </c>
       <c r="L75">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="M75">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N75">
         <v>0</v>
@@ -5931,18 +5944,18 @@
         <v>1</v>
       </c>
       <c r="T75" t="s">
-        <v>430</v>
+        <v>464</v>
       </c>
     </row>
     <row r="76" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="B76" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="C76" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="D76" t="s">
         <v>23</v>
@@ -5951,7 +5964,7 @@
         <v>79</v>
       </c>
       <c r="F76" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="G76" t="s">
         <v>175</v>
@@ -5963,10 +5976,10 @@
         <v>0</v>
       </c>
       <c r="L76">
-        <v>65</v>
+        <v>1</v>
       </c>
       <c r="M76">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="N76">
         <v>0</v>
@@ -5978,62 +5991,65 @@
         <v>1</v>
       </c>
       <c r="T76" t="s">
-        <v>303</v>
+        <v>429</v>
       </c>
     </row>
     <row r="77" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>304</v>
+        <v>299</v>
       </c>
       <c r="B77" t="s">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="C77" t="s">
-        <v>22</v>
+        <v>301</v>
       </c>
       <c r="D77" t="s">
         <v>23</v>
       </c>
       <c r="E77" t="s">
-        <v>24</v>
-      </c>
-      <c r="H77" t="s">
-        <v>25</v>
+        <v>79</v>
+      </c>
+      <c r="F77" t="s">
+        <v>299</v>
+      </c>
+      <c r="G77" t="s">
+        <v>175</v>
       </c>
       <c r="I77">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="K77">
         <v>0</v>
       </c>
       <c r="L77">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="M77">
         <v>5</v>
       </c>
       <c r="N77">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="O77" t="s">
-        <v>26</v>
+        <v>56</v>
       </c>
       <c r="P77">
         <v>1</v>
       </c>
       <c r="T77" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
     </row>
     <row r="78" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="B78" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="C78" t="s">
-        <v>44</v>
+        <v>22</v>
       </c>
       <c r="D78" t="s">
         <v>23</v>
@@ -6041,14 +6057,11 @@
       <c r="E78" t="s">
         <v>24</v>
       </c>
-      <c r="G78" t="s">
-        <v>33</v>
-      </c>
       <c r="H78" t="s">
         <v>25</v>
       </c>
       <c r="I78">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="K78">
         <v>0</v>
@@ -6057,10 +6070,10 @@
         <v>0</v>
       </c>
       <c r="M78">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="N78">
-        <v>0.35</v>
+        <v>0.5</v>
       </c>
       <c r="O78" t="s">
         <v>26</v>
@@ -6069,77 +6082,77 @@
         <v>1</v>
       </c>
       <c r="T78" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
     </row>
     <row r="79" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="B79" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="C79" t="s">
-        <v>189</v>
+        <v>44</v>
       </c>
       <c r="D79" t="s">
         <v>23</v>
       </c>
       <c r="E79" t="s">
-        <v>79</v>
-      </c>
-      <c r="F79" t="s">
-        <v>310</v>
+        <v>24</v>
       </c>
       <c r="G79" t="s">
-        <v>31</v>
+        <v>33</v>
+      </c>
+      <c r="H79" t="s">
+        <v>25</v>
       </c>
       <c r="I79">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="K79">
         <v>0</v>
       </c>
       <c r="L79">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M79">
         <v>8</v>
       </c>
       <c r="N79">
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="O79" t="s">
-        <v>56</v>
+        <v>26</v>
       </c>
       <c r="P79">
         <v>1</v>
       </c>
       <c r="T79" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
     </row>
     <row r="80" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="B80" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="C80" t="s">
-        <v>315</v>
+        <v>189</v>
       </c>
       <c r="D80" t="s">
-        <v>65</v>
+        <v>23</v>
       </c>
       <c r="E80" t="s">
         <v>79</v>
       </c>
       <c r="F80" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="G80" t="s">
-        <v>115</v>
+        <v>31</v>
       </c>
       <c r="I80">
         <v>0</v>
@@ -6148,42 +6161,42 @@
         <v>0</v>
       </c>
       <c r="L80">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M80">
-        <v>99999</v>
+        <v>8</v>
       </c>
       <c r="N80">
         <v>0</v>
       </c>
       <c r="O80" t="s">
-        <v>162</v>
+        <v>56</v>
       </c>
       <c r="P80">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="T80" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
     </row>
     <row r="81" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="B81" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="C81" t="s">
-        <v>86</v>
+        <v>314</v>
       </c>
       <c r="D81" t="s">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="E81" t="s">
         <v>79</v>
       </c>
       <c r="F81" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="G81" t="s">
         <v>115</v>
@@ -6195,33 +6208,33 @@
         <v>0</v>
       </c>
       <c r="L81">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="M81">
-        <v>8</v>
+        <v>99999</v>
       </c>
       <c r="N81">
         <v>0</v>
       </c>
       <c r="O81" t="s">
-        <v>56</v>
+        <v>162</v>
       </c>
       <c r="P81">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="T81" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
     </row>
     <row r="82" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="B82" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="C82" t="s">
-        <v>322</v>
+        <v>86</v>
       </c>
       <c r="D82" t="s">
         <v>23</v>
@@ -6230,10 +6243,10 @@
         <v>79</v>
       </c>
       <c r="F82" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="G82" t="s">
-        <v>198</v>
+        <v>115</v>
       </c>
       <c r="I82">
         <v>0</v>
@@ -6242,10 +6255,10 @@
         <v>0</v>
       </c>
       <c r="L82">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="M82">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="N82">
         <v>0</v>
@@ -6257,18 +6270,18 @@
         <v>1</v>
       </c>
       <c r="T82" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
     </row>
     <row r="83" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="B83" t="s">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="C83" t="s">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="D83" t="s">
         <v>23</v>
@@ -6277,10 +6290,10 @@
         <v>79</v>
       </c>
       <c r="F83" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="G83" t="s">
-        <v>217</v>
+        <v>198</v>
       </c>
       <c r="I83">
         <v>0</v>
@@ -6289,10 +6302,10 @@
         <v>0</v>
       </c>
       <c r="L83">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="M83">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N83">
         <v>0</v>
@@ -6304,68 +6317,65 @@
         <v>1</v>
       </c>
       <c r="T83" t="s">
-        <v>327</v>
+        <v>322</v>
       </c>
     </row>
     <row r="84" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A84" s="1" t="s">
-        <v>392</v>
-      </c>
-      <c r="B84" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="C84" s="1" t="s">
-        <v>258</v>
-      </c>
-      <c r="D84" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="E84" s="1" t="s">
+      <c r="A84" t="s">
+        <v>323</v>
+      </c>
+      <c r="B84" t="s">
+        <v>324</v>
+      </c>
+      <c r="C84" t="s">
+        <v>325</v>
+      </c>
+      <c r="D84" t="s">
+        <v>23</v>
+      </c>
+      <c r="E84" t="s">
         <v>79</v>
       </c>
-      <c r="F84" s="1" t="s">
-        <v>392</v>
-      </c>
-      <c r="G84" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="I84" s="1" t="s">
-        <v>394</v>
-      </c>
-      <c r="K84" s="1" t="s">
-        <v>394</v>
-      </c>
-      <c r="L84" s="1" t="s">
-        <v>394</v>
-      </c>
-      <c r="M84" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="N84" s="1" t="s">
-        <v>394</v>
-      </c>
-      <c r="O84" s="1" t="s">
+      <c r="F84" t="s">
+        <v>323</v>
+      </c>
+      <c r="G84" t="s">
+        <v>217</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="K84">
+        <v>0</v>
+      </c>
+      <c r="L84">
+        <v>25</v>
+      </c>
+      <c r="M84">
+        <v>4</v>
+      </c>
+      <c r="N84">
+        <v>0</v>
+      </c>
+      <c r="O84" t="s">
         <v>56</v>
       </c>
-      <c r="P84" s="1" t="s">
-        <v>396</v>
-      </c>
-      <c r="R84" s="1" t="s">
-        <v>397</v>
-      </c>
-      <c r="T84" s="1" t="s">
-        <v>398</v>
+      <c r="P84">
+        <v>1</v>
+      </c>
+      <c r="T84" t="s">
+        <v>326</v>
       </c>
     </row>
     <row r="85" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
-        <v>399</v>
+        <v>391</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>400</v>
+        <v>392</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>401</v>
+        <v>257</v>
       </c>
       <c r="D85" s="1" t="s">
         <v>65</v>
@@ -6374,48 +6384,48 @@
         <v>79</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>399</v>
+        <v>391</v>
       </c>
       <c r="G85" s="1" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="I85" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="K85" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="L85" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="M85" s="1" t="s">
         <v>394</v>
       </c>
-      <c r="K85" s="1" t="s">
-        <v>394</v>
-      </c>
-      <c r="L85" s="1" t="s">
-        <v>394</v>
-      </c>
-      <c r="M85" s="1" t="s">
-        <v>395</v>
-      </c>
       <c r="N85" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="O85" s="1" t="s">
         <v>56</v>
       </c>
       <c r="P85" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="R85" s="1" t="s">
         <v>396</v>
       </c>
-      <c r="R85" s="1" t="s">
-        <v>402</v>
-      </c>
       <c r="T85" s="1" t="s">
-        <v>403</v>
+        <v>397</v>
       </c>
     </row>
     <row r="86" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
-        <v>404</v>
+        <v>398</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>405</v>
+        <v>399</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>30</v>
+        <v>400</v>
       </c>
       <c r="D86" s="1" t="s">
         <v>65</v>
@@ -6424,48 +6434,48 @@
         <v>79</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>404</v>
+        <v>398</v>
       </c>
       <c r="G86" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I86" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="K86" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="L86" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="M86" s="1" t="s">
         <v>394</v>
       </c>
-      <c r="K86" s="1" t="s">
-        <v>394</v>
-      </c>
-      <c r="L86" s="1" t="s">
-        <v>394</v>
-      </c>
-      <c r="M86" s="1" t="s">
-        <v>395</v>
-      </c>
       <c r="N86" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="O86" s="1" t="s">
         <v>56</v>
       </c>
       <c r="P86" s="1" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="R86" s="1" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="T86" s="1" t="s">
-        <v>407</v>
+        <v>402</v>
       </c>
     </row>
     <row r="87" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
-        <v>408</v>
+        <v>403</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>409</v>
+        <v>404</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>299</v>
+        <v>30</v>
       </c>
       <c r="D87" s="1" t="s">
         <v>65</v>
@@ -6474,48 +6484,48 @@
         <v>79</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>408</v>
+        <v>403</v>
       </c>
       <c r="G87" s="1" t="s">
-        <v>175</v>
+        <v>31</v>
       </c>
       <c r="I87" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="K87" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="L87" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="M87" s="1" t="s">
         <v>394</v>
       </c>
-      <c r="K87" s="1" t="s">
-        <v>394</v>
-      </c>
-      <c r="L87" s="1" t="s">
-        <v>394</v>
-      </c>
-      <c r="M87" s="1" t="s">
-        <v>431</v>
-      </c>
       <c r="N87" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="O87" s="1" t="s">
         <v>56</v>
       </c>
       <c r="P87" s="1" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="R87" s="1" t="s">
-        <v>411</v>
+        <v>405</v>
       </c>
       <c r="T87" s="1" t="s">
-        <v>432</v>
+        <v>406</v>
       </c>
     </row>
     <row r="88" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
-        <v>412</v>
+        <v>407</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>413</v>
+        <v>408</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="D88" s="1" t="s">
         <v>65</v>
@@ -6524,48 +6534,48 @@
         <v>79</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>412</v>
+        <v>407</v>
       </c>
       <c r="G88" s="1" t="s">
         <v>175</v>
       </c>
       <c r="I88" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="K88" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="L88" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="M88" s="1" t="s">
-        <v>410</v>
+        <v>430</v>
       </c>
       <c r="N88" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="O88" s="1" t="s">
         <v>56</v>
       </c>
       <c r="P88" s="1" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="R88" s="1" t="s">
-        <v>426</v>
+        <v>410</v>
       </c>
       <c r="T88" s="1" t="s">
-        <v>414</v>
+        <v>431</v>
       </c>
     </row>
     <row r="89" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>416</v>
+        <v>412</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>417</v>
+        <v>301</v>
       </c>
       <c r="D89" s="1" t="s">
         <v>65</v>
@@ -6574,48 +6584,48 @@
         <v>79</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="G89" s="1" t="s">
-        <v>198</v>
+        <v>175</v>
       </c>
       <c r="I89" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="K89" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="L89" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="M89" s="1" t="s">
-        <v>418</v>
+        <v>409</v>
       </c>
       <c r="N89" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="O89" s="1" t="s">
         <v>56</v>
       </c>
       <c r="P89" s="1" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="R89" s="1" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="T89" s="1" t="s">
-        <v>428</v>
+        <v>413</v>
       </c>
     </row>
     <row r="90" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
-        <v>420</v>
+        <v>414</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>421</v>
+        <v>415</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>322</v>
+        <v>416</v>
       </c>
       <c r="D90" s="1" t="s">
         <v>65</v>
@@ -6624,48 +6634,48 @@
         <v>79</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>420</v>
+        <v>414</v>
       </c>
       <c r="G90" s="1" t="s">
         <v>198</v>
       </c>
       <c r="I90" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="K90" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="L90" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="M90" s="1" t="s">
-        <v>395</v>
+        <v>417</v>
       </c>
       <c r="N90" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="O90" s="1" t="s">
         <v>56</v>
       </c>
       <c r="P90" s="1" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="R90" s="1" t="s">
-        <v>419</v>
+        <v>426</v>
       </c>
       <c r="T90" s="1" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
     </row>
     <row r="91" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
-        <v>433</v>
+        <v>419</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>434</v>
+        <v>420</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>74</v>
+        <v>321</v>
       </c>
       <c r="D91" s="1" t="s">
         <v>65</v>
@@ -6674,45 +6684,48 @@
         <v>79</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>433</v>
+        <v>419</v>
+      </c>
+      <c r="G91" s="1" t="s">
+        <v>198</v>
       </c>
       <c r="I91" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="K91" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="L91" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="M91" s="1" t="s">
         <v>394</v>
       </c>
-      <c r="K91" s="1" t="s">
-        <v>394</v>
-      </c>
-      <c r="L91" s="1" t="s">
-        <v>394</v>
-      </c>
-      <c r="M91" s="1" t="s">
-        <v>435</v>
-      </c>
       <c r="N91" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="O91" s="1" t="s">
         <v>56</v>
       </c>
       <c r="P91" s="1" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="R91" s="1" t="s">
-        <v>436</v>
+        <v>418</v>
       </c>
       <c r="T91" s="1" t="s">
-        <v>437</v>
+        <v>428</v>
       </c>
     </row>
     <row r="92" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
-        <v>438</v>
+        <v>432</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>439</v>
+        <v>433</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>276</v>
+        <v>74</v>
       </c>
       <c r="D92" s="1" t="s">
         <v>65</v>
@@ -6721,48 +6734,45 @@
         <v>79</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>438</v>
+        <v>432</v>
       </c>
       <c r="I92" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="K92" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="L92" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="M92" s="1" t="s">
-        <v>395</v>
+        <v>434</v>
       </c>
       <c r="N92" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="O92" s="1" t="s">
         <v>56</v>
       </c>
       <c r="P92" s="1" t="s">
-        <v>396</v>
-      </c>
-      <c r="Q92" s="1" t="s">
-        <v>440</v>
+        <v>395</v>
       </c>
       <c r="R92" s="1" t="s">
-        <v>441</v>
+        <v>435</v>
       </c>
       <c r="T92" s="1" t="s">
-        <v>442</v>
+        <v>436</v>
       </c>
     </row>
     <row r="93" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
-        <v>443</v>
+        <v>437</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>444</v>
+        <v>438</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>30</v>
+        <v>275</v>
       </c>
       <c r="D93" s="1" t="s">
         <v>65</v>
@@ -6771,48 +6781,48 @@
         <v>79</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>443</v>
+        <v>437</v>
       </c>
       <c r="I93" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="K93" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="L93" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="M93" s="1" t="s">
         <v>394</v>
       </c>
-      <c r="K93" s="1" t="s">
-        <v>394</v>
-      </c>
-      <c r="L93" s="1" t="s">
-        <v>394</v>
-      </c>
-      <c r="M93" s="1" t="s">
-        <v>445</v>
-      </c>
       <c r="N93" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="O93" s="1" t="s">
         <v>56</v>
       </c>
       <c r="P93" s="1" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="Q93" s="1" t="s">
-        <v>446</v>
+        <v>439</v>
       </c>
       <c r="R93" s="1" t="s">
-        <v>447</v>
+        <v>440</v>
       </c>
       <c r="T93" s="1" t="s">
-        <v>448</v>
+        <v>441</v>
       </c>
     </row>
     <row r="94" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
-        <v>449</v>
+        <v>442</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>68</v>
+        <v>443</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>69</v>
+        <v>30</v>
       </c>
       <c r="D94" s="1" t="s">
         <v>65</v>
@@ -6821,172 +6831,222 @@
         <v>79</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>449</v>
+        <v>442</v>
       </c>
       <c r="I94" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="K94" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="L94" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="M94" s="1" t="s">
-        <v>395</v>
+        <v>444</v>
       </c>
       <c r="N94" s="1" t="s">
-        <v>450</v>
+        <v>393</v>
       </c>
       <c r="O94" s="1" t="s">
         <v>56</v>
       </c>
       <c r="P94" s="1" t="s">
-        <v>396</v>
-      </c>
-      <c r="S94" s="1" t="s">
-        <v>451</v>
+        <v>395</v>
+      </c>
+      <c r="Q94" s="1" t="s">
+        <v>445</v>
+      </c>
+      <c r="R94" s="1" t="s">
+        <v>446</v>
       </c>
       <c r="T94" s="1" t="s">
-        <v>452</v>
+        <v>447</v>
       </c>
     </row>
     <row r="95" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>454</v>
+        <v>68</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>455</v>
+        <v>69</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="E95" s="1" t="s">
         <v>79</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="I95" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="K95" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="L95" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="M95" s="1" t="s">
         <v>394</v>
       </c>
-      <c r="K95" s="1" t="s">
-        <v>394</v>
-      </c>
-      <c r="L95" s="1" t="s">
-        <v>394</v>
-      </c>
-      <c r="M95" s="1" t="s">
-        <v>456</v>
-      </c>
       <c r="N95" s="1" t="s">
-        <v>394</v>
+        <v>449</v>
       </c>
       <c r="O95" s="1" t="s">
         <v>56</v>
       </c>
       <c r="P95" s="1" t="s">
-        <v>396</v>
-      </c>
-      <c r="Q95" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="S95" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="T95" s="1" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="96" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A96" s="1" t="s">
+        <v>452</v>
+      </c>
+      <c r="B96" s="1" t="s">
+        <v>453</v>
+      </c>
+      <c r="C96" s="1" t="s">
+        <v>454</v>
+      </c>
+      <c r="D96" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E96" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="F96" s="1" t="s">
+        <v>452</v>
+      </c>
+      <c r="I96" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="K96" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="L96" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="M96" s="1" t="s">
+        <v>455</v>
+      </c>
+      <c r="N96" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="O96" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="P96" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="Q96" s="1" t="s">
+        <v>456</v>
+      </c>
+      <c r="T96" s="1" t="s">
         <v>457</v>
-      </c>
-      <c r="T95" s="1" t="s">
-        <v>458</v>
-      </c>
-    </row>
-    <row r="96" spans="1:20" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A96" t="s">
-        <v>466</v>
-      </c>
-      <c r="B96" t="s">
-        <v>467</v>
-      </c>
-      <c r="C96" t="s">
-        <v>468</v>
-      </c>
-      <c r="D96" t="s">
-        <v>469</v>
-      </c>
-      <c r="E96" t="s">
-        <v>470</v>
-      </c>
-      <c r="F96" t="s">
-        <v>466</v>
-      </c>
-      <c r="G96" t="s">
-        <v>471</v>
-      </c>
-      <c r="I96">
-        <v>0</v>
-      </c>
-      <c r="K96">
-        <v>0</v>
-      </c>
-      <c r="L96">
-        <v>2</v>
-      </c>
-      <c r="M96">
-        <v>1</v>
-      </c>
-      <c r="N96">
-        <v>0</v>
-      </c>
-      <c r="O96" t="s">
-        <v>463</v>
-      </c>
-      <c r="P96">
-        <v>50</v>
-      </c>
-      <c r="T96" t="s">
-        <v>472</v>
       </c>
     </row>
     <row r="97" spans="1:20" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
+        <v>465</v>
+      </c>
+      <c r="B97" t="s">
+        <v>466</v>
+      </c>
+      <c r="C97" t="s">
+        <v>467</v>
+      </c>
+      <c r="D97" t="s">
+        <v>468</v>
+      </c>
+      <c r="E97" t="s">
+        <v>469</v>
+      </c>
+      <c r="F97" t="s">
+        <v>465</v>
+      </c>
+      <c r="G97" t="s">
+        <v>470</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="K97">
+        <v>0</v>
+      </c>
+      <c r="L97">
+        <v>2</v>
+      </c>
+      <c r="M97">
+        <v>1</v>
+      </c>
+      <c r="N97">
+        <v>0</v>
+      </c>
+      <c r="O97" t="s">
+        <v>462</v>
+      </c>
+      <c r="P97" s="1" t="s">
+        <v>480</v>
+      </c>
+      <c r="T97" s="1" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="98" spans="1:20" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>472</v>
+      </c>
+      <c r="B98" t="s">
+        <v>473</v>
+      </c>
+      <c r="C98" t="s">
+        <v>74</v>
+      </c>
+      <c r="D98" t="s">
+        <v>65</v>
+      </c>
+      <c r="E98" t="s">
+        <v>79</v>
+      </c>
+      <c r="F98" t="s">
+        <v>472</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="K98">
+        <v>0</v>
+      </c>
+      <c r="L98">
+        <v>50</v>
+      </c>
+      <c r="M98">
+        <v>5</v>
+      </c>
+      <c r="N98">
+        <v>0</v>
+      </c>
+      <c r="O98" t="s">
+        <v>56</v>
+      </c>
+      <c r="P98">
+        <v>1</v>
+      </c>
+      <c r="T98" t="s">
         <v>474</v>
-      </c>
-      <c r="B97" t="s">
-        <v>475</v>
-      </c>
-      <c r="C97" t="s">
-        <v>74</v>
-      </c>
-      <c r="D97" t="s">
-        <v>65</v>
-      </c>
-      <c r="E97" t="s">
-        <v>79</v>
-      </c>
-      <c r="F97" t="s">
-        <v>474</v>
-      </c>
-      <c r="I97">
-        <v>0</v>
-      </c>
-      <c r="K97">
-        <v>0</v>
-      </c>
-      <c r="L97">
-        <v>50</v>
-      </c>
-      <c r="M97">
-        <v>5</v>
-      </c>
-      <c r="N97">
-        <v>0</v>
-      </c>
-      <c r="O97" t="s">
-        <v>56</v>
-      </c>
-      <c r="P97">
-        <v>1</v>
-      </c>
-      <c r="T97" t="s">
-        <v>476</v>
       </c>
     </row>
   </sheetData>
@@ -7011,32 +7071,32 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
@@ -7046,17 +7106,17 @@
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
@@ -7066,32 +7126,32 @@
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
@@ -7101,27 +7161,27 @@
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
@@ -7131,17 +7191,17 @@
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
@@ -7151,22 +7211,22 @@
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
@@ -7176,42 +7236,42 @@
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.25">
@@ -7221,17 +7281,17 @@
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.25">
@@ -7241,22 +7301,22 @@
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.25">
@@ -7266,147 +7326,147 @@
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="54" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="56" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="59" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="60" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="61" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="62" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="63" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="64" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="66" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="67" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="68" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="69" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="70" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="71" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="72" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="73" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="74" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="75" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="76" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="77" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="78" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
     </row>
     <row r="79" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="80" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="81" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
   </sheetData>

--- a/config/Excel/Status.xlsx
+++ b/config/Excel/Status.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\AppData\Local\Temp\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyGame\Idle-RPG\codex\config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D8D3AF8-42C0-448E-ACB0-F4BF0CE0998D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EEDE6AB-4DED-4236-AE80-A57AC7315B65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3090" yWindow="2310" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Status" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1031" uniqueCount="484">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1025" uniqueCount="483">
   <si>
     <t>狀態ID</t>
   </si>
@@ -1501,9 +1501,6 @@
   </si>
   <si>
     <t>20</t>
-  </si>
-  <si>
-    <t>5</t>
   </si>
   <si>
     <t>傳奇特效【貫日之刺】：突刺命中時機率使敵人重傷（效果值＝受到的傷害提高%）。沒有附加條件，狀態在身上就算數，走 skill2VulnACfg 的同一個 totalDmgPct；不疊層，重複命中只刷新時間。</t>
@@ -2103,7 +2100,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2112,6 +2109,9 @@
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="42">
@@ -5153,29 +5153,29 @@
       <c r="F58" s="1" t="s">
         <v>477</v>
       </c>
-      <c r="I58" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="K58" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="L58" s="1" t="s">
-        <v>480</v>
-      </c>
-      <c r="M58" s="1" t="s">
-        <v>481</v>
-      </c>
-      <c r="N58" s="1" t="s">
-        <v>393</v>
+      <c r="I58" s="3">
+        <v>0</v>
+      </c>
+      <c r="K58" s="3">
+        <v>0</v>
+      </c>
+      <c r="L58" s="3">
+        <v>20</v>
+      </c>
+      <c r="M58" s="3">
+        <v>5</v>
+      </c>
+      <c r="N58" s="3">
+        <v>0</v>
       </c>
       <c r="O58" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="P58" s="1" t="s">
-        <v>395</v>
+      <c r="P58" s="3">
+        <v>1</v>
       </c>
       <c r="T58" s="1" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="59" spans="1:20" x14ac:dyDescent="0.25">
@@ -7002,7 +7002,7 @@
         <v>480</v>
       </c>
       <c r="T97" s="1" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
     </row>
     <row r="98" spans="1:20" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">

--- a/config/Excel/Status.xlsx
+++ b/config/Excel/Status.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyGame\Idle-RPG\codex\config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EEDE6AB-4DED-4236-AE80-A57AC7315B65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2350C38-6130-4865-BDD1-B4283FA3E03A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Status" sheetId="1" r:id="rId1"/>
@@ -2100,7 +2100,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2109,9 +2109,6 @@
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="42">
@@ -2489,12 +2486,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:T98"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="18" max="18" width="12.375" customWidth="1"/>
+    <col min="18" max="18" width="12.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2556,7 +2553,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>20</v>
       </c>
@@ -2600,7 +2597,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>28</v>
       </c>
@@ -2647,7 +2644,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>33</v>
       </c>
@@ -2694,7 +2691,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>37</v>
       </c>
@@ -2741,7 +2738,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>42</v>
       </c>
@@ -2788,7 +2785,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>46</v>
       </c>
@@ -2838,7 +2835,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>52</v>
       </c>
@@ -2882,7 +2879,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>58</v>
       </c>
@@ -2926,7 +2923,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>62</v>
       </c>
@@ -2970,7 +2967,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>67</v>
       </c>
@@ -3017,7 +3014,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>72</v>
       </c>
@@ -3064,7 +3061,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>76</v>
       </c>
@@ -3108,7 +3105,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>81</v>
       </c>
@@ -3152,7 +3149,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>84</v>
       </c>
@@ -3196,7 +3193,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>88</v>
       </c>
@@ -3240,7 +3237,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="17" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>92</v>
       </c>
@@ -3284,7 +3281,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>96</v>
       </c>
@@ -3328,7 +3325,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="19" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>100</v>
       </c>
@@ -3372,7 +3369,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="20" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>104</v>
       </c>
@@ -3416,7 +3413,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="21" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>108</v>
       </c>
@@ -3460,7 +3457,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="22" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>112</v>
       </c>
@@ -3504,7 +3501,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="23" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>117</v>
       </c>
@@ -3551,7 +3548,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="24" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>121</v>
       </c>
@@ -3595,7 +3592,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="25" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>124</v>
       </c>
@@ -3642,7 +3639,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="26" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>127</v>
       </c>
@@ -3686,7 +3683,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="27" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>129</v>
       </c>
@@ -3730,7 +3727,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="28" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>131</v>
       </c>
@@ -3774,7 +3771,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="29" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>134</v>
       </c>
@@ -3827,7 +3824,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="30" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>137</v>
       </c>
@@ -3871,7 +3868,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="31" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>140</v>
       </c>
@@ -3915,7 +3912,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="32" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>143</v>
       </c>
@@ -3959,7 +3956,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="33" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>147</v>
       </c>
@@ -4003,7 +4000,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="34" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>151</v>
       </c>
@@ -4050,7 +4047,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="35" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>154</v>
       </c>
@@ -4097,7 +4094,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="36" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>158</v>
       </c>
@@ -4141,7 +4138,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="37" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>164</v>
       </c>
@@ -4191,7 +4188,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="38" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>166</v>
       </c>
@@ -4238,7 +4235,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="39" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>168</v>
       </c>
@@ -4285,7 +4282,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="40" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>172</v>
       </c>
@@ -4332,7 +4329,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="41" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>177</v>
       </c>
@@ -4376,7 +4373,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="42" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>180</v>
       </c>
@@ -4423,7 +4420,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="43" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>184</v>
       </c>
@@ -4470,7 +4467,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="44" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>187</v>
       </c>
@@ -4517,7 +4514,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="45" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>191</v>
       </c>
@@ -4564,7 +4561,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="46" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>195</v>
       </c>
@@ -4611,7 +4608,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="47" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>200</v>
       </c>
@@ -4661,7 +4658,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="48" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>204</v>
       </c>
@@ -4708,7 +4705,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="49" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>208</v>
       </c>
@@ -4755,7 +4752,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="50" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>212</v>
       </c>
@@ -4802,7 +4799,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="51" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>215</v>
       </c>
@@ -4849,7 +4846,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="52" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>219</v>
       </c>
@@ -4896,7 +4893,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="53" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>222</v>
       </c>
@@ -4943,7 +4940,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="54" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>225</v>
       </c>
@@ -4993,7 +4990,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="55" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>228</v>
       </c>
@@ -5040,7 +5037,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="56" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>231</v>
       </c>
@@ -5090,7 +5087,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="57" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>235</v>
       </c>
@@ -5134,7 +5131,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="58" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
         <v>477</v>
       </c>
@@ -5153,32 +5150,32 @@
       <c r="F58" s="1" t="s">
         <v>477</v>
       </c>
-      <c r="I58" s="3">
-        <v>0</v>
-      </c>
-      <c r="K58" s="3">
-        <v>0</v>
-      </c>
-      <c r="L58" s="3">
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="K58">
+        <v>0</v>
+      </c>
+      <c r="L58">
         <v>20</v>
       </c>
-      <c r="M58" s="3">
+      <c r="M58">
         <v>5</v>
       </c>
-      <c r="N58" s="3">
+      <c r="N58">
         <v>0</v>
       </c>
       <c r="O58" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="P58" s="3">
+      <c r="P58">
         <v>1</v>
       </c>
       <c r="T58" s="1" t="s">
         <v>481</v>
       </c>
     </row>
-    <row r="59" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>237</v>
       </c>
@@ -5225,7 +5222,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="60" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>241</v>
       </c>
@@ -5269,7 +5266,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="61" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>244</v>
       </c>
@@ -5313,7 +5310,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="62" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>248</v>
       </c>
@@ -5357,7 +5354,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="63" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>251</v>
       </c>
@@ -5401,7 +5398,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="64" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>255</v>
       </c>
@@ -5445,7 +5442,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="65" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>259</v>
       </c>
@@ -5492,7 +5489,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="66" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>263</v>
       </c>
@@ -5539,7 +5536,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="67" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>266</v>
       </c>
@@ -5586,7 +5583,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="68" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>270</v>
       </c>
@@ -5630,7 +5627,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="69" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>273</v>
       </c>
@@ -5674,7 +5671,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="70" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>277</v>
       </c>
@@ -5718,7 +5715,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="71" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>280</v>
       </c>
@@ -5762,7 +5759,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="72" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>284</v>
       </c>
@@ -5806,7 +5803,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="73" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>288</v>
       </c>
@@ -5853,7 +5850,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="74" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>291</v>
       </c>
@@ -5900,7 +5897,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="75" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>294</v>
       </c>
@@ -5947,7 +5944,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="76" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>296</v>
       </c>
@@ -5994,7 +5991,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="77" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>299</v>
       </c>
@@ -6041,7 +6038,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="78" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>303</v>
       </c>
@@ -6085,7 +6082,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="79" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>306</v>
       </c>
@@ -6132,7 +6129,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="80" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>309</v>
       </c>
@@ -6179,7 +6176,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="81" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>312</v>
       </c>
@@ -6226,7 +6223,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="82" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>316</v>
       </c>
@@ -6273,7 +6270,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="83" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>319</v>
       </c>
@@ -6320,7 +6317,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="84" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>323</v>
       </c>
@@ -6367,7 +6364,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="85" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A85" s="1" t="s">
         <v>391</v>
       </c>
@@ -6417,7 +6414,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="86" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A86" s="1" t="s">
         <v>398</v>
       </c>
@@ -6467,7 +6464,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="87" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A87" s="1" t="s">
         <v>403</v>
       </c>
@@ -6517,7 +6514,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="88" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A88" s="1" t="s">
         <v>407</v>
       </c>
@@ -6567,7 +6564,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="89" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A89" s="1" t="s">
         <v>411</v>
       </c>
@@ -6617,7 +6614,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="90" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A90" s="1" t="s">
         <v>414</v>
       </c>
@@ -6667,7 +6664,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="91" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A91" s="1" t="s">
         <v>419</v>
       </c>
@@ -6717,7 +6714,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="92" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A92" s="1" t="s">
         <v>432</v>
       </c>
@@ -6764,7 +6761,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="93" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A93" s="1" t="s">
         <v>437</v>
       </c>
@@ -6814,7 +6811,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="94" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A94" s="1" t="s">
         <v>442</v>
       </c>
@@ -6864,7 +6861,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="95" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A95" s="1" t="s">
         <v>448</v>
       </c>
@@ -6911,7 +6908,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="96" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A96" s="1" t="s">
         <v>452</v>
       </c>
@@ -6958,7 +6955,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="97" spans="1:20" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:20" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>465</v>
       </c>
@@ -7005,7 +7002,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="98" spans="1:20" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:20" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>472</v>
       </c>
@@ -7059,412 +7056,412 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:A81"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="125.625" customWidth="1"/>
+    <col min="1" max="1" width="125.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>327</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>328</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>384</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>329</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>384</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>331</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>332</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>384</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>333</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
         <v>334</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
         <v>335</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
         <v>336</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
         <v>337</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
         <v>384</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:1" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
         <v>338</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
         <v>339</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
         <v>341</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
         <v>384</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
         <v>342</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
         <v>343</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
         <v>384</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
         <v>344</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
         <v>345</v>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
         <v>346</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
         <v>384</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
         <v>347</v>
       </c>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
         <v>348</v>
       </c>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
         <v>349</v>
       </c>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
         <v>384</v>
       </c>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
         <v>350</v>
       </c>
     </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
         <v>351</v>
       </c>
     </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
         <v>352</v>
       </c>
     </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
         <v>384</v>
       </c>
     </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
         <v>353</v>
       </c>
     </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
         <v>354</v>
       </c>
     </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
         <v>384</v>
       </c>
     </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A48" s="2" t="s">
         <v>355</v>
       </c>
     </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A49" s="2" t="s">
         <v>356</v>
       </c>
     </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
         <v>357</v>
       </c>
     </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
         <v>384</v>
       </c>
     </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A52" s="2" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A53" s="2" t="s">
         <v>358</v>
       </c>
     </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="s">
         <v>359</v>
       </c>
     </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A55" s="2" t="s">
         <v>360</v>
       </c>
     </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A56" s="2" t="s">
         <v>361</v>
       </c>
     </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A57" s="2" t="s">
         <v>384</v>
       </c>
     </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A58" s="2" t="s">
         <v>362</v>
       </c>
     </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A59" s="2" t="s">
         <v>363</v>
       </c>
     </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A60" s="2" t="s">
         <v>364</v>
       </c>
     </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A61" s="2" t="s">
         <v>365</v>
       </c>
     </row>
-    <row r="62" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A62" s="2" t="s">
         <v>366</v>
       </c>
     </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A63" s="2" t="s">
         <v>367</v>
       </c>
     </row>
-    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A64" s="2" t="s">
         <v>368</v>
       </c>
     </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A65" s="2" t="s">
         <v>369</v>
       </c>
     </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A66" s="2" t="s">
         <v>384</v>
       </c>
     </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A67" s="2" t="s">
         <v>370</v>
       </c>
     </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A68" s="2" t="s">
         <v>371</v>
       </c>
     </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A69" s="2" t="s">
         <v>372</v>
       </c>
     </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A70" s="2" t="s">
         <v>373</v>
       </c>
     </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A71" s="2" t="s">
         <v>374</v>
       </c>
     </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A72" s="2" t="s">
         <v>384</v>
       </c>
     </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A73" s="2" t="s">
         <v>385</v>
       </c>
     </row>
-    <row r="74" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A74" s="2" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="75" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A75" s="2" t="s">
         <v>375</v>
       </c>
     </row>
-    <row r="76" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A76" s="2" t="s">
         <v>387</v>
       </c>
     </row>
-    <row r="77" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:1" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A77" s="2" t="s">
         <v>388</v>
       </c>
     </row>
-    <row r="78" spans="1:1" ht="33" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:1" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A78" s="2" t="s">
         <v>421</v>
       </c>
     </row>
-    <row r="79" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A79" s="2" t="s">
         <v>422</v>
       </c>
     </row>
-    <row r="80" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A80" s="2" t="s">
         <v>389</v>
       </c>
     </row>
-    <row r="81" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A81" s="2" t="s">
         <v>390</v>
       </c>

--- a/config/Excel/Status.xlsx
+++ b/config/Excel/Status.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyGame\Idle-RPG\codex\config\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyGame\Idle-RPG\codex\config\param-patches\archive\2026-10-28T09-13-38-681Z-5c0289f2-6d6e-4dc9-b908-37fafb7db390\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2350C38-6130-4865-BDD1-B4283FA3E03A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC9F8569-C13C-46D7-B298-B5A116AE7590}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="3015" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Status" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1025" uniqueCount="483">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1025" uniqueCount="484">
   <si>
     <t>狀態ID</t>
   </si>
@@ -451,9 +451,6 @@
   </si>
   <si>
     <t>鐵血裂傷</t>
-  </si>
-  <si>
-    <t>新版技能【鐵血之舞】：占最大生命比例的流血；自身流血直接扣生命、不吃護盾。</t>
   </si>
   <si>
     <t>sgGale</t>
@@ -1507,6 +1504,14 @@
   </si>
   <si>
     <t>傳奇【烈火狩】：火狩持續期間按節拍疊加火屬性傷害提升，最多 20 層，滿層只刷新時間；火狩全部消失後到期，與火焰增幅各自計算層數。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>skill</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>新版技能【鐵血之舞】：依施法者物理攻擊計算流血；附近敵人按自身流血基準的承受比例計算。自身流血直接扣生命、不吃護盾。</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -2100,7 +2105,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2109,6 +2114,9 @@
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="42">
@@ -2486,12 +2494,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:T98"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="18" max="18" width="12.33203125" customWidth="1"/>
+    <col min="18" max="18" width="12.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2553,7 +2561,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>20</v>
       </c>
@@ -2597,7 +2605,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>28</v>
       </c>
@@ -2644,7 +2652,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>33</v>
       </c>
@@ -2691,7 +2699,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>37</v>
       </c>
@@ -2738,7 +2746,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>42</v>
       </c>
@@ -2785,7 +2793,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>46</v>
       </c>
@@ -2835,7 +2843,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>52</v>
       </c>
@@ -2879,7 +2887,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>58</v>
       </c>
@@ -2923,7 +2931,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>62</v>
       </c>
@@ -2967,7 +2975,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>67</v>
       </c>
@@ -3014,7 +3022,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>72</v>
       </c>
@@ -3061,7 +3069,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>76</v>
       </c>
@@ -3105,7 +3113,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>81</v>
       </c>
@@ -3149,7 +3157,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>84</v>
       </c>
@@ -3193,7 +3201,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>88</v>
       </c>
@@ -3237,7 +3245,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="17" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>92</v>
       </c>
@@ -3281,7 +3289,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>96</v>
       </c>
@@ -3325,7 +3333,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="19" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>100</v>
       </c>
@@ -3369,7 +3377,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="20" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>104</v>
       </c>
@@ -3413,7 +3421,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="21" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>108</v>
       </c>
@@ -3457,12 +3465,12 @@
         <v>111</v>
       </c>
     </row>
-    <row r="22" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>112</v>
       </c>
       <c r="B22" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="C22" t="s">
         <v>113</v>
@@ -3498,10 +3506,10 @@
         <v>1</v>
       </c>
       <c r="T22" t="s">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="23" spans="1:20" x14ac:dyDescent="0.3">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="23" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>117</v>
       </c>
@@ -3548,7 +3556,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="24" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>121</v>
       </c>
@@ -3592,7 +3600,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="25" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>124</v>
       </c>
@@ -3639,7 +3647,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="26" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>127</v>
       </c>
@@ -3683,7 +3691,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="27" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>129</v>
       </c>
@@ -3727,7 +3735,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="28" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>131</v>
       </c>
@@ -3771,7 +3779,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="29" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>134</v>
       </c>
@@ -3815,16 +3823,16 @@
         <v>1</v>
       </c>
       <c r="Q29" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="S29" s="1" t="s">
         <v>376</v>
-      </c>
-      <c r="S29" s="1" t="s">
-        <v>377</v>
       </c>
       <c r="T29" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="30" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>137</v>
       </c>
@@ -3840,11 +3848,11 @@
       <c r="E30" t="s">
         <v>24</v>
       </c>
-      <c r="H30" t="s">
-        <v>49</v>
+      <c r="H30" s="3" t="s">
+        <v>482</v>
       </c>
       <c r="I30">
-        <v>3.5</v>
+        <v>100</v>
       </c>
       <c r="K30">
         <v>0</v>
@@ -3864,16 +3872,16 @@
       <c r="P30">
         <v>1</v>
       </c>
-      <c r="T30" t="s">
+      <c r="T30" s="3" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="31" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
         <v>139</v>
       </c>
-    </row>
-    <row r="31" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A31" t="s">
+      <c r="B31" t="s">
         <v>140</v>
-      </c>
-      <c r="B31" t="s">
-        <v>141</v>
       </c>
       <c r="C31" t="s">
         <v>114</v>
@@ -3885,7 +3893,7 @@
         <v>79</v>
       </c>
       <c r="F31" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I31">
         <v>0</v>
@@ -3909,15 +3917,15 @@
         <v>1</v>
       </c>
       <c r="T31" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="32" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
         <v>142</v>
       </c>
-    </row>
-    <row r="32" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A32" t="s">
+      <c r="B32" t="s">
         <v>143</v>
-      </c>
-      <c r="B32" t="s">
-        <v>144</v>
       </c>
       <c r="C32" t="s">
         <v>30</v>
@@ -3929,7 +3937,7 @@
         <v>79</v>
       </c>
       <c r="F32" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="I32">
         <v>0</v>
@@ -3953,15 +3961,15 @@
         <v>1</v>
       </c>
       <c r="T32" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="33" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
         <v>146</v>
       </c>
-    </row>
-    <row r="33" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A33" t="s">
+      <c r="B33" t="s">
         <v>147</v>
-      </c>
-      <c r="B33" t="s">
-        <v>148</v>
       </c>
       <c r="C33" t="s">
         <v>94</v>
@@ -3973,7 +3981,7 @@
         <v>79</v>
       </c>
       <c r="F33" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="I33">
         <v>0</v>
@@ -3997,18 +4005,18 @@
         <v>1</v>
       </c>
       <c r="T33" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="34" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
         <v>150</v>
       </c>
-    </row>
-    <row r="34" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A34" t="s">
+      <c r="B34" t="s">
         <v>151</v>
       </c>
-      <c r="B34" t="s">
+      <c r="C34" t="s">
         <v>152</v>
-      </c>
-      <c r="C34" t="s">
-        <v>153</v>
       </c>
       <c r="D34" t="s">
         <v>65</v>
@@ -4017,7 +4025,7 @@
         <v>79</v>
       </c>
       <c r="F34" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="I34">
         <v>0</v>
@@ -4041,21 +4049,21 @@
         <v>1</v>
       </c>
       <c r="R34" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="T34" s="1" t="s">
         <v>423</v>
       </c>
-      <c r="T34" s="1" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="35" spans="1:20" x14ac:dyDescent="0.3">
+    </row>
+    <row r="35" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
+        <v>153</v>
+      </c>
+      <c r="B35" t="s">
         <v>154</v>
       </c>
-      <c r="B35" t="s">
+      <c r="C35" t="s">
         <v>155</v>
-      </c>
-      <c r="C35" t="s">
-        <v>156</v>
       </c>
       <c r="D35" t="s">
         <v>65</v>
@@ -4064,7 +4072,7 @@
         <v>79</v>
       </c>
       <c r="F35" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="I35">
         <v>0</v>
@@ -4088,21 +4096,21 @@
         <v>1</v>
       </c>
       <c r="R35" s="1" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="T35" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="36" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
         <v>157</v>
       </c>
-    </row>
-    <row r="36" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A36" t="s">
+      <c r="B36" t="s">
         <v>158</v>
       </c>
-      <c r="B36" t="s">
+      <c r="C36" t="s">
         <v>159</v>
-      </c>
-      <c r="C36" t="s">
-        <v>160</v>
       </c>
       <c r="D36" t="s">
         <v>23</v>
@@ -4111,7 +4119,7 @@
         <v>79</v>
       </c>
       <c r="F36" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="I36">
         <v>0</v>
@@ -4129,21 +4137,21 @@
         <v>0</v>
       </c>
       <c r="O36" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="P36">
         <v>4</v>
       </c>
       <c r="T36" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="37" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
         <v>163</v>
       </c>
-    </row>
-    <row r="37" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A37" t="s">
+      <c r="B37" t="s">
         <v>164</v>
-      </c>
-      <c r="B37" t="s">
-        <v>165</v>
       </c>
       <c r="C37" t="s">
         <v>30</v>
@@ -4182,18 +4190,18 @@
         <v>1</v>
       </c>
       <c r="S37" s="1" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="T37" t="s">
-        <v>471</v>
-      </c>
-    </row>
-    <row r="38" spans="1:20" x14ac:dyDescent="0.3">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="38" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
+        <v>165</v>
+      </c>
+      <c r="B38" t="s">
         <v>166</v>
-      </c>
-      <c r="B38" t="s">
-        <v>167</v>
       </c>
       <c r="C38" t="s">
         <v>30</v>
@@ -4205,7 +4213,7 @@
         <v>79</v>
       </c>
       <c r="F38" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="G38" t="s">
         <v>31</v>
@@ -4226,24 +4234,24 @@
         <v>0</v>
       </c>
       <c r="O38" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="P38">
         <v>50</v>
       </c>
       <c r="T38" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="39" spans="1:20" x14ac:dyDescent="0.3">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="39" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
+        <v>167</v>
+      </c>
+      <c r="B39" t="s">
         <v>168</v>
       </c>
-      <c r="B39" t="s">
+      <c r="C39" t="s">
         <v>169</v>
-      </c>
-      <c r="C39" t="s">
-        <v>170</v>
       </c>
       <c r="D39" t="s">
         <v>65</v>
@@ -4252,7 +4260,7 @@
         <v>79</v>
       </c>
       <c r="F39" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="G39" t="s">
         <v>31</v>
@@ -4279,18 +4287,18 @@
         <v>1</v>
       </c>
       <c r="T39" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="40" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
         <v>171</v>
       </c>
-    </row>
-    <row r="40" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A40" t="s">
+      <c r="B40" t="s">
         <v>172</v>
       </c>
-      <c r="B40" t="s">
+      <c r="C40" t="s">
         <v>173</v>
-      </c>
-      <c r="C40" t="s">
-        <v>174</v>
       </c>
       <c r="D40" t="s">
         <v>65</v>
@@ -4299,10 +4307,10 @@
         <v>79</v>
       </c>
       <c r="F40" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="G40" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I40">
         <v>0</v>
@@ -4326,18 +4334,18 @@
         <v>1</v>
       </c>
       <c r="T40" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="41" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="41" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A41" t="s">
+      <c r="B41" t="s">
         <v>177</v>
       </c>
-      <c r="B41" t="s">
-        <v>178</v>
-      </c>
       <c r="C41" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D41" t="s">
         <v>65</v>
@@ -4346,7 +4354,7 @@
         <v>79</v>
       </c>
       <c r="F41" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I41">
         <v>0</v>
@@ -4370,18 +4378,18 @@
         <v>1</v>
       </c>
       <c r="T41" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="42" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
         <v>179</v>
       </c>
-    </row>
-    <row r="42" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A42" t="s">
+      <c r="B42" t="s">
         <v>180</v>
       </c>
-      <c r="B42" t="s">
+      <c r="C42" t="s">
         <v>181</v>
-      </c>
-      <c r="C42" t="s">
-        <v>182</v>
       </c>
       <c r="D42" t="s">
         <v>23</v>
@@ -4390,10 +4398,10 @@
         <v>79</v>
       </c>
       <c r="F42" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G42" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I42">
         <v>0</v>
@@ -4417,15 +4425,15 @@
         <v>1</v>
       </c>
       <c r="T42" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="43" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
         <v>183</v>
       </c>
-    </row>
-    <row r="43" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A43" t="s">
+      <c r="B43" t="s">
         <v>184</v>
-      </c>
-      <c r="B43" t="s">
-        <v>185</v>
       </c>
       <c r="C43" t="s">
         <v>35</v>
@@ -4464,18 +4472,18 @@
         <v>1</v>
       </c>
       <c r="T43" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="44" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
         <v>186</v>
       </c>
-    </row>
-    <row r="44" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A44" t="s">
+      <c r="B44" t="s">
         <v>187</v>
       </c>
-      <c r="B44" t="s">
+      <c r="C44" t="s">
         <v>188</v>
-      </c>
-      <c r="C44" t="s">
-        <v>189</v>
       </c>
       <c r="D44" t="s">
         <v>23</v>
@@ -4511,18 +4519,18 @@
         <v>1</v>
       </c>
       <c r="T44" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="45" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
         <v>190</v>
       </c>
-    </row>
-    <row r="45" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A45" t="s">
+      <c r="B45" t="s">
         <v>191</v>
       </c>
-      <c r="B45" t="s">
+      <c r="C45" t="s">
         <v>192</v>
-      </c>
-      <c r="C45" t="s">
-        <v>193</v>
       </c>
       <c r="D45" t="s">
         <v>65</v>
@@ -4531,7 +4539,7 @@
         <v>79</v>
       </c>
       <c r="F45" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G45" t="s">
         <v>115</v>
@@ -4558,18 +4566,18 @@
         <v>1</v>
       </c>
       <c r="T45" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="46" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
         <v>194</v>
       </c>
-    </row>
-    <row r="46" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A46" t="s">
+      <c r="B46" t="s">
         <v>195</v>
       </c>
-      <c r="B46" t="s">
+      <c r="C46" t="s">
         <v>196</v>
-      </c>
-      <c r="C46" t="s">
-        <v>197</v>
       </c>
       <c r="D46" t="s">
         <v>23</v>
@@ -4578,10 +4586,10 @@
         <v>79</v>
       </c>
       <c r="F46" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G46" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="I46">
         <v>0</v>
@@ -4599,24 +4607,24 @@
         <v>0</v>
       </c>
       <c r="O46" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="P46">
         <v>5</v>
       </c>
       <c r="T46" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="47" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
         <v>199</v>
       </c>
-    </row>
-    <row r="47" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A47" t="s">
+      <c r="B47" t="s">
         <v>200</v>
       </c>
-      <c r="B47" t="s">
+      <c r="C47" t="s">
         <v>201</v>
-      </c>
-      <c r="C47" t="s">
-        <v>202</v>
       </c>
       <c r="D47" t="s">
         <v>23</v>
@@ -4625,7 +4633,7 @@
         <v>24</v>
       </c>
       <c r="G47" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="H47" t="s">
         <v>25</v>
@@ -4652,21 +4660,21 @@
         <v>1</v>
       </c>
       <c r="S47" s="1" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="T47" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="48" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
         <v>203</v>
       </c>
-    </row>
-    <row r="48" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A48" t="s">
+      <c r="B48" t="s">
         <v>204</v>
       </c>
-      <c r="B48" t="s">
+      <c r="C48" t="s">
         <v>205</v>
-      </c>
-      <c r="C48" t="s">
-        <v>206</v>
       </c>
       <c r="D48" t="s">
         <v>23</v>
@@ -4675,10 +4683,10 @@
         <v>79</v>
       </c>
       <c r="F48" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="G48" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="I48">
         <v>0</v>
@@ -4702,18 +4710,18 @@
         <v>1</v>
       </c>
       <c r="T48" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="49" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
         <v>207</v>
       </c>
-    </row>
-    <row r="49" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A49" t="s">
+      <c r="B49" t="s">
         <v>208</v>
       </c>
-      <c r="B49" t="s">
+      <c r="C49" t="s">
         <v>209</v>
-      </c>
-      <c r="C49" t="s">
-        <v>210</v>
       </c>
       <c r="D49" t="s">
         <v>23</v>
@@ -4722,10 +4730,10 @@
         <v>79</v>
       </c>
       <c r="F49" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="G49" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="I49">
         <v>0</v>
@@ -4749,18 +4757,18 @@
         <v>1</v>
       </c>
       <c r="T49" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="50" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
         <v>211</v>
       </c>
-    </row>
-    <row r="50" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A50" t="s">
+      <c r="B50" t="s">
         <v>212</v>
       </c>
-      <c r="B50" t="s">
-        <v>213</v>
-      </c>
       <c r="C50" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D50" t="s">
         <v>65</v>
@@ -4769,10 +4777,10 @@
         <v>79</v>
       </c>
       <c r="F50" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G50" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="I50">
         <v>0</v>
@@ -4796,15 +4804,15 @@
         <v>1</v>
       </c>
       <c r="T50" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="51" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
         <v>214</v>
       </c>
-    </row>
-    <row r="51" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A51" t="s">
+      <c r="B51" t="s">
         <v>215</v>
-      </c>
-      <c r="B51" t="s">
-        <v>216</v>
       </c>
       <c r="C51" t="s">
         <v>114</v>
@@ -4816,10 +4824,10 @@
         <v>79</v>
       </c>
       <c r="F51" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="G51" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="I51">
         <v>0</v>
@@ -4837,21 +4845,21 @@
         <v>0</v>
       </c>
       <c r="O51" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="P51">
         <v>6</v>
       </c>
       <c r="T51" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="52" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
         <v>218</v>
       </c>
-    </row>
-    <row r="52" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A52" t="s">
+      <c r="B52" t="s">
         <v>219</v>
-      </c>
-      <c r="B52" t="s">
-        <v>220</v>
       </c>
       <c r="C52" t="s">
         <v>114</v>
@@ -4863,7 +4871,7 @@
         <v>24</v>
       </c>
       <c r="G52" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="H52" t="s">
         <v>25</v>
@@ -4890,18 +4898,18 @@
         <v>1</v>
       </c>
       <c r="T52" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="53" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
         <v>221</v>
       </c>
-    </row>
-    <row r="53" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A53" t="s">
+      <c r="B53" t="s">
         <v>222</v>
       </c>
-      <c r="B53" t="s">
+      <c r="C53" t="s">
         <v>223</v>
-      </c>
-      <c r="C53" t="s">
-        <v>224</v>
       </c>
       <c r="D53" t="s">
         <v>23</v>
@@ -4910,10 +4918,10 @@
         <v>79</v>
       </c>
       <c r="F53" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="G53" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="I53">
         <v>0</v>
@@ -4937,18 +4945,18 @@
         <v>1</v>
       </c>
       <c r="T53" t="s">
-        <v>475</v>
-      </c>
-    </row>
-    <row r="54" spans="1:20" x14ac:dyDescent="0.3">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="54" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
+        <v>224</v>
+      </c>
+      <c r="B54" t="s">
         <v>225</v>
       </c>
-      <c r="B54" t="s">
-        <v>226</v>
-      </c>
       <c r="C54" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D54" t="s">
         <v>65</v>
@@ -4957,10 +4965,10 @@
         <v>79</v>
       </c>
       <c r="F54" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="G54" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="I54">
         <v>0</v>
@@ -4984,18 +4992,18 @@
         <v>1</v>
       </c>
       <c r="R54" s="1" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="T54" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="55" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
         <v>227</v>
       </c>
-    </row>
-    <row r="55" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A55" t="s">
+      <c r="B55" t="s">
         <v>228</v>
-      </c>
-      <c r="B55" t="s">
-        <v>229</v>
       </c>
       <c r="C55" t="s">
         <v>90</v>
@@ -5007,10 +5015,10 @@
         <v>79</v>
       </c>
       <c r="F55" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="G55" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="I55">
         <v>0</v>
@@ -5034,18 +5042,18 @@
         <v>1</v>
       </c>
       <c r="T55" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="56" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
         <v>230</v>
       </c>
-    </row>
-    <row r="56" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A56" t="s">
+      <c r="B56" t="s">
         <v>231</v>
       </c>
-      <c r="B56" t="s">
+      <c r="C56" t="s">
         <v>232</v>
-      </c>
-      <c r="C56" t="s">
-        <v>233</v>
       </c>
       <c r="D56" t="s">
         <v>65</v>
@@ -5054,10 +5062,10 @@
         <v>79</v>
       </c>
       <c r="F56" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="G56" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="I56">
         <v>0</v>
@@ -5081,18 +5089,18 @@
         <v>1</v>
       </c>
       <c r="R56" s="1" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="T56" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="57" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
         <v>234</v>
       </c>
-    </row>
-    <row r="57" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A57" t="s">
+      <c r="B57" t="s">
         <v>235</v>
-      </c>
-      <c r="B57" t="s">
-        <v>236</v>
       </c>
       <c r="C57" t="s">
         <v>39</v>
@@ -5104,7 +5112,7 @@
         <v>79</v>
       </c>
       <c r="F57" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="I57">
         <v>0</v>
@@ -5122,24 +5130,24 @@
         <v>0</v>
       </c>
       <c r="O57" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="P57">
         <v>10</v>
       </c>
       <c r="T57" s="1" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="58" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A58" s="1" t="s">
         <v>476</v>
       </c>
-    </row>
-    <row r="58" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A58" s="1" t="s">
+      <c r="B58" s="1" t="s">
         <v>477</v>
       </c>
-      <c r="B58" s="1" t="s">
+      <c r="C58" s="1" t="s">
         <v>478</v>
-      </c>
-      <c r="C58" s="1" t="s">
-        <v>479</v>
       </c>
       <c r="D58" s="1" t="s">
         <v>23</v>
@@ -5148,7 +5156,7 @@
         <v>79</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="I58">
         <v>0</v>
@@ -5172,18 +5180,18 @@
         <v>1</v>
       </c>
       <c r="T58" s="1" t="s">
-        <v>481</v>
-      </c>
-    </row>
-    <row r="59" spans="1:20" x14ac:dyDescent="0.3">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="59" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
+        <v>236</v>
+      </c>
+      <c r="B59" t="s">
         <v>237</v>
       </c>
-      <c r="B59" t="s">
+      <c r="C59" t="s">
         <v>238</v>
-      </c>
-      <c r="C59" t="s">
-        <v>239</v>
       </c>
       <c r="D59" t="s">
         <v>23</v>
@@ -5192,7 +5200,7 @@
         <v>79</v>
       </c>
       <c r="F59" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="G59" t="s">
         <v>40</v>
@@ -5213,21 +5221,21 @@
         <v>0</v>
       </c>
       <c r="O59" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="P59">
         <v>100</v>
       </c>
       <c r="T59" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="60" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
         <v>240</v>
       </c>
-    </row>
-    <row r="60" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A60" t="s">
+      <c r="B60" t="s">
         <v>241</v>
-      </c>
-      <c r="B60" t="s">
-        <v>242</v>
       </c>
       <c r="C60" t="s">
         <v>22</v>
@@ -5263,18 +5271,18 @@
         <v>1</v>
       </c>
       <c r="T60" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="61" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
         <v>243</v>
       </c>
-    </row>
-    <row r="61" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A61" t="s">
+      <c r="B61" t="s">
         <v>244</v>
       </c>
-      <c r="B61" t="s">
+      <c r="C61" t="s">
         <v>245</v>
-      </c>
-      <c r="C61" t="s">
-        <v>246</v>
       </c>
       <c r="D61" t="s">
         <v>65</v>
@@ -5283,7 +5291,7 @@
         <v>79</v>
       </c>
       <c r="F61" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="I61">
         <v>0</v>
@@ -5307,15 +5315,15 @@
         <v>1</v>
       </c>
       <c r="T61" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="62" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
         <v>247</v>
       </c>
-    </row>
-    <row r="62" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A62" t="s">
+      <c r="B62" t="s">
         <v>248</v>
-      </c>
-      <c r="B62" t="s">
-        <v>249</v>
       </c>
       <c r="C62" t="s">
         <v>35</v>
@@ -5327,7 +5335,7 @@
         <v>79</v>
       </c>
       <c r="F62" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="I62">
         <v>0</v>
@@ -5345,24 +5353,24 @@
         <v>0</v>
       </c>
       <c r="O62" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="P62">
         <v>20</v>
       </c>
       <c r="T62" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="63" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
         <v>250</v>
       </c>
-    </row>
-    <row r="63" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A63" t="s">
+      <c r="B63" t="s">
         <v>251</v>
       </c>
-      <c r="B63" t="s">
+      <c r="C63" t="s">
         <v>252</v>
-      </c>
-      <c r="C63" t="s">
-        <v>253</v>
       </c>
       <c r="D63" t="s">
         <v>65</v>
@@ -5371,7 +5379,7 @@
         <v>79</v>
       </c>
       <c r="F63" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="I63">
         <v>0</v>
@@ -5395,18 +5403,18 @@
         <v>1</v>
       </c>
       <c r="T63" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="64" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
         <v>254</v>
       </c>
-    </row>
-    <row r="64" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A64" t="s">
+      <c r="B64" t="s">
         <v>255</v>
       </c>
-      <c r="B64" t="s">
+      <c r="C64" t="s">
         <v>256</v>
-      </c>
-      <c r="C64" t="s">
-        <v>257</v>
       </c>
       <c r="D64" t="s">
         <v>65</v>
@@ -5415,7 +5423,7 @@
         <v>79</v>
       </c>
       <c r="F64" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="I64">
         <v>0</v>
@@ -5433,24 +5441,24 @@
         <v>0</v>
       </c>
       <c r="O64" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="P64">
         <v>100</v>
       </c>
       <c r="T64" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="65" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
         <v>258</v>
       </c>
-    </row>
-    <row r="65" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A65" t="s">
+      <c r="B65" t="s">
         <v>259</v>
       </c>
-      <c r="B65" t="s">
+      <c r="C65" t="s">
         <v>260</v>
-      </c>
-      <c r="C65" t="s">
-        <v>261</v>
       </c>
       <c r="D65" t="s">
         <v>23</v>
@@ -5480,24 +5488,24 @@
         <v>0.5</v>
       </c>
       <c r="O65" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="P65">
         <v>10</v>
       </c>
       <c r="T65" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="66" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
         <v>262</v>
       </c>
-    </row>
-    <row r="66" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A66" t="s">
+      <c r="B66" t="s">
         <v>263</v>
       </c>
-      <c r="B66" t="s">
+      <c r="C66" t="s">
         <v>264</v>
-      </c>
-      <c r="C66" t="s">
-        <v>265</v>
       </c>
       <c r="D66" t="s">
         <v>23</v>
@@ -5527,24 +5535,24 @@
         <v>0.5</v>
       </c>
       <c r="O66" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="P66">
         <v>20</v>
       </c>
       <c r="T66" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="67" spans="1:20" x14ac:dyDescent="0.3">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="67" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
+        <v>265</v>
+      </c>
+      <c r="B67" t="s">
         <v>266</v>
       </c>
-      <c r="B67" t="s">
+      <c r="C67" t="s">
         <v>267</v>
-      </c>
-      <c r="C67" t="s">
-        <v>268</v>
       </c>
       <c r="D67" t="s">
         <v>65</v>
@@ -5553,7 +5561,7 @@
         <v>79</v>
       </c>
       <c r="F67" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="I67">
         <v>0</v>
@@ -5577,21 +5585,21 @@
         <v>1</v>
       </c>
       <c r="R67" s="1" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="T67" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="68" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
         <v>269</v>
       </c>
-    </row>
-    <row r="68" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A68" t="s">
+      <c r="B68" t="s">
         <v>270</v>
       </c>
-      <c r="B68" t="s">
-        <v>271</v>
-      </c>
       <c r="C68" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D68" t="s">
         <v>23</v>
@@ -5600,7 +5608,7 @@
         <v>79</v>
       </c>
       <c r="F68" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="I68">
         <v>0</v>
@@ -5624,18 +5632,18 @@
         <v>1</v>
       </c>
       <c r="T68" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="69" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
         <v>272</v>
       </c>
-    </row>
-    <row r="69" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A69" t="s">
+      <c r="B69" t="s">
         <v>273</v>
       </c>
-      <c r="B69" t="s">
+      <c r="C69" t="s">
         <v>274</v>
-      </c>
-      <c r="C69" t="s">
-        <v>275</v>
       </c>
       <c r="D69" t="s">
         <v>65</v>
@@ -5644,7 +5652,7 @@
         <v>79</v>
       </c>
       <c r="F69" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="I69">
         <v>0</v>
@@ -5668,15 +5676,15 @@
         <v>1</v>
       </c>
       <c r="T69" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="70" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
         <v>276</v>
       </c>
-    </row>
-    <row r="70" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A70" t="s">
+      <c r="B70" t="s">
         <v>277</v>
-      </c>
-      <c r="B70" t="s">
-        <v>278</v>
       </c>
       <c r="C70" t="s">
         <v>22</v>
@@ -5688,7 +5696,7 @@
         <v>79</v>
       </c>
       <c r="F70" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="I70">
         <v>0</v>
@@ -5706,24 +5714,24 @@
         <v>0</v>
       </c>
       <c r="O70" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="P70">
         <v>50</v>
       </c>
       <c r="T70" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="71" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
         <v>279</v>
       </c>
-    </row>
-    <row r="71" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A71" t="s">
+      <c r="B71" t="s">
         <v>280</v>
       </c>
-      <c r="B71" t="s">
+      <c r="C71" t="s">
         <v>281</v>
-      </c>
-      <c r="C71" t="s">
-        <v>282</v>
       </c>
       <c r="D71" t="s">
         <v>65</v>
@@ -5732,7 +5740,7 @@
         <v>79</v>
       </c>
       <c r="F71" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="I71">
         <v>0</v>
@@ -5750,24 +5758,24 @@
         <v>0</v>
       </c>
       <c r="O71" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="P71">
         <v>10</v>
       </c>
       <c r="T71" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="72" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
         <v>283</v>
       </c>
-    </row>
-    <row r="72" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A72" t="s">
+      <c r="B72" t="s">
         <v>284</v>
       </c>
-      <c r="B72" t="s">
+      <c r="C72" t="s">
         <v>285</v>
-      </c>
-      <c r="C72" t="s">
-        <v>286</v>
       </c>
       <c r="D72" t="s">
         <v>65</v>
@@ -5776,7 +5784,7 @@
         <v>79</v>
       </c>
       <c r="F72" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="I72">
         <v>0</v>
@@ -5794,24 +5802,24 @@
         <v>0</v>
       </c>
       <c r="O72" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="P72">
         <v>100</v>
       </c>
       <c r="T72" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="73" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
         <v>287</v>
       </c>
-    </row>
-    <row r="73" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A73" t="s">
+      <c r="B73" t="s">
         <v>288</v>
       </c>
-      <c r="B73" t="s">
+      <c r="C73" t="s">
         <v>289</v>
-      </c>
-      <c r="C73" t="s">
-        <v>290</v>
       </c>
       <c r="D73" t="s">
         <v>65</v>
@@ -5820,7 +5828,7 @@
         <v>79</v>
       </c>
       <c r="F73" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="I73">
         <v>0</v>
@@ -5844,21 +5852,21 @@
         <v>1</v>
       </c>
       <c r="R73" s="1" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="T73" t="s">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="74" spans="1:20" x14ac:dyDescent="0.3">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="74" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
+        <v>290</v>
+      </c>
+      <c r="B74" t="s">
         <v>291</v>
       </c>
-      <c r="B74" t="s">
-        <v>292</v>
-      </c>
       <c r="C74" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D74" t="s">
         <v>65</v>
@@ -5867,7 +5875,7 @@
         <v>79</v>
       </c>
       <c r="F74" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="G74" t="s">
         <v>31</v>
@@ -5894,15 +5902,15 @@
         <v>1</v>
       </c>
       <c r="T74" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="75" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
         <v>293</v>
       </c>
-    </row>
-    <row r="75" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A75" t="s">
+      <c r="B75" t="s">
         <v>294</v>
-      </c>
-      <c r="B75" t="s">
-        <v>295</v>
       </c>
       <c r="C75" t="s">
         <v>30</v>
@@ -5914,7 +5922,7 @@
         <v>79</v>
       </c>
       <c r="F75" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="G75" t="s">
         <v>31</v>
@@ -5941,18 +5949,18 @@
         <v>1</v>
       </c>
       <c r="T75" t="s">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="76" spans="1:20" x14ac:dyDescent="0.3">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="76" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
+        <v>295</v>
+      </c>
+      <c r="B76" t="s">
         <v>296</v>
       </c>
-      <c r="B76" t="s">
+      <c r="C76" t="s">
         <v>297</v>
-      </c>
-      <c r="C76" t="s">
-        <v>298</v>
       </c>
       <c r="D76" t="s">
         <v>23</v>
@@ -5961,10 +5969,10 @@
         <v>79</v>
       </c>
       <c r="F76" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="G76" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I76">
         <v>0</v>
@@ -5988,18 +5996,18 @@
         <v>1</v>
       </c>
       <c r="T76" t="s">
-        <v>429</v>
-      </c>
-    </row>
-    <row r="77" spans="1:20" x14ac:dyDescent="0.3">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="77" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
+        <v>298</v>
+      </c>
+      <c r="B77" t="s">
         <v>299</v>
       </c>
-      <c r="B77" t="s">
+      <c r="C77" t="s">
         <v>300</v>
-      </c>
-      <c r="C77" t="s">
-        <v>301</v>
       </c>
       <c r="D77" t="s">
         <v>23</v>
@@ -6008,10 +6016,10 @@
         <v>79</v>
       </c>
       <c r="F77" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="G77" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I77">
         <v>0</v>
@@ -6035,15 +6043,15 @@
         <v>1</v>
       </c>
       <c r="T77" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="78" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
         <v>302</v>
       </c>
-    </row>
-    <row r="78" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A78" t="s">
+      <c r="B78" t="s">
         <v>303</v>
-      </c>
-      <c r="B78" t="s">
-        <v>304</v>
       </c>
       <c r="C78" t="s">
         <v>22</v>
@@ -6079,15 +6087,15 @@
         <v>1</v>
       </c>
       <c r="T78" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="79" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
         <v>305</v>
       </c>
-    </row>
-    <row r="79" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A79" t="s">
+      <c r="B79" t="s">
         <v>306</v>
-      </c>
-      <c r="B79" t="s">
-        <v>307</v>
       </c>
       <c r="C79" t="s">
         <v>44</v>
@@ -6126,18 +6134,18 @@
         <v>1</v>
       </c>
       <c r="T79" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="80" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
         <v>308</v>
       </c>
-    </row>
-    <row r="80" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A80" t="s">
+      <c r="B80" t="s">
         <v>309</v>
       </c>
-      <c r="B80" t="s">
-        <v>310</v>
-      </c>
       <c r="C80" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D80" t="s">
         <v>23</v>
@@ -6146,7 +6154,7 @@
         <v>79</v>
       </c>
       <c r="F80" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="G80" t="s">
         <v>31</v>
@@ -6173,18 +6181,18 @@
         <v>1</v>
       </c>
       <c r="T80" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="81" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
         <v>311</v>
       </c>
-    </row>
-    <row r="81" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A81" t="s">
+      <c r="B81" t="s">
         <v>312</v>
       </c>
-      <c r="B81" t="s">
+      <c r="C81" t="s">
         <v>313</v>
-      </c>
-      <c r="C81" t="s">
-        <v>314</v>
       </c>
       <c r="D81" t="s">
         <v>65</v>
@@ -6193,7 +6201,7 @@
         <v>79</v>
       </c>
       <c r="F81" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="G81" t="s">
         <v>115</v>
@@ -6214,21 +6222,21 @@
         <v>0</v>
       </c>
       <c r="O81" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="P81">
         <v>100</v>
       </c>
       <c r="T81" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="82" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
         <v>315</v>
       </c>
-    </row>
-    <row r="82" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A82" t="s">
+      <c r="B82" t="s">
         <v>316</v>
-      </c>
-      <c r="B82" t="s">
-        <v>317</v>
       </c>
       <c r="C82" t="s">
         <v>86</v>
@@ -6240,7 +6248,7 @@
         <v>79</v>
       </c>
       <c r="F82" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="G82" t="s">
         <v>115</v>
@@ -6267,18 +6275,18 @@
         <v>1</v>
       </c>
       <c r="T82" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="83" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
         <v>318</v>
       </c>
-    </row>
-    <row r="83" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A83" t="s">
+      <c r="B83" t="s">
         <v>319</v>
       </c>
-      <c r="B83" t="s">
+      <c r="C83" t="s">
         <v>320</v>
-      </c>
-      <c r="C83" t="s">
-        <v>321</v>
       </c>
       <c r="D83" t="s">
         <v>23</v>
@@ -6287,10 +6295,10 @@
         <v>79</v>
       </c>
       <c r="F83" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="G83" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="I83">
         <v>0</v>
@@ -6314,18 +6322,18 @@
         <v>1</v>
       </c>
       <c r="T83" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="84" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
         <v>322</v>
       </c>
-    </row>
-    <row r="84" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A84" t="s">
+      <c r="B84" t="s">
         <v>323</v>
       </c>
-      <c r="B84" t="s">
+      <c r="C84" t="s">
         <v>324</v>
-      </c>
-      <c r="C84" t="s">
-        <v>325</v>
       </c>
       <c r="D84" t="s">
         <v>23</v>
@@ -6334,10 +6342,10 @@
         <v>79</v>
       </c>
       <c r="F84" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="G84" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="I84">
         <v>0</v>
@@ -6361,18 +6369,18 @@
         <v>1</v>
       </c>
       <c r="T84" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="85" spans="1:20" x14ac:dyDescent="0.3">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="85" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="B85" s="1" t="s">
         <v>391</v>
       </c>
-      <c r="B85" s="1" t="s">
-        <v>392</v>
-      </c>
       <c r="C85" s="1" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="D85" s="1" t="s">
         <v>65</v>
@@ -6381,48 +6389,48 @@
         <v>79</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="G85" s="1" t="s">
         <v>40</v>
       </c>
       <c r="I85" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="K85" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="L85" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="M85" s="1" t="s">
         <v>393</v>
       </c>
-      <c r="K85" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="L85" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="M85" s="1" t="s">
-        <v>394</v>
-      </c>
       <c r="N85" s="1" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="O85" s="1" t="s">
         <v>56</v>
       </c>
       <c r="P85" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="R85" s="1" t="s">
         <v>395</v>
       </c>
-      <c r="R85" s="1" t="s">
+      <c r="T85" s="1" t="s">
         <v>396</v>
       </c>
-      <c r="T85" s="1" t="s">
+    </row>
+    <row r="86" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A86" s="1" t="s">
         <v>397</v>
       </c>
-    </row>
-    <row r="86" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A86" s="1" t="s">
+      <c r="B86" s="1" t="s">
         <v>398</v>
       </c>
-      <c r="B86" s="1" t="s">
+      <c r="C86" s="1" t="s">
         <v>399</v>
-      </c>
-      <c r="C86" s="1" t="s">
-        <v>400</v>
       </c>
       <c r="D86" s="1" t="s">
         <v>65</v>
@@ -6431,45 +6439,45 @@
         <v>79</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="G86" s="1" t="s">
         <v>33</v>
       </c>
       <c r="I86" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="K86" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="L86" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="M86" s="1" t="s">
         <v>393</v>
       </c>
-      <c r="K86" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="L86" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="M86" s="1" t="s">
-        <v>394</v>
-      </c>
       <c r="N86" s="1" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="O86" s="1" t="s">
         <v>56</v>
       </c>
       <c r="P86" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="R86" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="T86" s="1" t="s">
         <v>401</v>
       </c>
-      <c r="T86" s="1" t="s">
+    </row>
+    <row r="87" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A87" s="1" t="s">
         <v>402</v>
       </c>
-    </row>
-    <row r="87" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A87" s="1" t="s">
+      <c r="B87" s="1" t="s">
         <v>403</v>
-      </c>
-      <c r="B87" s="1" t="s">
-        <v>404</v>
       </c>
       <c r="C87" s="1" t="s">
         <v>30</v>
@@ -6481,48 +6489,48 @@
         <v>79</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="G87" s="1" t="s">
         <v>31</v>
       </c>
       <c r="I87" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="K87" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="L87" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="M87" s="1" t="s">
         <v>393</v>
       </c>
-      <c r="K87" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="L87" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="M87" s="1" t="s">
-        <v>394</v>
-      </c>
       <c r="N87" s="1" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="O87" s="1" t="s">
         <v>56</v>
       </c>
       <c r="P87" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="R87" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="T87" s="1" t="s">
         <v>405</v>
       </c>
-      <c r="T87" s="1" t="s">
+    </row>
+    <row r="88" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A88" s="1" t="s">
         <v>406</v>
       </c>
-    </row>
-    <row r="88" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A88" s="1" t="s">
+      <c r="B88" s="1" t="s">
         <v>407</v>
       </c>
-      <c r="B88" s="1" t="s">
-        <v>408</v>
-      </c>
       <c r="C88" s="1" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="D88" s="1" t="s">
         <v>65</v>
@@ -6531,48 +6539,48 @@
         <v>79</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="G88" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I88" s="1" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="K88" s="1" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="L88" s="1" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="M88" s="1" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="N88" s="1" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="O88" s="1" t="s">
         <v>56</v>
       </c>
       <c r="P88" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="R88" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="T88" s="1" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="89" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A89" s="1" t="s">
         <v>410</v>
       </c>
-      <c r="T88" s="1" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="89" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A89" s="1" t="s">
+      <c r="B89" s="1" t="s">
         <v>411</v>
       </c>
-      <c r="B89" s="1" t="s">
-        <v>412</v>
-      </c>
       <c r="C89" s="1" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="D89" s="1" t="s">
         <v>65</v>
@@ -6581,48 +6589,48 @@
         <v>79</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="G89" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I89" s="1" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="K89" s="1" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="L89" s="1" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="M89" s="1" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="N89" s="1" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="O89" s="1" t="s">
         <v>56</v>
       </c>
       <c r="P89" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="R89" s="1" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="T89" s="1" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="90" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A90" s="1" t="s">
         <v>413</v>
       </c>
-    </row>
-    <row r="90" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A90" s="1" t="s">
+      <c r="B90" s="1" t="s">
         <v>414</v>
       </c>
-      <c r="B90" s="1" t="s">
+      <c r="C90" s="1" t="s">
         <v>415</v>
-      </c>
-      <c r="C90" s="1" t="s">
-        <v>416</v>
       </c>
       <c r="D90" s="1" t="s">
         <v>65</v>
@@ -6631,48 +6639,48 @@
         <v>79</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="G90" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="I90" s="1" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="K90" s="1" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="L90" s="1" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="M90" s="1" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="N90" s="1" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="O90" s="1" t="s">
         <v>56</v>
       </c>
       <c r="P90" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="R90" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="T90" s="1" t="s">
         <v>426</v>
       </c>
-      <c r="T90" s="1" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="91" spans="1:20" x14ac:dyDescent="0.3">
+    </row>
+    <row r="91" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="B91" s="1" t="s">
         <v>419</v>
       </c>
-      <c r="B91" s="1" t="s">
-        <v>420</v>
-      </c>
       <c r="C91" s="1" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="D91" s="1" t="s">
         <v>65</v>
@@ -6681,45 +6689,45 @@
         <v>79</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="G91" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="I91" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="K91" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="L91" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="M91" s="1" t="s">
         <v>393</v>
       </c>
-      <c r="K91" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="L91" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="M91" s="1" t="s">
-        <v>394</v>
-      </c>
       <c r="N91" s="1" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="O91" s="1" t="s">
         <v>56</v>
       </c>
       <c r="P91" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="R91" s="1" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="T91" s="1" t="s">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="92" spans="1:20" x14ac:dyDescent="0.3">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="92" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="B92" s="1" t="s">
         <v>432</v>
-      </c>
-      <c r="B92" s="1" t="s">
-        <v>433</v>
       </c>
       <c r="C92" s="1" t="s">
         <v>74</v>
@@ -6731,45 +6739,45 @@
         <v>79</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="I92" s="1" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="K92" s="1" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="L92" s="1" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="M92" s="1" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="N92" s="1" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="O92" s="1" t="s">
         <v>56</v>
       </c>
       <c r="P92" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="R92" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="T92" s="1" t="s">
         <v>435</v>
       </c>
-      <c r="T92" s="1" t="s">
+    </row>
+    <row r="93" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A93" s="1" t="s">
         <v>436</v>
       </c>
-    </row>
-    <row r="93" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A93" s="1" t="s">
+      <c r="B93" s="1" t="s">
         <v>437</v>
       </c>
-      <c r="B93" s="1" t="s">
-        <v>438</v>
-      </c>
       <c r="C93" s="1" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D93" s="1" t="s">
         <v>65</v>
@@ -6778,45 +6786,45 @@
         <v>79</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="I93" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="K93" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="L93" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="M93" s="1" t="s">
         <v>393</v>
       </c>
-      <c r="K93" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="L93" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="M93" s="1" t="s">
-        <v>394</v>
-      </c>
       <c r="N93" s="1" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="O93" s="1" t="s">
         <v>56</v>
       </c>
       <c r="P93" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="Q93" s="1" t="s">
+        <v>438</v>
+      </c>
+      <c r="R93" s="1" t="s">
         <v>439</v>
       </c>
-      <c r="R93" s="1" t="s">
+      <c r="T93" s="1" t="s">
         <v>440</v>
       </c>
-      <c r="T93" s="1" t="s">
+    </row>
+    <row r="94" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A94" s="1" t="s">
         <v>441</v>
       </c>
-    </row>
-    <row r="94" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A94" s="1" t="s">
+      <c r="B94" s="1" t="s">
         <v>442</v>
-      </c>
-      <c r="B94" s="1" t="s">
-        <v>443</v>
       </c>
       <c r="C94" s="1" t="s">
         <v>30</v>
@@ -6828,42 +6836,42 @@
         <v>79</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="I94" s="1" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="K94" s="1" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="L94" s="1" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="M94" s="1" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="N94" s="1" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="O94" s="1" t="s">
         <v>56</v>
       </c>
       <c r="P94" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="Q94" s="1" t="s">
+        <v>444</v>
+      </c>
+      <c r="R94" s="1" t="s">
         <v>445</v>
       </c>
-      <c r="R94" s="1" t="s">
+      <c r="T94" s="1" t="s">
         <v>446</v>
       </c>
-      <c r="T94" s="1" t="s">
+    </row>
+    <row r="95" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A95" s="1" t="s">
         <v>447</v>
-      </c>
-    </row>
-    <row r="95" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A95" s="1" t="s">
-        <v>448</v>
       </c>
       <c r="B95" s="1" t="s">
         <v>68</v>
@@ -6878,45 +6886,45 @@
         <v>79</v>
       </c>
       <c r="F95" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="I95" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="K95" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="L95" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="M95" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="N95" s="1" t="s">
         <v>448</v>
-      </c>
-      <c r="I95" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="K95" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="L95" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="M95" s="1" t="s">
-        <v>394</v>
-      </c>
-      <c r="N95" s="1" t="s">
-        <v>449</v>
       </c>
       <c r="O95" s="1" t="s">
         <v>56</v>
       </c>
       <c r="P95" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="S95" s="1" t="s">
+        <v>449</v>
+      </c>
+      <c r="T95" s="1" t="s">
         <v>450</v>
       </c>
-      <c r="T95" s="1" t="s">
+    </row>
+    <row r="96" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A96" s="1" t="s">
         <v>451</v>
       </c>
-    </row>
-    <row r="96" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A96" s="1" t="s">
+      <c r="B96" s="1" t="s">
         <v>452</v>
       </c>
-      <c r="B96" s="1" t="s">
+      <c r="C96" s="1" t="s">
         <v>453</v>
-      </c>
-      <c r="C96" s="1" t="s">
-        <v>454</v>
       </c>
       <c r="D96" s="1" t="s">
         <v>23</v>
@@ -6925,57 +6933,57 @@
         <v>79</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="I96" s="1" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="K96" s="1" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="L96" s="1" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="M96" s="1" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="N96" s="1" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="O96" s="1" t="s">
         <v>56</v>
       </c>
       <c r="P96" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="Q96" s="1" t="s">
+        <v>455</v>
+      </c>
+      <c r="T96" s="1" t="s">
         <v>456</v>
       </c>
-      <c r="T96" s="1" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="97" spans="1:20" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="97" spans="1:20" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
+        <v>464</v>
+      </c>
+      <c r="B97" t="s">
         <v>465</v>
       </c>
-      <c r="B97" t="s">
+      <c r="C97" t="s">
         <v>466</v>
       </c>
-      <c r="C97" t="s">
+      <c r="D97" t="s">
         <v>467</v>
       </c>
-      <c r="D97" t="s">
+      <c r="E97" t="s">
         <v>468</v>
       </c>
-      <c r="E97" t="s">
+      <c r="F97" t="s">
+        <v>464</v>
+      </c>
+      <c r="G97" t="s">
         <v>469</v>
-      </c>
-      <c r="F97" t="s">
-        <v>465</v>
-      </c>
-      <c r="G97" t="s">
-        <v>470</v>
       </c>
       <c r="I97">
         <v>0</v>
@@ -6993,21 +7001,21 @@
         <v>0</v>
       </c>
       <c r="O97" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="P97" s="1" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="T97" s="1" t="s">
-        <v>482</v>
-      </c>
-    </row>
-    <row r="98" spans="1:20" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="98" spans="1:20" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
+        <v>471</v>
+      </c>
+      <c r="B98" t="s">
         <v>472</v>
-      </c>
-      <c r="B98" t="s">
-        <v>473</v>
       </c>
       <c r="C98" t="s">
         <v>74</v>
@@ -7019,7 +7027,7 @@
         <v>79</v>
       </c>
       <c r="F98" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="I98">
         <v>0</v>
@@ -7043,7 +7051,7 @@
         <v>1</v>
       </c>
       <c r="T98" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
     </row>
   </sheetData>
@@ -7056,414 +7064,414 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:A81"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="125.6640625" customWidth="1"/>
+    <col min="1" max="1" width="125.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
         <v>327</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
         <v>328</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
         <v>329</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A6" s="2" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
         <v>331</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A10" s="2" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
         <v>333</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A14" s="2" t="s">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
         <v>334</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A15" s="2" t="s">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
         <v>335</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A16" s="2" t="s">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
         <v>336</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A17" s="2" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="20" spans="1:1" ht="32.4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A21" s="2" t="s">
         <v>338</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A21" s="2" t="s">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A22" s="2" t="s">
         <v>339</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A22" s="2" t="s">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A23" s="2" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A23" s="2" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A27" s="2" t="s">
         <v>342</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A27" s="2" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A31" s="2" t="s">
         <v>344</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A31" s="2" t="s">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A32" s="2" t="s">
         <v>345</v>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A32" s="2" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A36" s="2" t="s">
         <v>347</v>
       </c>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A36" s="2" t="s">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A37" s="2" t="s">
         <v>348</v>
       </c>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A37" s="2" t="s">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A38" s="2" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A39" s="2" t="s">
         <v>349</v>
       </c>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A38" s="2" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A39" s="2" t="s">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A40" s="2" t="s">
         <v>350</v>
       </c>
     </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A40" s="2" t="s">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A41" s="2" t="s">
         <v>351</v>
       </c>
     </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A41" s="2" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.3">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A45" s="2" t="s">
         <v>353</v>
       </c>
     </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A45" s="2" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.3">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A49" s="2" t="s">
         <v>355</v>
       </c>
     </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A49" s="2" t="s">
+    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A50" s="2" t="s">
         <v>356</v>
       </c>
     </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A50" s="2" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.3">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A54" s="2" t="s">
         <v>358</v>
       </c>
     </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A54" s="2" t="s">
+    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A55" s="2" t="s">
         <v>359</v>
       </c>
     </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A55" s="2" t="s">
+    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A56" s="2" t="s">
         <v>360</v>
       </c>
     </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A56" s="2" t="s">
+    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A57" s="2" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A58" s="2" t="s">
         <v>361</v>
       </c>
     </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A57" s="2" t="s">
+    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A59" s="2" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A60" s="2" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A61" s="2" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A62" s="2" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A63" s="2" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A64" s="2" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A65" s="2" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A66" s="2" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A67" s="2" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A68" s="2" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A69" s="2" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A70" s="2" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A71" s="2" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A72" s="2" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A73" s="2" t="s">
         <v>384</v>
       </c>
     </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A58" s="2" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A59" s="2" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A60" s="2" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A61" s="2" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="62" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A62" s="2" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A63" s="2" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="64" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A64" s="2" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A65" s="2" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A66" s="2" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A67" s="2" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A68" s="2" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A69" s="2" t="s">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A70" s="2" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A71" s="2" t="s">
+    <row r="74" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A74" s="2" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A75" s="2" t="s">
         <v>374</v>
       </c>
     </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A72" s="2" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A73" s="2" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="74" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A74" s="2" t="s">
+    <row r="76" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A76" s="2" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="75" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A75" s="2" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="76" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A76" s="2" t="s">
+    <row r="77" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A77" s="2" t="s">
         <v>387</v>
       </c>
     </row>
-    <row r="77" spans="1:1" ht="32.4" x14ac:dyDescent="0.3">
-      <c r="A77" s="2" t="s">
+    <row r="78" spans="1:1" ht="33" x14ac:dyDescent="0.25">
+      <c r="A78" s="2" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A79" s="2" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A80" s="2" t="s">
         <v>388</v>
       </c>
     </row>
-    <row r="78" spans="1:1" ht="32.4" x14ac:dyDescent="0.3">
-      <c r="A78" s="2" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="79" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A79" s="2" t="s">
-        <v>422</v>
-      </c>
-    </row>
-    <row r="80" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A80" s="2" t="s">
+    <row r="81" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A81" s="2" t="s">
         <v>389</v>
-      </c>
-    </row>
-    <row r="81" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A81" s="2" t="s">
-        <v>390</v>
       </c>
     </row>
   </sheetData>
